--- a/projects/qa-lab-miyonchat/test-case/qa-lab-miyonchat-tc-v1.0.xlsx
+++ b/projects/qa-lab-miyonchat/test-case/qa-lab-miyonchat-tc-v1.0.xlsx
@@ -26,7 +26,7 @@
     <definedName name="list_reporter">목록!$K$3:$K$3</definedName>
     <definedName name="list_assignee">목록!$L$3:$L$3</definedName>
     <definedName name="list_sprint">목록!$M$3:$M$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Case'!$B$4:$R$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Case'!$B$4:$R$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'이슈 관리 시트'!$B$2:$U$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -102,7 +102,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -136,27 +136,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E4D0EC"/>
+        <fgColor rgb="00ECD0EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECD7D0"/>
+        <fgColor rgb="00D0ECEC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0ECE3"/>
+        <fgColor rgb="00ECE1D0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0D8EC"/>
+        <fgColor rgb="00ECD0D5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0ECD5"/>
+        <fgColor rgb="00E0ECD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECD0E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECD5D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0ECE1"/>
       </patternFill>
     </fill>
     <fill>
@@ -166,27 +181,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0E6EC"/>
+        <fgColor rgb="00D0ECD6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7ECD0"/>
+        <fgColor rgb="00D0D5EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECD0E5"/>
+        <fgColor rgb="00D5ECD0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9ECD0"/>
+        <fgColor rgb="00E1D0EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECD0D7"/>
+        <fgColor rgb="00D0E0EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -259,7 +274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -334,15 +349,24 @@
     <xf numFmtId="0" fontId="5" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -352,11 +376,11 @@
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -884,7 +908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:R29"/>
+  <dimension ref="B2:R32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -910,7 +934,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>qa-lab-miyonchat-tree-v1.10</t>
+          <t>qa-lab-miyonchat-tree-v1.11</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
@@ -2113,7 +2137,7 @@
       </c>
       <c r="E25" s="26" t="inlineStr">
         <is>
-          <t>나머지 보호 화면 차단</t>
+          <t>채팅 탭 차단</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
@@ -2131,7 +2155,7 @@
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>채팅 탭 대신 로그인 화면 노출된다</t>
+          <t>채팅 탭 노출되지 않는다</t>
         </is>
       </c>
       <c r="J25" s="10" t="inlineStr">
@@ -2153,7 +2177,7 @@
       <c r="O25" s="18" t="n"/>
       <c r="P25" s="14" t="inlineStr">
         <is>
-          <t>주소는 차례로 `?screen=s5` · `?screen=s6` · `?screen=s8`입니다. 보호 화면 넷 중 대화방은 TC-GAT-001이 맡습니다</t>
+          <t>주소 끝에 `?screen=s5`를 붙입니다. 보호 화면마다 케이스를 나눈 것은 하나만 뚫렸을 때 어느 화면인지 TC ID로 읽히게 하기 위해서입니다</t>
         </is>
       </c>
       <c r="Q25" s="10" t="inlineStr">
@@ -2184,21 +2208,15 @@
       </c>
       <c r="E26" s="26" t="inlineStr">
         <is>
-          <t>나머지 보호 화면 차단</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr"/>
-      <c r="G26" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" s="14" t="inlineStr">
-        <is>
-          <t>MY 탭 주소로 직접 진입한다</t>
-        </is>
-      </c>
+          <t>채팅 탭 차단</t>
+        </is>
+      </c>
+      <c r="F26" s="19" t="n"/>
+      <c r="G26" s="19" t="n"/>
+      <c r="H26" s="19" t="n"/>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>MY 탭 대신 로그인 화면 노출된다</t>
+          <t>로그인 화면 노출된다</t>
         </is>
       </c>
       <c r="J26" s="10" t="inlineStr">
@@ -2218,7 +2236,7 @@
       <c r="M26" s="17" t="n"/>
       <c r="N26" s="18" t="n"/>
       <c r="O26" s="18" t="n"/>
-      <c r="P26" s="14" t="n"/>
+      <c r="P26" s="19" t="n"/>
       <c r="Q26" s="10" t="inlineStr">
         <is>
           <t>TC-GAT-002</t>
@@ -2245,23 +2263,27 @@
           <t>주소 직접 진입</t>
         </is>
       </c>
-      <c r="E27" s="26" t="inlineStr">
-        <is>
-          <t>나머지 보호 화면 차단</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr"/>
+      <c r="E27" s="27" t="inlineStr">
+        <is>
+          <t>MY 탭 차단</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>미로그인 상태</t>
+        </is>
+      </c>
       <c r="G27" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>내 작품 탭 주소로 직접 진입한다</t>
+          <t>MY 탭 주소로 직접 진입한다</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
-          <t>내 작품 탭 대신 로그인 화면 노출된다</t>
+          <t>MY 탭 노출되지 않는다</t>
         </is>
       </c>
       <c r="J27" s="10" t="inlineStr">
@@ -2281,10 +2303,14 @@
       <c r="M27" s="17" t="n"/>
       <c r="N27" s="18" t="n"/>
       <c r="O27" s="18" t="n"/>
-      <c r="P27" s="14" t="n"/>
+      <c r="P27" s="14" t="inlineStr">
+        <is>
+          <t>주소 끝에 `?screen=s6`을 붙입니다. 로그인 상태에서 같은 주소가 열리는 것은 TC-ENT-005가 봅니다</t>
+        </is>
+      </c>
       <c r="Q27" s="10" t="inlineStr">
         <is>
-          <t>TC-GAT-002</t>
+          <t>TC-GAT-003</t>
         </is>
       </c>
       <c r="R27" s="10" t="inlineStr">
@@ -2310,25 +2336,15 @@
       </c>
       <c r="E28" s="27" t="inlineStr">
         <is>
-          <t>공개 화면 통과</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>미로그인 상태</t>
-        </is>
-      </c>
-      <c r="G28" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="14" t="inlineStr">
-        <is>
-          <t>홈 화면 주소로 직접 진입한다</t>
-        </is>
-      </c>
+          <t>MY 탭 차단</t>
+        </is>
+      </c>
+      <c r="F28" s="19" t="n"/>
+      <c r="G28" s="19" t="n"/>
+      <c r="H28" s="19" t="n"/>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>로그인 화면 없이 홈 화면 노출된다</t>
+          <t>로그인 화면 노출된다</t>
         </is>
       </c>
       <c r="J28" s="10" t="inlineStr">
@@ -2338,7 +2354,7 @@
       </c>
       <c r="K28" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L28" s="16">
@@ -2348,11 +2364,7 @@
       <c r="M28" s="17" t="n"/>
       <c r="N28" s="18" t="n"/>
       <c r="O28" s="18" t="n"/>
-      <c r="P28" s="14" t="inlineStr">
-        <is>
-          <t>주소는 `?screen=s2` · `?screen=s7`입니다. 차단이 과하게 걸리지 않는지를 보는 자리라 위 차단 케이스들과 함께 읽습니다</t>
-        </is>
-      </c>
+      <c r="P28" s="19" t="n"/>
       <c r="Q28" s="10" t="inlineStr">
         <is>
           <t>TC-GAT-003</t>
@@ -2360,7 +2372,7 @@
       </c>
       <c r="R28" s="10" t="inlineStr">
         <is>
-          <t>결정적</t>
+          <t>금칙</t>
         </is>
       </c>
     </row>
@@ -2379,23 +2391,27 @@
           <t>주소 직접 진입</t>
         </is>
       </c>
-      <c r="E29" s="27" t="inlineStr">
-        <is>
-          <t>공개 화면 통과</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="inlineStr"/>
+      <c r="E29" s="28" t="inlineStr">
+        <is>
+          <t>내 작품 탭 차단</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>미로그인 상태</t>
+        </is>
+      </c>
       <c r="G29" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>커뮤니티 탭 주소로 직접 진입한다</t>
+          <t>내 작품 탭 주소로 직접 진입한다</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
-          <t>로그인 화면 없이 커뮤니티 탭 노출된다</t>
+          <t>내 작품 탭 노출되지 않는다</t>
         </is>
       </c>
       <c r="J29" s="10" t="inlineStr">
@@ -2405,7 +2421,7 @@
       </c>
       <c r="K29" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L29" s="16">
@@ -2415,25 +2431,230 @@
       <c r="M29" s="17" t="n"/>
       <c r="N29" s="18" t="n"/>
       <c r="O29" s="18" t="n"/>
-      <c r="P29" s="14" t="n"/>
+      <c r="P29" s="14" t="inlineStr">
+        <is>
+          <t>주소 끝에 `?screen=s8`을 붙입니다. 내 작품 탭은 스텁이지만 보호 화면이라 차단은 걸립니다</t>
+        </is>
+      </c>
       <c r="Q29" s="10" t="inlineStr">
         <is>
-          <t>TC-GAT-003</t>
+          <t>TC-GAT-004</t>
         </is>
       </c>
       <c r="R29" s="10" t="inlineStr">
         <is>
+          <t>금칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="B30" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>웹 진입</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="inlineStr">
+        <is>
+          <t>주소 직접 진입</t>
+        </is>
+      </c>
+      <c r="E30" s="28" t="inlineStr">
+        <is>
+          <t>내 작품 탭 차단</t>
+        </is>
+      </c>
+      <c r="F30" s="19" t="n"/>
+      <c r="G30" s="19" t="n"/>
+      <c r="H30" s="19" t="n"/>
+      <c r="I30" s="14" t="inlineStr">
+        <is>
+          <t>로그인 화면 노출된다</t>
+        </is>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K30" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L30" s="16">
+        <f>IF(COUNTIF(M30:M30,"Fail")&gt;0,"Fail",IF(COUNTIF(M30:M30,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M30:M30,"NI")&gt;0,"NI",IF(COUNTIF(M30:M30,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M30" s="17" t="n"/>
+      <c r="N30" s="18" t="n"/>
+      <c r="O30" s="18" t="n"/>
+      <c r="P30" s="19" t="n"/>
+      <c r="Q30" s="10" t="inlineStr">
+        <is>
+          <t>TC-GAT-004</t>
+        </is>
+      </c>
+      <c r="R30" s="10" t="inlineStr">
+        <is>
+          <t>금칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="B31" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>웹 진입</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>주소 직접 진입</t>
+        </is>
+      </c>
+      <c r="E31" s="29" t="inlineStr">
+        <is>
+          <t>홈 화면 통과</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>미로그인 상태</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>홈 화면 주소로 직접 진입한다</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
+        <is>
+          <t>로그인 화면 없이 홈 화면 노출된다</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K31" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L31" s="16">
+        <f>IF(COUNTIF(M31:M31,"Fail")&gt;0,"Fail",IF(COUNTIF(M31:M31,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M31:M31,"NI")&gt;0,"NI",IF(COUNTIF(M31:M31,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M31" s="17" t="n"/>
+      <c r="N31" s="18" t="n"/>
+      <c r="O31" s="18" t="n"/>
+      <c r="P31" s="14" t="inlineStr">
+        <is>
+          <t>주소 끝에 `?screen=s2`를 붙입니다. 차단이 공개 화면까지 과하게 걸리지 않는지를 보는 자리라 위 차단 케이스들과 함께 읽습니다</t>
+        </is>
+      </c>
+      <c r="Q31" s="10" t="inlineStr">
+        <is>
+          <t>TC-GAT-005</t>
+        </is>
+      </c>
+      <c r="R31" s="10" t="inlineStr">
+        <is>
           <t>결정적</t>
         </is>
       </c>
     </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="B32" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>웹 진입</t>
+        </is>
+      </c>
+      <c r="D32" s="23" t="inlineStr">
+        <is>
+          <t>주소 직접 진입</t>
+        </is>
+      </c>
+      <c r="E32" s="30" t="inlineStr">
+        <is>
+          <t>커뮤니티 탭 통과</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>미로그인 상태</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>커뮤니티 탭 주소로 직접 진입한다</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
+        <is>
+          <t>로그인 화면 없이 커뮤니티 탭 노출된다</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L32" s="16">
+        <f>IF(COUNTIF(M32:M32,"Fail")&gt;0,"Fail",IF(COUNTIF(M32:M32,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M32:M32,"NI")&gt;0,"NI",IF(COUNTIF(M32:M32,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M32" s="17" t="n"/>
+      <c r="N32" s="18" t="n"/>
+      <c r="O32" s="18" t="n"/>
+      <c r="P32" s="14" t="inlineStr">
+        <is>
+          <t>주소 끝에 `?screen=s7`을 붙입니다. 커뮤니티 탭은 전시용 정적이지만 공개 화면이라 통과합니다</t>
+        </is>
+      </c>
+      <c r="Q32" s="10" t="inlineStr">
+        <is>
+          <t>TC-GAT-006</t>
+        </is>
+      </c>
+      <c r="R32" s="10" t="inlineStr">
+        <is>
+          <t>결정적</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B4:R29"/>
-  <mergeCells count="47">
+  <autoFilter ref="B4:R32"/>
+  <mergeCells count="59">
     <mergeCell ref="M3"/>
     <mergeCell ref="L9"/>
     <mergeCell ref="G17:G18"/>
+    <mergeCell ref="H29:H30"/>
     <mergeCell ref="P22:P23"/>
+    <mergeCell ref="F25:F26"/>
     <mergeCell ref="B9:K9"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="N3:N4"/>
@@ -2444,6 +2665,7 @@
     <mergeCell ref="G19:G20"/>
     <mergeCell ref="B5:K5"/>
     <mergeCell ref="P11:P12"/>
+    <mergeCell ref="P27:P28"/>
     <mergeCell ref="H17:H18"/>
     <mergeCell ref="F22:F23"/>
     <mergeCell ref="G3:G4"/>
@@ -2455,15 +2677,20 @@
     <mergeCell ref="L7"/>
     <mergeCell ref="H19:H20"/>
     <mergeCell ref="G14:G15"/>
+    <mergeCell ref="G29:G30"/>
     <mergeCell ref="P19:P20"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="H27:H28"/>
     <mergeCell ref="P3:P4"/>
     <mergeCell ref="L3"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="B2:E2"/>
+    <mergeCell ref="G25:G26"/>
     <mergeCell ref="N5:R9"/>
     <mergeCell ref="L5"/>
+    <mergeCell ref="F29:F30"/>
     <mergeCell ref="H14:H15"/>
     <mergeCell ref="G22:G23"/>
     <mergeCell ref="P14:P15"/>
@@ -2471,12 +2698,16 @@
     <mergeCell ref="L8"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="F19:F20"/>
+    <mergeCell ref="G27:G28"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="F2:R2"/>
     <mergeCell ref="G11:G12"/>
+    <mergeCell ref="P29:P30"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="P25:P26"/>
   </mergeCells>
   <conditionalFormatting sqref="M10:M500">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -2558,536 +2789,536 @@
   </cols>
   <sheetData>
     <row r="2" ht="19" customHeight="1">
-      <c r="B2" s="28" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>커버리지 요약</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" s="32" t="inlineStr">
         <is>
           <t>Test Case 시트를 참조하는 수식으로 자동 집계됩니다. 행을 추가하면 아래 범위를 넓히세요.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="33" t="inlineStr">
         <is>
           <t>기준 골격 버전</t>
         </is>
       </c>
-      <c r="C4" s="31" t="inlineStr">
-        <is>
-          <t>qa-lab-miyonchat-tree-v1.10</t>
-        </is>
-      </c>
-      <c r="D4" s="32" t="n"/>
-      <c r="E4" s="32" t="n"/>
+      <c r="C4" s="34" t="inlineStr">
+        <is>
+          <t>qa-lab-miyonchat-tree-v1.11</t>
+        </is>
+      </c>
+      <c r="D4" s="35" t="n"/>
+      <c r="E4" s="35" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>1-Depth (영역)</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
+      <c r="C5" s="36" t="inlineStr">
         <is>
           <t>TC 수</t>
         </is>
       </c>
-      <c r="D5" s="33" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="E5" s="32" t="n"/>
-      <c r="F5" s="32" t="n"/>
-      <c r="G5" s="33" t="inlineStr">
+      <c r="E5" s="35" t="n"/>
+      <c r="F5" s="35" t="n"/>
+      <c r="G5" s="36" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H5" s="32" t="n"/>
-      <c r="I5" s="32" t="n"/>
-      <c r="J5" s="32" t="n"/>
-      <c r="K5" s="32" t="n"/>
+      <c r="H5" s="35" t="n"/>
+      <c r="I5" s="35" t="n"/>
+      <c r="J5" s="35" t="n"/>
+      <c r="K5" s="35" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="32" t="n"/>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="34" t="inlineStr">
+      <c r="B6" s="35" t="n"/>
+      <c r="C6" s="35" t="n"/>
+      <c r="D6" s="37" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="37" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F6" s="34" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G6" s="34" t="inlineStr">
+      <c r="G6" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="H6" s="34" t="inlineStr">
+      <c r="H6" s="37" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="I6" s="34" t="inlineStr">
+      <c r="I6" s="37" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="J6" s="34" t="inlineStr">
+      <c r="J6" s="37" t="inlineStr">
         <is>
           <t>Pass율</t>
         </is>
       </c>
-      <c r="K6" s="32" t="n"/>
+      <c r="K6" s="35" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="38" t="inlineStr">
         <is>
           <t>웹 진입</t>
         </is>
       </c>
-      <c r="C7" s="36">
+      <c r="C7" s="39">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B7)</f>
         <v/>
       </c>
-      <c r="D7" s="36">
+      <c r="D7" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B7,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E7" s="36">
+      <c r="E7" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B7,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F7" s="36">
+      <c r="F7" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B7,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G7" s="36">
+      <c r="G7" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B7,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H7" s="36">
+      <c r="H7" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B7,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I7" s="36">
+      <c r="I7" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B7,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J7" s="37">
+      <c r="J7" s="40">
         <f>IF(G7+H7=0,"",G7/(G7+H7))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="35" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>전역 셸</t>
         </is>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="39">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B8)</f>
         <v/>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B8,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E8" s="36">
+      <c r="E8" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B8,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F8" s="36">
+      <c r="F8" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B8,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B8,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H8" s="36">
+      <c r="H8" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B8,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I8" s="36">
+      <c r="I8" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B8,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J8" s="37">
+      <c r="J8" s="40">
         <f>IF(G8+H8=0,"",G8/(G8+H8))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>홈 화면</t>
         </is>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="39">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B9)</f>
         <v/>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B9,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B9,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F9" s="36">
+      <c r="F9" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B9,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G9" s="36">
+      <c r="G9" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B9,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H9" s="36">
+      <c r="H9" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B9,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I9" s="36">
+      <c r="I9" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B9,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J9" s="37">
+      <c r="J9" s="40">
         <f>IF(G9+H9=0,"",G9/(G9+H9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="35" t="inlineStr">
+      <c r="B10" s="38" t="inlineStr">
         <is>
           <t>캐릭터 페이지</t>
         </is>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="39">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B10)</f>
         <v/>
       </c>
-      <c r="D10" s="36">
+      <c r="D10" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B10,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E10" s="36">
+      <c r="E10" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B10,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F10" s="36">
+      <c r="F10" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B10,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B10,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H10" s="36">
+      <c r="H10" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B10,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I10" s="36">
+      <c r="I10" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B10,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J10" s="37">
+      <c r="J10" s="40">
         <f>IF(G10+H10=0,"",G10/(G10+H10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
         <is>
           <t>대화 프로필 화면</t>
         </is>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="39">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B11)</f>
         <v/>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B11,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E11" s="36">
+      <c r="E11" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B11,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B11,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B11,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H11" s="36">
+      <c r="H11" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B11,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I11" s="36">
+      <c r="I11" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B11,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J11" s="37">
+      <c r="J11" s="40">
         <f>IF(G11+H11=0,"",G11/(G11+H11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="38" t="inlineStr">
         <is>
           <t>대화방</t>
         </is>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="39">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B12)</f>
         <v/>
       </c>
-      <c r="D12" s="36">
+      <c r="D12" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B12,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E12" s="36">
+      <c r="E12" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B12,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B12,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B12,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H12" s="36">
+      <c r="H12" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B12,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I12" s="36">
+      <c r="I12" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B12,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J12" s="37">
+      <c r="J12" s="40">
         <f>IF(G12+H12=0,"",G12/(G12+H12))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="35" t="inlineStr">
+      <c r="B13" s="38" t="inlineStr">
         <is>
           <t>채팅 탭</t>
         </is>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="39">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B13)</f>
         <v/>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B13,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E13" s="36">
+      <c r="E13" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B13,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F13" s="36">
+      <c r="F13" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B13,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B13,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H13" s="36">
+      <c r="H13" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B13,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I13" s="36">
+      <c r="I13" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B13,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J13" s="37">
+      <c r="J13" s="40">
         <f>IF(G13+H13=0,"",G13/(G13+H13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="35" t="inlineStr">
+      <c r="B14" s="38" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="39">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B14)</f>
         <v/>
       </c>
-      <c r="D14" s="36">
+      <c r="D14" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B14,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E14" s="36">
+      <c r="E14" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B14,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B14,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B14,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H14" s="36">
+      <c r="H14" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B14,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I14" s="36">
+      <c r="I14" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B14,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J14" s="37">
+      <c r="J14" s="40">
         <f>IF(G14+H14=0,"",G14/(G14+H14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="35" t="inlineStr">
+      <c r="B15" s="38" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="39">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B15)</f>
         <v/>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B15,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B15,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B15,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G15" s="36">
+      <c r="G15" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B15,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B15,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I15" s="36">
+      <c r="I15" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B15,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J15" s="37">
+      <c r="J15" s="40">
         <f>IF(G15+H15=0,"",G15/(G15+H15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="35" t="inlineStr">
+      <c r="B16" s="38" t="inlineStr">
         <is>
           <t>스텁·정적</t>
         </is>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="39">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B16)</f>
         <v/>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B16,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E16" s="36">
+      <c r="E16" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B16,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F16" s="36">
+      <c r="F16" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B16,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G16" s="36">
+      <c r="G16" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B16,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H16" s="36">
+      <c r="H16" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B16,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I16" s="36">
+      <c r="I16" s="39">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B16,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J16" s="37">
+      <c r="J16" s="40">
         <f>IF(G16+H16=0,"",G16/(G16+H16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="38" t="inlineStr">
+      <c r="B17" s="41" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="C17" s="39">
+      <c r="C17" s="42">
         <f>SUM(C7:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="42">
         <f>SUM(D7:D16)</f>
         <v/>
       </c>
-      <c r="E17" s="39">
+      <c r="E17" s="42">
         <f>SUM(E7:E16)</f>
         <v/>
       </c>
-      <c r="F17" s="39">
+      <c r="F17" s="42">
         <f>SUM(F7:F16)</f>
         <v/>
       </c>
-      <c r="G17" s="39">
+      <c r="G17" s="42">
         <f>SUM(G7:G16)</f>
         <v/>
       </c>
-      <c r="H17" s="39">
+      <c r="H17" s="42">
         <f>SUM(H7:H16)</f>
         <v/>
       </c>
-      <c r="I17" s="39">
+      <c r="I17" s="42">
         <f>SUM(I7:I16)</f>
         <v/>
       </c>
-      <c r="J17" s="40">
+      <c r="J17" s="43">
         <f>IF(G17+H17=0,"",G17/(G17+H17))</f>
         <v/>
       </c>
-      <c r="K17" s="39">
+      <c r="K17" s="42">
         <f>SUM(K7:K16)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="29" t="inlineStr">
+      <c r="B19" s="32" t="inlineStr">
         <is>
           <t>TC 수 = 스텝 행 수(1-Depth 기준) · Pass/Fail/Blocked도 같은 행 단위(Result 열) · Pass율 = Pass ÷ (Pass + Fail) — NI·Blocked는 분모에서 제외합니다</t>
         </is>
@@ -3138,129 +3369,129 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1">
-      <c r="B2" s="41" t="inlineStr">
+      <c r="B2" s="44" t="inlineStr">
         <is>
           <t>프로젝트 ID</t>
         </is>
       </c>
-      <c r="C2" s="41" t="inlineStr">
+      <c r="C2" s="44" t="inlineStr">
         <is>
           <t>Issue No.</t>
         </is>
       </c>
-      <c r="D2" s="41" t="inlineStr">
+      <c r="D2" s="44" t="inlineStr">
         <is>
           <t>이슈 상태</t>
         </is>
       </c>
-      <c r="E2" s="41" t="inlineStr">
+      <c r="E2" s="44" t="inlineStr">
         <is>
           <t>요약(Summary)</t>
         </is>
       </c>
-      <c r="F2" s="41" t="inlineStr">
+      <c r="F2" s="44" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="G2" s="41" t="inlineStr">
+      <c r="G2" s="44" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="H2" s="41" t="inlineStr">
+      <c r="H2" s="44" t="inlineStr">
         <is>
           <t>빈도</t>
         </is>
       </c>
-      <c r="I2" s="41" t="inlineStr">
+      <c r="I2" s="44" t="inlineStr">
         <is>
           <t>영향 받는 버전</t>
         </is>
       </c>
-      <c r="J2" s="41" t="inlineStr">
+      <c r="J2" s="44" t="inlineStr">
         <is>
           <t>수정 버전</t>
         </is>
       </c>
-      <c r="K2" s="41" t="inlineStr">
+      <c r="K2" s="44" t="inlineStr">
         <is>
           <t>해결책</t>
         </is>
       </c>
-      <c r="L2" s="41" t="inlineStr">
+      <c r="L2" s="44" t="inlineStr">
         <is>
           <t>환경</t>
         </is>
       </c>
-      <c r="M2" s="41" t="inlineStr">
+      <c r="M2" s="44" t="inlineStr">
         <is>
           <t>레이블</t>
         </is>
       </c>
-      <c r="N2" s="41" t="inlineStr">
+      <c r="N2" s="44" t="inlineStr">
         <is>
           <t>보고자</t>
         </is>
       </c>
-      <c r="O2" s="41" t="inlineStr">
+      <c r="O2" s="44" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="P2" s="41" t="inlineStr">
+      <c r="P2" s="44" t="inlineStr">
         <is>
           <t>관측자</t>
         </is>
       </c>
-      <c r="Q2" s="41" t="inlineStr">
+      <c r="Q2" s="44" t="inlineStr">
         <is>
           <t>첨부파일</t>
         </is>
       </c>
-      <c r="R2" s="41" t="inlineStr">
+      <c r="R2" s="44" t="inlineStr">
         <is>
           <t>스프린트</t>
         </is>
       </c>
-      <c r="S2" s="41" t="inlineStr">
+      <c r="S2" s="44" t="inlineStr">
         <is>
           <t>이슈 등록일</t>
         </is>
       </c>
-      <c r="T2" s="41" t="inlineStr">
+      <c r="T2" s="44" t="inlineStr">
         <is>
           <t>이슈 최종 수정일자</t>
         </is>
       </c>
-      <c r="U2" s="41" t="inlineStr">
+      <c r="U2" s="44" t="inlineStr">
         <is>
           <t>이슈 상태 최종 변경일자</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="42" t="inlineStr">
+      <c r="B3" s="45" t="inlineStr">
         <is>
           <t>miyonchat</t>
         </is>
       </c>
-      <c r="C3" s="42" t="inlineStr">
+      <c r="C3" s="45" t="inlineStr">
         <is>
           <t>miyonchat-1</t>
         </is>
       </c>
-      <c r="D3" s="42" t="inlineStr">
+      <c r="D3" s="45" t="inlineStr">
         <is>
           <t>Resolved</t>
         </is>
       </c>
-      <c r="E3" s="43" t="inlineStr">
+      <c r="E3" s="46" t="inlineStr">
         <is>
           <t>디버그 콘솔 &gt; 전체 초기화(reset) 수행 &gt; 계정 A 로그인 시, 성인 인증이 해제된 상태로 시작됨</t>
         </is>
       </c>
-      <c r="F3" s="43" t="inlineStr">
+      <c r="F3" s="46" t="inlineStr">
         <is>
           <t>Pre-condition: SUT 진입
 Reproduce Step: 디버그 콘솔 열기 &gt; [전체 초기화] 선택 &gt; 계정 A로 로그인 &gt; 간편 프로필 확인
@@ -3269,69 +3500,69 @@
 QA Comment: 계정 상태 생성 함수에 계정 식별자를 전달하지 않아 기본값 판정이 항상 거짓이 됨. 자동화가 매 테스트 전 reset()을 호출하는 구조라, 남아 있으면 게이팅 계열 TC 전체가 미인증 상태에서 실행되어 결과를 신뢰할 수 없음</t>
         </is>
       </c>
-      <c r="G3" s="42" t="inlineStr">
+      <c r="G3" s="45" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H3" s="42" t="inlineStr">
+      <c r="H3" s="45" t="inlineStr">
         <is>
           <t>Always</t>
         </is>
       </c>
-      <c r="I3" s="42" t="inlineStr">
+      <c r="I3" s="45" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev_RC1</t>
         </is>
       </c>
-      <c r="J3" s="42" t="inlineStr">
+      <c r="J3" s="45" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev_RC2</t>
         </is>
       </c>
-      <c r="K3" s="42" t="inlineStr">
+      <c r="K3" s="45" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="L3" s="42" t="inlineStr">
+      <c r="L3" s="45" t="inlineStr">
         <is>
           <t>PC웹</t>
         </is>
       </c>
-      <c r="M3" s="42" t="inlineStr">
+      <c r="M3" s="45" t="inlineStr">
         <is>
           <t>계정/게이팅</t>
         </is>
       </c>
-      <c r="N3" s="42" t="inlineStr">
+      <c r="N3" s="45" t="inlineStr">
         <is>
           <t>정준호</t>
         </is>
       </c>
-      <c r="O3" s="42" t="inlineStr">
+      <c r="O3" s="45" t="inlineStr">
         <is>
           <t>Claude Opus 5</t>
         </is>
       </c>
-      <c r="P3" s="42" t="inlineStr"/>
-      <c r="Q3" s="42" t="inlineStr"/>
-      <c r="R3" s="42" t="inlineStr">
+      <c r="P3" s="45" t="inlineStr"/>
+      <c r="Q3" s="45" t="inlineStr"/>
+      <c r="R3" s="45" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev</t>
         </is>
       </c>
-      <c r="S3" s="42" t="inlineStr">
+      <c r="S3" s="45" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="T3" s="42" t="inlineStr">
+      <c r="T3" s="45" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="U3" s="42" t="inlineStr">
+      <c r="U3" s="45" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
@@ -3434,297 +3665,297 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="47" t="inlineStr">
         <is>
           <t>프로젝트</t>
         </is>
       </c>
-      <c r="C2" s="44" t="inlineStr">
+      <c r="C2" s="47" t="inlineStr">
         <is>
           <t>실행 주체</t>
         </is>
       </c>
-      <c r="D2" s="44" t="inlineStr">
+      <c r="D2" s="47" t="inlineStr">
         <is>
           <t>이슈 상태</t>
         </is>
       </c>
-      <c r="E2" s="44" t="inlineStr">
+      <c r="E2" s="47" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="F2" s="44" t="inlineStr">
+      <c r="F2" s="47" t="inlineStr">
         <is>
           <t>빈도</t>
         </is>
       </c>
-      <c r="G2" s="44" t="inlineStr">
+      <c r="G2" s="47" t="inlineStr">
         <is>
           <t>버전(영향/수정 공용)</t>
         </is>
       </c>
-      <c r="H2" s="44" t="inlineStr">
+      <c r="H2" s="47" t="inlineStr">
         <is>
           <t>해결책</t>
         </is>
       </c>
-      <c r="I2" s="44" t="inlineStr">
+      <c r="I2" s="47" t="inlineStr">
         <is>
           <t>환경</t>
         </is>
       </c>
-      <c r="J2" s="44" t="inlineStr">
+      <c r="J2" s="47" t="inlineStr">
         <is>
           <t>레이블</t>
         </is>
       </c>
-      <c r="K2" s="44" t="inlineStr">
+      <c r="K2" s="47" t="inlineStr">
         <is>
           <t>보고자</t>
         </is>
       </c>
-      <c r="L2" s="44" t="inlineStr">
+      <c r="L2" s="47" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="M2" s="44" t="inlineStr">
+      <c r="M2" s="47" t="inlineStr">
         <is>
           <t>스프린트</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="45" t="inlineStr">
+      <c r="B3" s="48" t="inlineStr">
         <is>
           <t>miyonchat</t>
         </is>
       </c>
-      <c r="C3" s="45" t="inlineStr">
+      <c r="C3" s="48" t="inlineStr">
         <is>
           <t>자동화 전용</t>
         </is>
       </c>
-      <c r="D3" s="45" t="inlineStr">
+      <c r="D3" s="48" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="E3" s="45" t="inlineStr">
+      <c r="E3" s="48" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F3" s="45" t="inlineStr">
+      <c r="F3" s="48" t="inlineStr">
         <is>
           <t>Always</t>
         </is>
       </c>
-      <c r="G3" s="45" t="inlineStr">
+      <c r="G3" s="48" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev_RC1</t>
         </is>
       </c>
-      <c r="H3" s="45" t="inlineStr">
+      <c r="H3" s="48" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="I3" s="45" t="inlineStr">
+      <c r="I3" s="48" t="inlineStr">
         <is>
           <t>PC웹</t>
         </is>
       </c>
-      <c r="J3" s="45" t="inlineStr">
+      <c r="J3" s="48" t="inlineStr">
         <is>
           <t>앱 진입/세션</t>
         </is>
       </c>
-      <c r="K3" s="45" t="inlineStr">
+      <c r="K3" s="48" t="inlineStr">
         <is>
           <t>정준호</t>
         </is>
       </c>
-      <c r="L3" s="45" t="inlineStr">
+      <c r="L3" s="48" t="inlineStr">
         <is>
           <t>Claude Opus 5</t>
         </is>
       </c>
-      <c r="M3" s="45" t="inlineStr">
+      <c r="M3" s="48" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="C4" s="45" t="inlineStr">
+      <c r="C4" s="48" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="48" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="E4" s="45" t="inlineStr">
+      <c r="E4" s="48" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="48" t="inlineStr">
         <is>
           <t>Often</t>
         </is>
       </c>
-      <c r="G4" s="45" t="inlineStr">
+      <c r="G4" s="48" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev_RC2</t>
         </is>
       </c>
-      <c r="H4" s="45" t="inlineStr">
+      <c r="H4" s="48" t="inlineStr">
         <is>
           <t>Won't Do</t>
         </is>
       </c>
-      <c r="J4" s="45" t="inlineStr">
+      <c r="J4" s="48" t="inlineStr">
         <is>
           <t>계정/게이팅</t>
         </is>
       </c>
-      <c r="M4" s="45" t="inlineStr">
+      <c r="M4" s="48" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_RT1</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="45" t="inlineStr">
+      <c r="C5" s="48" t="inlineStr">
         <is>
           <t>사람 전용</t>
         </is>
       </c>
-      <c r="D5" s="45" t="inlineStr">
+      <c r="D5" s="48" t="inlineStr">
         <is>
           <t>Resolved</t>
         </is>
       </c>
-      <c r="E5" s="45" t="inlineStr">
+      <c r="E5" s="48" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F5" s="45" t="inlineStr">
+      <c r="F5" s="48" t="inlineStr">
         <is>
           <t>Sometimes</t>
         </is>
       </c>
-      <c r="G5" s="45" t="inlineStr">
+      <c r="G5" s="48" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev_RC3</t>
         </is>
       </c>
-      <c r="H5" s="45" t="inlineStr">
+      <c r="H5" s="48" t="inlineStr">
         <is>
           <t>Won't Fix</t>
         </is>
       </c>
-      <c r="J5" s="45" t="inlineStr">
+      <c r="J5" s="48" t="inlineStr">
         <is>
           <t>탐색/발견</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="D6" s="45" t="inlineStr">
+      <c r="D6" s="48" t="inlineStr">
         <is>
           <t>Reopen</t>
         </is>
       </c>
-      <c r="F6" s="45" t="inlineStr">
+      <c r="F6" s="48" t="inlineStr">
         <is>
           <t>Once</t>
         </is>
       </c>
-      <c r="G6" s="45" t="inlineStr">
+      <c r="G6" s="48" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_RT1_RC1</t>
         </is>
       </c>
-      <c r="H6" s="45" t="inlineStr">
+      <c r="H6" s="48" t="inlineStr">
         <is>
           <t>Duplicate</t>
         </is>
       </c>
-      <c r="J6" s="45" t="inlineStr">
+      <c r="J6" s="48" t="inlineStr">
         <is>
           <t>유저 페르소나</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="D7" s="45" t="inlineStr">
+      <c r="D7" s="48" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="H7" s="45" t="inlineStr">
+      <c r="H7" s="48" t="inlineStr">
         <is>
           <t>Incomplete</t>
         </is>
       </c>
-      <c r="J7" s="45" t="inlineStr">
+      <c r="J7" s="48" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="H8" s="45" t="inlineStr">
+      <c r="H8" s="48" t="inlineStr">
         <is>
           <t>Cannot Reproduce</t>
         </is>
       </c>
-      <c r="J8" s="45" t="inlineStr">
+      <c r="J8" s="48" t="inlineStr">
         <is>
           <t>서사 시스템</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="H9" s="45" t="inlineStr">
+      <c r="H9" s="48" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="J9" s="45" t="inlineStr">
+      <c r="J9" s="48" t="inlineStr">
         <is>
           <t>대화 세션</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="H10" s="45" t="inlineStr">
+      <c r="H10" s="48" t="inlineStr">
         <is>
           <t>Declined</t>
         </is>
       </c>
-      <c r="J10" s="45" t="inlineStr">
+      <c r="J10" s="48" t="inlineStr">
         <is>
           <t>세이브/로드</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="J11" s="45" t="inlineStr">
+      <c r="J11" s="48" t="inlineStr">
         <is>
           <t>메모리/컨텍스트</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="J12" s="45" t="inlineStr">
+      <c r="J12" s="48" t="inlineStr">
         <is>
           <t>입력/출력 세이프티</t>
         </is>
@@ -3779,1082 +4010,1082 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="46" t="inlineStr">
+      <c r="B2" s="49" t="inlineStr">
         <is>
           <t>명세서 — 시트 규칙 정본</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="47" t="inlineStr">
+      <c r="B3" s="50" t="inlineStr">
         <is>
           <t>이 시트가 구조 규칙의 정본입니다. rules/tc-sheet-format.md와 짝으로 교차 검증하며, 불일치 발견 시 임의 판단 없이 사용자에게 기준을 확인합니다. 서식(색·테두리·폰트)의 정본은 design-template/xlsx-design-guide.md입니다.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>1. 시트 구성</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="44" t="inlineStr">
+      <c r="B6" s="47" t="inlineStr">
         <is>
           <t>시트</t>
         </is>
       </c>
-      <c r="C6" s="44" t="inlineStr">
+      <c r="C6" s="47" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B7" s="46" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="C7" s="43" t="inlineStr">
+      <c r="C7" s="46" t="inlineStr">
         <is>
           <t>TC 작성과 실행 기록. 노란 셀은 실행 단계에서 채워집니다</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="43" t="inlineStr">
+      <c r="B8" s="46" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="C8" s="43" t="inlineStr">
+      <c r="C8" s="46" t="inlineStr">
         <is>
           <t>행 단위 자동 집계(1-Depth 기준). 기준 골격 버전(C4)은 생성 시 자동 기입됩니다</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="43" t="inlineStr">
+      <c r="B9" s="46" t="inlineStr">
         <is>
           <t>이슈 관리 시트</t>
         </is>
       </c>
-      <c r="C9" s="43" t="inlineStr">
+      <c r="C9" s="46" t="inlineStr">
         <is>
           <t>결함 기록(내장 운영, JIRA 미사용) — JIRA 이슈 등록·관리 방식을 시트로 표현. Issue No.로 Test Case와 연결합니다. 정본은 별도 파일 test-case/{프로젝트}-issues.json이며 이 시트는 그 파생입니다</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="43" t="inlineStr">
+      <c r="B10" s="46" t="inlineStr">
         <is>
           <t>목록</t>
         </is>
       </c>
-      <c r="C10" s="43" t="inlineStr">
+      <c r="C10" s="46" t="inlineStr">
         <is>
           <t>드롭다운 참조 목록의 정본. 숨기지 않고 맨 뒤에 둡니다</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="43" t="inlineStr">
+      <c r="B11" s="46" t="inlineStr">
         <is>
           <t>명세서</t>
         </is>
       </c>
-      <c r="C11" s="43" t="inlineStr">
+      <c r="C11" s="46" t="inlineStr">
         <is>
           <t>이 시트 — 구조 규칙의 정본</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="28" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>2. 컬럼 정의 (Test Case)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="44" t="inlineStr">
+      <c r="B14" s="47" t="inlineStr">
         <is>
           <t>컬럼</t>
         </is>
       </c>
-      <c r="C14" s="44" t="inlineStr">
+      <c r="C14" s="47" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="D14" s="44" t="inlineStr">
+      <c r="D14" s="47" t="inlineStr">
         <is>
           <t>채우는 규칙</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="43" t="inlineStr">
+      <c r="B15" s="46" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C15" s="43" t="inlineStr">
+      <c r="C15" s="46" t="inlineStr">
         <is>
           <t>행 번호</t>
         </is>
       </c>
-      <c r="D15" s="43" t="inlineStr">
+      <c r="D15" s="46" t="inlineStr">
         <is>
           <t>자동 수식(ROW() 기준). 직접 입력하지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="43" t="inlineStr">
+      <c r="B16" s="46" t="inlineStr">
         <is>
           <t>1~7-Depth</t>
         </is>
       </c>
-      <c r="C16" s="43" t="inlineStr">
+      <c r="C16" s="46" t="inlineStr">
         <is>
           <t>기능 계층</t>
         </is>
       </c>
-      <c r="D16" s="43" t="inlineStr">
+      <c r="D16" s="46" t="inlineStr">
         <is>
           <t>행마다 반복(기대결과 추가 행 포함 — 집계·필터의 전제). 의미 있는 깊이까지만 쓰고 나머지는 빈칸. 병합하지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="43" t="inlineStr">
+      <c r="B17" s="46" t="inlineStr">
         <is>
           <t>Pre-Condition</t>
         </is>
       </c>
-      <c r="C17" s="43" t="inlineStr">
+      <c r="C17" s="46" t="inlineStr">
         <is>
           <t>사전조건</t>
         </is>
       </c>
-      <c r="D17" s="43" t="inlineStr">
+      <c r="D17" s="46" t="inlineStr">
         <is>
           <t>TN 1행에 케이스 진입 조건. 중간 스텝에 앞 스텝이 만들지 못하는 새 상태(시간 경과·외부 변화 등)가 필요하면 그 행에도 적습니다 — 앞 스텝의 결과로 성립한 상태는 제외. 같은 조건이 걸리는 스텝 행 범위는 세로 병합하되 케이스 전체 병합은 금지</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="43" t="inlineStr">
+      <c r="B18" s="46" t="inlineStr">
         <is>
           <t>TN</t>
         </is>
       </c>
-      <c r="C18" s="43" t="inlineStr">
+      <c r="C18" s="46" t="inlineStr">
         <is>
           <t>스텝 번호</t>
         </is>
       </c>
-      <c r="D18" s="43" t="inlineStr">
+      <c r="D18" s="46" t="inlineStr">
         <is>
           <t>케이스마다 1부터. 새 케이스가 시작되면 1로 복귀. 한 스텝의 기대결과가 여러 행이면(TN 값 무관) Test-Step과 함께 그 범위를 세로 병합합니다 — 반복 기재하면 독립 동작 여러 개로 오독됩니다</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="43" t="inlineStr">
+      <c r="B19" s="46" t="inlineStr">
         <is>
           <t>Test-Step</t>
         </is>
       </c>
-      <c r="C19" s="43" t="inlineStr">
+      <c r="C19" s="46" t="inlineStr">
         <is>
           <t>수행 동작</t>
         </is>
       </c>
-      <c r="D19" s="43" t="inlineStr">
+      <c r="D19" s="46" t="inlineStr">
         <is>
           <t>「~한다」 체. TN과 같은 범위로 세로 병합</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="43" t="inlineStr">
+      <c r="B20" s="46" t="inlineStr">
         <is>
           <t>Expected-Result</t>
         </is>
       </c>
-      <c r="C20" s="43" t="inlineStr">
+      <c r="C20" s="46" t="inlineStr">
         <is>
           <t>기대 결과</t>
         </is>
       </c>
-      <c r="D20" s="43" t="inlineStr">
+      <c r="D20" s="46" t="inlineStr">
         <is>
           <t>「~된다」 체. 판정 가능한 문장 — 임계·합격선·시도 횟수는 문장 안에 숫자로. 한 행 = 한 판정이므로 병합하지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="43" t="inlineStr">
+      <c r="B21" s="46" t="inlineStr">
         <is>
           <t>실행 주체</t>
         </is>
       </c>
-      <c r="C21" s="43" t="inlineStr">
+      <c r="C21" s="46" t="inlineStr">
         <is>
           <t>누가 수행하는가</t>
         </is>
       </c>
-      <c r="D21" s="43" t="inlineStr">
+      <c r="D21" s="46" t="inlineStr">
         <is>
           <t>행마다 반복(드롭다운 3종). 자동화 전용 = 사람이 화면만 봐서 판정 불가 / 사람 전용 = 자동화가 판정 기준을 못 세움 / 공통 = 기본값. 반복 횟수는 판정 근거가 아니며 「사람이 1회 봐도 의미가 있는가」로 갈립니다</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="43" t="inlineStr">
+      <c r="B22" s="46" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="C22" s="43" t="inlineStr">
+      <c r="C22" s="46" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="D22" s="43" t="inlineStr">
+      <c r="D22" s="46" t="inlineStr">
         <is>
           <t>행마다 반복. High/Medium/Low — 케이스의 속성이지만 Summary가 행 단위로 집계하므로 행마다 값을 둡니다</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="43" t="inlineStr">
+      <c r="B23" s="46" t="inlineStr">
         <is>
           <t>Total Result</t>
         </is>
       </c>
-      <c r="C23" s="43" t="inlineStr">
+      <c r="C23" s="46" t="inlineStr">
         <is>
           <t>행 판정</t>
         </is>
       </c>
-      <c r="D23" s="43" t="inlineStr">
+      <c r="D23" s="46" t="inlineStr">
         <is>
           <t>수식 열. 병합하지 않고 데이터 한 행씩 세웁니다 — 같은 플랫폼에 단말이 여럿일 때 그 행의 단말 결과를 요약합니다. 직접 입력하지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="43" t="inlineStr">
+      <c r="B24" s="46" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="C24" s="43" t="inlineStr">
+      <c r="C24" s="46" t="inlineStr">
         <is>
           <t>스텝 실행 결과</t>
         </is>
       </c>
-      <c r="D24" s="43" t="inlineStr">
+      <c r="D24" s="46" t="inlineStr">
         <is>
           <t>드롭다운 4종(아래 상태값 정의). 실행 단계에서 채움 — 노란 셀</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="43" t="inlineStr">
+      <c r="B25" s="46" t="inlineStr">
         <is>
           <t>Issue No.</t>
         </is>
       </c>
-      <c r="C25" s="43" t="inlineStr">
+      <c r="C25" s="46" t="inlineStr">
         <is>
           <t>관련 이슈</t>
         </is>
       </c>
-      <c r="D25" s="43" t="inlineStr">
+      <c r="D25" s="46" t="inlineStr">
         <is>
           <t>해당 TC를 수행하는 과정에서 이슈가 발생하면, 먼저 이슈 관리 시트에 이슈를 등록하고 거기서 부여된 Issue No.를 이 칸에 적습니다. 실행 단계에서 채움 — 노란 셀</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="43" t="inlineStr">
+      <c r="B26" s="46" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="C26" s="43" t="inlineStr">
+      <c r="C26" s="46" t="inlineStr">
         <is>
           <t>수행 중 기록</t>
         </is>
       </c>
-      <c r="D26" s="43" t="inlineStr">
+      <c r="D26" s="46" t="inlineStr">
         <is>
           <t>TC를 수행하다 생긴 문제·관찰을 실행 단계에서 적습니다 — 노란 셀. 설계 시점에는 비어 있습니다</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="43" t="inlineStr">
+      <c r="B27" s="46" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="C27" s="43" t="inlineStr">
+      <c r="C27" s="46" t="inlineStr">
         <is>
           <t>수행 전 참고사항</t>
         </is>
       </c>
-      <c r="D27" s="43" t="inlineStr">
+      <c r="D27" s="46" t="inlineStr">
         <is>
           <t>사람이 읽을 안내만 담습니다 — ①함께 볼 것 ②수행 방법 ③조건 만드는 법. 케이스 메타는 2026-08-03 개정으로 TC ID·검증유형 열이 따로 갖습니다. 스텝 범위 세로 병합</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="43" t="inlineStr">
+      <c r="B28" s="46" t="inlineStr">
         <is>
           <t>TC ID</t>
         </is>
       </c>
-      <c r="C28" s="43" t="inlineStr">
+      <c r="C28" s="46" t="inlineStr">
         <is>
           <t>조인 키</t>
         </is>
       </c>
-      <c r="D28" s="43" t="inlineStr">
+      <c r="D28" s="46" t="inlineStr">
         <is>
           <t>행마다 반복. 자동화 케이스명·추적 매트릭스·이슈 연결이 참조합니다. 사람의 실행 동선에서 빼려고 Note 우측 참조 블록에 둡니다</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="43" t="inlineStr">
+      <c r="B29" s="46" t="inlineStr">
         <is>
           <t>검증유형</t>
         </is>
       </c>
-      <c r="C29" s="43" t="inlineStr">
+      <c r="C29" s="46" t="inlineStr">
         <is>
           <t>판정 방식</t>
         </is>
       </c>
-      <c r="D29" s="43" t="inlineStr">
+      <c r="D29" s="46" t="inlineStr">
         <is>
           <t>행마다 반복(드롭다운 4종). 반복 횟수는 시트에 적지 않습니다 — 수동 실행자가 자기에게 내려진 지시로 오독하기 때문입니다. 반복은 자동화가 수행하며, 사람은 어떤 유형이든 1회입니다. 확률적·루브릭을 사람이 1회 수행했다면 결과는 Pass가 아니라 관찰 기록이고, 판정은 자동화 반복이나 채점이 담당합니다</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="28" t="inlineStr">
+      <c r="B31" s="31" t="inlineStr">
         <is>
           <t>3. 상태값 정의</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="44" t="inlineStr">
+      <c r="B32" s="47" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="C32" s="44" t="inlineStr">
+      <c r="C32" s="47" t="inlineStr">
         <is>
           <t>정의</t>
         </is>
       </c>
-      <c r="D32" s="44" t="inlineStr">
+      <c r="D32" s="47" t="inlineStr">
         <is>
           <t>Pass율 분모</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="43" t="inlineStr">
+      <c r="B33" s="46" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C33" s="43" t="inlineStr">
+      <c r="C33" s="46" t="inlineStr">
         <is>
           <t>성공</t>
         </is>
       </c>
-      <c r="D33" s="43" t="inlineStr">
+      <c r="D33" s="46" t="inlineStr">
         <is>
           <t>포함</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="43" t="inlineStr">
+      <c r="B34" s="46" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="C34" s="43" t="inlineStr">
+      <c r="C34" s="46" t="inlineStr">
         <is>
           <t>실패</t>
         </is>
       </c>
-      <c r="D34" s="43" t="inlineStr">
+      <c r="D34" s="46" t="inlineStr">
         <is>
           <t>포함</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="43" t="inlineStr">
+      <c r="B35" s="46" t="inlineStr">
         <is>
           <t>NI</t>
         </is>
       </c>
-      <c r="C35" s="43" t="inlineStr">
+      <c r="C35" s="46" t="inlineStr">
         <is>
           <t>미구현이거나 스펙에 없어 실행 대상이 아님 (Not Implemented)</t>
         </is>
       </c>
-      <c r="D35" s="43" t="inlineStr">
+      <c r="D35" s="46" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="43" t="inlineStr">
+      <c r="B36" s="46" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="C36" s="43" t="inlineStr">
+      <c r="C36" s="46" t="inlineStr">
         <is>
           <t>기능은 구현됐으나 확인할 수 없는 상태 — 선행 케이스 Fail·환경 결함·데이터 준비 불가 등. 사유는 실행 과정에서 Comment에 적습니다</t>
         </is>
       </c>
-      <c r="D36" s="43" t="inlineStr">
+      <c r="D36" s="46" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="47" t="inlineStr">
+      <c r="B37" s="50" t="inlineStr">
         <is>
           <t>Pass율 = Pass ÷ (Pass + Fail). NI·Blocked를 분모에 넣지 않는 이유는 결함 1건이 후속 Blocked 수만큼 중복 계상되는 것을 막기 위해서입니다.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="28" t="inlineStr">
+      <c r="B39" s="31" t="inlineStr">
         <is>
           <t>4. Total Result 규칙</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="44" t="inlineStr">
+      <c r="B40" s="47" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C40" s="44" t="inlineStr">
+      <c r="C40" s="47" t="inlineStr">
         <is>
           <t>규칙</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="43" t="inlineStr">
+      <c r="B41" s="46" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="C41" s="43" t="inlineStr">
+      <c r="C41" s="46" t="inlineStr">
         <is>
           <t>Fail &gt; Blocked &gt; NI &gt; Pass — 스텝 중 하나라도 Fail이면 케이스 Fail</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="43" t="inlineStr">
+      <c r="B42" s="46" t="inlineStr">
         <is>
           <t>수식 원형</t>
         </is>
       </c>
-      <c r="C42" s="43" t="inlineStr">
+      <c r="C42" s="46" t="inlineStr">
         <is>
           <t>IF(COUNTIF(범위,"Fail")&gt;0,"Fail",IF(COUNTIF(범위,"Blocked")&gt;0,"Blocked",IF(COUNTIF(범위,"NI")&gt;0,"NI",IF(COUNTIF(범위,"Pass")&gt;0,"Pass","")))) — 셀에는 앞에 = 를 붙여 사용합니다. 아무것도 실행되지 않은 케이스는 빈칸입니다</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="43" t="inlineStr">
+      <c r="B43" s="46" t="inlineStr">
         <is>
           <t>병합</t>
         </is>
       </c>
-      <c r="C43" s="43" t="inlineStr">
+      <c r="C43" s="46" t="inlineStr">
         <is>
           <t>하지 않습니다 — 데이터 한 행씩 세웁니다. 같은 플랫폼에 단말이 여럿일 때 그 행의 단말 결과를 하나로 요약하는 자리입니다</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="28" t="inlineStr">
+      <c r="B45" s="31" t="inlineStr">
         <is>
           <t>5. TC ID 체계</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="44" t="inlineStr">
+      <c r="B46" s="47" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C46" s="44" t="inlineStr">
+      <c r="C46" s="47" t="inlineStr">
         <is>
           <t>규칙</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="43" t="inlineStr">
+      <c r="B47" s="46" t="inlineStr">
         <is>
           <t>형식</t>
         </is>
       </c>
-      <c r="C47" s="43" t="inlineStr">
+      <c r="C47" s="46" t="inlineStr">
         <is>
           <t>TC-{영역코드}-{번호 3자리} — 예: TC-ENT-001</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="43" t="inlineStr">
+      <c r="B48" s="46" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="C48" s="43" t="inlineStr">
+      <c r="C48" s="46" t="inlineStr">
         <is>
           <t>영역 안에서만 증가합니다. 다른 영역에 케이스가 추가돼도 기존 ID가 흔들리지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="43" t="inlineStr">
+      <c r="B49" s="46" t="inlineStr">
         <is>
           <t>영역코드</t>
         </is>
       </c>
-      <c r="C49" s="43" t="inlineStr">
+      <c r="C49" s="46" t="inlineStr">
         <is>
           <t>기능 트리 1-Depth당 하나. 프로젝트별 매핑표는 아래 §5-1이며, 정의가 없는 프로젝트에서는 그 절이 나오지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="43" t="inlineStr">
+      <c r="B50" s="46" t="inlineStr">
         <is>
           <t>기재 위치</t>
         </is>
       </c>
-      <c r="C50" s="43" t="inlineStr">
+      <c r="C50" s="46" t="inlineStr">
         <is>
           <t>Note의 첫 토큰(케이스 메타의 맨 앞). 자동화 케이스명·추적 매트릭스·이슈 연결이 이 ID를 참조합니다. Comment는 설계 시점에 비어 있는 실행 기록 칸이므로 설계 데이터를 두지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="28" t="inlineStr">
+      <c r="B52" s="31" t="inlineStr">
         <is>
           <t>5-1. 영역코드 매핑</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="47" t="inlineStr">
+      <c r="B53" s="50" t="inlineStr">
         <is>
           <t>키는 기능 트리 1-Depth 영역명이며, 이슈 관리 시트 「레이블」 목록과 같은 값을 씁니다. 코드는 영문 표기의 앞 세 글자이고, 한 영역에 하나씩만 둡니다. 정본은 TC 설계 입력(tc-input json)의 area_codes입니다.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="44" t="inlineStr">
+      <c r="B54" s="47" t="inlineStr">
         <is>
           <t>영역 (기능 트리 1-Depth)</t>
         </is>
       </c>
-      <c r="C54" s="44" t="inlineStr">
+      <c r="C54" s="47" t="inlineStr">
         <is>
           <t>코드</t>
         </is>
       </c>
-      <c r="D54" s="44" t="inlineStr">
+      <c r="D54" s="47" t="inlineStr">
         <is>
           <t>영문 표기</t>
         </is>
       </c>
-      <c r="E54" s="44" t="inlineStr">
+      <c r="E54" s="47" t="inlineStr">
         <is>
           <t>TC ID 예</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="43" t="inlineStr">
+      <c r="B55" s="46" t="inlineStr">
         <is>
           <t>앱 진입/세션</t>
         </is>
       </c>
-      <c r="C55" s="43" t="inlineStr">
+      <c r="C55" s="46" t="inlineStr">
         <is>
           <t>ENT</t>
         </is>
       </c>
-      <c r="D55" s="43" t="inlineStr">
+      <c r="D55" s="46" t="inlineStr">
         <is>
           <t>Entry &amp; Session</t>
         </is>
       </c>
-      <c r="E55" s="43" t="inlineStr">
+      <c r="E55" s="46" t="inlineStr">
         <is>
           <t>TC-ENT-001</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="43" t="inlineStr">
+      <c r="B56" s="46" t="inlineStr">
         <is>
           <t>계정/게이팅</t>
         </is>
       </c>
-      <c r="C56" s="43" t="inlineStr">
+      <c r="C56" s="46" t="inlineStr">
         <is>
           <t>GAT</t>
         </is>
       </c>
-      <c r="D56" s="43" t="inlineStr">
+      <c r="D56" s="46" t="inlineStr">
         <is>
           <t>Gating (account &amp; age)</t>
         </is>
       </c>
-      <c r="E56" s="43" t="inlineStr">
+      <c r="E56" s="46" t="inlineStr">
         <is>
           <t>TC-GAT-001</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="43" t="inlineStr">
+      <c r="B57" s="46" t="inlineStr">
         <is>
           <t>탐색/발견</t>
         </is>
       </c>
-      <c r="C57" s="43" t="inlineStr">
+      <c r="C57" s="46" t="inlineStr">
         <is>
           <t>DSC</t>
         </is>
       </c>
-      <c r="D57" s="43" t="inlineStr">
+      <c r="D57" s="46" t="inlineStr">
         <is>
           <t>Discovery</t>
         </is>
       </c>
-      <c r="E57" s="43" t="inlineStr">
+      <c r="E57" s="46" t="inlineStr">
         <is>
           <t>TC-DSC-001</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="43" t="inlineStr">
+      <c r="B58" s="46" t="inlineStr">
         <is>
           <t>유저 페르소나</t>
         </is>
       </c>
-      <c r="C58" s="43" t="inlineStr">
+      <c r="C58" s="46" t="inlineStr">
         <is>
           <t>PRF</t>
         </is>
       </c>
-      <c r="D58" s="43" t="inlineStr">
+      <c r="D58" s="46" t="inlineStr">
         <is>
           <t>Profile (dialogue persona)</t>
         </is>
       </c>
-      <c r="E58" s="43" t="inlineStr">
+      <c r="E58" s="46" t="inlineStr">
         <is>
           <t>TC-PRF-001</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="43" t="inlineStr">
+      <c r="B59" s="46" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
-      <c r="C59" s="43" t="inlineStr">
+      <c r="C59" s="46" t="inlineStr">
         <is>
           <t>CUR</t>
         </is>
       </c>
-      <c r="D59" s="43" t="inlineStr">
+      <c r="D59" s="46" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="E59" s="43" t="inlineStr">
+      <c r="E59" s="46" t="inlineStr">
         <is>
           <t>TC-CUR-001</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="43" t="inlineStr">
+      <c r="B60" s="46" t="inlineStr">
         <is>
           <t>서사 시스템</t>
         </is>
       </c>
-      <c r="C60" s="43" t="inlineStr">
+      <c r="C60" s="46" t="inlineStr">
         <is>
           <t>NAR</t>
         </is>
       </c>
-      <c r="D60" s="43" t="inlineStr">
+      <c r="D60" s="46" t="inlineStr">
         <is>
           <t>Narrative</t>
         </is>
       </c>
-      <c r="E60" s="43" t="inlineStr">
+      <c r="E60" s="46" t="inlineStr">
         <is>
           <t>TC-NAR-001</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="43" t="inlineStr">
+      <c r="B61" s="46" t="inlineStr">
         <is>
           <t>대화 세션</t>
         </is>
       </c>
-      <c r="C61" s="43" t="inlineStr">
+      <c r="C61" s="46" t="inlineStr">
         <is>
           <t>CHT</t>
         </is>
       </c>
-      <c r="D61" s="43" t="inlineStr">
+      <c r="D61" s="46" t="inlineStr">
         <is>
           <t>Chat session</t>
         </is>
       </c>
-      <c r="E61" s="43" t="inlineStr">
+      <c r="E61" s="46" t="inlineStr">
         <is>
           <t>TC-CHT-001</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="43" t="inlineStr">
+      <c r="B62" s="46" t="inlineStr">
         <is>
           <t>세이브/로드</t>
         </is>
       </c>
-      <c r="C62" s="43" t="inlineStr">
+      <c r="C62" s="46" t="inlineStr">
         <is>
           <t>SAV</t>
         </is>
       </c>
-      <c r="D62" s="43" t="inlineStr">
+      <c r="D62" s="46" t="inlineStr">
         <is>
           <t>Save &amp; Load</t>
         </is>
       </c>
-      <c r="E62" s="43" t="inlineStr">
+      <c r="E62" s="46" t="inlineStr">
         <is>
           <t>TC-SAV-001</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="43" t="inlineStr">
+      <c r="B63" s="46" t="inlineStr">
         <is>
           <t>메모리/컨텍스트</t>
         </is>
       </c>
-      <c r="C63" s="43" t="inlineStr">
+      <c r="C63" s="46" t="inlineStr">
         <is>
           <t>MEM</t>
         </is>
       </c>
-      <c r="D63" s="43" t="inlineStr">
+      <c r="D63" s="46" t="inlineStr">
         <is>
           <t>Memory &amp; Context</t>
         </is>
       </c>
-      <c r="E63" s="43" t="inlineStr">
+      <c r="E63" s="46" t="inlineStr">
         <is>
           <t>TC-MEM-001</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="43" t="inlineStr">
+      <c r="B64" s="46" t="inlineStr">
         <is>
           <t>입력/출력 세이프티</t>
         </is>
       </c>
-      <c r="C64" s="43" t="inlineStr">
+      <c r="C64" s="46" t="inlineStr">
         <is>
           <t>SAF</t>
         </is>
       </c>
-      <c r="D64" s="43" t="inlineStr">
+      <c r="D64" s="46" t="inlineStr">
         <is>
           <t>Safety (input &amp; output)</t>
         </is>
       </c>
-      <c r="E64" s="43" t="inlineStr">
+      <c r="E64" s="46" t="inlineStr">
         <is>
           <t>TC-SAF-001</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="28" t="inlineStr">
+      <c r="B66" s="31" t="inlineStr">
         <is>
           <t>6. 플랫폼 열 규칙</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="44" t="inlineStr">
+      <c r="B67" s="47" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C67" s="44" t="inlineStr">
+      <c r="C67" s="47" t="inlineStr">
         <is>
           <t>규칙</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="43" t="inlineStr">
+      <c r="B68" s="46" t="inlineStr">
         <is>
           <t>기본값</t>
         </is>
       </c>
-      <c r="C68" s="43" t="inlineStr">
+      <c r="C68" s="46" t="inlineStr">
         <is>
           <t>마스터는 Web / And / iOS 3열</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="43" t="inlineStr">
+      <c r="B69" s="46" t="inlineStr">
         <is>
           <t>프로젝트 조정</t>
         </is>
       </c>
-      <c r="C69" s="43" t="inlineStr">
+      <c r="C69" s="46" t="inlineStr">
         <is>
           <t>TC 설계 시작 시 대상 플랫폼을 사용자에게 재확인하고, Test Case의 Total Result·Result 하위 열과 Summary의 플랫폼 열을 함께 조정합니다</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="28" t="inlineStr">
+      <c r="B71" s="31" t="inlineStr">
         <is>
           <t>7. 입력 규칙</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="44" t="inlineStr">
+      <c r="B72" s="47" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C72" s="44" t="inlineStr">
+      <c r="C72" s="47" t="inlineStr">
         <is>
           <t>규칙</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="43" t="inlineStr">
+      <c r="B73" s="46" t="inlineStr">
         <is>
           <t>실행 채움 셀(노랑)</t>
         </is>
       </c>
-      <c r="C73" s="43" t="inlineStr">
+      <c r="C73" s="46" t="inlineStr">
         <is>
           <t>설계 시점에는 비어 있고 실행 단계에서 채워지는 칸 — 환경 블록·Result·Issue No.·Comment. 채우는 주체가 사람이든 자동화든 설계자는 건드리지 않습니다. 설계 데이터는 노란 칸에 두지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="43" t="inlineStr">
+      <c r="B74" s="46" t="inlineStr">
         <is>
           <t>설계 셀</t>
         </is>
       </c>
-      <c r="C74" s="43" t="inlineStr">
+      <c r="C74" s="46" t="inlineStr">
         <is>
           <t>Depth·절차·기대결과는 실행 중 수정하지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="43" t="inlineStr">
+      <c r="B75" s="46" t="inlineStr">
         <is>
           <t>틀 고정</t>
         </is>
       </c>
-      <c r="C75" s="43" t="inlineStr">
+      <c r="C75" s="46" t="inlineStr">
         <is>
           <t>데이터 첫 행 위. 스크롤해도 2행 제목·헤더·환경 블록이 남으며, 그 구간은 회색(#BFBFBF)과 Total/Result 띠(#F9D7BE)로 데이터와 갈라 둡니다. A열과 1행은 값도 색도 두지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="43" t="inlineStr">
+      <c r="B76" s="46" t="inlineStr">
         <is>
           <t>자동 필터</t>
         </is>
       </c>
-      <c r="C76" s="43" t="inlineStr">
+      <c r="C76" s="46" t="inlineStr">
         <is>
           <t>헤더 행에 걸어 둡니다. 실행 주체·검증유형·Priority처럼 케이스 단위 값으로 거르면 한 케이스의 행이 통째로 남거나 빠져 스텝 범위 병합이 깨지지 않습니다. Result 같은 행 단위 값으로 거르면 케이스 중간이 잘려 병합이 어색해집니다</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="43" t="inlineStr">
+      <c r="B77" s="46" t="inlineStr">
         <is>
           <t>뎁스 채움 색</t>
         </is>
       </c>
-      <c r="C77" s="43" t="inlineStr">
+      <c r="C77" s="46" t="inlineStr">
         <is>
           <t>뎁스 열의 값 있는 셀만 텍스트별 고유색으로 채웁니다 — 같은 텍스트는 같은 색, 인접한 다른 텍스트와는 색상환에서 멀어지게 배정. 케이스명 칸과 빈칸은 흰 배경. 규칙 정본은 xlsx-design-guide.md §5</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="43" t="inlineStr">
+      <c r="B78" s="46" t="inlineStr">
         <is>
           <t>기준 골격 버전</t>
         </is>
       </c>
-      <c r="C78" s="43" t="inlineStr">
+      <c r="C78" s="46" t="inlineStr">
         <is>
           <t>Summary C4에 생성 스크립트가 자동 기입합니다 — 형식 {프로젝트}-tree-v{X.Y}. TC 설계 입력(tc-input json)의 값을 그대로 쓰므로 사람이 옮겨 적지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="28" t="inlineStr">
+      <c r="B80" s="31" t="inlineStr">
         <is>
           <t>8. 컬럼 정의 (이슈 관리 시트)</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="47" t="inlineStr">
+      <c r="B81" s="50" t="inlineStr">
         <is>
           <t>이슈 기록의 정본은 test-case/{프로젝트}-issues.json입니다. TC 설계 원본과 파일을 나눈 이유는 크기가 아니라 생명주기입니다 — TC 세트는 확정되면 고정되지만 이슈는 실행하면서 계속 늘고 상태가 바뀌므로, 한 파일에 두면 이슈 갱신 때마다 설계 원본이 변경되어 확정 시점이 흐려집니다.</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="44" t="inlineStr">
+      <c r="B82" s="47" t="inlineStr">
         <is>
           <t>컬럼</t>
         </is>
       </c>
-      <c r="C82" s="44" t="inlineStr">
+      <c r="C82" s="47" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="D82" s="44" t="inlineStr">
+      <c r="D82" s="47" t="inlineStr">
         <is>
           <t>채우는 규칙</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="43" t="inlineStr">
+      <c r="B83" s="46" t="inlineStr">
         <is>
           <t>프로젝트 ID</t>
         </is>
       </c>
-      <c r="C83" s="43" t="inlineStr">
+      <c r="C83" s="46" t="inlineStr">
         <is>
           <t>프로젝트 식별자</t>
         </is>
       </c>
-      <c r="D83" s="43" t="inlineStr">
+      <c r="D83" s="46" t="inlineStr">
         <is>
           <t>SUT명 기준. 목록 시트 참조</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="43" t="inlineStr">
+      <c r="B84" s="46" t="inlineStr">
         <is>
           <t>Issue No.</t>
         </is>
       </c>
-      <c r="C84" s="43" t="inlineStr">
+      <c r="C84" s="46" t="inlineStr">
         <is>
           <t>발생한 이슈의 식별자</t>
         </is>
       </c>
-      <c r="D84" s="43" t="inlineStr">
+      <c r="D84" s="46" t="inlineStr">
         <is>
           <t>발생한 이슈를 등록하며 부여합니다 — {프로젝트}-{생성 번호순} (1 &gt; 2 &gt; 3 &gt; …). TC 수행 중 발생한 이슈라면 이 번호를 Test Case 시트의 Issue No.에 적어 잇습니다</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="43" t="inlineStr">
+      <c r="B85" s="46" t="inlineStr">
         <is>
           <t>이슈 상태</t>
         </is>
       </c>
-      <c r="C85" s="43" t="inlineStr">
+      <c r="C85" s="46" t="inlineStr">
         <is>
           <t>이슈의 현재 상태</t>
         </is>
       </c>
-      <c r="D85" s="43" t="inlineStr">
+      <c r="D85" s="46" t="inlineStr">
         <is>
           <t>Open: 열린 상태(재현됨) / In Progress: 담당자가 수정 진행 중 / Resolved: 해결됨 / Reopen: 해결된 이슈가 재현되어 다시 엶 / Closed: 재현되지 않아 닫음</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="43" t="inlineStr">
+      <c r="B86" s="46" t="inlineStr">
         <is>
           <t>요약(Summary)</t>
         </is>
       </c>
-      <c r="C86" s="43" t="inlineStr">
+      <c r="C86" s="46" t="inlineStr">
         <is>
           <t>이슈 제목</t>
         </is>
       </c>
-      <c r="D86" s="43" t="inlineStr">
+      <c r="D86" s="46" t="inlineStr">
         <is>
           <t>재현 경로 요약 — 문단 구분은 "&gt;", 마지막은 무엇이 잘못됐는지 수동태로.
 ex) rules/ 폴더 이동 &gt; A.md 실행 시, 크래시 발생됨</t>
@@ -4862,68 +5093,68 @@
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="43" t="inlineStr">
+      <c r="B87" s="46" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="C87" s="43" t="inlineStr">
+      <c r="C87" s="46" t="inlineStr">
         <is>
           <t>재현 방법 상세</t>
         </is>
       </c>
-      <c r="D87" s="43" t="inlineStr">
+      <c r="D87" s="46" t="inlineStr">
         <is>
           <t>Pre-condition(사전 조건) / Reproduce Step(재현 스텝) / Actual Result(실제 결과, ~됨) / Expected Result(기대 결과, ~되어야 함) / QA Comment(참고) 순서로 작성</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="43" t="inlineStr">
+      <c r="B88" s="46" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="C88" s="43" t="inlineStr">
+      <c r="C88" s="46" t="inlineStr">
         <is>
           <t>이슈 심각도</t>
         </is>
       </c>
-      <c r="D88" s="43" t="inlineStr">
+      <c r="D88" s="46" t="inlineStr">
         <is>
           <t>High: 크래시·진입 불가 등 치명 / Medium: 진입은 되나 기능 미동작 / Low: 문구·표기 오류</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="43" t="inlineStr">
+      <c r="B89" s="46" t="inlineStr">
         <is>
           <t>빈도</t>
         </is>
       </c>
-      <c r="C89" s="43" t="inlineStr">
+      <c r="C89" s="46" t="inlineStr">
         <is>
           <t>발생 빈도</t>
         </is>
       </c>
-      <c r="D89" s="43" t="inlineStr">
+      <c r="D89" s="46" t="inlineStr">
         <is>
           <t>Always: 항상 / Often: 종종(70% 이상) / Sometimes: 가끔(70% 미만) / Once: 1회만</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="43" t="inlineStr">
+      <c r="B90" s="46" t="inlineStr">
         <is>
           <t>영향 받는 버전</t>
         </is>
       </c>
-      <c r="C90" s="43" t="inlineStr">
+      <c r="C90" s="46" t="inlineStr">
         <is>
           <t>이슈가 재현되는 빌드</t>
         </is>
       </c>
-      <c r="D90" s="43" t="inlineStr">
+      <c r="D90" s="46" t="inlineStr">
         <is>
           <t>{테스트환경}_{개발목표버전}_{스프린트}_{확인버전} 네 토막.
 테스트환경=어디서 확인했는가(PC웹) / 개발목표버전=무엇을 향해 개발 중인가(Ver1.0) / 스프린트=그 목표 버전의 주 목표(Dev, RT1=Release Train 1차) / 확인버전=그 시점의 RC 빌드(RC=Release Candidate).
@@ -4933,271 +5164,271 @@
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="43" t="inlineStr">
+      <c r="B91" s="46" t="inlineStr">
         <is>
           <t>수정 버전</t>
         </is>
       </c>
-      <c r="C91" s="43" t="inlineStr">
+      <c r="C91" s="46" t="inlineStr">
         <is>
           <t>이슈가 수정된 버전</t>
         </is>
       </c>
-      <c r="D91" s="43" t="inlineStr">
+      <c r="D91" s="46" t="inlineStr">
         <is>
           <t>영향 받는 버전과 같은 목록을 사용합니다</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="43" t="inlineStr">
+      <c r="B92" s="46" t="inlineStr">
         <is>
           <t>해결책</t>
         </is>
       </c>
-      <c r="C92" s="43" t="inlineStr">
+      <c r="C92" s="46" t="inlineStr">
         <is>
           <t>수정 방향</t>
         </is>
       </c>
-      <c r="D92" s="43" t="inlineStr">
+      <c r="D92" s="46" t="inlineStr">
         <is>
           <t>Fixed: 코드 수정으로 대응 / Won't Do: 환경·기술 지원 불가로 미대응 / Won't Fix: 수정 필요하나 지금은 안 함 / Duplicate: 동일 건 존재 / Incomplete: 이슈 자체가 잘못됨 / Cannot Reproduce: 재현 불가 / Done: 기획·정책 결정으로 이슈 아님 확정 / Declined(QA Only): QA선에서 이슈로 보지 않음</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="43" t="inlineStr">
+      <c r="B93" s="46" t="inlineStr">
         <is>
           <t>환경</t>
         </is>
       </c>
-      <c r="C93" s="43" t="inlineStr">
+      <c r="C93" s="46" t="inlineStr">
         <is>
           <t>발생 디바이스</t>
         </is>
       </c>
-      <c r="D93" s="43" t="inlineStr">
+      <c r="D93" s="46" t="inlineStr">
         <is>
           <t>PC웹 / Android / iOS</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="43" t="inlineStr">
+      <c r="B94" s="46" t="inlineStr">
         <is>
           <t>레이블</t>
         </is>
       </c>
-      <c r="C94" s="43" t="inlineStr">
+      <c r="C94" s="46" t="inlineStr">
         <is>
           <t>발생 영역</t>
         </is>
       </c>
-      <c r="D94" s="43" t="inlineStr">
+      <c r="D94" s="46" t="inlineStr">
         <is>
           <t>기능 트리 1-Depth 영역명 — 목록 시트 참조. 트리 개정 시 목록만 갱신하고 기존 행 값은 소급 변경하지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="43" t="inlineStr">
+      <c r="B95" s="46" t="inlineStr">
         <is>
           <t>보고자</t>
         </is>
       </c>
-      <c r="C95" s="43" t="inlineStr">
+      <c r="C95" s="46" t="inlineStr">
         <is>
           <t>이슈 등록자</t>
         </is>
       </c>
-      <c r="D95" s="43" t="inlineStr">
+      <c r="D95" s="46" t="inlineStr">
         <is>
           <t>목록 참조</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="43" t="inlineStr">
+      <c r="B96" s="46" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="C96" s="43" t="inlineStr">
+      <c r="C96" s="46" t="inlineStr">
         <is>
           <t>이슈 수정 담당자</t>
         </is>
       </c>
-      <c r="D96" s="43" t="inlineStr">
+      <c r="D96" s="46" t="inlineStr">
         <is>
           <t>목록 참조</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="43" t="inlineStr">
+      <c r="B97" s="46" t="inlineStr">
         <is>
           <t>관측자</t>
         </is>
       </c>
-      <c r="C97" s="43" t="inlineStr">
+      <c r="C97" s="46" t="inlineStr">
         <is>
           <t>함께 팔로우할 인원</t>
         </is>
       </c>
-      <c r="D97" s="43" t="inlineStr">
+      <c r="D97" s="46" t="inlineStr">
         <is>
           <t>드롭다운 없음 — 쉼표 구분 자유 입력(멀티 선택은 xlsx 표준 기능에 없음)</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="43" t="inlineStr">
+      <c r="B98" s="46" t="inlineStr">
         <is>
           <t>첨부파일</t>
         </is>
       </c>
-      <c r="C98" s="43" t="inlineStr">
+      <c r="C98" s="46" t="inlineStr">
         <is>
           <t>재현 증적</t>
         </is>
       </c>
-      <c r="D98" s="43" t="inlineStr">
+      <c r="D98" s="46" t="inlineStr">
         <is>
           <t>재현 영상·이미지의 경로 또는 링크</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="43" t="inlineStr">
+      <c r="B99" s="46" t="inlineStr">
         <is>
           <t>스프린트</t>
         </is>
       </c>
-      <c r="C99" s="43" t="inlineStr">
+      <c r="C99" s="46" t="inlineStr">
         <is>
           <t>QA 진행 단위</t>
         </is>
       </c>
-      <c r="D99" s="43" t="inlineStr">
+      <c r="D99" s="46" t="inlineStr">
         <is>
           <t>영향 받는 버전에서 확인버전(RC)을 뺀 앞 세 토막 — {테스트환경}_{개발목표버전}_{스프린트}. 스프린트 하나가 RC1·RC2·RC3에 걸치므로 스프린트는 사이클을, 버전은 그 안의 빌드를 가리킵니다. 발견 단계도 이 칸으로 갈립니다 — ex) PC웹_Ver1.0_Dev(개발 단계 자체 발견) / PC웹_Ver1.0_RT1(QA 사이클 검출). 목록 참조</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="43" t="inlineStr">
+      <c r="B100" s="46" t="inlineStr">
         <is>
           <t>이슈 등록일</t>
         </is>
       </c>
-      <c r="C100" s="43" t="inlineStr">
+      <c r="C100" s="46" t="inlineStr">
         <is>
           <t>최초 등록일</t>
         </is>
       </c>
-      <c r="D100" s="43" t="inlineStr">
+      <c r="D100" s="46" t="inlineStr">
         <is>
           <t>YYYY-MM-DD. 이후 변경하지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="43" t="inlineStr">
+      <c r="B101" s="46" t="inlineStr">
         <is>
           <t>이슈 최종 수정일자</t>
         </is>
       </c>
-      <c r="C101" s="43" t="inlineStr">
+      <c r="C101" s="46" t="inlineStr">
         <is>
           <t>내용 최종 수정일</t>
         </is>
       </c>
-      <c r="D101" s="43" t="inlineStr">
+      <c r="D101" s="46" t="inlineStr">
         <is>
           <t>YYYY-MM-DD. 요약·설명 등 내용이 바뀔 때 갱신</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="43" t="inlineStr">
+      <c r="B102" s="46" t="inlineStr">
         <is>
           <t>이슈 상태 최종 변경일자</t>
         </is>
       </c>
-      <c r="C102" s="43" t="inlineStr">
+      <c r="C102" s="46" t="inlineStr">
         <is>
           <t>상태 최종 변경일</t>
         </is>
       </c>
-      <c r="D102" s="43" t="inlineStr">
+      <c r="D102" s="46" t="inlineStr">
         <is>
           <t>YYYY-MM-DD. 이슈 상태가 바뀔 때 갱신</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="B104" s="28" t="inlineStr">
+      <c r="B104" s="31" t="inlineStr">
         <is>
           <t>9. 목록 시트 규칙</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="B105" s="44" t="inlineStr">
+      <c r="B105" s="47" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C105" s="44" t="inlineStr">
+      <c r="C105" s="47" t="inlineStr">
         <is>
           <t>규칙</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="B106" s="43" t="inlineStr">
+      <c r="B106" s="46" t="inlineStr">
         <is>
           <t>지위</t>
         </is>
       </c>
-      <c r="C106" s="43" t="inlineStr">
+      <c r="C106" s="46" t="inlineStr">
         <is>
           <t>드롭다운 참조의 정본 — 전 시트의 데이터 검증이 이 시트를 참조합니다</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="B107" s="43" t="inlineStr">
+      <c r="B107" s="46" t="inlineStr">
         <is>
           <t>노출</t>
         </is>
       </c>
-      <c r="C107" s="43" t="inlineStr">
+      <c r="C107" s="46" t="inlineStr">
         <is>
           <t>숨기지 않고 맨 뒤 배치 — 값 체계 자체가 전시물입니다</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="B108" s="43" t="inlineStr">
+      <c r="B108" s="46" t="inlineStr">
         <is>
           <t>갱신</t>
         </is>
       </c>
-      <c r="C108" s="43" t="inlineStr">
+      <c r="C108" s="46" t="inlineStr">
         <is>
           <t>항목 추가는 행 추가로. 명칭 변경은 목록만 교체하고 기존 데이터 행은 소급 변경하지 않습니다(검증은 신규 입력에만 작동)</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="B109" s="43" t="inlineStr">
+      <c r="B109" s="46" t="inlineStr">
         <is>
           <t>레이블 동기</t>
         </is>
       </c>
-      <c r="C109" s="43" t="inlineStr">
+      <c r="C109" s="46" t="inlineStr">
         <is>
           <t>기능 트리 개정 시 레이블 목록을 함께 갱신합니다(정본 수정 체크리스트 연동)</t>
         </is>

--- a/projects/qa-lab-miyonchat/test-case/qa-lab-miyonchat-tc-v1.0.xlsx
+++ b/projects/qa-lab-miyonchat/test-case/qa-lab-miyonchat-tc-v1.0.xlsx
@@ -16,17 +16,18 @@
   <definedNames>
     <definedName name="list_project">목록!$B$3:$B$3</definedName>
     <definedName name="list_exec">목록!$C$3:$C$5</definedName>
-    <definedName name="list_status">목록!$D$3:$D$7</definedName>
-    <definedName name="list_priority">목록!$E$3:$E$5</definedName>
-    <definedName name="list_frequency">목록!$F$3:$F$6</definedName>
-    <definedName name="list_version">목록!$G$3:$G$6</definedName>
-    <definedName name="list_resolution">목록!$H$3:$H$10</definedName>
-    <definedName name="list_env">목록!$I$3:$I$3</definedName>
-    <definedName name="list_label">목록!$J$3:$J$12</definedName>
-    <definedName name="list_reporter">목록!$K$3:$K$3</definedName>
-    <definedName name="list_assignee">목록!$L$3:$L$3</definedName>
-    <definedName name="list_sprint">목록!$M$3:$M$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Case'!$B$4:$R$32</definedName>
+    <definedName name="list_state">목록!$D$3:$D$7</definedName>
+    <definedName name="list_status">목록!$E$3:$E$7</definedName>
+    <definedName name="list_priority">목록!$F$3:$F$5</definedName>
+    <definedName name="list_frequency">목록!$G$3:$G$6</definedName>
+    <definedName name="list_version">목록!$H$3:$H$6</definedName>
+    <definedName name="list_resolution">목록!$I$3:$I$10</definedName>
+    <definedName name="list_env">목록!$J$3:$J$3</definedName>
+    <definedName name="list_label">목록!$K$3:$K$12</definedName>
+    <definedName name="list_reporter">목록!$L$3:$L$3</definedName>
+    <definedName name="list_assignee">목록!$M$3:$M$3</definedName>
+    <definedName name="list_sprint">목록!$N$3:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Case'!$B$4:$S$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'이슈 관리 시트'!$B$2:$U$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -102,7 +103,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="42">
     <fill>
       <patternFill/>
     </fill>
@@ -136,42 +137,112 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECD0EC"/>
+        <fgColor rgb="00DBD0EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0ECEC"/>
+        <fgColor rgb="00E2ECD0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECE1D0"/>
+        <fgColor rgb="00ECD0DC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECD0D5"/>
+        <fgColor rgb="00D0ECE8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0ECD0"/>
+        <fgColor rgb="00ECD0D2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECD0E1"/>
+        <fgColor rgb="00D0DDEC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECD5D0"/>
+        <fgColor rgb="00D0EBEC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0ECE1"/>
+        <fgColor rgb="00ECD7D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0D0EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECE0D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4D0EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7ECD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECD0EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDECD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9ECD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECD0D7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0E6EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4ECD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0E1EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0ECD1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1D0EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0ECD5"/>
       </patternFill>
     </fill>
     <fill>
@@ -181,27 +252,52 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0ECD6"/>
+        <fgColor rgb="00D0ECDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0D5EC"/>
+        <fgColor rgb="00D0D8EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5ECD0"/>
+        <fgColor rgb="00ECD2D0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E1D0EC"/>
+        <fgColor rgb="00E9D0EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0E0EC"/>
+        <fgColor rgb="00ECDCD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECD0E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0ECDF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECD0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0D3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0ECE3"/>
       </patternFill>
     </fill>
     <fill>
@@ -274,7 +370,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -358,15 +454,73 @@
     <xf numFmtId="0" fontId="5" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="37" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="40" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -376,11 +530,11 @@
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="41" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -908,7 +1062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:R32"/>
+  <dimension ref="B2:S59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -929,12 +1083,13 @@
     <col width="30" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="2" ht="22" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>qa-lab-miyonchat-tree-v1.11</t>
+          <t>qa-lab-miyonchat-tree-v1.12</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
@@ -1027,6 +1182,11 @@
       <c r="R3" s="2" t="inlineStr">
         <is>
           <t>검증유형</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>상태</t>
         </is>
       </c>
     </row>
@@ -1056,6 +1216,7 @@
       <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="n"/>
       <c r="R4" s="4" t="n"/>
+      <c r="S4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="5" t="inlineStr">
@@ -1214,7 +1375,7 @@
       <c r="O10" s="18" t="n"/>
       <c r="P10" s="14" t="inlineStr">
         <is>
-          <t>상태는 디버그 콘솔 상태 스위처 「미로그인」으로 만들고 [저장]합니다. 공개 범위의 정본은 system-spec §1-1입니다</t>
+          <t>상태는 디버그 콘솔 상태 스위처 「미로그인」으로 만들고 [저장]합니다. 미로그인 열람 범위의 정본은 system-spec §1-1입니다</t>
         </is>
       </c>
       <c r="Q10" s="10" t="inlineStr">
@@ -1225,6 +1386,11 @@
       <c r="R10" s="10" t="inlineStr">
         <is>
           <t>결정적</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
         </is>
       </c>
     </row>
@@ -1290,6 +1456,11 @@
           <t>결정적</t>
         </is>
       </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="B12" s="10">
@@ -1347,6 +1518,11 @@
           <t>결정적</t>
         </is>
       </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="B13" s="10">
@@ -1416,6 +1592,11 @@
       <c r="R13" s="10" t="inlineStr">
         <is>
           <t>결정적</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>성인 인증</t>
         </is>
       </c>
     </row>
@@ -1481,6 +1662,11 @@
           <t>결정적</t>
         </is>
       </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>성인 인증</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="B15" s="10">
@@ -1538,6 +1724,11 @@
           <t>결정적</t>
         </is>
       </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>성인 인증</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="B16" s="10">
@@ -1596,7 +1787,7 @@
       <c r="O16" s="18" t="n"/>
       <c r="P16" s="14" t="inlineStr">
         <is>
-          <t>만료는 상태 스위처 「세션 만료」로 만듭니다. 만료 뒤 보호 동작이 막히는지는 TC-ENT-004가 잇습니다</t>
+          <t>만료는 상태 스위처 「세션 만료」로 만듭니다. 만료 뒤 로그인 필요 동작이 막히는지는 TC-ENT-004가 잇습니다</t>
         </is>
       </c>
       <c r="Q16" s="10" t="inlineStr">
@@ -1607,6 +1798,11 @@
       <c r="R16" s="10" t="inlineStr">
         <is>
           <t>결정적</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>세션 만료</t>
         </is>
       </c>
     </row>
@@ -1672,6 +1868,11 @@
           <t>결정적</t>
         </is>
       </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>세션 만료</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="B18" s="10">
@@ -1729,6 +1930,11 @@
           <t>결정적</t>
         </is>
       </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>세션 만료</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="B19" s="10">
@@ -1747,7 +1953,7 @@
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>세션 만료 상태 보호 동작 차단</t>
+          <t>세션 만료 상태 로그인 필요 동작 차단</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
@@ -1787,7 +1993,7 @@
       <c r="O19" s="18" t="n"/>
       <c r="P19" s="14" t="inlineStr">
         <is>
-          <t>TC-ENT-003의 만료 흐름을 이어받는 케이스라 웹 진입에 두었습니다. 만료 상태에서 막히는 보호 동작의 목록은 system-spec §1-1 세션 만료 행입니다</t>
+          <t>TC-ENT-003의 만료 흐름을 이어받는 케이스라 웹 진입에 두었습니다. 만료 상태에서 막히는 로그인 필요 동작의 목록은 system-spec §1-1 세션 만료 행입니다</t>
         </is>
       </c>
       <c r="Q19" s="10" t="inlineStr">
@@ -1798,6 +2004,11 @@
       <c r="R19" s="10" t="inlineStr">
         <is>
           <t>금칙</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>세션 만료</t>
         </is>
       </c>
     </row>
@@ -1818,7 +2029,7 @@
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>세션 만료 상태 보호 동작 차단</t>
+          <t>세션 만료 상태 로그인 필요 동작 차단</t>
         </is>
       </c>
       <c r="F20" s="19" t="n"/>
@@ -1857,6 +2068,11 @@
           <t>금칙</t>
         </is>
       </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>세션 만료</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="B21" s="10">
@@ -1875,7 +2091,7 @@
       </c>
       <c r="E21" s="24" t="inlineStr">
         <is>
-          <t>로그인 상태 보호 화면 직접 진입</t>
+          <t>로그인 상태 로그인 필요 화면 직접 진입</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
@@ -1928,6 +2144,11 @@
           <t>결정적</t>
         </is>
       </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>성인 인증</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="B22" s="10">
@@ -1946,7 +2167,7 @@
       </c>
       <c r="E22" s="25" t="inlineStr">
         <is>
-          <t>보호 화면 차단과 로그인 후 복귀</t>
+          <t>로그인 필요 화면 차단과 로그인 후 복귀</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -1999,6 +2220,11 @@
           <t>금칙</t>
         </is>
       </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="B23" s="10">
@@ -2017,7 +2243,7 @@
       </c>
       <c r="E23" s="25" t="inlineStr">
         <is>
-          <t>보호 화면 차단과 로그인 후 복귀</t>
+          <t>로그인 필요 화면 차단과 로그인 후 복귀</t>
         </is>
       </c>
       <c r="F23" s="19" t="n"/>
@@ -2056,6 +2282,11 @@
           <t>금칙</t>
         </is>
       </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="B24" s="10">
@@ -2074,7 +2305,7 @@
       </c>
       <c r="E24" s="25" t="inlineStr">
         <is>
-          <t>보호 화면 차단과 로그인 후 복귀</t>
+          <t>로그인 필요 화면 차단과 로그인 후 복귀</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr"/>
@@ -2119,6 +2350,11 @@
           <t>금칙</t>
         </is>
       </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="B25" s="10">
@@ -2177,7 +2413,7 @@
       <c r="O25" s="18" t="n"/>
       <c r="P25" s="14" t="inlineStr">
         <is>
-          <t>주소 끝에 `?screen=s5`를 붙입니다. 보호 화면마다 케이스를 나눈 것은 하나만 뚫렸을 때 어느 화면인지 TC ID로 읽히게 하기 위해서입니다</t>
+          <t>주소 끝에 `?screen=s5`를 붙입니다. 로그인 필요 화면마다 케이스를 나눈 것은 하나만 뚫렸을 때 어느 화면인지 TC ID로 읽히게 하기 위해서입니다</t>
         </is>
       </c>
       <c r="Q25" s="10" t="inlineStr">
@@ -2188,6 +2424,11 @@
       <c r="R25" s="10" t="inlineStr">
         <is>
           <t>금칙</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
         </is>
       </c>
     </row>
@@ -2247,6 +2488,11 @@
           <t>금칙</t>
         </is>
       </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="B27" s="10">
@@ -2316,6 +2562,11 @@
       <c r="R27" s="10" t="inlineStr">
         <is>
           <t>금칙</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
         </is>
       </c>
     </row>
@@ -2375,6 +2626,11 @@
           <t>금칙</t>
         </is>
       </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="B29" s="10">
@@ -2433,7 +2689,7 @@
       <c r="O29" s="18" t="n"/>
       <c r="P29" s="14" t="inlineStr">
         <is>
-          <t>주소 끝에 `?screen=s8`을 붙입니다. 내 작품 탭은 스텁이지만 보호 화면이라 차단은 걸립니다</t>
+          <t>주소 끝에 `?screen=s8`을 붙입니다. 내 작품 탭은 스텁이지만 로그인 필요 화면이라 차단은 걸립니다</t>
         </is>
       </c>
       <c r="Q29" s="10" t="inlineStr">
@@ -2444,6 +2700,11 @@
       <c r="R29" s="10" t="inlineStr">
         <is>
           <t>금칙</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
         </is>
       </c>
     </row>
@@ -2503,6 +2764,11 @@
           <t>금칙</t>
         </is>
       </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="B31" s="10">
@@ -2561,7 +2827,7 @@
       <c r="O31" s="18" t="n"/>
       <c r="P31" s="14" t="inlineStr">
         <is>
-          <t>주소 끝에 `?screen=s2`를 붙입니다. 차단이 공개 화면까지 과하게 걸리지 않는지를 보는 자리라 위 차단 케이스들과 함께 읽습니다</t>
+          <t>주소 끝에 `?screen=s2`를 붙입니다. 차단이 미로그인 열람 화면까지 과하게 걸리지 않는지를 보는 자리라 위 차단 케이스들과 함께 읽습니다</t>
         </is>
       </c>
       <c r="Q31" s="10" t="inlineStr">
@@ -2572,6 +2838,11 @@
       <c r="R31" s="10" t="inlineStr">
         <is>
           <t>결정적</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2903,7 @@
       <c r="O32" s="18" t="n"/>
       <c r="P32" s="14" t="inlineStr">
         <is>
-          <t>주소 끝에 `?screen=s7`을 붙입니다. 커뮤니티 탭은 전시용 정적이지만 공개 화면이라 통과합니다</t>
+          <t>주소 끝에 `?screen=s7`을 붙입니다. 커뮤니티 탭은 전시용 정적이지만 미로그인 열람 화면이라 통과합니다</t>
         </is>
       </c>
       <c r="Q32" s="10" t="inlineStr">
@@ -2645,69 +2916,2003 @@
           <t>결정적</t>
         </is>
       </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="B33" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C33" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D33" s="32" t="inlineStr">
+        <is>
+          <t>상단 바</t>
+        </is>
+      </c>
+      <c r="E33" s="33" t="inlineStr">
+        <is>
+          <t>로고로 홈 복귀</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>계정 A로 로그인해 캐릭터 페이지를 연 상태</t>
+        </is>
+      </c>
+      <c r="G33" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="14" t="inlineStr">
+        <is>
+          <t>상단 바 로고 선택한다</t>
+        </is>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
+        <is>
+          <t>홈 화면 노출된다</t>
+        </is>
+      </c>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L33" s="16">
+        <f>IF(COUNTIF(M33:M33,"Fail")&gt;0,"Fail",IF(COUNTIF(M33:M33,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M33:M33,"NI")&gt;0,"NI",IF(COUNTIF(M33:M33,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M33" s="17" t="n"/>
+      <c r="N33" s="18" t="n"/>
+      <c r="O33" s="18" t="n"/>
+      <c r="P33" s="14" t="inlineStr">
+        <is>
+          <t>홈이 아닌 화면에서 눌렀을 때 복귀하는지를 봅니다. 홈에서 다시 누를 때의 동작은 TC-DSC-002가 맡습니다</t>
+        </is>
+      </c>
+      <c r="Q33" s="10" t="inlineStr">
+        <is>
+          <t>TC-DSC-001</t>
+        </is>
+      </c>
+      <c r="R33" s="10" t="inlineStr">
+        <is>
+          <t>결정적</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>성인 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="B34" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C34" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D34" s="32" t="inlineStr">
+        <is>
+          <t>상단 바</t>
+        </is>
+      </c>
+      <c r="E34" s="34" t="inlineStr">
+        <is>
+          <t>홈에서 로고 재선택</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>계정 A로 로그인해 홈 화면을 아래로 스크롤한 상태</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>상단 바 로고 선택한다</t>
+        </is>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
+        <is>
+          <t>홈 화면 유지된다</t>
+        </is>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K34" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L34" s="16">
+        <f>IF(COUNTIF(M34:M34,"Fail")&gt;0,"Fail",IF(COUNTIF(M34:M34,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M34:M34,"NI")&gt;0,"NI",IF(COUNTIF(M34:M34,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M34" s="17" t="n"/>
+      <c r="N34" s="18" t="n"/>
+      <c r="O34" s="18" t="n"/>
+      <c r="P34" s="14" t="inlineStr">
+        <is>
+          <t>같은 버튼이 화면에 따라 다르게 동작하는 자리라 TC-DSC-001과 나눴습니다</t>
+        </is>
+      </c>
+      <c r="Q34" s="10" t="inlineStr">
+        <is>
+          <t>TC-DSC-002</t>
+        </is>
+      </c>
+      <c r="R34" s="10" t="inlineStr">
+        <is>
+          <t>결정적</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>성인 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="B35" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C35" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D35" s="32" t="inlineStr">
+        <is>
+          <t>상단 바</t>
+        </is>
+      </c>
+      <c r="E35" s="34" t="inlineStr">
+        <is>
+          <t>홈에서 로고 재선택</t>
+        </is>
+      </c>
+      <c r="F35" s="19" t="n"/>
+      <c r="G35" s="19" t="n"/>
+      <c r="H35" s="19" t="n"/>
+      <c r="I35" s="14" t="inlineStr">
+        <is>
+          <t>목록이 최상단으로 스크롤된다</t>
+        </is>
+      </c>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K35" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L35" s="16">
+        <f>IF(COUNTIF(M35:M35,"Fail")&gt;0,"Fail",IF(COUNTIF(M35:M35,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M35:M35,"NI")&gt;0,"NI",IF(COUNTIF(M35:M35,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M35" s="17" t="n"/>
+      <c r="N35" s="18" t="n"/>
+      <c r="O35" s="18" t="n"/>
+      <c r="P35" s="19" t="n"/>
+      <c r="Q35" s="10" t="inlineStr">
+        <is>
+          <t>TC-DSC-002</t>
+        </is>
+      </c>
+      <c r="R35" s="10" t="inlineStr">
+        <is>
+          <t>결정적</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>성인 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="B36" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C36" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D36" s="32" t="inlineStr">
+        <is>
+          <t>상단 바</t>
+        </is>
+      </c>
+      <c r="E36" s="35" t="inlineStr">
+        <is>
+          <t>페이지 제목 부분일치 검색</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>계정 A로 로그인한 상태</t>
+        </is>
+      </c>
+      <c r="G36" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>상단 바 검색에 페이지 제목의 일부를 입력하고 실행한다</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
+        <is>
+          <t>홈 화면에 검색 결과 노출된다</t>
+        </is>
+      </c>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K36" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L36" s="16">
+        <f>IF(COUNTIF(M36:M36,"Fail")&gt;0,"Fail",IF(COUNTIF(M36:M36,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M36:M36,"NI")&gt;0,"NI",IF(COUNTIF(M36:M36,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M36" s="17" t="n"/>
+      <c r="N36" s="18" t="n"/>
+      <c r="O36" s="18" t="n"/>
+      <c r="P36" s="14" t="inlineStr">
+        <is>
+          <t>기본 데이터에서는 「우산」으로 「비 오는 날의 우산」이 걸립니다. 검색 결과가 별도 화면이 아니라 홈 화면에 표시되는 점을 함께 봅니다</t>
+        </is>
+      </c>
+      <c r="Q36" s="10" t="inlineStr">
+        <is>
+          <t>TC-DSC-003</t>
+        </is>
+      </c>
+      <c r="R36" s="10" t="inlineStr">
+        <is>
+          <t>결정적</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>성인 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="B37" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C37" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D37" s="32" t="inlineStr">
+        <is>
+          <t>상단 바</t>
+        </is>
+      </c>
+      <c r="E37" s="35" t="inlineStr">
+        <is>
+          <t>페이지 제목 부분일치 검색</t>
+        </is>
+      </c>
+      <c r="F37" s="19" t="n"/>
+      <c r="G37" s="19" t="n"/>
+      <c r="H37" s="19" t="n"/>
+      <c r="I37" s="14" t="inlineStr">
+        <is>
+          <t>입력한 조각을 제목에 포함한 작품이 결과에 노출된다</t>
+        </is>
+      </c>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L37" s="16">
+        <f>IF(COUNTIF(M37:M37,"Fail")&gt;0,"Fail",IF(COUNTIF(M37:M37,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M37:M37,"NI")&gt;0,"NI",IF(COUNTIF(M37:M37,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M37" s="17" t="n"/>
+      <c r="N37" s="18" t="n"/>
+      <c r="O37" s="18" t="n"/>
+      <c r="P37" s="19" t="n"/>
+      <c r="Q37" s="10" t="inlineStr">
+        <is>
+          <t>TC-DSC-003</t>
+        </is>
+      </c>
+      <c r="R37" s="10" t="inlineStr">
+        <is>
+          <t>결정적</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>성인 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="B38" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C38" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D38" s="32" t="inlineStr">
+        <is>
+          <t>상단 바</t>
+        </is>
+      </c>
+      <c r="E38" s="36" t="inlineStr">
+        <is>
+          <t>페이지 카테고리 부분일치 검색</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>계정 A로 로그인한 상태</t>
+        </is>
+      </c>
+      <c r="G38" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>상단 바 검색에 페이지 카테고리명을 입력하고 실행한다</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
+        <is>
+          <t>그 카테고리를 가진 작품이 결과에 노출된다</t>
+        </is>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L38" s="16">
+        <f>IF(COUNTIF(M38:M38,"Fail")&gt;0,"Fail",IF(COUNTIF(M38:M38,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M38:M38,"NI")&gt;0,"NI",IF(COUNTIF(M38:M38,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M38" s="17" t="n"/>
+      <c r="N38" s="18" t="n"/>
+      <c r="O38" s="18" t="n"/>
+      <c r="P38" s="14" t="inlineStr">
+        <is>
+          <t>기본 데이터에서는 「로맨스」로 세 작품이 걸립니다. 제목과 카테고리 두 축이 모두 검색 대상이라 TC-DSC-003과 나눴습니다</t>
+        </is>
+      </c>
+      <c r="Q38" s="10" t="inlineStr">
+        <is>
+          <t>TC-DSC-004</t>
+        </is>
+      </c>
+      <c r="R38" s="10" t="inlineStr">
+        <is>
+          <t>결정적</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>성인 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="B39" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C39" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D39" s="32" t="inlineStr">
+        <is>
+          <t>상단 바</t>
+        </is>
+      </c>
+      <c r="E39" s="37" t="inlineStr">
+        <is>
+          <t>검색 결과 0건 안내</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>계정 A로 로그인한 상태</t>
+        </is>
+      </c>
+      <c r="G39" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>상단 바 검색에 어느 제목·카테고리와도 겹치지 않는 문자열을 입력하고 실행한다</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
+        <is>
+          <t>결과 0건 안내 문구 노출된다</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K39" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L39" s="16">
+        <f>IF(COUNTIF(M39:M39,"Fail")&gt;0,"Fail",IF(COUNTIF(M39:M39,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M39:M39,"NI")&gt;0,"NI",IF(COUNTIF(M39:M39,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M39" s="17" t="n"/>
+      <c r="N39" s="18" t="n"/>
+      <c r="O39" s="18" t="n"/>
+      <c r="P39" s="14" t="inlineStr">
+        <is>
+          <t>빈 결과에서 목록만 비고 안내가 없으면 검색이 안 걸린 것인지 결과가 없는 것인지 구분되지 않습니다</t>
+        </is>
+      </c>
+      <c r="Q39" s="10" t="inlineStr">
+        <is>
+          <t>TC-DSC-005</t>
+        </is>
+      </c>
+      <c r="R39" s="10" t="inlineStr">
+        <is>
+          <t>결정적</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>성인 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="B40" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C40" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D40" s="32" t="inlineStr">
+        <is>
+          <t>상단 바</t>
+        </is>
+      </c>
+      <c r="E40" s="38" t="inlineStr">
+        <is>
+          <t>알림 목록이 데이터 시트를 반영</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>계정 A로 로그인한 상태</t>
+        </is>
+      </c>
+      <c r="G40" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>상단 바 알림 선택한다</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
+        <is>
+          <t>알림 목록 노출된다</t>
+        </is>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K40" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L40" s="16">
+        <f>IF(COUNTIF(M40:M40,"Fail")&gt;0,"Fail",IF(COUNTIF(M40:M40,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M40:M40,"NI")&gt;0,"NI",IF(COUNTIF(M40:M40,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M40" s="17" t="n"/>
+      <c r="N40" s="18" t="n"/>
+      <c r="O40" s="18" t="n"/>
+      <c r="P40" s="14" t="inlineStr">
+        <is>
+          <t>발생 로직은 없고 표시 반영만 검증합니다. 항목은 디버그 콘솔에서 늘리고 비울 수 있습니다</t>
+        </is>
+      </c>
+      <c r="Q40" s="10" t="inlineStr">
+        <is>
+          <t>TC-DSC-006</t>
+        </is>
+      </c>
+      <c r="R40" s="10" t="inlineStr">
+        <is>
+          <t>결정적</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>성인 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="B41" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C41" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D41" s="32" t="inlineStr">
+        <is>
+          <t>상단 바</t>
+        </is>
+      </c>
+      <c r="E41" s="38" t="inlineStr">
+        <is>
+          <t>알림 목록이 데이터 시트를 반영</t>
+        </is>
+      </c>
+      <c r="F41" s="19" t="n"/>
+      <c r="G41" s="19" t="n"/>
+      <c r="H41" s="19" t="n"/>
+      <c r="I41" s="14" t="inlineStr">
+        <is>
+          <t>데이터 시트의 알림 항목이 목록에 노출된다</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K41" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L41" s="16">
+        <f>IF(COUNTIF(M41:M41,"Fail")&gt;0,"Fail",IF(COUNTIF(M41:M41,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M41:M41,"NI")&gt;0,"NI",IF(COUNTIF(M41:M41,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M41" s="17" t="n"/>
+      <c r="N41" s="18" t="n"/>
+      <c r="O41" s="18" t="n"/>
+      <c r="P41" s="19" t="n"/>
+      <c r="Q41" s="10" t="inlineStr">
+        <is>
+          <t>TC-DSC-006</t>
+        </is>
+      </c>
+      <c r="R41" s="10" t="inlineStr">
+        <is>
+          <t>결정적</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>성인 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="B42" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C42" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D42" s="32" t="inlineStr">
+        <is>
+          <t>상단 바</t>
+        </is>
+      </c>
+      <c r="E42" s="39" t="inlineStr">
+        <is>
+          <t>알림 빈 상태 안내</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>계정 A로 로그인하고 디버그 콘솔에서 알림을 모두 비운 상태</t>
+        </is>
+      </c>
+      <c r="G42" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="14" t="inlineStr">
+        <is>
+          <t>상단 바 알림 선택한다</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
+        <is>
+          <t>빈 상태 안내 노출된다</t>
+        </is>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K42" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L42" s="16">
+        <f>IF(COUNTIF(M42:M42,"Fail")&gt;0,"Fail",IF(COUNTIF(M42:M42,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M42:M42,"NI")&gt;0,"NI",IF(COUNTIF(M42:M42,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M42" s="17" t="n"/>
+      <c r="N42" s="18" t="n"/>
+      <c r="O42" s="18" t="n"/>
+      <c r="P42" s="14" t="inlineStr">
+        <is>
+          <t>디버그 콘솔의 [알림 비우기] 뒤 [저장]으로 조건을 만듭니다</t>
+        </is>
+      </c>
+      <c r="Q42" s="10" t="inlineStr">
+        <is>
+          <t>TC-DSC-007</t>
+        </is>
+      </c>
+      <c r="R42" s="10" t="inlineStr">
+        <is>
+          <t>결정적</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>성인 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="B43" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C43" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D43" s="32" t="inlineStr">
+        <is>
+          <t>상단 바</t>
+        </is>
+      </c>
+      <c r="E43" s="40" t="inlineStr">
+        <is>
+          <t>미로그인 알림 열람 차단</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>미로그인 상태</t>
+        </is>
+      </c>
+      <c r="G43" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>상단 바 알림 선택한다</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
+        <is>
+          <t>알림 목록 노출되지 않는다</t>
+        </is>
+      </c>
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K43" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L43" s="16">
+        <f>IF(COUNTIF(M43:M43,"Fail")&gt;0,"Fail",IF(COUNTIF(M43:M43,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M43:M43,"NI")&gt;0,"NI",IF(COUNTIF(M43:M43,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M43" s="17" t="n"/>
+      <c r="N43" s="18" t="n"/>
+      <c r="O43" s="18" t="n"/>
+      <c r="P43" s="14" t="inlineStr">
+        <is>
+          <t>알림 열람은 명세 §1-1의 로그인 필요 동작입니다. 상단 바에는 잔액·간편 프로필 대신 로그인 버튼이 놓입니다</t>
+        </is>
+      </c>
+      <c r="Q43" s="10" t="inlineStr">
+        <is>
+          <t>TC-GAT-007</t>
+        </is>
+      </c>
+      <c r="R43" s="10" t="inlineStr">
+        <is>
+          <t>금칙</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="B44" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C44" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D44" s="32" t="inlineStr">
+        <is>
+          <t>상단 바</t>
+        </is>
+      </c>
+      <c r="E44" s="40" t="inlineStr">
+        <is>
+          <t>미로그인 알림 열람 차단</t>
+        </is>
+      </c>
+      <c r="F44" s="19" t="n"/>
+      <c r="G44" s="19" t="n"/>
+      <c r="H44" s="19" t="n"/>
+      <c r="I44" s="14" t="inlineStr">
+        <is>
+          <t>로그인 모달 노출된다</t>
+        </is>
+      </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K44" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L44" s="16">
+        <f>IF(COUNTIF(M44:M44,"Fail")&gt;0,"Fail",IF(COUNTIF(M44:M44,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M44:M44,"NI")&gt;0,"NI",IF(COUNTIF(M44:M44,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M44" s="17" t="n"/>
+      <c r="N44" s="18" t="n"/>
+      <c r="O44" s="18" t="n"/>
+      <c r="P44" s="19" t="n"/>
+      <c r="Q44" s="10" t="inlineStr">
+        <is>
+          <t>TC-GAT-007</t>
+        </is>
+      </c>
+      <c r="R44" s="10" t="inlineStr">
+        <is>
+          <t>금칙</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="B45" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C45" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D45" s="41" t="inlineStr">
+        <is>
+          <t>하단 내비</t>
+        </is>
+      </c>
+      <c r="E45" s="42" t="inlineStr">
+        <is>
+          <t>홈 탭 재선택</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>계정 A로 로그인해 홈 화면에서 랭킹 칩을 고르고 아래로 스크롤한 상태</t>
+        </is>
+      </c>
+      <c r="G45" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>하단 내비 홈 탭 선택한다</t>
+        </is>
+      </c>
+      <c r="I45" s="14" t="inlineStr">
+        <is>
+          <t>활성 필터 칩 유지된다</t>
+        </is>
+      </c>
+      <c r="J45" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K45" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L45" s="16">
+        <f>IF(COUNTIF(M45:M45,"Fail")&gt;0,"Fail",IF(COUNTIF(M45:M45,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M45:M45,"NI")&gt;0,"NI",IF(COUNTIF(M45:M45,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M45" s="17" t="n"/>
+      <c r="N45" s="18" t="n"/>
+      <c r="O45" s="18" t="n"/>
+      <c r="P45" s="14" t="inlineStr">
+        <is>
+          <t>칩이 기본값으로 돌아가면 「돌아왔을 때 그대로인가」를 확인할 수 없습니다</t>
+        </is>
+      </c>
+      <c r="Q45" s="10" t="inlineStr">
+        <is>
+          <t>TC-DSC-008</t>
+        </is>
+      </c>
+      <c r="R45" s="10" t="inlineStr">
+        <is>
+          <t>결정적</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>성인 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="B46" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C46" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D46" s="41" t="inlineStr">
+        <is>
+          <t>하단 내비</t>
+        </is>
+      </c>
+      <c r="E46" s="42" t="inlineStr">
+        <is>
+          <t>홈 탭 재선택</t>
+        </is>
+      </c>
+      <c r="F46" s="19" t="n"/>
+      <c r="G46" s="19" t="n"/>
+      <c r="H46" s="19" t="n"/>
+      <c r="I46" s="14" t="inlineStr">
+        <is>
+          <t>목록이 최상단으로 스크롤된다</t>
+        </is>
+      </c>
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K46" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L46" s="16">
+        <f>IF(COUNTIF(M46:M46,"Fail")&gt;0,"Fail",IF(COUNTIF(M46:M46,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M46:M46,"NI")&gt;0,"NI",IF(COUNTIF(M46:M46,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M46" s="17" t="n"/>
+      <c r="N46" s="18" t="n"/>
+      <c r="O46" s="18" t="n"/>
+      <c r="P46" s="19" t="n"/>
+      <c r="Q46" s="10" t="inlineStr">
+        <is>
+          <t>TC-DSC-008</t>
+        </is>
+      </c>
+      <c r="R46" s="10" t="inlineStr">
+        <is>
+          <t>결정적</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>성인 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="B47" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C47" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D47" s="41" t="inlineStr">
+        <is>
+          <t>하단 내비</t>
+        </is>
+      </c>
+      <c r="E47" s="43" t="inlineStr">
+        <is>
+          <t>미로그인 채팅 탭 차단</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="inlineStr">
+        <is>
+          <t>미로그인 상태</t>
+        </is>
+      </c>
+      <c r="G47" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>하단 내비 채팅 탭 선택한다</t>
+        </is>
+      </c>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>채팅 탭 열리지 않는다</t>
+        </is>
+      </c>
+      <c r="J47" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K47" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L47" s="16">
+        <f>IF(COUNTIF(M47:M47,"Fail")&gt;0,"Fail",IF(COUNTIF(M47:M47,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M47:M47,"NI")&gt;0,"NI",IF(COUNTIF(M47:M47,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M47" s="17" t="n"/>
+      <c r="N47" s="18" t="n"/>
+      <c r="O47" s="18" t="n"/>
+      <c r="P47" s="14" t="inlineStr">
+        <is>
+          <t>셸 안에서 막히는 경우라 로그인 화면이 아니라 모달이 뜨고 뒤 화면은 그대로 남습니다(system-spec §1-1)</t>
+        </is>
+      </c>
+      <c r="Q47" s="10" t="inlineStr">
+        <is>
+          <t>TC-GAT-008</t>
+        </is>
+      </c>
+      <c r="R47" s="10" t="inlineStr">
+        <is>
+          <t>금칙</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="B48" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C48" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D48" s="41" t="inlineStr">
+        <is>
+          <t>하단 내비</t>
+        </is>
+      </c>
+      <c r="E48" s="43" t="inlineStr">
+        <is>
+          <t>미로그인 채팅 탭 차단</t>
+        </is>
+      </c>
+      <c r="F48" s="19" t="n"/>
+      <c r="G48" s="19" t="n"/>
+      <c r="H48" s="19" t="n"/>
+      <c r="I48" s="14" t="inlineStr">
+        <is>
+          <t>로그인 모달 노출된다</t>
+        </is>
+      </c>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K48" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L48" s="16">
+        <f>IF(COUNTIF(M48:M48,"Fail")&gt;0,"Fail",IF(COUNTIF(M48:M48,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M48:M48,"NI")&gt;0,"NI",IF(COUNTIF(M48:M48,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M48" s="17" t="n"/>
+      <c r="N48" s="18" t="n"/>
+      <c r="O48" s="18" t="n"/>
+      <c r="P48" s="19" t="n"/>
+      <c r="Q48" s="10" t="inlineStr">
+        <is>
+          <t>TC-GAT-008</t>
+        </is>
+      </c>
+      <c r="R48" s="10" t="inlineStr">
+        <is>
+          <t>금칙</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="B49" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C49" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D49" s="41" t="inlineStr">
+        <is>
+          <t>하단 내비</t>
+        </is>
+      </c>
+      <c r="E49" s="44" t="inlineStr">
+        <is>
+          <t>미로그인 MY 탭 차단</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>미로그인 상태</t>
+        </is>
+      </c>
+      <c r="G49" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>하단 내비 MY 탭 선택한다</t>
+        </is>
+      </c>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>MY 탭 열리지 않는다</t>
+        </is>
+      </c>
+      <c r="J49" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K49" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L49" s="16">
+        <f>IF(COUNTIF(M49:M49,"Fail")&gt;0,"Fail",IF(COUNTIF(M49:M49,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M49:M49,"NI")&gt;0,"NI",IF(COUNTIF(M49:M49,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M49" s="17" t="n"/>
+      <c r="N49" s="18" t="n"/>
+      <c r="O49" s="18" t="n"/>
+      <c r="P49" s="14" t="inlineStr">
+        <is>
+          <t>탭마다 케이스를 나눈 것은 하나만 뚫렸을 때 어느 탭인지 TC ID로 읽히게 하기 위해서입니다</t>
+        </is>
+      </c>
+      <c r="Q49" s="10" t="inlineStr">
+        <is>
+          <t>TC-GAT-009</t>
+        </is>
+      </c>
+      <c r="R49" s="10" t="inlineStr">
+        <is>
+          <t>금칙</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="B50" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C50" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D50" s="41" t="inlineStr">
+        <is>
+          <t>하단 내비</t>
+        </is>
+      </c>
+      <c r="E50" s="44" t="inlineStr">
+        <is>
+          <t>미로그인 MY 탭 차단</t>
+        </is>
+      </c>
+      <c r="F50" s="19" t="n"/>
+      <c r="G50" s="19" t="n"/>
+      <c r="H50" s="19" t="n"/>
+      <c r="I50" s="14" t="inlineStr">
+        <is>
+          <t>로그인 모달 노출된다</t>
+        </is>
+      </c>
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K50" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L50" s="16">
+        <f>IF(COUNTIF(M50:M50,"Fail")&gt;0,"Fail",IF(COUNTIF(M50:M50,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M50:M50,"NI")&gt;0,"NI",IF(COUNTIF(M50:M50,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M50" s="17" t="n"/>
+      <c r="N50" s="18" t="n"/>
+      <c r="O50" s="18" t="n"/>
+      <c r="P50" s="19" t="n"/>
+      <c r="Q50" s="10" t="inlineStr">
+        <is>
+          <t>TC-GAT-009</t>
+        </is>
+      </c>
+      <c r="R50" s="10" t="inlineStr">
+        <is>
+          <t>금칙</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="B51" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C51" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D51" s="41" t="inlineStr">
+        <is>
+          <t>하단 내비</t>
+        </is>
+      </c>
+      <c r="E51" s="45" t="inlineStr">
+        <is>
+          <t>미로그인 내 작품 탭 차단</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>미로그인 상태</t>
+        </is>
+      </c>
+      <c r="G51" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>하단 내비 내 작품 탭 선택한다</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
+        <is>
+          <t>내 작품 탭 열리지 않는다</t>
+        </is>
+      </c>
+      <c r="J51" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K51" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L51" s="16">
+        <f>IF(COUNTIF(M51:M51,"Fail")&gt;0,"Fail",IF(COUNTIF(M51:M51,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M51:M51,"NI")&gt;0,"NI",IF(COUNTIF(M51:M51,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M51" s="17" t="n"/>
+      <c r="N51" s="18" t="n"/>
+      <c r="O51" s="18" t="n"/>
+      <c r="P51" s="14" t="inlineStr">
+        <is>
+          <t>내 작품 탭은 스텁이지만 로그인 필요 화면이라 차단은 걸립니다</t>
+        </is>
+      </c>
+      <c r="Q51" s="10" t="inlineStr">
+        <is>
+          <t>TC-GAT-010</t>
+        </is>
+      </c>
+      <c r="R51" s="10" t="inlineStr">
+        <is>
+          <t>금칙</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="B52" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C52" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D52" s="41" t="inlineStr">
+        <is>
+          <t>하단 내비</t>
+        </is>
+      </c>
+      <c r="E52" s="45" t="inlineStr">
+        <is>
+          <t>미로그인 내 작품 탭 차단</t>
+        </is>
+      </c>
+      <c r="F52" s="19" t="n"/>
+      <c r="G52" s="19" t="n"/>
+      <c r="H52" s="19" t="n"/>
+      <c r="I52" s="14" t="inlineStr">
+        <is>
+          <t>로그인 모달 노출된다</t>
+        </is>
+      </c>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K52" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L52" s="16">
+        <f>IF(COUNTIF(M52:M52,"Fail")&gt;0,"Fail",IF(COUNTIF(M52:M52,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M52:M52,"NI")&gt;0,"NI",IF(COUNTIF(M52:M52,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M52" s="17" t="n"/>
+      <c r="N52" s="18" t="n"/>
+      <c r="O52" s="18" t="n"/>
+      <c r="P52" s="19" t="n"/>
+      <c r="Q52" s="10" t="inlineStr">
+        <is>
+          <t>TC-GAT-010</t>
+        </is>
+      </c>
+      <c r="R52" s="10" t="inlineStr">
+        <is>
+          <t>금칙</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="B53" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C53" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D53" s="41" t="inlineStr">
+        <is>
+          <t>하단 내비</t>
+        </is>
+      </c>
+      <c r="E53" s="46" t="inlineStr">
+        <is>
+          <t>미로그인 커뮤니티 탭 통과</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="inlineStr">
+        <is>
+          <t>미로그인 상태</t>
+        </is>
+      </c>
+      <c r="G53" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="14" t="inlineStr">
+        <is>
+          <t>하단 내비 커뮤니티 탭 선택한다</t>
+        </is>
+      </c>
+      <c r="I53" s="14" t="inlineStr">
+        <is>
+          <t>커뮤니티 탭 노출된다</t>
+        </is>
+      </c>
+      <c r="J53" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K53" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L53" s="16">
+        <f>IF(COUNTIF(M53:M53,"Fail")&gt;0,"Fail",IF(COUNTIF(M53:M53,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M53:M53,"NI")&gt;0,"NI",IF(COUNTIF(M53:M53,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M53" s="17" t="n"/>
+      <c r="N53" s="18" t="n"/>
+      <c r="O53" s="18" t="n"/>
+      <c r="P53" s="14" t="inlineStr">
+        <is>
+          <t>차단이 공개 탭까지 과하게 걸리지 않는지를 보는 자리라 위 차단 케이스들과 함께 읽습니다</t>
+        </is>
+      </c>
+      <c r="Q53" s="10" t="inlineStr">
+        <is>
+          <t>TC-DSC-009</t>
+        </is>
+      </c>
+      <c r="R53" s="10" t="inlineStr">
+        <is>
+          <t>결정적</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="B54" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C54" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D54" s="41" t="inlineStr">
+        <is>
+          <t>하단 내비</t>
+        </is>
+      </c>
+      <c r="E54" s="46" t="inlineStr">
+        <is>
+          <t>미로그인 커뮤니티 탭 통과</t>
+        </is>
+      </c>
+      <c r="F54" s="19" t="n"/>
+      <c r="G54" s="19" t="n"/>
+      <c r="H54" s="19" t="n"/>
+      <c r="I54" s="14" t="inlineStr">
+        <is>
+          <t>로그인 모달 노출되지 않는다</t>
+        </is>
+      </c>
+      <c r="J54" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K54" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L54" s="16">
+        <f>IF(COUNTIF(M54:M54,"Fail")&gt;0,"Fail",IF(COUNTIF(M54:M54,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M54:M54,"NI")&gt;0,"NI",IF(COUNTIF(M54:M54,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M54" s="17" t="n"/>
+      <c r="N54" s="18" t="n"/>
+      <c r="O54" s="18" t="n"/>
+      <c r="P54" s="19" t="n"/>
+      <c r="Q54" s="10" t="inlineStr">
+        <is>
+          <t>TC-DSC-009</t>
+        </is>
+      </c>
+      <c r="R54" s="10" t="inlineStr">
+        <is>
+          <t>결정적</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="B55" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C55" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D55" s="47" t="inlineStr">
+        <is>
+          <t>로그인 모달</t>
+        </is>
+      </c>
+      <c r="E55" s="48" t="inlineStr">
+        <is>
+          <t>막힌 동작 이어받기</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>미로그인 상태에서 채팅 탭이 막혀 로그인 모달이 뜬 상태</t>
+        </is>
+      </c>
+      <c r="G55" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>로그인 모달에서 계정 A 선택한다</t>
+        </is>
+      </c>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>로그인 모달 닫힌다</t>
+        </is>
+      </c>
+      <c r="J55" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K55" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L55" s="16">
+        <f>IF(COUNTIF(M55:M55,"Fail")&gt;0,"Fail",IF(COUNTIF(M55:M55,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M55:M55,"NI")&gt;0,"NI",IF(COUNTIF(M55:M55,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M55" s="17" t="n"/>
+      <c r="N55" s="18" t="n"/>
+      <c r="O55" s="18" t="n"/>
+      <c r="P55" s="14" t="inlineStr">
+        <is>
+          <t>막을 때는 아무것도 수행하지 않고 풀리면 그때 수행한다는 규칙의 짝입니다(system-spec §1-1)</t>
+        </is>
+      </c>
+      <c r="Q55" s="10" t="inlineStr">
+        <is>
+          <t>TC-ENT-006</t>
+        </is>
+      </c>
+      <c r="R55" s="10" t="inlineStr">
+        <is>
+          <t>결정적</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>미로그인, 성인 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="B56" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C56" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D56" s="47" t="inlineStr">
+        <is>
+          <t>로그인 모달</t>
+        </is>
+      </c>
+      <c r="E56" s="48" t="inlineStr">
+        <is>
+          <t>막힌 동작 이어받기</t>
+        </is>
+      </c>
+      <c r="F56" s="19" t="n"/>
+      <c r="G56" s="19" t="n"/>
+      <c r="H56" s="19" t="n"/>
+      <c r="I56" s="14" t="inlineStr">
+        <is>
+          <t>막혔던 채팅 탭 열린다</t>
+        </is>
+      </c>
+      <c r="J56" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K56" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L56" s="16">
+        <f>IF(COUNTIF(M56:M56,"Fail")&gt;0,"Fail",IF(COUNTIF(M56:M56,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M56:M56,"NI")&gt;0,"NI",IF(COUNTIF(M56:M56,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M56" s="17" t="n"/>
+      <c r="N56" s="18" t="n"/>
+      <c r="O56" s="18" t="n"/>
+      <c r="P56" s="19" t="n"/>
+      <c r="Q56" s="10" t="inlineStr">
+        <is>
+          <t>TC-ENT-006</t>
+        </is>
+      </c>
+      <c r="R56" s="10" t="inlineStr">
+        <is>
+          <t>결정적</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>미로그인, 성인 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="B57" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C57" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D57" s="47" t="inlineStr">
+        <is>
+          <t>로그인 모달</t>
+        </is>
+      </c>
+      <c r="E57" s="49" t="inlineStr">
+        <is>
+          <t>로그인 모달 닫기</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
+        <is>
+          <t>미로그인 상태에서 채팅 탭이 막혀 로그인 모달이 뜬 상태</t>
+        </is>
+      </c>
+      <c r="G57" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
+          <t>로그인 모달 닫기 선택한다</t>
+        </is>
+      </c>
+      <c r="I57" s="14" t="inlineStr">
+        <is>
+          <t>로그인 모달 닫힌다</t>
+        </is>
+      </c>
+      <c r="J57" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K57" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L57" s="16">
+        <f>IF(COUNTIF(M57:M57,"Fail")&gt;0,"Fail",IF(COUNTIF(M57:M57,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M57:M57,"NI")&gt;0,"NI",IF(COUNTIF(M57:M57,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M57" s="17" t="n"/>
+      <c r="N57" s="18" t="n"/>
+      <c r="O57" s="18" t="n"/>
+      <c r="P57" s="14" t="inlineStr">
+        <is>
+          <t>모달은 뒤 화면을 살려 두므로 닫으면 제자리입니다. 막힌 동작이 몰래 수행되지 않았는지도 함께 봅니다</t>
+        </is>
+      </c>
+      <c r="Q57" s="10" t="inlineStr">
+        <is>
+          <t>TC-ENT-007</t>
+        </is>
+      </c>
+      <c r="R57" s="10" t="inlineStr">
+        <is>
+          <t>결정적</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="B58" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C58" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D58" s="47" t="inlineStr">
+        <is>
+          <t>로그인 모달</t>
+        </is>
+      </c>
+      <c r="E58" s="49" t="inlineStr">
+        <is>
+          <t>로그인 모달 닫기</t>
+        </is>
+      </c>
+      <c r="F58" s="50" t="n"/>
+      <c r="G58" s="50" t="n"/>
+      <c r="H58" s="50" t="n"/>
+      <c r="I58" s="14" t="inlineStr">
+        <is>
+          <t>모달이 뜨기 전 보던 화면 유지된다</t>
+        </is>
+      </c>
+      <c r="J58" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K58" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L58" s="16">
+        <f>IF(COUNTIF(M58:M58,"Fail")&gt;0,"Fail",IF(COUNTIF(M58:M58,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M58:M58,"NI")&gt;0,"NI",IF(COUNTIF(M58:M58,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M58" s="17" t="n"/>
+      <c r="N58" s="18" t="n"/>
+      <c r="O58" s="18" t="n"/>
+      <c r="P58" s="50" t="n"/>
+      <c r="Q58" s="10" t="inlineStr">
+        <is>
+          <t>TC-ENT-007</t>
+        </is>
+      </c>
+      <c r="R58" s="10" t="inlineStr">
+        <is>
+          <t>결정적</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="B59" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C59" s="31" t="inlineStr">
+        <is>
+          <t>전역 셸</t>
+        </is>
+      </c>
+      <c r="D59" s="47" t="inlineStr">
+        <is>
+          <t>로그인 모달</t>
+        </is>
+      </c>
+      <c r="E59" s="49" t="inlineStr">
+        <is>
+          <t>로그인 모달 닫기</t>
+        </is>
+      </c>
+      <c r="F59" s="19" t="n"/>
+      <c r="G59" s="19" t="n"/>
+      <c r="H59" s="19" t="n"/>
+      <c r="I59" s="14" t="inlineStr">
+        <is>
+          <t>채팅 탭 열리지 않는다</t>
+        </is>
+      </c>
+      <c r="J59" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K59" s="10" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L59" s="16">
+        <f>IF(COUNTIF(M59:M59,"Fail")&gt;0,"Fail",IF(COUNTIF(M59:M59,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M59:M59,"NI")&gt;0,"NI",IF(COUNTIF(M59:M59,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M59" s="17" t="n"/>
+      <c r="N59" s="18" t="n"/>
+      <c r="O59" s="18" t="n"/>
+      <c r="P59" s="19" t="n"/>
+      <c r="Q59" s="10" t="inlineStr">
+        <is>
+          <t>TC-ENT-007</t>
+        </is>
+      </c>
+      <c r="R59" s="10" t="inlineStr">
+        <is>
+          <t>결정적</t>
+        </is>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="B4:R32"/>
-  <mergeCells count="59">
-    <mergeCell ref="M3"/>
+  <autoFilter ref="B4:S59"/>
+  <mergeCells count="104">
+    <mergeCell ref="F53:F54"/>
+    <mergeCell ref="H53:H54"/>
     <mergeCell ref="L9"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="H29:H30"/>
     <mergeCell ref="P22:P23"/>
-    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="P34:P35"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="B6:K6"/>
+    <mergeCell ref="H55:H56"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="H45:H46"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G49:G50"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="G51:G52"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="B8:K8"/>
+    <mergeCell ref="L8"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="P57:P59"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="P25:P26"/>
+    <mergeCell ref="H57:H59"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="P51:P52"/>
+    <mergeCell ref="H43:H44"/>
     <mergeCell ref="B9:K9"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="L6"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="B6:K6"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="H49:H50"/>
     <mergeCell ref="B5:K5"/>
     <mergeCell ref="P11:P12"/>
-    <mergeCell ref="P27:P28"/>
     <mergeCell ref="H17:H18"/>
     <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="P36:P37"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="P53:P54"/>
+    <mergeCell ref="F2:S2"/>
+    <mergeCell ref="G57:G59"/>
+    <mergeCell ref="P47:P48"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="L5"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="M3"/>
+    <mergeCell ref="H29:H30"/>
+    <mergeCell ref="P40:P41"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="P49:P50"/>
+    <mergeCell ref="P27:P28"/>
+    <mergeCell ref="G53:G54"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="N5:S9"/>
+    <mergeCell ref="H51:H52"/>
     <mergeCell ref="P17:P18"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="B7:K7"/>
-    <mergeCell ref="L7"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="G55:G56"/>
     <mergeCell ref="P19:P20"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="F43:F44"/>
     <mergeCell ref="P3:P4"/>
     <mergeCell ref="L3"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="N5:R9"/>
-    <mergeCell ref="L5"/>
+    <mergeCell ref="F49:F50"/>
     <mergeCell ref="F29:F30"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="G22:G23"/>
     <mergeCell ref="P14:P15"/>
-    <mergeCell ref="B8:K8"/>
-    <mergeCell ref="L8"/>
-    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="P55:P56"/>
+    <mergeCell ref="P45:P46"/>
+    <mergeCell ref="G43:G44"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="L6"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="F57:F59"/>
+    <mergeCell ref="B7:K7"/>
+    <mergeCell ref="L7"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="G29:G30"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="G45:G46"/>
+    <mergeCell ref="P43:P44"/>
+    <mergeCell ref="H25:H26"/>
     <mergeCell ref="F19:F20"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="F2:R2"/>
-    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="G47:G48"/>
     <mergeCell ref="P29:P30"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="P25:P26"/>
+    <mergeCell ref="G40:G41"/>
   </mergeCells>
   <conditionalFormatting sqref="M10:M500">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
@@ -2789,536 +4994,536 @@
   </cols>
   <sheetData>
     <row r="2" ht="19" customHeight="1">
-      <c r="B2" s="31" t="inlineStr">
+      <c r="B2" s="51" t="inlineStr">
         <is>
           <t>커버리지 요약</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="32" t="inlineStr">
+      <c r="B3" s="52" t="inlineStr">
         <is>
           <t>Test Case 시트를 참조하는 수식으로 자동 집계됩니다. 행을 추가하면 아래 범위를 넓히세요.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="33" t="inlineStr">
+      <c r="B4" s="53" t="inlineStr">
         <is>
           <t>기준 골격 버전</t>
         </is>
       </c>
-      <c r="C4" s="34" t="inlineStr">
-        <is>
-          <t>qa-lab-miyonchat-tree-v1.11</t>
-        </is>
-      </c>
-      <c r="D4" s="35" t="n"/>
-      <c r="E4" s="35" t="n"/>
+      <c r="C4" s="54" t="inlineStr">
+        <is>
+          <t>qa-lab-miyonchat-tree-v1.12</t>
+        </is>
+      </c>
+      <c r="D4" s="55" t="n"/>
+      <c r="E4" s="55" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="56" t="inlineStr">
         <is>
           <t>1-Depth (영역)</t>
         </is>
       </c>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="C5" s="56" t="inlineStr">
         <is>
           <t>TC 수</t>
         </is>
       </c>
-      <c r="D5" s="36" t="inlineStr">
+      <c r="D5" s="56" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="E5" s="35" t="n"/>
-      <c r="F5" s="35" t="n"/>
-      <c r="G5" s="36" t="inlineStr">
+      <c r="E5" s="55" t="n"/>
+      <c r="F5" s="55" t="n"/>
+      <c r="G5" s="56" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H5" s="35" t="n"/>
-      <c r="I5" s="35" t="n"/>
-      <c r="J5" s="35" t="n"/>
-      <c r="K5" s="35" t="n"/>
+      <c r="H5" s="55" t="n"/>
+      <c r="I5" s="55" t="n"/>
+      <c r="J5" s="55" t="n"/>
+      <c r="K5" s="55" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="35" t="n"/>
-      <c r="C6" s="35" t="n"/>
-      <c r="D6" s="37" t="inlineStr">
+      <c r="B6" s="55" t="n"/>
+      <c r="C6" s="55" t="n"/>
+      <c r="D6" s="57" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E6" s="37" t="inlineStr">
+      <c r="E6" s="57" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F6" s="37" t="inlineStr">
+      <c r="F6" s="57" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G6" s="37" t="inlineStr">
+      <c r="G6" s="57" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="H6" s="37" t="inlineStr">
+      <c r="H6" s="57" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="I6" s="37" t="inlineStr">
+      <c r="I6" s="57" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="J6" s="37" t="inlineStr">
+      <c r="J6" s="57" t="inlineStr">
         <is>
           <t>Pass율</t>
         </is>
       </c>
-      <c r="K6" s="35" t="n"/>
+      <c r="K6" s="55" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="38" t="inlineStr">
+      <c r="B7" s="58" t="inlineStr">
         <is>
           <t>웹 진입</t>
         </is>
       </c>
-      <c r="C7" s="39">
+      <c r="C7" s="59">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B7)</f>
         <v/>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B7,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E7" s="39">
+      <c r="E7" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B7,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B7,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G7" s="39">
+      <c r="G7" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B7,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H7" s="39">
+      <c r="H7" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B7,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I7" s="39">
+      <c r="I7" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B7,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J7" s="40">
+      <c r="J7" s="60">
         <f>IF(G7+H7=0,"",G7/(G7+H7))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="58" t="inlineStr">
         <is>
           <t>전역 셸</t>
         </is>
       </c>
-      <c r="C8" s="39">
+      <c r="C8" s="59">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B8)</f>
         <v/>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B8,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E8" s="39">
+      <c r="E8" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B8,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F8" s="39">
+      <c r="F8" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B8,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G8" s="39">
+      <c r="G8" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B8,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H8" s="39">
+      <c r="H8" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B8,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I8" s="39">
+      <c r="I8" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B8,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J8" s="40">
+      <c r="J8" s="60">
         <f>IF(G8+H8=0,"",G8/(G8+H8))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="38" t="inlineStr">
+      <c r="B9" s="58" t="inlineStr">
         <is>
           <t>홈 화면</t>
         </is>
       </c>
-      <c r="C9" s="39">
+      <c r="C9" s="59">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B9)</f>
         <v/>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B9,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E9" s="39">
+      <c r="E9" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B9,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F9" s="39">
+      <c r="F9" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B9,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G9" s="39">
+      <c r="G9" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B9,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H9" s="39">
+      <c r="H9" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B9,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I9" s="39">
+      <c r="I9" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B9,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J9" s="40">
+      <c r="J9" s="60">
         <f>IF(G9+H9=0,"",G9/(G9+H9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="38" t="inlineStr">
+      <c r="B10" s="58" t="inlineStr">
         <is>
           <t>캐릭터 페이지</t>
         </is>
       </c>
-      <c r="C10" s="39">
+      <c r="C10" s="59">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B10)</f>
         <v/>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B10,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E10" s="39">
+      <c r="E10" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B10,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F10" s="39">
+      <c r="F10" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B10,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G10" s="39">
+      <c r="G10" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B10,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H10" s="39">
+      <c r="H10" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B10,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I10" s="39">
+      <c r="I10" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B10,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J10" s="40">
+      <c r="J10" s="60">
         <f>IF(G10+H10=0,"",G10/(G10+H10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="58" t="inlineStr">
         <is>
           <t>대화 프로필 화면</t>
         </is>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="59">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B11)</f>
         <v/>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B11,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E11" s="39">
+      <c r="E11" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B11,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F11" s="39">
+      <c r="F11" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B11,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G11" s="39">
+      <c r="G11" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B11,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H11" s="39">
+      <c r="H11" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B11,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I11" s="39">
+      <c r="I11" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B11,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J11" s="40">
+      <c r="J11" s="60">
         <f>IF(G11+H11=0,"",G11/(G11+H11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="38" t="inlineStr">
+      <c r="B12" s="58" t="inlineStr">
         <is>
           <t>대화방</t>
         </is>
       </c>
-      <c r="C12" s="39">
+      <c r="C12" s="59">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B12)</f>
         <v/>
       </c>
-      <c r="D12" s="39">
+      <c r="D12" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B12,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E12" s="39">
+      <c r="E12" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B12,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F12" s="39">
+      <c r="F12" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B12,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G12" s="39">
+      <c r="G12" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B12,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H12" s="39">
+      <c r="H12" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B12,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I12" s="39">
+      <c r="I12" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B12,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J12" s="40">
+      <c r="J12" s="60">
         <f>IF(G12+H12=0,"",G12/(G12+H12))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="38" t="inlineStr">
+      <c r="B13" s="58" t="inlineStr">
         <is>
           <t>채팅 탭</t>
         </is>
       </c>
-      <c r="C13" s="39">
+      <c r="C13" s="59">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B13)</f>
         <v/>
       </c>
-      <c r="D13" s="39">
+      <c r="D13" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B13,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E13" s="39">
+      <c r="E13" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B13,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F13" s="39">
+      <c r="F13" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B13,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G13" s="39">
+      <c r="G13" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B13,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H13" s="39">
+      <c r="H13" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B13,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I13" s="39">
+      <c r="I13" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B13,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J13" s="40">
+      <c r="J13" s="60">
         <f>IF(G13+H13=0,"",G13/(G13+H13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="38" t="inlineStr">
+      <c r="B14" s="58" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
-      <c r="C14" s="39">
+      <c r="C14" s="59">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B14)</f>
         <v/>
       </c>
-      <c r="D14" s="39">
+      <c r="D14" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B14,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E14" s="39">
+      <c r="E14" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B14,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F14" s="39">
+      <c r="F14" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B14,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G14" s="39">
+      <c r="G14" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B14,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H14" s="39">
+      <c r="H14" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B14,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I14" s="39">
+      <c r="I14" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B14,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J14" s="40">
+      <c r="J14" s="60">
         <f>IF(G14+H14=0,"",G14/(G14+H14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="38" t="inlineStr">
+      <c r="B15" s="58" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
-      <c r="C15" s="39">
+      <c r="C15" s="59">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B15)</f>
         <v/>
       </c>
-      <c r="D15" s="39">
+      <c r="D15" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B15,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E15" s="39">
+      <c r="E15" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B15,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F15" s="39">
+      <c r="F15" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B15,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G15" s="39">
+      <c r="G15" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B15,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H15" s="39">
+      <c r="H15" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B15,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I15" s="39">
+      <c r="I15" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B15,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J15" s="40">
+      <c r="J15" s="60">
         <f>IF(G15+H15=0,"",G15/(G15+H15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="38" t="inlineStr">
+      <c r="B16" s="58" t="inlineStr">
         <is>
           <t>스텁·정적</t>
         </is>
       </c>
-      <c r="C16" s="39">
+      <c r="C16" s="59">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B16)</f>
         <v/>
       </c>
-      <c r="D16" s="39">
+      <c r="D16" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B16,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E16" s="39">
+      <c r="E16" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B16,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F16" s="39">
+      <c r="F16" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B16,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G16" s="39">
+      <c r="G16" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B16,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H16" s="39">
+      <c r="H16" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B16,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I16" s="39">
+      <c r="I16" s="59">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B16,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J16" s="40">
+      <c r="J16" s="60">
         <f>IF(G16+H16=0,"",G16/(G16+H16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="41" t="inlineStr">
+      <c r="B17" s="61" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="C17" s="42">
+      <c r="C17" s="62">
         <f>SUM(C7:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="42">
+      <c r="D17" s="62">
         <f>SUM(D7:D16)</f>
         <v/>
       </c>
-      <c r="E17" s="42">
+      <c r="E17" s="62">
         <f>SUM(E7:E16)</f>
         <v/>
       </c>
-      <c r="F17" s="42">
+      <c r="F17" s="62">
         <f>SUM(F7:F16)</f>
         <v/>
       </c>
-      <c r="G17" s="42">
+      <c r="G17" s="62">
         <f>SUM(G7:G16)</f>
         <v/>
       </c>
-      <c r="H17" s="42">
+      <c r="H17" s="62">
         <f>SUM(H7:H16)</f>
         <v/>
       </c>
-      <c r="I17" s="42">
+      <c r="I17" s="62">
         <f>SUM(I7:I16)</f>
         <v/>
       </c>
-      <c r="J17" s="43">
+      <c r="J17" s="63">
         <f>IF(G17+H17=0,"",G17/(G17+H17))</f>
         <v/>
       </c>
-      <c r="K17" s="42">
+      <c r="K17" s="62">
         <f>SUM(K7:K16)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="32" t="inlineStr">
+      <c r="B19" s="52" t="inlineStr">
         <is>
           <t>TC 수 = 스텝 행 수(1-Depth 기준) · Pass/Fail/Blocked도 같은 행 단위(Result 열) · Pass율 = Pass ÷ (Pass + Fail) — NI·Blocked는 분모에서 제외합니다</t>
         </is>
@@ -3369,129 +5574,129 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1">
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="64" t="inlineStr">
         <is>
           <t>프로젝트 ID</t>
         </is>
       </c>
-      <c r="C2" s="44" t="inlineStr">
+      <c r="C2" s="64" t="inlineStr">
         <is>
           <t>Issue No.</t>
         </is>
       </c>
-      <c r="D2" s="44" t="inlineStr">
+      <c r="D2" s="64" t="inlineStr">
         <is>
           <t>이슈 상태</t>
         </is>
       </c>
-      <c r="E2" s="44" t="inlineStr">
+      <c r="E2" s="64" t="inlineStr">
         <is>
           <t>요약(Summary)</t>
         </is>
       </c>
-      <c r="F2" s="44" t="inlineStr">
+      <c r="F2" s="64" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="G2" s="44" t="inlineStr">
+      <c r="G2" s="64" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="H2" s="44" t="inlineStr">
+      <c r="H2" s="64" t="inlineStr">
         <is>
           <t>빈도</t>
         </is>
       </c>
-      <c r="I2" s="44" t="inlineStr">
+      <c r="I2" s="64" t="inlineStr">
         <is>
           <t>영향 받는 버전</t>
         </is>
       </c>
-      <c r="J2" s="44" t="inlineStr">
+      <c r="J2" s="64" t="inlineStr">
         <is>
           <t>수정 버전</t>
         </is>
       </c>
-      <c r="K2" s="44" t="inlineStr">
+      <c r="K2" s="64" t="inlineStr">
         <is>
           <t>해결책</t>
         </is>
       </c>
-      <c r="L2" s="44" t="inlineStr">
+      <c r="L2" s="64" t="inlineStr">
         <is>
           <t>환경</t>
         </is>
       </c>
-      <c r="M2" s="44" t="inlineStr">
+      <c r="M2" s="64" t="inlineStr">
         <is>
           <t>레이블</t>
         </is>
       </c>
-      <c r="N2" s="44" t="inlineStr">
+      <c r="N2" s="64" t="inlineStr">
         <is>
           <t>보고자</t>
         </is>
       </c>
-      <c r="O2" s="44" t="inlineStr">
+      <c r="O2" s="64" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="P2" s="44" t="inlineStr">
+      <c r="P2" s="64" t="inlineStr">
         <is>
           <t>관측자</t>
         </is>
       </c>
-      <c r="Q2" s="44" t="inlineStr">
+      <c r="Q2" s="64" t="inlineStr">
         <is>
           <t>첨부파일</t>
         </is>
       </c>
-      <c r="R2" s="44" t="inlineStr">
+      <c r="R2" s="64" t="inlineStr">
         <is>
           <t>스프린트</t>
         </is>
       </c>
-      <c r="S2" s="44" t="inlineStr">
+      <c r="S2" s="64" t="inlineStr">
         <is>
           <t>이슈 등록일</t>
         </is>
       </c>
-      <c r="T2" s="44" t="inlineStr">
+      <c r="T2" s="64" t="inlineStr">
         <is>
           <t>이슈 최종 수정일자</t>
         </is>
       </c>
-      <c r="U2" s="44" t="inlineStr">
+      <c r="U2" s="64" t="inlineStr">
         <is>
           <t>이슈 상태 최종 변경일자</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="45" t="inlineStr">
+      <c r="B3" s="65" t="inlineStr">
         <is>
           <t>miyonchat</t>
         </is>
       </c>
-      <c r="C3" s="45" t="inlineStr">
+      <c r="C3" s="65" t="inlineStr">
         <is>
           <t>miyonchat-1</t>
         </is>
       </c>
-      <c r="D3" s="45" t="inlineStr">
+      <c r="D3" s="65" t="inlineStr">
         <is>
           <t>Resolved</t>
         </is>
       </c>
-      <c r="E3" s="46" t="inlineStr">
+      <c r="E3" s="66" t="inlineStr">
         <is>
           <t>디버그 콘솔 &gt; 전체 초기화(reset) 수행 &gt; 계정 A 로그인 시, 성인 인증이 해제된 상태로 시작됨</t>
         </is>
       </c>
-      <c r="F3" s="46" t="inlineStr">
+      <c r="F3" s="66" t="inlineStr">
         <is>
           <t>Pre-condition: SUT 진입
 Reproduce Step: 디버그 콘솔 열기 &gt; [전체 초기화] 선택 &gt; 계정 A로 로그인 &gt; 간편 프로필 확인
@@ -3500,69 +5705,69 @@
 QA Comment: 계정 상태 생성 함수에 계정 식별자를 전달하지 않아 기본값 판정이 항상 거짓이 됨. 자동화가 매 테스트 전 reset()을 호출하는 구조라, 남아 있으면 게이팅 계열 TC 전체가 미인증 상태에서 실행되어 결과를 신뢰할 수 없음</t>
         </is>
       </c>
-      <c r="G3" s="45" t="inlineStr">
+      <c r="G3" s="65" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H3" s="45" t="inlineStr">
+      <c r="H3" s="65" t="inlineStr">
         <is>
           <t>Always</t>
         </is>
       </c>
-      <c r="I3" s="45" t="inlineStr">
+      <c r="I3" s="65" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev_RC1</t>
         </is>
       </c>
-      <c r="J3" s="45" t="inlineStr">
+      <c r="J3" s="65" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev_RC2</t>
         </is>
       </c>
-      <c r="K3" s="45" t="inlineStr">
+      <c r="K3" s="65" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="L3" s="45" t="inlineStr">
+      <c r="L3" s="65" t="inlineStr">
         <is>
           <t>PC웹</t>
         </is>
       </c>
-      <c r="M3" s="45" t="inlineStr">
+      <c r="M3" s="65" t="inlineStr">
         <is>
           <t>계정/게이팅</t>
         </is>
       </c>
-      <c r="N3" s="45" t="inlineStr">
+      <c r="N3" s="65" t="inlineStr">
         <is>
           <t>정준호</t>
         </is>
       </c>
-      <c r="O3" s="45" t="inlineStr">
+      <c r="O3" s="65" t="inlineStr">
         <is>
           <t>Claude Opus 5</t>
         </is>
       </c>
-      <c r="P3" s="45" t="inlineStr"/>
-      <c r="Q3" s="45" t="inlineStr"/>
-      <c r="R3" s="45" t="inlineStr">
+      <c r="P3" s="65" t="inlineStr"/>
+      <c r="Q3" s="65" t="inlineStr"/>
+      <c r="R3" s="65" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev</t>
         </is>
       </c>
-      <c r="S3" s="45" t="inlineStr">
+      <c r="S3" s="65" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="T3" s="45" t="inlineStr">
+      <c r="T3" s="65" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="U3" s="45" t="inlineStr">
+      <c r="U3" s="65" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
@@ -3646,316 +5851,347 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M12"/>
+  <dimension ref="B2:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="47" t="inlineStr">
+      <c r="B2" s="67" t="inlineStr">
         <is>
           <t>프로젝트</t>
         </is>
       </c>
-      <c r="C2" s="47" t="inlineStr">
+      <c r="C2" s="67" t="inlineStr">
         <is>
           <t>실행 주체</t>
         </is>
       </c>
-      <c r="D2" s="47" t="inlineStr">
+      <c r="D2" s="67" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="E2" s="67" t="inlineStr">
         <is>
           <t>이슈 상태</t>
         </is>
       </c>
-      <c r="E2" s="47" t="inlineStr">
+      <c r="F2" s="67" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="F2" s="47" t="inlineStr">
+      <c r="G2" s="67" t="inlineStr">
         <is>
           <t>빈도</t>
         </is>
       </c>
-      <c r="G2" s="47" t="inlineStr">
+      <c r="H2" s="67" t="inlineStr">
         <is>
           <t>버전(영향/수정 공용)</t>
         </is>
       </c>
-      <c r="H2" s="47" t="inlineStr">
+      <c r="I2" s="67" t="inlineStr">
         <is>
           <t>해결책</t>
         </is>
       </c>
-      <c r="I2" s="47" t="inlineStr">
+      <c r="J2" s="67" t="inlineStr">
         <is>
           <t>환경</t>
         </is>
       </c>
-      <c r="J2" s="47" t="inlineStr">
+      <c r="K2" s="67" t="inlineStr">
         <is>
           <t>레이블</t>
         </is>
       </c>
-      <c r="K2" s="47" t="inlineStr">
+      <c r="L2" s="67" t="inlineStr">
         <is>
           <t>보고자</t>
         </is>
       </c>
-      <c r="L2" s="47" t="inlineStr">
+      <c r="M2" s="67" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="M2" s="47" t="inlineStr">
+      <c r="N2" s="67" t="inlineStr">
         <is>
           <t>스프린트</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="48" t="inlineStr">
+      <c r="B3" s="68" t="inlineStr">
         <is>
           <t>miyonchat</t>
         </is>
       </c>
-      <c r="C3" s="48" t="inlineStr">
+      <c r="C3" s="68" t="inlineStr">
         <is>
           <t>자동화 전용</t>
         </is>
       </c>
-      <c r="D3" s="48" t="inlineStr">
+      <c r="D3" s="68" t="inlineStr">
+        <is>
+          <t>미로그인</t>
+        </is>
+      </c>
+      <c r="E3" s="68" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="E3" s="48" t="inlineStr">
+      <c r="F3" s="68" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F3" s="48" t="inlineStr">
+      <c r="G3" s="68" t="inlineStr">
         <is>
           <t>Always</t>
         </is>
       </c>
-      <c r="G3" s="48" t="inlineStr">
+      <c r="H3" s="68" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev_RC1</t>
         </is>
       </c>
-      <c r="H3" s="48" t="inlineStr">
+      <c r="I3" s="68" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="I3" s="48" t="inlineStr">
+      <c r="J3" s="68" t="inlineStr">
         <is>
           <t>PC웹</t>
         </is>
       </c>
-      <c r="J3" s="48" t="inlineStr">
+      <c r="K3" s="68" t="inlineStr">
         <is>
           <t>앱 진입/세션</t>
         </is>
       </c>
-      <c r="K3" s="48" t="inlineStr">
+      <c r="L3" s="68" t="inlineStr">
         <is>
           <t>정준호</t>
         </is>
       </c>
-      <c r="L3" s="48" t="inlineStr">
+      <c r="M3" s="68" t="inlineStr">
         <is>
           <t>Claude Opus 5</t>
         </is>
       </c>
-      <c r="M3" s="48" t="inlineStr">
+      <c r="N3" s="68" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="C4" s="48" t="inlineStr">
+      <c r="C4" s="68" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="D4" s="48" t="inlineStr">
+      <c r="D4" s="68" t="inlineStr">
+        <is>
+          <t>본인인증 미진행</t>
+        </is>
+      </c>
+      <c r="E4" s="68" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="E4" s="48" t="inlineStr">
+      <c r="F4" s="68" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F4" s="48" t="inlineStr">
+      <c r="G4" s="68" t="inlineStr">
         <is>
           <t>Often</t>
         </is>
       </c>
-      <c r="G4" s="48" t="inlineStr">
+      <c r="H4" s="68" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev_RC2</t>
         </is>
       </c>
-      <c r="H4" s="48" t="inlineStr">
+      <c r="I4" s="68" t="inlineStr">
         <is>
           <t>Won't Do</t>
         </is>
       </c>
-      <c r="J4" s="48" t="inlineStr">
+      <c r="K4" s="68" t="inlineStr">
         <is>
           <t>계정/게이팅</t>
         </is>
       </c>
-      <c r="M4" s="48" t="inlineStr">
+      <c r="N4" s="68" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_RT1</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="48" t="inlineStr">
+      <c r="C5" s="68" t="inlineStr">
         <is>
           <t>사람 전용</t>
         </is>
       </c>
-      <c r="D5" s="48" t="inlineStr">
+      <c r="D5" s="68" t="inlineStr">
+        <is>
+          <t>성인 인증</t>
+        </is>
+      </c>
+      <c r="E5" s="68" t="inlineStr">
         <is>
           <t>Resolved</t>
         </is>
       </c>
-      <c r="E5" s="48" t="inlineStr">
+      <c r="F5" s="68" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="F5" s="48" t="inlineStr">
+      <c r="G5" s="68" t="inlineStr">
         <is>
           <t>Sometimes</t>
         </is>
       </c>
-      <c r="G5" s="48" t="inlineStr">
+      <c r="H5" s="68" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev_RC3</t>
         </is>
       </c>
-      <c r="H5" s="48" t="inlineStr">
+      <c r="I5" s="68" t="inlineStr">
         <is>
           <t>Won't Fix</t>
         </is>
       </c>
-      <c r="J5" s="48" t="inlineStr">
+      <c r="K5" s="68" t="inlineStr">
         <is>
           <t>탐색/발견</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="D6" s="48" t="inlineStr">
+      <c r="D6" s="68" t="inlineStr">
+        <is>
+          <t>미성년</t>
+        </is>
+      </c>
+      <c r="E6" s="68" t="inlineStr">
         <is>
           <t>Reopen</t>
         </is>
       </c>
-      <c r="F6" s="48" t="inlineStr">
+      <c r="G6" s="68" t="inlineStr">
         <is>
           <t>Once</t>
         </is>
       </c>
-      <c r="G6" s="48" t="inlineStr">
+      <c r="H6" s="68" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_RT1_RC1</t>
         </is>
       </c>
-      <c r="H6" s="48" t="inlineStr">
+      <c r="I6" s="68" t="inlineStr">
         <is>
           <t>Duplicate</t>
         </is>
       </c>
-      <c r="J6" s="48" t="inlineStr">
+      <c r="K6" s="68" t="inlineStr">
         <is>
           <t>유저 페르소나</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="D7" s="48" t="inlineStr">
+      <c r="D7" s="68" t="inlineStr">
+        <is>
+          <t>세션 만료</t>
+        </is>
+      </c>
+      <c r="E7" s="68" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="H7" s="48" t="inlineStr">
+      <c r="I7" s="68" t="inlineStr">
         <is>
           <t>Incomplete</t>
         </is>
       </c>
-      <c r="J7" s="48" t="inlineStr">
+      <c r="K7" s="68" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="H8" s="48" t="inlineStr">
+      <c r="I8" s="68" t="inlineStr">
         <is>
           <t>Cannot Reproduce</t>
         </is>
       </c>
-      <c r="J8" s="48" t="inlineStr">
+      <c r="K8" s="68" t="inlineStr">
         <is>
           <t>서사 시스템</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="H9" s="48" t="inlineStr">
+      <c r="I9" s="68" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="J9" s="48" t="inlineStr">
+      <c r="K9" s="68" t="inlineStr">
         <is>
           <t>대화 세션</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="H10" s="48" t="inlineStr">
+      <c r="I10" s="68" t="inlineStr">
         <is>
           <t>Declined</t>
         </is>
       </c>
-      <c r="J10" s="48" t="inlineStr">
+      <c r="K10" s="68" t="inlineStr">
         <is>
           <t>세이브/로드</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="J11" s="48" t="inlineStr">
+      <c r="K11" s="68" t="inlineStr">
         <is>
           <t>메모리/컨텍스트</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="J12" s="48" t="inlineStr">
+      <c r="K12" s="68" t="inlineStr">
         <is>
           <t>입력/출력 세이프티</t>
         </is>
@@ -4000,7 +6236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E109"/>
+  <dimension ref="B2:E110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4010,1151 +6246,1168 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="49" t="inlineStr">
+      <c r="B2" s="69" t="inlineStr">
         <is>
           <t>명세서 — 시트 규칙 정본</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="50" t="inlineStr">
+      <c r="B3" s="70" t="inlineStr">
         <is>
           <t>이 시트가 구조 규칙의 정본입니다. rules/tc-sheet-format.md와 짝으로 교차 검증하며, 불일치 발견 시 임의 판단 없이 사용자에게 기준을 확인합니다. 서식(색·테두리·폰트)의 정본은 design-template/xlsx-design-guide.md입니다.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="51" t="inlineStr">
         <is>
           <t>1. 시트 구성</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="47" t="inlineStr">
+      <c r="B6" s="67" t="inlineStr">
         <is>
           <t>시트</t>
         </is>
       </c>
-      <c r="C6" s="47" t="inlineStr">
+      <c r="C6" s="67" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="46" t="inlineStr">
+      <c r="B7" s="66" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="C7" s="46" t="inlineStr">
+      <c r="C7" s="66" t="inlineStr">
         <is>
           <t>TC 작성과 실행 기록. 노란 셀은 실행 단계에서 채워집니다</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="46" t="inlineStr">
+      <c r="B8" s="66" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="C8" s="46" t="inlineStr">
+      <c r="C8" s="66" t="inlineStr">
         <is>
           <t>행 단위 자동 집계(1-Depth 기준). 기준 골격 버전(C4)은 생성 시 자동 기입됩니다</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="46" t="inlineStr">
+      <c r="B9" s="66" t="inlineStr">
         <is>
           <t>이슈 관리 시트</t>
         </is>
       </c>
-      <c r="C9" s="46" t="inlineStr">
+      <c r="C9" s="66" t="inlineStr">
         <is>
           <t>결함 기록(내장 운영, JIRA 미사용) — JIRA 이슈 등록·관리 방식을 시트로 표현. Issue No.로 Test Case와 연결합니다. 정본은 별도 파일 test-case/{프로젝트}-issues.json이며 이 시트는 그 파생입니다</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="46" t="inlineStr">
+      <c r="B10" s="66" t="inlineStr">
         <is>
           <t>목록</t>
         </is>
       </c>
-      <c r="C10" s="46" t="inlineStr">
+      <c r="C10" s="66" t="inlineStr">
         <is>
           <t>드롭다운 참조 목록의 정본. 숨기지 않고 맨 뒤에 둡니다</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="46" t="inlineStr">
+      <c r="B11" s="66" t="inlineStr">
         <is>
           <t>명세서</t>
         </is>
       </c>
-      <c r="C11" s="46" t="inlineStr">
+      <c r="C11" s="66" t="inlineStr">
         <is>
           <t>이 시트 — 구조 규칙의 정본</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" s="51" t="inlineStr">
         <is>
           <t>2. 컬럼 정의 (Test Case)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="47" t="inlineStr">
+      <c r="B14" s="67" t="inlineStr">
         <is>
           <t>컬럼</t>
         </is>
       </c>
-      <c r="C14" s="47" t="inlineStr">
+      <c r="C14" s="67" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="D14" s="47" t="inlineStr">
+      <c r="D14" s="67" t="inlineStr">
         <is>
           <t>채우는 규칙</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="46" t="inlineStr">
+      <c r="B15" s="66" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C15" s="46" t="inlineStr">
+      <c r="C15" s="66" t="inlineStr">
         <is>
           <t>행 번호</t>
         </is>
       </c>
-      <c r="D15" s="46" t="inlineStr">
+      <c r="D15" s="66" t="inlineStr">
         <is>
           <t>자동 수식(ROW() 기준). 직접 입력하지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="46" t="inlineStr">
+      <c r="B16" s="66" t="inlineStr">
         <is>
           <t>1~7-Depth</t>
         </is>
       </c>
-      <c r="C16" s="46" t="inlineStr">
+      <c r="C16" s="66" t="inlineStr">
         <is>
           <t>기능 계층</t>
         </is>
       </c>
-      <c r="D16" s="46" t="inlineStr">
+      <c r="D16" s="66" t="inlineStr">
         <is>
           <t>행마다 반복(기대결과 추가 행 포함 — 집계·필터의 전제). 의미 있는 깊이까지만 쓰고 나머지는 빈칸. 병합하지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="46" t="inlineStr">
+      <c r="B17" s="66" t="inlineStr">
         <is>
           <t>Pre-Condition</t>
         </is>
       </c>
-      <c r="C17" s="46" t="inlineStr">
+      <c r="C17" s="66" t="inlineStr">
         <is>
           <t>사전조건</t>
         </is>
       </c>
-      <c r="D17" s="46" t="inlineStr">
+      <c r="D17" s="66" t="inlineStr">
         <is>
           <t>TN 1행에 케이스 진입 조건. 중간 스텝에 앞 스텝이 만들지 못하는 새 상태(시간 경과·외부 변화 등)가 필요하면 그 행에도 적습니다 — 앞 스텝의 결과로 성립한 상태는 제외. 같은 조건이 걸리는 스텝 행 범위는 세로 병합하되 케이스 전체 병합은 금지</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="46" t="inlineStr">
+      <c r="B18" s="66" t="inlineStr">
         <is>
           <t>TN</t>
         </is>
       </c>
-      <c r="C18" s="46" t="inlineStr">
+      <c r="C18" s="66" t="inlineStr">
         <is>
           <t>스텝 번호</t>
         </is>
       </c>
-      <c r="D18" s="46" t="inlineStr">
+      <c r="D18" s="66" t="inlineStr">
         <is>
           <t>케이스마다 1부터. 새 케이스가 시작되면 1로 복귀. 한 스텝의 기대결과가 여러 행이면(TN 값 무관) Test-Step과 함께 그 범위를 세로 병합합니다 — 반복 기재하면 독립 동작 여러 개로 오독됩니다</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="46" t="inlineStr">
+      <c r="B19" s="66" t="inlineStr">
         <is>
           <t>Test-Step</t>
         </is>
       </c>
-      <c r="C19" s="46" t="inlineStr">
+      <c r="C19" s="66" t="inlineStr">
         <is>
           <t>수행 동작</t>
         </is>
       </c>
-      <c r="D19" s="46" t="inlineStr">
+      <c r="D19" s="66" t="inlineStr">
         <is>
           <t>「~한다」 체. TN과 같은 범위로 세로 병합</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="46" t="inlineStr">
+      <c r="B20" s="66" t="inlineStr">
         <is>
           <t>Expected-Result</t>
         </is>
       </c>
-      <c r="C20" s="46" t="inlineStr">
+      <c r="C20" s="66" t="inlineStr">
         <is>
           <t>기대 결과</t>
         </is>
       </c>
-      <c r="D20" s="46" t="inlineStr">
+      <c r="D20" s="66" t="inlineStr">
         <is>
           <t>「~된다」 체. 판정 가능한 문장 — 임계·합격선·시도 횟수는 문장 안에 숫자로. 한 행 = 한 판정이므로 병합하지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="46" t="inlineStr">
+      <c r="B21" s="66" t="inlineStr">
         <is>
           <t>실행 주체</t>
         </is>
       </c>
-      <c r="C21" s="46" t="inlineStr">
+      <c r="C21" s="66" t="inlineStr">
         <is>
           <t>누가 수행하는가</t>
         </is>
       </c>
-      <c r="D21" s="46" t="inlineStr">
+      <c r="D21" s="66" t="inlineStr">
         <is>
           <t>행마다 반복(드롭다운 3종). 자동화 전용 = 사람이 화면만 봐서 판정 불가 / 사람 전용 = 자동화가 판정 기준을 못 세움 / 공통 = 기본값. 반복 횟수는 판정 근거가 아니며 「사람이 1회 봐도 의미가 있는가」로 갈립니다</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="46" t="inlineStr">
+      <c r="B22" s="66" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="C22" s="46" t="inlineStr">
+      <c r="C22" s="66" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="D22" s="46" t="inlineStr">
+      <c r="D22" s="66" t="inlineStr">
         <is>
           <t>행마다 반복. High/Medium/Low — 케이스의 속성이지만 Summary가 행 단위로 집계하므로 행마다 값을 둡니다</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="46" t="inlineStr">
+      <c r="B23" s="66" t="inlineStr">
         <is>
           <t>Total Result</t>
         </is>
       </c>
-      <c r="C23" s="46" t="inlineStr">
+      <c r="C23" s="66" t="inlineStr">
         <is>
           <t>행 판정</t>
         </is>
       </c>
-      <c r="D23" s="46" t="inlineStr">
+      <c r="D23" s="66" t="inlineStr">
         <is>
           <t>수식 열. 병합하지 않고 데이터 한 행씩 세웁니다 — 같은 플랫폼에 단말이 여럿일 때 그 행의 단말 결과를 요약합니다. 직접 입력하지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="46" t="inlineStr">
+      <c r="B24" s="66" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="C24" s="46" t="inlineStr">
+      <c r="C24" s="66" t="inlineStr">
         <is>
           <t>스텝 실행 결과</t>
         </is>
       </c>
-      <c r="D24" s="46" t="inlineStr">
+      <c r="D24" s="66" t="inlineStr">
         <is>
           <t>드롭다운 4종(아래 상태값 정의). 실행 단계에서 채움 — 노란 셀</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="46" t="inlineStr">
+      <c r="B25" s="66" t="inlineStr">
         <is>
           <t>Issue No.</t>
         </is>
       </c>
-      <c r="C25" s="46" t="inlineStr">
+      <c r="C25" s="66" t="inlineStr">
         <is>
           <t>관련 이슈</t>
         </is>
       </c>
-      <c r="D25" s="46" t="inlineStr">
+      <c r="D25" s="66" t="inlineStr">
         <is>
           <t>해당 TC를 수행하는 과정에서 이슈가 발생하면, 먼저 이슈 관리 시트에 이슈를 등록하고 거기서 부여된 Issue No.를 이 칸에 적습니다. 실행 단계에서 채움 — 노란 셀</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="46" t="inlineStr">
+      <c r="B26" s="66" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="C26" s="46" t="inlineStr">
+      <c r="C26" s="66" t="inlineStr">
         <is>
           <t>수행 중 기록</t>
         </is>
       </c>
-      <c r="D26" s="46" t="inlineStr">
+      <c r="D26" s="66" t="inlineStr">
         <is>
           <t>TC를 수행하다 생긴 문제·관찰을 실행 단계에서 적습니다 — 노란 셀. 설계 시점에는 비어 있습니다</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="46" t="inlineStr">
+      <c r="B27" s="66" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="C27" s="46" t="inlineStr">
+      <c r="C27" s="66" t="inlineStr">
         <is>
           <t>수행 전 참고사항</t>
         </is>
       </c>
-      <c r="D27" s="46" t="inlineStr">
+      <c r="D27" s="66" t="inlineStr">
         <is>
           <t>사람이 읽을 안내만 담습니다 — ①함께 볼 것 ②수행 방법 ③조건 만드는 법. 케이스 메타는 2026-08-03 개정으로 TC ID·검증유형 열이 따로 갖습니다. 스텝 범위 세로 병합</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="46" t="inlineStr">
+      <c r="B28" s="66" t="inlineStr">
         <is>
           <t>TC ID</t>
         </is>
       </c>
-      <c r="C28" s="46" t="inlineStr">
+      <c r="C28" s="66" t="inlineStr">
         <is>
           <t>조인 키</t>
         </is>
       </c>
-      <c r="D28" s="46" t="inlineStr">
+      <c r="D28" s="66" t="inlineStr">
         <is>
           <t>행마다 반복. 자동화 케이스명·추적 매트릭스·이슈 연결이 참조합니다. 사람의 실행 동선에서 빼려고 Note 우측 참조 블록에 둡니다</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="46" t="inlineStr">
+      <c r="B29" s="66" t="inlineStr">
         <is>
           <t>검증유형</t>
         </is>
       </c>
-      <c r="C29" s="46" t="inlineStr">
+      <c r="C29" s="66" t="inlineStr">
         <is>
           <t>판정 방식</t>
         </is>
       </c>
-      <c r="D29" s="46" t="inlineStr">
+      <c r="D29" s="66" t="inlineStr">
         <is>
           <t>행마다 반복(드롭다운 4종). 반복 횟수는 시트에 적지 않습니다 — 수동 실행자가 자기에게 내려진 지시로 오독하기 때문입니다. 반복은 자동화가 수행하며, 사람은 어떤 유형이든 1회입니다. 확률적·루브릭을 사람이 1회 수행했다면 결과는 Pass가 아니라 관찰 기록이고, 판정은 자동화 반복이나 채점이 담당합니다</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="31" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="66" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="C30" s="66" t="inlineStr">
+        <is>
+          <t>케이스가 밟는 게이팅·세션 상태 (2026-08-04 신설)</t>
+        </is>
+      </c>
+      <c r="D30" s="66" t="inlineStr">
+        <is>
+          <t>행마다 반복. 값 5종은 목록 시트가 정본이고 복수 상태는 쉼표로 적습니다(전환 케이스 — 드롭다운을 걸지 않는 이유). 자동 필터를 「포함」 조건으로 걸어 상태별 TC를 추출하고, 트리의 [상태:] 선언과 맞물려 잎×상태 커버리지를 대조합니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="51" t="inlineStr">
         <is>
           <t>3. 상태값 정의</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="47" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="67" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="C32" s="47" t="inlineStr">
+      <c r="C33" s="67" t="inlineStr">
         <is>
           <t>정의</t>
         </is>
       </c>
-      <c r="D32" s="47" t="inlineStr">
+      <c r="D33" s="67" t="inlineStr">
         <is>
           <t>Pass율 분모</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="46" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="66" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C33" s="46" t="inlineStr">
+      <c r="C34" s="66" t="inlineStr">
         <is>
           <t>성공</t>
         </is>
       </c>
-      <c r="D33" s="46" t="inlineStr">
+      <c r="D34" s="66" t="inlineStr">
         <is>
           <t>포함</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="46" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="66" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="C34" s="46" t="inlineStr">
+      <c r="C35" s="66" t="inlineStr">
         <is>
           <t>실패</t>
         </is>
       </c>
-      <c r="D34" s="46" t="inlineStr">
+      <c r="D35" s="66" t="inlineStr">
         <is>
           <t>포함</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="46" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="66" t="inlineStr">
         <is>
           <t>NI</t>
         </is>
       </c>
-      <c r="C35" s="46" t="inlineStr">
+      <c r="C36" s="66" t="inlineStr">
         <is>
           <t>미구현이거나 스펙에 없어 실행 대상이 아님 (Not Implemented)</t>
         </is>
       </c>
-      <c r="D35" s="46" t="inlineStr">
+      <c r="D36" s="66" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="46" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="66" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="C36" s="46" t="inlineStr">
+      <c r="C37" s="66" t="inlineStr">
         <is>
           <t>기능은 구현됐으나 확인할 수 없는 상태 — 선행 케이스 Fail·환경 결함·데이터 준비 불가 등. 사유는 실행 과정에서 Comment에 적습니다</t>
         </is>
       </c>
-      <c r="D36" s="46" t="inlineStr">
+      <c r="D37" s="66" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="50" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="70" t="inlineStr">
         <is>
           <t>Pass율 = Pass ÷ (Pass + Fail). NI·Blocked를 분모에 넣지 않는 이유는 결함 1건이 후속 Blocked 수만큼 중복 계상되는 것을 막기 위해서입니다.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="31" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="51" t="inlineStr">
         <is>
           <t>4. Total Result 규칙</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="47" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="67" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C40" s="47" t="inlineStr">
+      <c r="C41" s="67" t="inlineStr">
         <is>
           <t>규칙</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="46" t="inlineStr">
+    <row r="42">
+      <c r="B42" s="66" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="C41" s="46" t="inlineStr">
+      <c r="C42" s="66" t="inlineStr">
         <is>
           <t>Fail &gt; Blocked &gt; NI &gt; Pass — 스텝 중 하나라도 Fail이면 케이스 Fail</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="46" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="66" t="inlineStr">
         <is>
           <t>수식 원형</t>
         </is>
       </c>
-      <c r="C42" s="46" t="inlineStr">
+      <c r="C43" s="66" t="inlineStr">
         <is>
           <t>IF(COUNTIF(범위,"Fail")&gt;0,"Fail",IF(COUNTIF(범위,"Blocked")&gt;0,"Blocked",IF(COUNTIF(범위,"NI")&gt;0,"NI",IF(COUNTIF(범위,"Pass")&gt;0,"Pass","")))) — 셀에는 앞에 = 를 붙여 사용합니다. 아무것도 실행되지 않은 케이스는 빈칸입니다</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="46" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="66" t="inlineStr">
         <is>
           <t>병합</t>
         </is>
       </c>
-      <c r="C43" s="46" t="inlineStr">
+      <c r="C44" s="66" t="inlineStr">
         <is>
           <t>하지 않습니다 — 데이터 한 행씩 세웁니다. 같은 플랫폼에 단말이 여럿일 때 그 행의 단말 결과를 하나로 요약하는 자리입니다</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="31" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="51" t="inlineStr">
         <is>
           <t>5. TC ID 체계</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="47" t="inlineStr">
+    <row r="47">
+      <c r="B47" s="67" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C46" s="47" t="inlineStr">
+      <c r="C47" s="67" t="inlineStr">
         <is>
           <t>규칙</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="B47" s="46" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="66" t="inlineStr">
         <is>
           <t>형식</t>
         </is>
       </c>
-      <c r="C47" s="46" t="inlineStr">
+      <c r="C48" s="66" t="inlineStr">
         <is>
           <t>TC-{영역코드}-{번호 3자리} — 예: TC-ENT-001</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="46" t="inlineStr">
+    <row r="49">
+      <c r="B49" s="66" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="C48" s="46" t="inlineStr">
+      <c r="C49" s="66" t="inlineStr">
         <is>
           <t>영역 안에서만 증가합니다. 다른 영역에 케이스가 추가돼도 기존 ID가 흔들리지 않습니다</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="46" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="66" t="inlineStr">
         <is>
           <t>영역코드</t>
         </is>
       </c>
-      <c r="C49" s="46" t="inlineStr">
+      <c r="C50" s="66" t="inlineStr">
         <is>
           <t>기능 트리 1-Depth당 하나. 프로젝트별 매핑표는 아래 §5-1이며, 정의가 없는 프로젝트에서는 그 절이 나오지 않습니다</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="46" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="66" t="inlineStr">
         <is>
           <t>기재 위치</t>
         </is>
       </c>
-      <c r="C50" s="46" t="inlineStr">
+      <c r="C51" s="66" t="inlineStr">
         <is>
           <t>Note의 첫 토큰(케이스 메타의 맨 앞). 자동화 케이스명·추적 매트릭스·이슈 연결이 이 ID를 참조합니다. Comment는 설계 시점에 비어 있는 실행 기록 칸이므로 설계 데이터를 두지 않습니다</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="31" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="51" t="inlineStr">
         <is>
           <t>5-1. 영역코드 매핑</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="50" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="70" t="inlineStr">
         <is>
           <t>키는 기능 트리 1-Depth 영역명이며, 이슈 관리 시트 「레이블」 목록과 같은 값을 씁니다. 코드는 영문 표기의 앞 세 글자이고, 한 영역에 하나씩만 둡니다. 정본은 TC 설계 입력(tc-input json)의 area_codes입니다.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="47" t="inlineStr">
+    <row r="55">
+      <c r="B55" s="67" t="inlineStr">
         <is>
           <t>영역 (기능 트리 1-Depth)</t>
         </is>
       </c>
-      <c r="C54" s="47" t="inlineStr">
+      <c r="C55" s="67" t="inlineStr">
         <is>
           <t>코드</t>
         </is>
       </c>
-      <c r="D54" s="47" t="inlineStr">
+      <c r="D55" s="67" t="inlineStr">
         <is>
           <t>영문 표기</t>
         </is>
       </c>
-      <c r="E54" s="47" t="inlineStr">
+      <c r="E55" s="67" t="inlineStr">
         <is>
           <t>TC ID 예</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="46" t="inlineStr">
+    <row r="56">
+      <c r="B56" s="66" t="inlineStr">
         <is>
           <t>앱 진입/세션</t>
         </is>
       </c>
-      <c r="C55" s="46" t="inlineStr">
+      <c r="C56" s="66" t="inlineStr">
         <is>
           <t>ENT</t>
         </is>
       </c>
-      <c r="D55" s="46" t="inlineStr">
+      <c r="D56" s="66" t="inlineStr">
         <is>
           <t>Entry &amp; Session</t>
         </is>
       </c>
-      <c r="E55" s="46" t="inlineStr">
+      <c r="E56" s="66" t="inlineStr">
         <is>
           <t>TC-ENT-001</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="46" t="inlineStr">
+    <row r="57">
+      <c r="B57" s="66" t="inlineStr">
         <is>
           <t>계정/게이팅</t>
         </is>
       </c>
-      <c r="C56" s="46" t="inlineStr">
+      <c r="C57" s="66" t="inlineStr">
         <is>
           <t>GAT</t>
         </is>
       </c>
-      <c r="D56" s="46" t="inlineStr">
+      <c r="D57" s="66" t="inlineStr">
         <is>
           <t>Gating (account &amp; age)</t>
         </is>
       </c>
-      <c r="E56" s="46" t="inlineStr">
+      <c r="E57" s="66" t="inlineStr">
         <is>
           <t>TC-GAT-001</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="46" t="inlineStr">
+    <row r="58">
+      <c r="B58" s="66" t="inlineStr">
         <is>
           <t>탐색/발견</t>
         </is>
       </c>
-      <c r="C57" s="46" t="inlineStr">
+      <c r="C58" s="66" t="inlineStr">
         <is>
           <t>DSC</t>
         </is>
       </c>
-      <c r="D57" s="46" t="inlineStr">
+      <c r="D58" s="66" t="inlineStr">
         <is>
           <t>Discovery</t>
         </is>
       </c>
-      <c r="E57" s="46" t="inlineStr">
+      <c r="E58" s="66" t="inlineStr">
         <is>
           <t>TC-DSC-001</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="46" t="inlineStr">
+    <row r="59">
+      <c r="B59" s="66" t="inlineStr">
         <is>
           <t>유저 페르소나</t>
         </is>
       </c>
-      <c r="C58" s="46" t="inlineStr">
+      <c r="C59" s="66" t="inlineStr">
         <is>
           <t>PRF</t>
         </is>
       </c>
-      <c r="D58" s="46" t="inlineStr">
+      <c r="D59" s="66" t="inlineStr">
         <is>
           <t>Profile (dialogue persona)</t>
         </is>
       </c>
-      <c r="E58" s="46" t="inlineStr">
+      <c r="E59" s="66" t="inlineStr">
         <is>
           <t>TC-PRF-001</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="46" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="66" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
-      <c r="C59" s="46" t="inlineStr">
+      <c r="C60" s="66" t="inlineStr">
         <is>
           <t>CUR</t>
         </is>
       </c>
-      <c r="D59" s="46" t="inlineStr">
+      <c r="D60" s="66" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="E59" s="46" t="inlineStr">
+      <c r="E60" s="66" t="inlineStr">
         <is>
           <t>TC-CUR-001</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="46" t="inlineStr">
+    <row r="61">
+      <c r="B61" s="66" t="inlineStr">
         <is>
           <t>서사 시스템</t>
         </is>
       </c>
-      <c r="C60" s="46" t="inlineStr">
+      <c r="C61" s="66" t="inlineStr">
         <is>
           <t>NAR</t>
         </is>
       </c>
-      <c r="D60" s="46" t="inlineStr">
+      <c r="D61" s="66" t="inlineStr">
         <is>
           <t>Narrative</t>
         </is>
       </c>
-      <c r="E60" s="46" t="inlineStr">
+      <c r="E61" s="66" t="inlineStr">
         <is>
           <t>TC-NAR-001</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="46" t="inlineStr">
+    <row r="62">
+      <c r="B62" s="66" t="inlineStr">
         <is>
           <t>대화 세션</t>
         </is>
       </c>
-      <c r="C61" s="46" t="inlineStr">
+      <c r="C62" s="66" t="inlineStr">
         <is>
           <t>CHT</t>
         </is>
       </c>
-      <c r="D61" s="46" t="inlineStr">
+      <c r="D62" s="66" t="inlineStr">
         <is>
           <t>Chat session</t>
         </is>
       </c>
-      <c r="E61" s="46" t="inlineStr">
+      <c r="E62" s="66" t="inlineStr">
         <is>
           <t>TC-CHT-001</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" s="46" t="inlineStr">
+    <row r="63">
+      <c r="B63" s="66" t="inlineStr">
         <is>
           <t>세이브/로드</t>
         </is>
       </c>
-      <c r="C62" s="46" t="inlineStr">
+      <c r="C63" s="66" t="inlineStr">
         <is>
           <t>SAV</t>
         </is>
       </c>
-      <c r="D62" s="46" t="inlineStr">
+      <c r="D63" s="66" t="inlineStr">
         <is>
           <t>Save &amp; Load</t>
         </is>
       </c>
-      <c r="E62" s="46" t="inlineStr">
+      <c r="E63" s="66" t="inlineStr">
         <is>
           <t>TC-SAV-001</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="46" t="inlineStr">
+    <row r="64">
+      <c r="B64" s="66" t="inlineStr">
         <is>
           <t>메모리/컨텍스트</t>
         </is>
       </c>
-      <c r="C63" s="46" t="inlineStr">
+      <c r="C64" s="66" t="inlineStr">
         <is>
           <t>MEM</t>
         </is>
       </c>
-      <c r="D63" s="46" t="inlineStr">
+      <c r="D64" s="66" t="inlineStr">
         <is>
           <t>Memory &amp; Context</t>
         </is>
       </c>
-      <c r="E63" s="46" t="inlineStr">
+      <c r="E64" s="66" t="inlineStr">
         <is>
           <t>TC-MEM-001</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="46" t="inlineStr">
+    <row r="65">
+      <c r="B65" s="66" t="inlineStr">
         <is>
           <t>입력/출력 세이프티</t>
         </is>
       </c>
-      <c r="C64" s="46" t="inlineStr">
+      <c r="C65" s="66" t="inlineStr">
         <is>
           <t>SAF</t>
         </is>
       </c>
-      <c r="D64" s="46" t="inlineStr">
+      <c r="D65" s="66" t="inlineStr">
         <is>
           <t>Safety (input &amp; output)</t>
         </is>
       </c>
-      <c r="E64" s="46" t="inlineStr">
+      <c r="E65" s="66" t="inlineStr">
         <is>
           <t>TC-SAF-001</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" s="31" t="inlineStr">
+    <row r="67">
+      <c r="B67" s="51" t="inlineStr">
         <is>
           <t>6. 플랫폼 열 규칙</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" s="47" t="inlineStr">
+    <row r="68">
+      <c r="B68" s="67" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C67" s="47" t="inlineStr">
+      <c r="C68" s="67" t="inlineStr">
         <is>
           <t>규칙</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" s="46" t="inlineStr">
+    <row r="69">
+      <c r="B69" s="66" t="inlineStr">
         <is>
           <t>기본값</t>
         </is>
       </c>
-      <c r="C68" s="46" t="inlineStr">
+      <c r="C69" s="66" t="inlineStr">
         <is>
           <t>마스터는 Web / And / iOS 3열</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" s="46" t="inlineStr">
+    <row r="70">
+      <c r="B70" s="66" t="inlineStr">
         <is>
           <t>프로젝트 조정</t>
         </is>
       </c>
-      <c r="C69" s="46" t="inlineStr">
+      <c r="C70" s="66" t="inlineStr">
         <is>
           <t>TC 설계 시작 시 대상 플랫폼을 사용자에게 재확인하고, Test Case의 Total Result·Result 하위 열과 Summary의 플랫폼 열을 함께 조정합니다</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" s="31" t="inlineStr">
+    <row r="72">
+      <c r="B72" s="51" t="inlineStr">
         <is>
           <t>7. 입력 규칙</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" s="47" t="inlineStr">
+    <row r="73">
+      <c r="B73" s="67" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C72" s="47" t="inlineStr">
+      <c r="C73" s="67" t="inlineStr">
         <is>
           <t>규칙</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" s="46" t="inlineStr">
+    <row r="74">
+      <c r="B74" s="66" t="inlineStr">
         <is>
           <t>실행 채움 셀(노랑)</t>
         </is>
       </c>
-      <c r="C73" s="46" t="inlineStr">
+      <c r="C74" s="66" t="inlineStr">
         <is>
           <t>설계 시점에는 비어 있고 실행 단계에서 채워지는 칸 — 환경 블록·Result·Issue No.·Comment. 채우는 주체가 사람이든 자동화든 설계자는 건드리지 않습니다. 설계 데이터는 노란 칸에 두지 않습니다</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" s="46" t="inlineStr">
+    <row r="75">
+      <c r="B75" s="66" t="inlineStr">
         <is>
           <t>설계 셀</t>
         </is>
       </c>
-      <c r="C74" s="46" t="inlineStr">
+      <c r="C75" s="66" t="inlineStr">
         <is>
           <t>Depth·절차·기대결과는 실행 중 수정하지 않습니다</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="B75" s="46" t="inlineStr">
+    <row r="76">
+      <c r="B76" s="66" t="inlineStr">
         <is>
           <t>틀 고정</t>
         </is>
       </c>
-      <c r="C75" s="46" t="inlineStr">
+      <c r="C76" s="66" t="inlineStr">
         <is>
           <t>데이터 첫 행 위. 스크롤해도 2행 제목·헤더·환경 블록이 남으며, 그 구간은 회색(#BFBFBF)과 Total/Result 띠(#F9D7BE)로 데이터와 갈라 둡니다. A열과 1행은 값도 색도 두지 않습니다</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" s="46" t="inlineStr">
+    <row r="77">
+      <c r="B77" s="66" t="inlineStr">
         <is>
           <t>자동 필터</t>
         </is>
       </c>
-      <c r="C76" s="46" t="inlineStr">
+      <c r="C77" s="66" t="inlineStr">
         <is>
           <t>헤더 행에 걸어 둡니다. 실행 주체·검증유형·Priority처럼 케이스 단위 값으로 거르면 한 케이스의 행이 통째로 남거나 빠져 스텝 범위 병합이 깨지지 않습니다. Result 같은 행 단위 값으로 거르면 케이스 중간이 잘려 병합이 어색해집니다</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" s="46" t="inlineStr">
+    <row r="78">
+      <c r="B78" s="66" t="inlineStr">
         <is>
           <t>뎁스 채움 색</t>
         </is>
       </c>
-      <c r="C77" s="46" t="inlineStr">
+      <c r="C78" s="66" t="inlineStr">
         <is>
           <t>뎁스 열의 값 있는 셀만 텍스트별 고유색으로 채웁니다 — 같은 텍스트는 같은 색, 인접한 다른 텍스트와는 색상환에서 멀어지게 배정. 케이스명 칸과 빈칸은 흰 배경. 규칙 정본은 xlsx-design-guide.md §5</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" s="46" t="inlineStr">
+    <row r="79">
+      <c r="B79" s="66" t="inlineStr">
         <is>
           <t>기준 골격 버전</t>
         </is>
       </c>
-      <c r="C78" s="46" t="inlineStr">
+      <c r="C79" s="66" t="inlineStr">
         <is>
           <t>Summary C4에 생성 스크립트가 자동 기입합니다 — 형식 {프로젝트}-tree-v{X.Y}. TC 설계 입력(tc-input json)의 값을 그대로 쓰므로 사람이 옮겨 적지 않습니다</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="B80" s="31" t="inlineStr">
+    <row r="81">
+      <c r="B81" s="51" t="inlineStr">
         <is>
           <t>8. 컬럼 정의 (이슈 관리 시트)</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="B81" s="50" t="inlineStr">
+    <row r="82">
+      <c r="B82" s="70" t="inlineStr">
         <is>
           <t>이슈 기록의 정본은 test-case/{프로젝트}-issues.json입니다. TC 설계 원본과 파일을 나눈 이유는 크기가 아니라 생명주기입니다 — TC 세트는 확정되면 고정되지만 이슈는 실행하면서 계속 늘고 상태가 바뀌므로, 한 파일에 두면 이슈 갱신 때마다 설계 원본이 변경되어 확정 시점이 흐려집니다.</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="B82" s="47" t="inlineStr">
+    <row r="83">
+      <c r="B83" s="67" t="inlineStr">
         <is>
           <t>컬럼</t>
         </is>
       </c>
-      <c r="C82" s="47" t="inlineStr">
+      <c r="C83" s="67" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="D82" s="47" t="inlineStr">
+      <c r="D83" s="67" t="inlineStr">
         <is>
           <t>채우는 규칙</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" s="46" t="inlineStr">
+    <row r="84">
+      <c r="B84" s="66" t="inlineStr">
         <is>
           <t>프로젝트 ID</t>
         </is>
       </c>
-      <c r="C83" s="46" t="inlineStr">
+      <c r="C84" s="66" t="inlineStr">
         <is>
           <t>프로젝트 식별자</t>
         </is>
       </c>
-      <c r="D83" s="46" t="inlineStr">
+      <c r="D84" s="66" t="inlineStr">
         <is>
           <t>SUT명 기준. 목록 시트 참조</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" s="46" t="inlineStr">
+    <row r="85">
+      <c r="B85" s="66" t="inlineStr">
         <is>
           <t>Issue No.</t>
         </is>
       </c>
-      <c r="C84" s="46" t="inlineStr">
+      <c r="C85" s="66" t="inlineStr">
         <is>
           <t>발생한 이슈의 식별자</t>
         </is>
       </c>
-      <c r="D84" s="46" t="inlineStr">
+      <c r="D85" s="66" t="inlineStr">
         <is>
           <t>발생한 이슈를 등록하며 부여합니다 — {프로젝트}-{생성 번호순} (1 &gt; 2 &gt; 3 &gt; …). TC 수행 중 발생한 이슈라면 이 번호를 Test Case 시트의 Issue No.에 적어 잇습니다</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="B85" s="46" t="inlineStr">
+    <row r="86">
+      <c r="B86" s="66" t="inlineStr">
         <is>
           <t>이슈 상태</t>
         </is>
       </c>
-      <c r="C85" s="46" t="inlineStr">
+      <c r="C86" s="66" t="inlineStr">
         <is>
           <t>이슈의 현재 상태</t>
         </is>
       </c>
-      <c r="D85" s="46" t="inlineStr">
+      <c r="D86" s="66" t="inlineStr">
         <is>
           <t>Open: 열린 상태(재현됨) / In Progress: 담당자가 수정 진행 중 / Resolved: 해결됨 / Reopen: 해결된 이슈가 재현되어 다시 엶 / Closed: 재현되지 않아 닫음</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" s="46" t="inlineStr">
+    <row r="87">
+      <c r="B87" s="66" t="inlineStr">
         <is>
           <t>요약(Summary)</t>
         </is>
       </c>
-      <c r="C86" s="46" t="inlineStr">
+      <c r="C87" s="66" t="inlineStr">
         <is>
           <t>이슈 제목</t>
         </is>
       </c>
-      <c r="D86" s="46" t="inlineStr">
+      <c r="D87" s="66" t="inlineStr">
         <is>
           <t>재현 경로 요약 — 문단 구분은 "&gt;", 마지막은 무엇이 잘못됐는지 수동태로.
 ex) rules/ 폴더 이동 &gt; A.md 실행 시, 크래시 발생됨</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" s="46" t="inlineStr">
+    <row r="88">
+      <c r="B88" s="66" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="C87" s="46" t="inlineStr">
+      <c r="C88" s="66" t="inlineStr">
         <is>
           <t>재현 방법 상세</t>
         </is>
       </c>
-      <c r="D87" s="46" t="inlineStr">
+      <c r="D88" s="66" t="inlineStr">
         <is>
           <t>Pre-condition(사전 조건) / Reproduce Step(재현 스텝) / Actual Result(실제 결과, ~됨) / Expected Result(기대 결과, ~되어야 함) / QA Comment(참고) 순서로 작성</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" s="46" t="inlineStr">
+    <row r="89">
+      <c r="B89" s="66" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="C88" s="46" t="inlineStr">
+      <c r="C89" s="66" t="inlineStr">
         <is>
           <t>이슈 심각도</t>
         </is>
       </c>
-      <c r="D88" s="46" t="inlineStr">
+      <c r="D89" s="66" t="inlineStr">
         <is>
           <t>High: 크래시·진입 불가 등 치명 / Medium: 진입은 되나 기능 미동작 / Low: 문구·표기 오류</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="B89" s="46" t="inlineStr">
+    <row r="90">
+      <c r="B90" s="66" t="inlineStr">
         <is>
           <t>빈도</t>
         </is>
       </c>
-      <c r="C89" s="46" t="inlineStr">
+      <c r="C90" s="66" t="inlineStr">
         <is>
           <t>발생 빈도</t>
         </is>
       </c>
-      <c r="D89" s="46" t="inlineStr">
+      <c r="D90" s="66" t="inlineStr">
         <is>
           <t>Always: 항상 / Often: 종종(70% 이상) / Sometimes: 가끔(70% 미만) / Once: 1회만</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" s="46" t="inlineStr">
+    <row r="91">
+      <c r="B91" s="66" t="inlineStr">
         <is>
           <t>영향 받는 버전</t>
         </is>
       </c>
-      <c r="C90" s="46" t="inlineStr">
+      <c r="C91" s="66" t="inlineStr">
         <is>
           <t>이슈가 재현되는 빌드</t>
         </is>
       </c>
-      <c r="D90" s="46" t="inlineStr">
+      <c r="D91" s="66" t="inlineStr">
         <is>
           <t>{테스트환경}_{개발목표버전}_{스프린트}_{확인버전} 네 토막.
 테스트환경=어디서 확인했는가(PC웹) / 개발목표버전=무엇을 향해 개발 중인가(Ver1.0) / 스프린트=그 목표 버전의 주 목표(Dev, RT1=Release Train 1차) / 확인버전=그 시점의 RC 빌드(RC=Release Candidate).
@@ -5163,272 +7416,272 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="B91" s="46" t="inlineStr">
+    <row r="92">
+      <c r="B92" s="66" t="inlineStr">
         <is>
           <t>수정 버전</t>
         </is>
       </c>
-      <c r="C91" s="46" t="inlineStr">
+      <c r="C92" s="66" t="inlineStr">
         <is>
           <t>이슈가 수정된 버전</t>
         </is>
       </c>
-      <c r="D91" s="46" t="inlineStr">
+      <c r="D92" s="66" t="inlineStr">
         <is>
           <t>영향 받는 버전과 같은 목록을 사용합니다</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="B92" s="46" t="inlineStr">
+    <row r="93">
+      <c r="B93" s="66" t="inlineStr">
         <is>
           <t>해결책</t>
         </is>
       </c>
-      <c r="C92" s="46" t="inlineStr">
+      <c r="C93" s="66" t="inlineStr">
         <is>
           <t>수정 방향</t>
         </is>
       </c>
-      <c r="D92" s="46" t="inlineStr">
+      <c r="D93" s="66" t="inlineStr">
         <is>
           <t>Fixed: 코드 수정으로 대응 / Won't Do: 환경·기술 지원 불가로 미대응 / Won't Fix: 수정 필요하나 지금은 안 함 / Duplicate: 동일 건 존재 / Incomplete: 이슈 자체가 잘못됨 / Cannot Reproduce: 재현 불가 / Done: 기획·정책 결정으로 이슈 아님 확정 / Declined(QA Only): QA선에서 이슈로 보지 않음</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="B93" s="46" t="inlineStr">
+    <row r="94">
+      <c r="B94" s="66" t="inlineStr">
         <is>
           <t>환경</t>
         </is>
       </c>
-      <c r="C93" s="46" t="inlineStr">
+      <c r="C94" s="66" t="inlineStr">
         <is>
           <t>발생 디바이스</t>
         </is>
       </c>
-      <c r="D93" s="46" t="inlineStr">
+      <c r="D94" s="66" t="inlineStr">
         <is>
           <t>PC웹 / Android / iOS</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="B94" s="46" t="inlineStr">
+    <row r="95">
+      <c r="B95" s="66" t="inlineStr">
         <is>
           <t>레이블</t>
         </is>
       </c>
-      <c r="C94" s="46" t="inlineStr">
+      <c r="C95" s="66" t="inlineStr">
         <is>
           <t>발생 영역</t>
         </is>
       </c>
-      <c r="D94" s="46" t="inlineStr">
+      <c r="D95" s="66" t="inlineStr">
         <is>
           <t>기능 트리 1-Depth 영역명 — 목록 시트 참조. 트리 개정 시 목록만 갱신하고 기존 행 값은 소급 변경하지 않습니다</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="B95" s="46" t="inlineStr">
+    <row r="96">
+      <c r="B96" s="66" t="inlineStr">
         <is>
           <t>보고자</t>
         </is>
       </c>
-      <c r="C95" s="46" t="inlineStr">
+      <c r="C96" s="66" t="inlineStr">
         <is>
           <t>이슈 등록자</t>
         </is>
       </c>
-      <c r="D95" s="46" t="inlineStr">
+      <c r="D96" s="66" t="inlineStr">
         <is>
           <t>목록 참조</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" s="46" t="inlineStr">
+    <row r="97">
+      <c r="B97" s="66" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="C96" s="46" t="inlineStr">
+      <c r="C97" s="66" t="inlineStr">
         <is>
           <t>이슈 수정 담당자</t>
         </is>
       </c>
-      <c r="D96" s="46" t="inlineStr">
+      <c r="D97" s="66" t="inlineStr">
         <is>
           <t>목록 참조</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="B97" s="46" t="inlineStr">
+    <row r="98">
+      <c r="B98" s="66" t="inlineStr">
         <is>
           <t>관측자</t>
         </is>
       </c>
-      <c r="C97" s="46" t="inlineStr">
+      <c r="C98" s="66" t="inlineStr">
         <is>
           <t>함께 팔로우할 인원</t>
         </is>
       </c>
-      <c r="D97" s="46" t="inlineStr">
+      <c r="D98" s="66" t="inlineStr">
         <is>
           <t>드롭다운 없음 — 쉼표 구분 자유 입력(멀티 선택은 xlsx 표준 기능에 없음)</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="B98" s="46" t="inlineStr">
+    <row r="99">
+      <c r="B99" s="66" t="inlineStr">
         <is>
           <t>첨부파일</t>
         </is>
       </c>
-      <c r="C98" s="46" t="inlineStr">
+      <c r="C99" s="66" t="inlineStr">
         <is>
           <t>재현 증적</t>
         </is>
       </c>
-      <c r="D98" s="46" t="inlineStr">
+      <c r="D99" s="66" t="inlineStr">
         <is>
           <t>재현 영상·이미지의 경로 또는 링크</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="B99" s="46" t="inlineStr">
+    <row r="100">
+      <c r="B100" s="66" t="inlineStr">
         <is>
           <t>스프린트</t>
         </is>
       </c>
-      <c r="C99" s="46" t="inlineStr">
+      <c r="C100" s="66" t="inlineStr">
         <is>
           <t>QA 진행 단위</t>
         </is>
       </c>
-      <c r="D99" s="46" t="inlineStr">
+      <c r="D100" s="66" t="inlineStr">
         <is>
           <t>영향 받는 버전에서 확인버전(RC)을 뺀 앞 세 토막 — {테스트환경}_{개발목표버전}_{스프린트}. 스프린트 하나가 RC1·RC2·RC3에 걸치므로 스프린트는 사이클을, 버전은 그 안의 빌드를 가리킵니다. 발견 단계도 이 칸으로 갈립니다 — ex) PC웹_Ver1.0_Dev(개발 단계 자체 발견) / PC웹_Ver1.0_RT1(QA 사이클 검출). 목록 참조</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="B100" s="46" t="inlineStr">
+    <row r="101">
+      <c r="B101" s="66" t="inlineStr">
         <is>
           <t>이슈 등록일</t>
         </is>
       </c>
-      <c r="C100" s="46" t="inlineStr">
+      <c r="C101" s="66" t="inlineStr">
         <is>
           <t>최초 등록일</t>
         </is>
       </c>
-      <c r="D100" s="46" t="inlineStr">
+      <c r="D101" s="66" t="inlineStr">
         <is>
           <t>YYYY-MM-DD. 이후 변경하지 않습니다</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="B101" s="46" t="inlineStr">
+    <row r="102">
+      <c r="B102" s="66" t="inlineStr">
         <is>
           <t>이슈 최종 수정일자</t>
         </is>
       </c>
-      <c r="C101" s="46" t="inlineStr">
+      <c r="C102" s="66" t="inlineStr">
         <is>
           <t>내용 최종 수정일</t>
         </is>
       </c>
-      <c r="D101" s="46" t="inlineStr">
+      <c r="D102" s="66" t="inlineStr">
         <is>
           <t>YYYY-MM-DD. 요약·설명 등 내용이 바뀔 때 갱신</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="B102" s="46" t="inlineStr">
+    <row r="103">
+      <c r="B103" s="66" t="inlineStr">
         <is>
           <t>이슈 상태 최종 변경일자</t>
         </is>
       </c>
-      <c r="C102" s="46" t="inlineStr">
+      <c r="C103" s="66" t="inlineStr">
         <is>
           <t>상태 최종 변경일</t>
         </is>
       </c>
-      <c r="D102" s="46" t="inlineStr">
+      <c r="D103" s="66" t="inlineStr">
         <is>
           <t>YYYY-MM-DD. 이슈 상태가 바뀔 때 갱신</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="B104" s="31" t="inlineStr">
+    <row r="105">
+      <c r="B105" s="51" t="inlineStr">
         <is>
           <t>9. 목록 시트 규칙</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="B105" s="47" t="inlineStr">
+    <row r="106">
+      <c r="B106" s="67" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C105" s="47" t="inlineStr">
+      <c r="C106" s="67" t="inlineStr">
         <is>
           <t>규칙</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="B106" s="46" t="inlineStr">
+    <row r="107">
+      <c r="B107" s="66" t="inlineStr">
         <is>
           <t>지위</t>
         </is>
       </c>
-      <c r="C106" s="46" t="inlineStr">
+      <c r="C107" s="66" t="inlineStr">
         <is>
           <t>드롭다운 참조의 정본 — 전 시트의 데이터 검증이 이 시트를 참조합니다</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="B107" s="46" t="inlineStr">
+    <row r="108">
+      <c r="B108" s="66" t="inlineStr">
         <is>
           <t>노출</t>
         </is>
       </c>
-      <c r="C107" s="46" t="inlineStr">
+      <c r="C108" s="66" t="inlineStr">
         <is>
           <t>숨기지 않고 맨 뒤 배치 — 값 체계 자체가 전시물입니다</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="B108" s="46" t="inlineStr">
+    <row r="109">
+      <c r="B109" s="66" t="inlineStr">
         <is>
           <t>갱신</t>
         </is>
       </c>
-      <c r="C108" s="46" t="inlineStr">
+      <c r="C109" s="66" t="inlineStr">
         <is>
           <t>항목 추가는 행 추가로. 명칭 변경은 목록만 교체하고 기존 데이터 행은 소급 변경하지 않습니다(검증은 신규 입력에만 작동)</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="B109" s="46" t="inlineStr">
+    <row r="110">
+      <c r="B110" s="66" t="inlineStr">
         <is>
           <t>레이블 동기</t>
         </is>
       </c>
-      <c r="C109" s="46" t="inlineStr">
+      <c r="C110" s="66" t="inlineStr">
         <is>
           <t>기능 트리 개정 시 레이블 목록을 함께 갱신합니다(정본 수정 체크리스트 연동)</t>
         </is>

--- a/projects/qa-lab-miyonchat/test-case/qa-lab-miyonchat-tc-v1.0.xlsx
+++ b/projects/qa-lab-miyonchat/test-case/qa-lab-miyonchat-tc-v1.0.xlsx
@@ -28,7 +28,7 @@
     <definedName name="list_assignee">목록!$M$3:$M$3</definedName>
     <definedName name="list_sprint">목록!$N$3:$N$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Case'!$B$4:$S$300</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'이슈 관리 시트'!$B$2:$U$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'이슈 관리 시트'!$B$2:$U$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23698,7 +23698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:U3"/>
+  <dimension ref="B2:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -23924,8 +23924,204 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="B4" s="191" t="inlineStr">
+        <is>
+          <t>miyonchat</t>
+        </is>
+      </c>
+      <c r="C4" s="191" t="inlineStr">
+        <is>
+          <t>miyonchat-2</t>
+        </is>
+      </c>
+      <c r="D4" s="191" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="E4" s="192" t="inlineStr">
+        <is>
+          <t>세션 만료 상태에서 브라우저 새로고침 시, 만료가 풀리고 로그인 상태로 되살아남</t>
+        </is>
+      </c>
+      <c r="F4" s="192" t="inlineStr">
+        <is>
+          <t>Pre-condition: 계정 A로 로그인한 상태
+Reproduce Step: 디버그 콘솔 &gt; 상태 스위처 [세션 만료] &gt; [저장] &gt; 브라우저 새로고침(F5)
+Actual Result: 로그인 상태(active)로 복원되어 만료 안내가 사라지고 로그인 필요 화면에 그대로 진입됨
+Expected Result: 만료는 로그인이 풀린 상태이므로 복원 대상이 아니며(system-spec §1-3), 새로고침 후에도 미로그인으로 남아야 함
+QA Comment: 세션 지속(RC22)을 넣으면서 expireSession()이 메모리 상태만 만료로 바꾸고 브라우저 저장소의 세션은 그대로 두어, 다음 부팅의 복원이 그 저장분을 읽어 만료를 덮어씀. 실서비스라면 만료된 세션을 새로고침만으로 되살릴 수 있는 우회 경로가 됨. TC-GAT-011(만료 상태 로그인 필요 화면 직접 진입)을 자동화하다 검출</t>
+        </is>
+      </c>
+      <c r="G4" s="191" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H4" s="191" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="I4" s="191" t="inlineStr">
+        <is>
+          <t>PC웹_Ver1.0_Dev_RC22</t>
+        </is>
+      </c>
+      <c r="J4" s="191" t="inlineStr">
+        <is>
+          <t>PC웹_Ver1.0_Dev_RC23</t>
+        </is>
+      </c>
+      <c r="K4" s="191" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="L4" s="191" t="inlineStr">
+        <is>
+          <t>PC웹</t>
+        </is>
+      </c>
+      <c r="M4" s="191" t="inlineStr">
+        <is>
+          <t>계정/게이팅</t>
+        </is>
+      </c>
+      <c r="N4" s="191" t="inlineStr">
+        <is>
+          <t>정준호</t>
+        </is>
+      </c>
+      <c r="O4" s="191" t="inlineStr">
+        <is>
+          <t>Claude Opus 5</t>
+        </is>
+      </c>
+      <c r="P4" s="191" t="inlineStr"/>
+      <c r="Q4" s="191" t="inlineStr"/>
+      <c r="R4" s="191" t="inlineStr">
+        <is>
+          <t>PC웹_Ver1.0_Dev</t>
+        </is>
+      </c>
+      <c r="S4" s="191" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="T4" s="191" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U4" s="191" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="191" t="inlineStr">
+        <is>
+          <t>miyonchat</t>
+        </is>
+      </c>
+      <c r="C5" s="191" t="inlineStr">
+        <is>
+          <t>miyonchat-3</t>
+        </is>
+      </c>
+      <c r="D5" s="191" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="E5" s="192" t="inlineStr">
+        <is>
+          <t>세션 만료 상태에서 전송·저장·미션 수령이 그대로 수행됨 (차단이 안내 모달의 딤에만 의존)</t>
+        </is>
+      </c>
+      <c r="F5" s="192" t="inlineStr">
+        <is>
+          <t>Pre-condition: 계정 A로 로그인해 대화방에 진입한 상태
+Reproduce Step: 디버그 콘솔 &gt; 상태 스위처 [세션 만료] &gt; [저장] &gt; 대화방에서 전송 시도(자동화는 sendMessage 직접 호출) &gt; 잔액·메시지 확인
+Actual Result: 전송이 수행되어 캔디 10이 차감되고 메시지가 쌓임. 슬롯 저장과 데일리 미션 수령도 성공함
+Expected Result: 만료 상태에서는 전송·저장·수령이 모두 막혀야 함(system-spec §1-1 세션 만료 행)
+QA Comment: `canAct()`가 「만료 상태에서는 전송·저장·수령이 모두 막힙니다」라는 주석과 함께 정의되어 있으나 **어디에서도 호출되지 않는 죽은 코드**였음. 실제 차단은 만료 안내 모달이 화면을 덮는 것에만 의존하고 있어, 모달이 뜨지 않는 경로가 생기면 게이트가 통째로 사라짐. sendMessage·saveSlot·claimDaily·claimWelcome 네 곳에 게이트를 넣어 동작 자체에서 막도록 수정. TC-ENT-004(만료 상태 전송 차단)를 자동화하다 검출</t>
+        </is>
+      </c>
+      <c r="G5" s="191" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H5" s="191" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="I5" s="191" t="inlineStr">
+        <is>
+          <t>PC웹_Ver1.0_Dev_RC23</t>
+        </is>
+      </c>
+      <c r="J5" s="191" t="inlineStr">
+        <is>
+          <t>PC웹_Ver1.0_Dev_RC24</t>
+        </is>
+      </c>
+      <c r="K5" s="191" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="L5" s="191" t="inlineStr">
+        <is>
+          <t>PC웹</t>
+        </is>
+      </c>
+      <c r="M5" s="191" t="inlineStr">
+        <is>
+          <t>앱 진입/세션</t>
+        </is>
+      </c>
+      <c r="N5" s="191" t="inlineStr">
+        <is>
+          <t>정준호</t>
+        </is>
+      </c>
+      <c r="O5" s="191" t="inlineStr">
+        <is>
+          <t>Claude Opus 5</t>
+        </is>
+      </c>
+      <c r="P5" s="191" t="inlineStr"/>
+      <c r="Q5" s="191" t="inlineStr"/>
+      <c r="R5" s="191" t="inlineStr">
+        <is>
+          <t>PC웹_Ver1.0_Dev</t>
+        </is>
+      </c>
+      <c r="S5" s="191" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="T5" s="191" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="U5" s="191" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B2:U3"/>
+  <autoFilter ref="B2:U5"/>
   <conditionalFormatting sqref="D3:D200">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="5">
       <formula>"Open"</formula>

--- a/projects/qa-lab-miyonchat/test-case/qa-lab-miyonchat-tc-v1.0.xlsx
+++ b/projects/qa-lab-miyonchat/test-case/qa-lab-miyonchat-tc-v1.0.xlsx
@@ -27,7 +27,7 @@
     <definedName name="list_reporter">목록!$L$3:$L$3</definedName>
     <definedName name="list_assignee">목록!$M$3:$M$3</definedName>
     <definedName name="list_sprint">목록!$N$3:$N$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Case'!$B$4:$S$304</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Case'!$B$4:$S$306</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'이슈 관리 시트'!$B$2:$U$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -103,7 +103,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="75">
+  <fills count="76">
     <fill>
       <patternFill/>
     </fill>
@@ -142,12 +142,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0ECE5"/>
+        <fgColor rgb="00D0ECE4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DAD0EC"/>
+        <fgColor rgb="00D0D1EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -157,7 +157,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0EAEC"/>
+        <fgColor rgb="00D0EBEC"/>
       </patternFill>
     </fill>
     <fill>
@@ -167,22 +167,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0ECE2"/>
+        <fgColor rgb="00D0ECE1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCECD0"/>
+        <fgColor rgb="00DFECD0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECD0E4"/>
+        <fgColor rgb="00ECD0E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0ECE0"/>
+        <fgColor rgb="00D0ECDD"/>
       </patternFill>
     </fill>
     <fill>
@@ -192,12 +192,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECDBD0"/>
+        <fgColor rgb="00ECD1D0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0D9EC"/>
+        <fgColor rgb="00D0DAEC"/>
       </patternFill>
     </fill>
     <fill>
@@ -207,7 +207,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0D0EC"/>
+        <fgColor rgb="00E6D0EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -217,27 +217,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0E2EC"/>
+        <fgColor rgb="00D0E6EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECD0DB"/>
+        <fgColor rgb="00ECDFD0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5ECD0"/>
+        <fgColor rgb="00DAECD0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E3D0EC"/>
+        <fgColor rgb="00E1D0EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0E7EC"/>
+        <fgColor rgb="00D0E8EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -247,17 +247,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0ECDE"/>
+        <fgColor rgb="00D0ECDF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECD0EB"/>
+        <fgColor rgb="00EBD0EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5D0EC"/>
+        <fgColor rgb="00E4D0EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -267,22 +267,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0ECEC"/>
+        <fgColor rgb="00D0ECDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DAECD0"/>
+        <fgColor rgb="00DDECD0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D7D0EC"/>
+        <fgColor rgb="00DFD0EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECD0DD"/>
+        <fgColor rgb="00ECD0DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -297,27 +297,77 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0ECDB"/>
+        <fgColor rgb="00D0ECEB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECE2D0"/>
+        <fgColor rgb="00ECE1D0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DED0EC"/>
+        <fgColor rgb="00E4ECD0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DFECD0"/>
+        <fgColor rgb="00DDD0EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0ECE9"/>
+        <fgColor rgb="00D0ECE8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECD0DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D3D0EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0ECD1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1D0EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0ECE6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECD0EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DAD0EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0ECD6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8D0EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6D0EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -327,52 +377,82 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E1D0EC"/>
+        <fgColor rgb="00D0D8EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0ECD4"/>
+        <fgColor rgb="00E1ECD0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5D0EC"/>
+        <fgColor rgb="00ECD0E4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0ECE7"/>
+        <fgColor rgb="00ECD6D0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E3ECD0"/>
+        <fgColor rgb="00D0D6EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCD0EC"/>
+        <fgColor rgb="00D1ECD0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0ECD6"/>
+        <fgColor rgb="00D0D3EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAD0EC"/>
+        <fgColor rgb="00D0ECD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D3D0EC"/>
+        <fgColor rgb="00D0DDEC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D0E0EC"/>
+        <fgColor rgb="00D6ECD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0E4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECDAD0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0ECD8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8D0EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECD0E1"/>
       </patternFill>
     </fill>
     <fill>
@@ -382,87 +462,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECD0E6"/>
+        <fgColor rgb="00D0E1EC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECD6D0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D0DEEC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D0ECD0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D0D2EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D0ECD2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D0D4EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D0ECD9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D0D7EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8D0EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ECD1D0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E1ECD0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D0E5EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ECD0E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ECDFD0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D0DBEC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ECD0E9"/>
+        <fgColor rgb="00ECD0E8"/>
       </patternFill>
     </fill>
     <fill>
@@ -535,7 +540,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -719,19 +724,19 @@
     <xf numFmtId="0" fontId="4" fillId="53" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="54" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="54" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="55" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="55" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="56" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="57" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="57" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="58" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="58" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="59" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -752,10 +757,10 @@
     <xf numFmtId="0" fontId="4" fillId="64" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="65" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="65" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="66" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="66" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="67" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -767,24 +772,27 @@
     <xf numFmtId="0" fontId="4" fillId="69" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="70" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="70" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="71" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="71" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="72" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="73" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="73" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="74" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="74" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="75" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -794,11 +802,11 @@
     <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="74" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="74" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="75" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="75" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="74" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="75" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1326,7 +1334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:S304"/>
+  <dimension ref="B2:S306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1353,7 +1361,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>qa-lab-miyonchat-tree-v1.13</t>
+          <t>qa-lab-miyonchat-tree-v1.14</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
@@ -17613,12 +17621,12 @@
           <t>페르소나 준수</t>
         </is>
       </c>
-      <c r="E250" s="13" t="inlineStr"/>
-      <c r="F250" s="13" t="inlineStr">
+      <c r="E250" s="65" t="inlineStr">
         <is>
           <t>성인 계정으로 로그인하고 이름·호칭을 정한 프로필로 대화방에 진입한 상태</t>
         </is>
       </c>
+      <c r="F250" s="13" t="inlineStr"/>
       <c r="G250" s="14" t="n">
         <v>1</v>
       </c>
@@ -17685,7 +17693,11 @@
           <t>페르소나 준수</t>
         </is>
       </c>
-      <c r="E251" s="13" t="inlineStr"/>
+      <c r="E251" s="65" t="inlineStr">
+        <is>
+          <t>성인 계정으로 로그인하고 이름·호칭을 정한 프로필로 대화방에 진입한 상태</t>
+        </is>
+      </c>
       <c r="F251" s="18" t="n"/>
       <c r="G251" s="18" t="n"/>
       <c r="H251" s="18" t="n"/>
@@ -17733,43 +17745,43 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C252" s="65" t="inlineStr">
-        <is>
-          <t>채팅 탭</t>
-        </is>
-      </c>
-      <c r="D252" s="66" t="inlineStr">
-        <is>
-          <t>방 목록</t>
-        </is>
-      </c>
-      <c r="E252" s="13" t="inlineStr"/>
-      <c r="F252" s="13" t="inlineStr">
-        <is>
-          <t>성인 계정으로 로그인하고 대화방이 둘 이상 있는 상태</t>
-        </is>
-      </c>
+      <c r="C252" s="49" t="inlineStr">
+        <is>
+          <t>대화방</t>
+        </is>
+      </c>
+      <c r="D252" s="64" t="inlineStr">
+        <is>
+          <t>페르소나 준수</t>
+        </is>
+      </c>
+      <c r="E252" s="65" t="inlineStr">
+        <is>
+          <t>성인 계정으로 로그인하고 이름·호칭을 정한 프로필로 대화방에 진입한 상태</t>
+        </is>
+      </c>
+      <c r="F252" s="13" t="inlineStr"/>
       <c r="G252" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H252" s="13" t="inlineStr">
         <is>
-          <t>채팅 탭을 연다</t>
+          <t>열 턴을 전송해 응답을 모은다</t>
         </is>
       </c>
       <c r="I252" s="13" t="inlineStr">
         <is>
-          <t>방 목록이 노출된다</t>
+          <t>열 턴의 응답이 모두 표시된다</t>
         </is>
       </c>
       <c r="J252" s="10" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>사람 전용</t>
         </is>
       </c>
       <c r="K252" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L252" s="15">
@@ -17781,17 +17793,17 @@
       <c r="O252" s="17" t="n"/>
       <c r="P252" s="13" t="inlineStr">
         <is>
-          <t>캐릭터 페이지의 대화방 목록과 다른 화면입니다 — 여기는 캐릭터를 가리지 않고 전부 모읍니다</t>
+          <t>채점 기준의 정본은 spec/design/…-rubric.md입니다 — 페르소나 반영·관계 단계 말투 일치·맥락 일관성 3축을 0~2점으로 매기고 합계 5점 이상이 합격입니다. 자동화하지 않습니다(정의서 §0). 점수는 automation/result/rubric-scores.csv에 회차별로 남기고 리포트가 자동 결과와 한곳에서 집계합니다. 채점 대상은 mock 응답이라 계측이며 품질 지표로 서술하지 않습니다. 회차를 늘릴 때는 시드를 바꾸는데, 후보 선택이 「시드 % 후보 수」라 후보가 둘인 턴에서는 홀·짝 두 갈래만 나옵니다 — 홀수끼리 바꿔도 같은 응답이 나옵니다</t>
         </is>
       </c>
       <c r="Q252" s="10" t="inlineStr">
         <is>
-          <t>TC-CHT-010</t>
+          <t>TC-PRF-011</t>
         </is>
       </c>
       <c r="R252" s="10" t="inlineStr">
         <is>
-          <t>결정적</t>
+          <t>루브릭</t>
         </is>
       </c>
       <c r="S252" s="10" t="inlineStr">
@@ -17805,33 +17817,43 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C253" s="65" t="inlineStr">
-        <is>
-          <t>채팅 탭</t>
-        </is>
-      </c>
-      <c r="D253" s="66" t="inlineStr">
-        <is>
-          <t>방 목록</t>
-        </is>
-      </c>
-      <c r="E253" s="13" t="inlineStr"/>
-      <c r="F253" s="27" t="n"/>
-      <c r="G253" s="27" t="n"/>
-      <c r="H253" s="27" t="n"/>
+      <c r="C253" s="49" t="inlineStr">
+        <is>
+          <t>대화방</t>
+        </is>
+      </c>
+      <c r="D253" s="64" t="inlineStr">
+        <is>
+          <t>페르소나 준수</t>
+        </is>
+      </c>
+      <c r="E253" s="65" t="inlineStr">
+        <is>
+          <t>성인 계정으로 로그인하고 이름·호칭을 정한 프로필로 대화방에 진입한 상태</t>
+        </is>
+      </c>
+      <c r="F253" s="13" t="inlineStr"/>
+      <c r="G253" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H253" s="13" t="inlineStr">
+        <is>
+          <t>마지막 응답을 루브릭 3축으로 채점한다</t>
+        </is>
+      </c>
       <c r="I253" s="13" t="inlineStr">
         <is>
-          <t>방 수와 대화수 합계가 노출된다</t>
+          <t>3축 합계가 6점 만점에 5점 이상이 된다</t>
         </is>
       </c>
       <c r="J253" s="10" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>사람 전용</t>
         </is>
       </c>
       <c r="K253" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L253" s="15">
@@ -17841,15 +17863,15 @@
       <c r="M253" s="16" t="n"/>
       <c r="N253" s="17" t="n"/>
       <c r="O253" s="17" t="n"/>
-      <c r="P253" s="27" t="n"/>
+      <c r="P253" s="13" t="n"/>
       <c r="Q253" s="10" t="inlineStr">
         <is>
-          <t>TC-CHT-010</t>
+          <t>TC-PRF-011</t>
         </is>
       </c>
       <c r="R253" s="10" t="inlineStr">
         <is>
-          <t>결정적</t>
+          <t>루브릭</t>
         </is>
       </c>
       <c r="S253" s="10" t="inlineStr">
@@ -17863,23 +17885,33 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C254" s="65" t="inlineStr">
+      <c r="C254" s="66" t="inlineStr">
         <is>
           <t>채팅 탭</t>
         </is>
       </c>
-      <c r="D254" s="66" t="inlineStr">
+      <c r="D254" s="67" t="inlineStr">
         <is>
           <t>방 목록</t>
         </is>
       </c>
       <c r="E254" s="13" t="inlineStr"/>
-      <c r="F254" s="18" t="n"/>
-      <c r="G254" s="18" t="n"/>
-      <c r="H254" s="18" t="n"/>
+      <c r="F254" s="13" t="inlineStr">
+        <is>
+          <t>성인 계정으로 로그인하고 대화방이 둘 이상 있는 상태</t>
+        </is>
+      </c>
+      <c r="G254" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H254" s="13" t="inlineStr">
+        <is>
+          <t>채팅 탭을 연다</t>
+        </is>
+      </c>
       <c r="I254" s="13" t="inlineStr">
         <is>
-          <t>방마다 프로필·단계·턴이 노출된다</t>
+          <t>방 목록이 노출된다</t>
         </is>
       </c>
       <c r="J254" s="10" t="inlineStr">
@@ -17899,7 +17931,11 @@
       <c r="M254" s="16" t="n"/>
       <c r="N254" s="17" t="n"/>
       <c r="O254" s="17" t="n"/>
-      <c r="P254" s="18" t="n"/>
+      <c r="P254" s="13" t="inlineStr">
+        <is>
+          <t>캐릭터 페이지의 대화방 목록과 다른 화면입니다 — 여기는 캐릭터를 가리지 않고 전부 모읍니다</t>
+        </is>
+      </c>
       <c r="Q254" s="10" t="inlineStr">
         <is>
           <t>TC-CHT-010</t>
@@ -17921,33 +17957,23 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C255" s="65" t="inlineStr">
+      <c r="C255" s="66" t="inlineStr">
         <is>
           <t>채팅 탭</t>
         </is>
       </c>
-      <c r="D255" s="66" t="inlineStr">
+      <c r="D255" s="67" t="inlineStr">
         <is>
           <t>방 목록</t>
         </is>
       </c>
-      <c r="E255" s="67" t="inlineStr">
-        <is>
-          <t>성인 계정으로 로그인해 채팅 탭을 연 상태</t>
-        </is>
-      </c>
-      <c r="F255" s="13" t="inlineStr"/>
-      <c r="G255" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H255" s="13" t="inlineStr">
-        <is>
-          <t>방 항목을 선택한다</t>
-        </is>
-      </c>
+      <c r="E255" s="13" t="inlineStr"/>
+      <c r="F255" s="27" t="n"/>
+      <c r="G255" s="27" t="n"/>
+      <c r="H255" s="27" t="n"/>
       <c r="I255" s="13" t="inlineStr">
         <is>
-          <t>그 방으로 재진입된다</t>
+          <t>방 수와 대화수 합계가 노출된다</t>
         </is>
       </c>
       <c r="J255" s="10" t="inlineStr">
@@ -17957,7 +17983,7 @@
       </c>
       <c r="K255" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L255" s="15">
@@ -17967,14 +17993,10 @@
       <c r="M255" s="16" t="n"/>
       <c r="N255" s="17" t="n"/>
       <c r="O255" s="17" t="n"/>
-      <c r="P255" s="13" t="inlineStr">
-        <is>
-          <t>대화방에 오는 길 넷 중 하나입니다 — 각 경로의 진입 검증은 출발 화면에 남습니다</t>
-        </is>
-      </c>
+      <c r="P255" s="27" t="n"/>
       <c r="Q255" s="10" t="inlineStr">
         <is>
-          <t>TC-CHT-011</t>
+          <t>TC-CHT-010</t>
         </is>
       </c>
       <c r="R255" s="10" t="inlineStr">
@@ -17993,33 +18015,23 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C256" s="65" t="inlineStr">
+      <c r="C256" s="66" t="inlineStr">
         <is>
           <t>채팅 탭</t>
         </is>
       </c>
-      <c r="D256" s="66" t="inlineStr">
+      <c r="D256" s="67" t="inlineStr">
         <is>
           <t>방 목록</t>
         </is>
       </c>
-      <c r="E256" s="67" t="inlineStr">
-        <is>
-          <t>성인 계정으로 로그인해 채팅 탭을 연 상태</t>
-        </is>
-      </c>
-      <c r="F256" s="13" t="inlineStr"/>
-      <c r="G256" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H256" s="13" t="inlineStr">
-        <is>
-          <t>방 삭제를 선택한다</t>
-        </is>
-      </c>
+      <c r="E256" s="13" t="inlineStr"/>
+      <c r="F256" s="18" t="n"/>
+      <c r="G256" s="18" t="n"/>
+      <c r="H256" s="18" t="n"/>
       <c r="I256" s="13" t="inlineStr">
         <is>
-          <t>확인 모달 노출된다</t>
+          <t>방마다 프로필·단계·턴이 노출된다</t>
         </is>
       </c>
       <c r="J256" s="10" t="inlineStr">
@@ -18039,14 +18051,10 @@
       <c r="M256" s="16" t="n"/>
       <c r="N256" s="17" t="n"/>
       <c r="O256" s="17" t="n"/>
-      <c r="P256" s="13" t="inlineStr">
-        <is>
-          <t>되돌릴 수 없는 동작이라 한 번 묻습니다. 한도까지 찼을 때 슬롯을 비우는 수단이기도 합니다</t>
-        </is>
-      </c>
+      <c r="P256" s="18" t="n"/>
       <c r="Q256" s="10" t="inlineStr">
         <is>
-          <t>TC-CHT-012</t>
+          <t>TC-CHT-010</t>
         </is>
       </c>
       <c r="R256" s="10" t="inlineStr">
@@ -18065,33 +18073,33 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C257" s="65" t="inlineStr">
+      <c r="C257" s="66" t="inlineStr">
         <is>
           <t>채팅 탭</t>
         </is>
       </c>
-      <c r="D257" s="66" t="inlineStr">
+      <c r="D257" s="67" t="inlineStr">
         <is>
           <t>방 목록</t>
         </is>
       </c>
-      <c r="E257" s="67" t="inlineStr">
+      <c r="E257" s="68" t="inlineStr">
         <is>
           <t>성인 계정으로 로그인해 채팅 탭을 연 상태</t>
         </is>
       </c>
       <c r="F257" s="13" t="inlineStr"/>
       <c r="G257" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H257" s="13" t="inlineStr">
         <is>
-          <t>확인 모달에서 진행한다</t>
+          <t>방 항목을 선택한다</t>
         </is>
       </c>
       <c r="I257" s="13" t="inlineStr">
         <is>
-          <t>방이 목록에서 빠진다</t>
+          <t>그 방으로 재진입된다</t>
         </is>
       </c>
       <c r="J257" s="10" t="inlineStr">
@@ -18101,7 +18109,7 @@
       </c>
       <c r="K257" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L257" s="15">
@@ -18111,10 +18119,14 @@
       <c r="M257" s="16" t="n"/>
       <c r="N257" s="17" t="n"/>
       <c r="O257" s="17" t="n"/>
-      <c r="P257" s="13" t="n"/>
+      <c r="P257" s="13" t="inlineStr">
+        <is>
+          <t>대화방에 오는 길 넷 중 하나입니다 — 각 경로의 진입 검증은 출발 화면에 남습니다</t>
+        </is>
+      </c>
       <c r="Q257" s="10" t="inlineStr">
         <is>
-          <t>TC-CHT-012</t>
+          <t>TC-CHT-011</t>
         </is>
       </c>
       <c r="R257" s="10" t="inlineStr">
@@ -18133,27 +18145,33 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C258" s="65" t="inlineStr">
+      <c r="C258" s="66" t="inlineStr">
         <is>
           <t>채팅 탭</t>
         </is>
       </c>
-      <c r="D258" s="66" t="inlineStr">
+      <c r="D258" s="67" t="inlineStr">
         <is>
           <t>방 목록</t>
         </is>
       </c>
-      <c r="E258" s="67" t="inlineStr">
+      <c r="E258" s="68" t="inlineStr">
         <is>
           <t>성인 계정으로 로그인해 채팅 탭을 연 상태</t>
         </is>
       </c>
-      <c r="F258" s="13" t="n"/>
-      <c r="G258" s="18" t="n"/>
-      <c r="H258" s="18" t="n"/>
+      <c r="F258" s="13" t="inlineStr"/>
+      <c r="G258" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H258" s="13" t="inlineStr">
+        <is>
+          <t>방 삭제를 선택한다</t>
+        </is>
+      </c>
       <c r="I258" s="13" t="inlineStr">
         <is>
-          <t>방 수와 대화수 합계가 함께 줄어든다</t>
+          <t>확인 모달 노출된다</t>
         </is>
       </c>
       <c r="J258" s="10" t="inlineStr">
@@ -18173,7 +18191,11 @@
       <c r="M258" s="16" t="n"/>
       <c r="N258" s="17" t="n"/>
       <c r="O258" s="17" t="n"/>
-      <c r="P258" s="18" t="n"/>
+      <c r="P258" s="13" t="inlineStr">
+        <is>
+          <t>되돌릴 수 없는 동작이라 한 번 묻습니다. 한도까지 찼을 때 슬롯을 비우는 수단이기도 합니다</t>
+        </is>
+      </c>
       <c r="Q258" s="10" t="inlineStr">
         <is>
           <t>TC-CHT-012</t>
@@ -18195,33 +18217,33 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C259" s="65" t="inlineStr">
+      <c r="C259" s="66" t="inlineStr">
         <is>
           <t>채팅 탭</t>
         </is>
       </c>
-      <c r="D259" s="66" t="inlineStr">
+      <c r="D259" s="67" t="inlineStr">
         <is>
           <t>방 목록</t>
         </is>
       </c>
-      <c r="E259" s="13" t="inlineStr"/>
-      <c r="F259" s="13" t="inlineStr">
-        <is>
-          <t>성인 계정으로 로그인하고 대화방이 하나도 없는 상태</t>
-        </is>
-      </c>
+      <c r="E259" s="68" t="inlineStr">
+        <is>
+          <t>성인 계정으로 로그인해 채팅 탭을 연 상태</t>
+        </is>
+      </c>
+      <c r="F259" s="13" t="inlineStr"/>
       <c r="G259" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H259" s="13" t="inlineStr">
         <is>
-          <t>채팅 탭을 연다</t>
+          <t>확인 모달에서 진행한다</t>
         </is>
       </c>
       <c r="I259" s="13" t="inlineStr">
         <is>
-          <t>빈 상태 안내 노출된다</t>
+          <t>방이 목록에서 빠진다</t>
         </is>
       </c>
       <c r="J259" s="10" t="inlineStr">
@@ -18231,7 +18253,7 @@
       </c>
       <c r="K259" s="10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L259" s="15">
@@ -18241,14 +18263,10 @@
       <c r="M259" s="16" t="n"/>
       <c r="N259" s="17" t="n"/>
       <c r="O259" s="17" t="n"/>
-      <c r="P259" s="13" t="inlineStr">
-        <is>
-          <t>첫 사용 화면이라 목록만 비면 로딩 중인지 방이 없는지 구분되지 않습니다</t>
-        </is>
-      </c>
+      <c r="P259" s="13" t="n"/>
       <c r="Q259" s="10" t="inlineStr">
         <is>
-          <t>TC-CHT-013</t>
+          <t>TC-CHT-012</t>
         </is>
       </c>
       <c r="R259" s="10" t="inlineStr">
@@ -18267,33 +18285,27 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C260" s="68" t="inlineStr">
-        <is>
-          <t>MY 탭</t>
-        </is>
-      </c>
-      <c r="D260" s="69" t="inlineStr">
-        <is>
-          <t>프로필 요약</t>
-        </is>
-      </c>
-      <c r="E260" s="13" t="inlineStr"/>
-      <c r="F260" s="13" t="inlineStr">
-        <is>
-          <t>성인 계정으로 로그인하고 대화방이 둘 이상 있는 상태</t>
-        </is>
-      </c>
-      <c r="G260" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H260" s="13" t="inlineStr">
-        <is>
-          <t>MY 탭을 연다</t>
-        </is>
-      </c>
+      <c r="C260" s="66" t="inlineStr">
+        <is>
+          <t>채팅 탭</t>
+        </is>
+      </c>
+      <c r="D260" s="67" t="inlineStr">
+        <is>
+          <t>방 목록</t>
+        </is>
+      </c>
+      <c r="E260" s="68" t="inlineStr">
+        <is>
+          <t>성인 계정으로 로그인해 채팅 탭을 연 상태</t>
+        </is>
+      </c>
+      <c r="F260" s="13" t="n"/>
+      <c r="G260" s="18" t="n"/>
+      <c r="H260" s="18" t="n"/>
       <c r="I260" s="13" t="inlineStr">
         <is>
-          <t>대화수 합계가 방별 대화수의 합과 일치한다</t>
+          <t>방 수와 대화수 합계가 함께 줄어든다</t>
         </is>
       </c>
       <c r="J260" s="10" t="inlineStr">
@@ -18313,14 +18325,10 @@
       <c r="M260" s="16" t="n"/>
       <c r="N260" s="17" t="n"/>
       <c r="O260" s="17" t="n"/>
-      <c r="P260" s="13" t="inlineStr">
-        <is>
-          <t>합계가 어긋나면 방 쪽인지 합계 쪽인지 갈라야 하므로 방별 대화수와 함께 읽습니다</t>
-        </is>
-      </c>
+      <c r="P260" s="18" t="n"/>
       <c r="Q260" s="10" t="inlineStr">
         <is>
-          <t>TC-DSC-047</t>
+          <t>TC-CHT-012</t>
         </is>
       </c>
       <c r="R260" s="10" t="inlineStr">
@@ -18339,23 +18347,33 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C261" s="68" t="inlineStr">
-        <is>
-          <t>MY 탭</t>
-        </is>
-      </c>
-      <c r="D261" s="69" t="inlineStr">
-        <is>
-          <t>프로필 요약</t>
+      <c r="C261" s="66" t="inlineStr">
+        <is>
+          <t>채팅 탭</t>
+        </is>
+      </c>
+      <c r="D261" s="67" t="inlineStr">
+        <is>
+          <t>방 목록</t>
         </is>
       </c>
       <c r="E261" s="13" t="inlineStr"/>
-      <c r="F261" s="18" t="n"/>
-      <c r="G261" s="18" t="n"/>
-      <c r="H261" s="18" t="n"/>
+      <c r="F261" s="13" t="inlineStr">
+        <is>
+          <t>성인 계정으로 로그인하고 대화방이 하나도 없는 상태</t>
+        </is>
+      </c>
+      <c r="G261" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H261" s="13" t="inlineStr">
+        <is>
+          <t>채팅 탭을 연다</t>
+        </is>
+      </c>
       <c r="I261" s="13" t="inlineStr">
         <is>
-          <t>방 수가 함께 노출된다</t>
+          <t>빈 상태 안내 노출된다</t>
         </is>
       </c>
       <c r="J261" s="10" t="inlineStr">
@@ -18365,7 +18383,7 @@
       </c>
       <c r="K261" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L261" s="15">
@@ -18375,10 +18393,14 @@
       <c r="M261" s="16" t="n"/>
       <c r="N261" s="17" t="n"/>
       <c r="O261" s="17" t="n"/>
-      <c r="P261" s="18" t="n"/>
+      <c r="P261" s="13" t="inlineStr">
+        <is>
+          <t>첫 사용 화면이라 목록만 비면 로딩 중인지 방이 없는지 구분되지 않습니다</t>
+        </is>
+      </c>
       <c r="Q261" s="10" t="inlineStr">
         <is>
-          <t>TC-DSC-047</t>
+          <t>TC-CHT-013</t>
         </is>
       </c>
       <c r="R261" s="10" t="inlineStr">
@@ -18397,12 +18419,12 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C262" s="68" t="inlineStr">
+      <c r="C262" s="69" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
-      <c r="D262" s="69" t="inlineStr">
+      <c r="D262" s="70" t="inlineStr">
         <is>
           <t>프로필 요약</t>
         </is>
@@ -18410,7 +18432,7 @@
       <c r="E262" s="13" t="inlineStr"/>
       <c r="F262" s="13" t="inlineStr">
         <is>
-          <t>성인 계정으로 로그인해 MY 탭을 연 상태</t>
+          <t>성인 계정으로 로그인하고 대화방이 둘 이상 있는 상태</t>
         </is>
       </c>
       <c r="G262" s="14" t="n">
@@ -18418,12 +18440,12 @@
       </c>
       <c r="H262" s="13" t="inlineStr">
         <is>
-          <t>팔로워·팔로잉 영역을 확인한다</t>
+          <t>MY 탭을 연다</t>
         </is>
       </c>
       <c r="I262" s="13" t="inlineStr">
         <is>
-          <t>시트 값이 그대로 노출된다</t>
+          <t>대화수 합계가 방별 대화수의 합과 일치한다</t>
         </is>
       </c>
       <c r="J262" s="10" t="inlineStr">
@@ -18433,7 +18455,7 @@
       </c>
       <c r="K262" s="10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L262" s="15">
@@ -18445,12 +18467,12 @@
       <c r="O262" s="17" t="n"/>
       <c r="P262" s="13" t="inlineStr">
         <is>
-          <t>소셜은 제외 영역이라 로직 없이 표시만 합니다. 값은 디버그 콘솔의 계정 속성에서 옮깁니다</t>
+          <t>합계가 어긋나면 방 쪽인지 합계 쪽인지 갈라야 하므로 방별 대화수와 함께 읽습니다</t>
         </is>
       </c>
       <c r="Q262" s="10" t="inlineStr">
         <is>
-          <t>TC-DSC-048</t>
+          <t>TC-DSC-047</t>
         </is>
       </c>
       <c r="R262" s="10" t="inlineStr">
@@ -18469,12 +18491,12 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C263" s="68" t="inlineStr">
+      <c r="C263" s="69" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
-      <c r="D263" s="69" t="inlineStr">
+      <c r="D263" s="70" t="inlineStr">
         <is>
           <t>프로필 요약</t>
         </is>
@@ -18485,7 +18507,7 @@
       <c r="H263" s="18" t="n"/>
       <c r="I263" s="13" t="inlineStr">
         <is>
-          <t>팔로우 동작이 제공되지 않는다</t>
+          <t>방 수가 함께 노출된다</t>
         </is>
       </c>
       <c r="J263" s="10" t="inlineStr">
@@ -18495,7 +18517,7 @@
       </c>
       <c r="K263" s="10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L263" s="15">
@@ -18508,7 +18530,7 @@
       <c r="P263" s="18" t="n"/>
       <c r="Q263" s="10" t="inlineStr">
         <is>
-          <t>TC-DSC-048</t>
+          <t>TC-DSC-047</t>
         </is>
       </c>
       <c r="R263" s="10" t="inlineStr">
@@ -18527,20 +18549,20 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C264" s="68" t="inlineStr">
+      <c r="C264" s="69" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
       <c r="D264" s="70" t="inlineStr">
         <is>
-          <t>활동 목록</t>
+          <t>프로필 요약</t>
         </is>
       </c>
       <c r="E264" s="13" t="inlineStr"/>
       <c r="F264" s="13" t="inlineStr">
         <is>
-          <t>성인 계정으로 로그인하고 좋아요와 스크랩을 한 작품이 있는 상태</t>
+          <t>성인 계정으로 로그인해 MY 탭을 연 상태</t>
         </is>
       </c>
       <c r="G264" s="14" t="n">
@@ -18548,12 +18570,12 @@
       </c>
       <c r="H264" s="13" t="inlineStr">
         <is>
-          <t>MY 탭의 활동 목록을 확인한다</t>
+          <t>팔로워·팔로잉 영역을 확인한다</t>
         </is>
       </c>
       <c r="I264" s="13" t="inlineStr">
         <is>
-          <t>좋아요·스크랩한 작품이 목록에 노출된다</t>
+          <t>시트 값이 그대로 노출된다</t>
         </is>
       </c>
       <c r="J264" s="10" t="inlineStr">
@@ -18563,7 +18585,7 @@
       </c>
       <c r="K264" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L264" s="15">
@@ -18575,12 +18597,12 @@
       <c r="O264" s="17" t="n"/>
       <c r="P264" s="13" t="inlineStr">
         <is>
-          <t>캐릭터 페이지의 토글과 짝입니다 — 토글이 여기 반영되는지가 검증 대상입니다</t>
+          <t>소셜은 제외 영역이라 로직 없이 표시만 합니다. 값은 디버그 콘솔의 계정 속성에서 옮깁니다</t>
         </is>
       </c>
       <c r="Q264" s="10" t="inlineStr">
         <is>
-          <t>TC-DSC-049</t>
+          <t>TC-DSC-048</t>
         </is>
       </c>
       <c r="R264" s="10" t="inlineStr">
@@ -18599,29 +18621,23 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C265" s="68" t="inlineStr">
+      <c r="C265" s="69" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
       <c r="D265" s="70" t="inlineStr">
         <is>
-          <t>활동 목록</t>
+          <t>프로필 요약</t>
         </is>
       </c>
       <c r="E265" s="13" t="inlineStr"/>
-      <c r="F265" s="13" t="inlineStr"/>
-      <c r="G265" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="H265" s="13" t="inlineStr">
-        <is>
-          <t>항목을 선택한다</t>
-        </is>
-      </c>
+      <c r="F265" s="18" t="n"/>
+      <c r="G265" s="18" t="n"/>
+      <c r="H265" s="18" t="n"/>
       <c r="I265" s="13" t="inlineStr">
         <is>
-          <t>그 캐릭터 페이지로 이동된다</t>
+          <t>팔로우 동작이 제공되지 않는다</t>
         </is>
       </c>
       <c r="J265" s="10" t="inlineStr">
@@ -18631,7 +18647,7 @@
       </c>
       <c r="K265" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L265" s="15">
@@ -18641,10 +18657,10 @@
       <c r="M265" s="16" t="n"/>
       <c r="N265" s="17" t="n"/>
       <c r="O265" s="17" t="n"/>
-      <c r="P265" s="13" t="n"/>
+      <c r="P265" s="18" t="n"/>
       <c r="Q265" s="10" t="inlineStr">
         <is>
-          <t>TC-DSC-049</t>
+          <t>TC-DSC-048</t>
         </is>
       </c>
       <c r="R265" s="10" t="inlineStr">
@@ -18663,12 +18679,12 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C266" s="68" t="inlineStr">
+      <c r="C266" s="69" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
-      <c r="D266" s="70" t="inlineStr">
+      <c r="D266" s="71" t="inlineStr">
         <is>
           <t>활동 목록</t>
         </is>
@@ -18676,7 +18692,7 @@
       <c r="E266" s="13" t="inlineStr"/>
       <c r="F266" s="13" t="inlineStr">
         <is>
-          <t>성인 계정으로 로그인하고 좋아요·스크랩이 없는 상태</t>
+          <t>성인 계정으로 로그인하고 좋아요와 스크랩을 한 작품이 있는 상태</t>
         </is>
       </c>
       <c r="G266" s="14" t="n">
@@ -18689,7 +18705,7 @@
       </c>
       <c r="I266" s="13" t="inlineStr">
         <is>
-          <t>빈 상태 안내 노출된다</t>
+          <t>좋아요·스크랩한 작품이 목록에 노출된다</t>
         </is>
       </c>
       <c r="J266" s="10" t="inlineStr">
@@ -18699,7 +18715,7 @@
       </c>
       <c r="K266" s="10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L266" s="15">
@@ -18711,12 +18727,12 @@
       <c r="O266" s="17" t="n"/>
       <c r="P266" s="13" t="inlineStr">
         <is>
-          <t>좋아요와 스크랩이 각자 목록을 가지므로 둘 다 빈 상태를 확인합니다</t>
+          <t>캐릭터 페이지의 토글과 짝입니다 — 토글이 여기 반영되는지가 검증 대상입니다</t>
         </is>
       </c>
       <c r="Q266" s="10" t="inlineStr">
         <is>
-          <t>TC-DSC-050</t>
+          <t>TC-DSC-049</t>
         </is>
       </c>
       <c r="R266" s="10" t="inlineStr">
@@ -18735,33 +18751,29 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C267" s="68" t="inlineStr">
+      <c r="C267" s="69" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
       <c r="D267" s="71" t="inlineStr">
         <is>
-          <t>게이팅 상태</t>
+          <t>활동 목록</t>
         </is>
       </c>
       <c r="E267" s="13" t="inlineStr"/>
-      <c r="F267" s="13" t="inlineStr">
-        <is>
-          <t>성인 계정으로 로그인해 MY 탭을 연 상태</t>
-        </is>
-      </c>
+      <c r="F267" s="13" t="inlineStr"/>
       <c r="G267" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H267" s="13" t="inlineStr">
         <is>
-          <t>게이팅 상태 영역을 확인한다</t>
+          <t>항목을 선택한다</t>
         </is>
       </c>
       <c r="I267" s="13" t="inlineStr">
         <is>
-          <t>현재 게이팅 상태가 노출된다</t>
+          <t>그 캐릭터 페이지로 이동된다</t>
         </is>
       </c>
       <c r="J267" s="10" t="inlineStr">
@@ -18781,14 +18793,10 @@
       <c r="M267" s="16" t="n"/>
       <c r="N267" s="17" t="n"/>
       <c r="O267" s="17" t="n"/>
-      <c r="P267" s="13" t="inlineStr">
-        <is>
-          <t>언세이프가 왜 가려졌는지 판단하려면 지금 어느 상태인지 화면에서 읽혀야 합니다</t>
-        </is>
-      </c>
+      <c r="P267" s="13" t="n"/>
       <c r="Q267" s="10" t="inlineStr">
         <is>
-          <t>TC-GAT-017</t>
+          <t>TC-DSC-049</t>
         </is>
       </c>
       <c r="R267" s="10" t="inlineStr">
@@ -18807,20 +18815,20 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C268" s="68" t="inlineStr">
+      <c r="C268" s="69" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
-      <c r="D268" s="72" t="inlineStr">
-        <is>
-          <t>세이프티 필터</t>
+      <c r="D268" s="71" t="inlineStr">
+        <is>
+          <t>활동 목록</t>
         </is>
       </c>
       <c r="E268" s="13" t="inlineStr"/>
       <c r="F268" s="13" t="inlineStr">
         <is>
-          <t>성인 계정으로 로그인해 MY 탭을 연 상태</t>
+          <t>성인 계정으로 로그인하고 좋아요·스크랩이 없는 상태</t>
         </is>
       </c>
       <c r="G268" s="14" t="n">
@@ -18828,12 +18836,12 @@
       </c>
       <c r="H268" s="13" t="inlineStr">
         <is>
-          <t>세이프티 필터를 켠다</t>
+          <t>MY 탭의 활동 목록을 확인한다</t>
         </is>
       </c>
       <c r="I268" s="13" t="inlineStr">
         <is>
-          <t>켜짐으로 표시된다</t>
+          <t>빈 상태 안내 노출된다</t>
         </is>
       </c>
       <c r="J268" s="10" t="inlineStr">
@@ -18843,7 +18851,7 @@
       </c>
       <c r="K268" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L268" s="15">
@@ -18855,17 +18863,17 @@
       <c r="O268" s="17" t="n"/>
       <c r="P268" s="13" t="inlineStr">
         <is>
-          <t>필터는 숨기고 게이팅은 가린 채 남기는 것이라 층이 다릅니다. 토글을 누르는 MY 탭 소속이며 확인은 홈에서 합니다</t>
+          <t>좋아요와 스크랩이 각자 목록을 가지므로 둘 다 빈 상태를 확인합니다</t>
         </is>
       </c>
       <c r="Q268" s="10" t="inlineStr">
         <is>
-          <t>TC-GAT-018</t>
+          <t>TC-DSC-050</t>
         </is>
       </c>
       <c r="R268" s="10" t="inlineStr">
         <is>
-          <t>금칙</t>
+          <t>결정적</t>
         </is>
       </c>
       <c r="S268" s="10" t="inlineStr">
@@ -18879,29 +18887,33 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C269" s="68" t="inlineStr">
+      <c r="C269" s="69" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
       <c r="D269" s="72" t="inlineStr">
         <is>
-          <t>세이프티 필터</t>
+          <t>게이팅 상태</t>
         </is>
       </c>
       <c r="E269" s="13" t="inlineStr"/>
-      <c r="F269" s="13" t="inlineStr"/>
+      <c r="F269" s="13" t="inlineStr">
+        <is>
+          <t>성인 계정으로 로그인해 MY 탭을 연 상태</t>
+        </is>
+      </c>
       <c r="G269" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H269" s="13" t="inlineStr">
         <is>
-          <t>홈 탭으로 이동한다</t>
+          <t>게이팅 상태 영역을 확인한다</t>
         </is>
       </c>
       <c r="I269" s="13" t="inlineStr">
         <is>
-          <t>언세이프 작품이 홈 목록에서 빠진다</t>
+          <t>현재 게이팅 상태가 노출된다</t>
         </is>
       </c>
       <c r="J269" s="10" t="inlineStr">
@@ -18921,15 +18933,19 @@
       <c r="M269" s="16" t="n"/>
       <c r="N269" s="17" t="n"/>
       <c r="O269" s="17" t="n"/>
-      <c r="P269" s="13" t="n"/>
+      <c r="P269" s="13" t="inlineStr">
+        <is>
+          <t>언세이프가 왜 가려졌는지 판단하려면 지금 어느 상태인지 화면에서 읽혀야 합니다</t>
+        </is>
+      </c>
       <c r="Q269" s="10" t="inlineStr">
         <is>
-          <t>TC-GAT-018</t>
+          <t>TC-GAT-017</t>
         </is>
       </c>
       <c r="R269" s="10" t="inlineStr">
         <is>
-          <t>금칙</t>
+          <t>결정적</t>
         </is>
       </c>
       <c r="S269" s="10" t="inlineStr">
@@ -18943,12 +18959,12 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C270" s="68" t="inlineStr">
+      <c r="C270" s="69" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
-      <c r="D270" s="72" t="inlineStr">
+      <c r="D270" s="73" t="inlineStr">
         <is>
           <t>세이프티 필터</t>
         </is>
@@ -18956,7 +18972,7 @@
       <c r="E270" s="13" t="inlineStr"/>
       <c r="F270" s="13" t="inlineStr">
         <is>
-          <t>성인 인증을 하지 않은 계정으로 로그인한 상태</t>
+          <t>성인 계정으로 로그인해 MY 탭을 연 상태</t>
         </is>
       </c>
       <c r="G270" s="14" t="n">
@@ -18964,12 +18980,12 @@
       </c>
       <c r="H270" s="13" t="inlineStr">
         <is>
-          <t>MY 탭의 세이프티 필터 영역을 확인한다</t>
+          <t>세이프티 필터를 켠다</t>
         </is>
       </c>
       <c r="I270" s="13" t="inlineStr">
         <is>
-          <t>토글이 노출되지 않는다</t>
+          <t>켜짐으로 표시된다</t>
         </is>
       </c>
       <c r="J270" s="10" t="inlineStr">
@@ -18991,12 +19007,12 @@
       <c r="O270" s="17" t="n"/>
       <c r="P270" s="13" t="inlineStr">
         <is>
-          <t>성인 인증 계정에만 노출되는 것이 스펙입니다 — 미인증에게 보이면 결함입니다</t>
+          <t>필터는 숨기고 게이팅은 가린 채 남기는 것이라 층이 다릅니다. 토글을 누르는 MY 탭 소속이며 확인은 홈에서 합니다</t>
         </is>
       </c>
       <c r="Q270" s="10" t="inlineStr">
         <is>
-          <t>TC-GAT-019</t>
+          <t>TC-GAT-018</t>
         </is>
       </c>
       <c r="R270" s="10" t="inlineStr">
@@ -19006,7 +19022,7 @@
       </c>
       <c r="S270" s="10" t="inlineStr">
         <is>
-          <t>본인인증 미진행</t>
+          <t>성인 인증</t>
         </is>
       </c>
     </row>
@@ -19015,23 +19031,29 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C271" s="68" t="inlineStr">
+      <c r="C271" s="69" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
-      <c r="D271" s="72" t="inlineStr">
+      <c r="D271" s="73" t="inlineStr">
         <is>
           <t>세이프티 필터</t>
         </is>
       </c>
       <c r="E271" s="13" t="inlineStr"/>
-      <c r="F271" s="18" t="n"/>
-      <c r="G271" s="18" t="n"/>
-      <c r="H271" s="18" t="n"/>
+      <c r="F271" s="13" t="inlineStr"/>
+      <c r="G271" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H271" s="13" t="inlineStr">
+        <is>
+          <t>홈 탭으로 이동한다</t>
+        </is>
+      </c>
       <c r="I271" s="13" t="inlineStr">
         <is>
-          <t>미노출 안내 노출된다</t>
+          <t>언세이프 작품이 홈 목록에서 빠진다</t>
         </is>
       </c>
       <c r="J271" s="10" t="inlineStr">
@@ -19051,10 +19073,10 @@
       <c r="M271" s="16" t="n"/>
       <c r="N271" s="17" t="n"/>
       <c r="O271" s="17" t="n"/>
-      <c r="P271" s="18" t="n"/>
+      <c r="P271" s="13" t="n"/>
       <c r="Q271" s="10" t="inlineStr">
         <is>
-          <t>TC-GAT-019</t>
+          <t>TC-GAT-018</t>
         </is>
       </c>
       <c r="R271" s="10" t="inlineStr">
@@ -19064,7 +19086,7 @@
       </c>
       <c r="S271" s="10" t="inlineStr">
         <is>
-          <t>본인인증 미진행</t>
+          <t>성인 인증</t>
         </is>
       </c>
     </row>
@@ -19073,12 +19095,12 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C272" s="68" t="inlineStr">
+      <c r="C272" s="69" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
-      <c r="D272" s="72" t="inlineStr">
+      <c r="D272" s="73" t="inlineStr">
         <is>
           <t>세이프티 필터</t>
         </is>
@@ -19086,7 +19108,7 @@
       <c r="E272" s="13" t="inlineStr"/>
       <c r="F272" s="13" t="inlineStr">
         <is>
-          <t>미성년 계정으로 로그인해 MY 탭을 연 상태</t>
+          <t>성인 인증을 하지 않은 계정으로 로그인한 상태</t>
         </is>
       </c>
       <c r="G272" s="14" t="n">
@@ -19121,12 +19143,12 @@
       <c r="O272" s="17" t="n"/>
       <c r="P272" s="13" t="inlineStr">
         <is>
-          <t>미성년은 언세이프가 원천 차단이라 필터를 켤 이유 자체가 없습니다</t>
+          <t>성인 인증 계정에만 노출되는 것이 스펙입니다 — 미인증에게 보이면 결함입니다</t>
         </is>
       </c>
       <c r="Q272" s="10" t="inlineStr">
         <is>
-          <t>TC-GAT-020</t>
+          <t>TC-GAT-019</t>
         </is>
       </c>
       <c r="R272" s="10" t="inlineStr">
@@ -19136,7 +19158,7 @@
       </c>
       <c r="S272" s="10" t="inlineStr">
         <is>
-          <t>미성년</t>
+          <t>본인인증 미진행</t>
         </is>
       </c>
     </row>
@@ -19145,12 +19167,12 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C273" s="68" t="inlineStr">
+      <c r="C273" s="69" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
-      <c r="D273" s="72" t="inlineStr">
+      <c r="D273" s="73" t="inlineStr">
         <is>
           <t>세이프티 필터</t>
         </is>
@@ -19184,7 +19206,7 @@
       <c r="P273" s="18" t="n"/>
       <c r="Q273" s="10" t="inlineStr">
         <is>
-          <t>TC-GAT-020</t>
+          <t>TC-GAT-019</t>
         </is>
       </c>
       <c r="R273" s="10" t="inlineStr">
@@ -19194,7 +19216,7 @@
       </c>
       <c r="S273" s="10" t="inlineStr">
         <is>
-          <t>미성년</t>
+          <t>본인인증 미진행</t>
         </is>
       </c>
     </row>
@@ -19203,20 +19225,20 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C274" s="68" t="inlineStr">
+      <c r="C274" s="69" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
       <c r="D274" s="73" t="inlineStr">
         <is>
-          <t>로그아웃</t>
+          <t>세이프티 필터</t>
         </is>
       </c>
       <c r="E274" s="13" t="inlineStr"/>
       <c r="F274" s="13" t="inlineStr">
         <is>
-          <t>성인 계정으로 로그인해 MY 탭을 연 상태</t>
+          <t>미성년 계정으로 로그인해 MY 탭을 연 상태</t>
         </is>
       </c>
       <c r="G274" s="14" t="n">
@@ -19224,12 +19246,12 @@
       </c>
       <c r="H274" s="13" t="inlineStr">
         <is>
-          <t>로그아웃을 선택한다</t>
+          <t>MY 탭의 세이프티 필터 영역을 확인한다</t>
         </is>
       </c>
       <c r="I274" s="13" t="inlineStr">
         <is>
-          <t>미로그인 상태의 홈 화면으로 복귀된다</t>
+          <t>토글이 노출되지 않는다</t>
         </is>
       </c>
       <c r="J274" s="10" t="inlineStr">
@@ -19251,22 +19273,22 @@
       <c r="O274" s="17" t="n"/>
       <c r="P274" s="13" t="inlineStr">
         <is>
-          <t>로그인 화면이 아니라 홈으로 갑니다 — 로그인 화면은 URL 직접 진입으로 막혔을 때만 뜹니다</t>
+          <t>미성년은 언세이프가 원천 차단이라 필터를 켤 이유 자체가 없습니다</t>
         </is>
       </c>
       <c r="Q274" s="10" t="inlineStr">
         <is>
-          <t>TC-ENT-008</t>
+          <t>TC-GAT-020</t>
         </is>
       </c>
       <c r="R274" s="10" t="inlineStr">
         <is>
-          <t>결정적</t>
+          <t>금칙</t>
         </is>
       </c>
       <c r="S274" s="10" t="inlineStr">
         <is>
-          <t>성인 인증</t>
+          <t>미성년</t>
         </is>
       </c>
     </row>
@@ -19275,14 +19297,14 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C275" s="68" t="inlineStr">
+      <c r="C275" s="69" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
       <c r="D275" s="73" t="inlineStr">
         <is>
-          <t>로그아웃</t>
+          <t>세이프티 필터</t>
         </is>
       </c>
       <c r="E275" s="13" t="inlineStr"/>
@@ -19291,7 +19313,7 @@
       <c r="H275" s="18" t="n"/>
       <c r="I275" s="13" t="inlineStr">
         <is>
-          <t>잔액 대신 로그인 버튼이 노출된다</t>
+          <t>미노출 안내 노출된다</t>
         </is>
       </c>
       <c r="J275" s="10" t="inlineStr">
@@ -19314,17 +19336,17 @@
       <c r="P275" s="18" t="n"/>
       <c r="Q275" s="10" t="inlineStr">
         <is>
-          <t>TC-ENT-008</t>
+          <t>TC-GAT-020</t>
         </is>
       </c>
       <c r="R275" s="10" t="inlineStr">
         <is>
-          <t>결정적</t>
+          <t>금칙</t>
         </is>
       </c>
       <c r="S275" s="10" t="inlineStr">
         <is>
-          <t>성인 인증</t>
+          <t>미성년</t>
         </is>
       </c>
     </row>
@@ -19333,12 +19355,12 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C276" s="68" t="inlineStr">
+      <c r="C276" s="69" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
-      <c r="D276" s="73" t="inlineStr">
+      <c r="D276" s="74" t="inlineStr">
         <is>
           <t>로그아웃</t>
         </is>
@@ -19346,7 +19368,7 @@
       <c r="E276" s="13" t="inlineStr"/>
       <c r="F276" s="13" t="inlineStr">
         <is>
-          <t>성인 계정으로 로그인해 대화·세이브·재화를 남긴 상태</t>
+          <t>성인 계정으로 로그인해 MY 탭을 연 상태</t>
         </is>
       </c>
       <c r="G276" s="14" t="n">
@@ -19354,22 +19376,22 @@
       </c>
       <c r="H276" s="13" t="inlineStr">
         <is>
-          <t>로그아웃한다</t>
+          <t>로그아웃을 선택한다</t>
         </is>
       </c>
       <c r="I276" s="13" t="inlineStr">
         <is>
-          <t>미로그인 홈으로 복귀된다</t>
+          <t>미로그인 상태의 홈 화면으로 복귀된다</t>
         </is>
       </c>
       <c r="J276" s="10" t="inlineStr">
         <is>
-          <t>자동화 전용</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="K276" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L276" s="15">
@@ -19381,17 +19403,17 @@
       <c r="O276" s="17" t="n"/>
       <c r="P276" s="13" t="inlineStr">
         <is>
-          <t>저장소 잔존은 화면만 봐서는 판정할 수 없어 상태 훅으로 확인합니다. 세션 지속(§1-3)이 계정 스코프를 저장하므로, 로그아웃이 그 저장분까지 지우는지가 이 케이스의 핵심입니다</t>
+          <t>로그인 화면이 아니라 홈으로 갑니다 — 로그인 화면은 URL 직접 진입으로 막혔을 때만 뜹니다</t>
         </is>
       </c>
       <c r="Q276" s="10" t="inlineStr">
         <is>
-          <t>TC-ENT-009</t>
+          <t>TC-ENT-008</t>
         </is>
       </c>
       <c r="R276" s="10" t="inlineStr">
         <is>
-          <t>금칙</t>
+          <t>결정적</t>
         </is>
       </c>
       <c r="S276" s="10" t="inlineStr">
@@ -19405,39 +19427,33 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C277" s="68" t="inlineStr">
+      <c r="C277" s="69" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
-      <c r="D277" s="73" t="inlineStr">
+      <c r="D277" s="74" t="inlineStr">
         <is>
           <t>로그아웃</t>
         </is>
       </c>
       <c r="E277" s="13" t="inlineStr"/>
-      <c r="F277" s="13" t="inlineStr"/>
-      <c r="G277" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="H277" s="13" t="inlineStr">
-        <is>
-          <t>화면과 저장소를 확인한다</t>
-        </is>
-      </c>
+      <c r="F277" s="18" t="n"/>
+      <c r="G277" s="18" t="n"/>
+      <c r="H277" s="18" t="n"/>
       <c r="I277" s="13" t="inlineStr">
         <is>
-          <t>앞 계정의 대화·세이브·재화가 화면에 남지 않는다</t>
+          <t>잔액 대신 로그인 버튼이 노출된다</t>
         </is>
       </c>
       <c r="J277" s="10" t="inlineStr">
         <is>
-          <t>자동화 전용</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="K277" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L277" s="15">
@@ -19447,15 +19463,15 @@
       <c r="M277" s="16" t="n"/>
       <c r="N277" s="17" t="n"/>
       <c r="O277" s="17" t="n"/>
-      <c r="P277" s="13" t="n"/>
+      <c r="P277" s="18" t="n"/>
       <c r="Q277" s="10" t="inlineStr">
         <is>
-          <t>TC-ENT-009</t>
+          <t>TC-ENT-008</t>
         </is>
       </c>
       <c r="R277" s="10" t="inlineStr">
         <is>
-          <t>금칙</t>
+          <t>결정적</t>
         </is>
       </c>
       <c r="S277" s="10" t="inlineStr">
@@ -19469,23 +19485,33 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C278" s="68" t="inlineStr">
+      <c r="C278" s="69" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
-      <c r="D278" s="73" t="inlineStr">
+      <c r="D278" s="74" t="inlineStr">
         <is>
           <t>로그아웃</t>
         </is>
       </c>
       <c r="E278" s="13" t="inlineStr"/>
-      <c r="F278" s="13" t="n"/>
-      <c r="G278" s="18" t="n"/>
-      <c r="H278" s="18" t="n"/>
+      <c r="F278" s="13" t="inlineStr">
+        <is>
+          <t>성인 계정으로 로그인해 대화·세이브·재화를 남긴 상태</t>
+        </is>
+      </c>
+      <c r="G278" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H278" s="13" t="inlineStr">
+        <is>
+          <t>로그아웃한다</t>
+        </is>
+      </c>
       <c r="I278" s="13" t="inlineStr">
         <is>
-          <t>저장소에도 남지 않는다</t>
+          <t>미로그인 홈으로 복귀된다</t>
         </is>
       </c>
       <c r="J278" s="10" t="inlineStr">
@@ -19505,7 +19531,11 @@
       <c r="M278" s="16" t="n"/>
       <c r="N278" s="17" t="n"/>
       <c r="O278" s="17" t="n"/>
-      <c r="P278" s="18" t="n"/>
+      <c r="P278" s="13" t="inlineStr">
+        <is>
+          <t>저장소 잔존은 화면만 봐서는 판정할 수 없어 상태 훅으로 확인합니다. 세션 지속(§1-3)이 계정 스코프를 저장하므로, 로그아웃이 그 저장분까지 지우는지가 이 케이스의 핵심입니다</t>
+        </is>
+      </c>
       <c r="Q278" s="10" t="inlineStr">
         <is>
           <t>TC-ENT-009</t>
@@ -19527,33 +19557,29 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C279" s="68" t="inlineStr">
+      <c r="C279" s="69" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
       <c r="D279" s="74" t="inlineStr">
         <is>
-          <t>계정 전환</t>
+          <t>로그아웃</t>
         </is>
       </c>
       <c r="E279" s="13" t="inlineStr"/>
-      <c r="F279" s="13" t="inlineStr">
-        <is>
-          <t>미성년 계정으로 쓰다 로그아웃하고 성인 계정으로 로그인한 상태</t>
-        </is>
-      </c>
+      <c r="F279" s="13" t="inlineStr"/>
       <c r="G279" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H279" s="13" t="inlineStr">
         <is>
-          <t>대화·세이브·재화를 확인한다</t>
+          <t>화면과 저장소를 확인한다</t>
         </is>
       </c>
       <c r="I279" s="13" t="inlineStr">
         <is>
-          <t>계정 A의 데이터만 노출된다</t>
+          <t>앞 계정의 대화·세이브·재화가 화면에 남지 않는다</t>
         </is>
       </c>
       <c r="J279" s="10" t="inlineStr">
@@ -19573,14 +19599,10 @@
       <c r="M279" s="16" t="n"/>
       <c r="N279" s="17" t="n"/>
       <c r="O279" s="17" t="n"/>
-      <c r="P279" s="13" t="inlineStr">
-        <is>
-          <t>전환은 로그아웃이 첫 동작이라 MY 탭 소속입니다. 두 상태를 함께 밟는 케이스라 상태 열에 둘을 적습니다</t>
-        </is>
-      </c>
+      <c r="P279" s="13" t="n"/>
       <c r="Q279" s="10" t="inlineStr">
         <is>
-          <t>TC-GAT-021</t>
+          <t>TC-ENT-009</t>
         </is>
       </c>
       <c r="R279" s="10" t="inlineStr">
@@ -19590,7 +19612,7 @@
       </c>
       <c r="S279" s="10" t="inlineStr">
         <is>
-          <t>성인 인증, 미성년</t>
+          <t>성인 인증</t>
         </is>
       </c>
     </row>
@@ -19599,23 +19621,23 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C280" s="68" t="inlineStr">
+      <c r="C280" s="69" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
       <c r="D280" s="74" t="inlineStr">
         <is>
-          <t>계정 전환</t>
+          <t>로그아웃</t>
         </is>
       </c>
       <c r="E280" s="13" t="inlineStr"/>
-      <c r="F280" s="18" t="n"/>
+      <c r="F280" s="13" t="n"/>
       <c r="G280" s="18" t="n"/>
       <c r="H280" s="18" t="n"/>
       <c r="I280" s="13" t="inlineStr">
         <is>
-          <t>계정 B의 데이터가 섞이지 않는다</t>
+          <t>저장소에도 남지 않는다</t>
         </is>
       </c>
       <c r="J280" s="10" t="inlineStr">
@@ -19638,7 +19660,7 @@
       <c r="P280" s="18" t="n"/>
       <c r="Q280" s="10" t="inlineStr">
         <is>
-          <t>TC-GAT-021</t>
+          <t>TC-ENT-009</t>
         </is>
       </c>
       <c r="R280" s="10" t="inlineStr">
@@ -19648,7 +19670,7 @@
       </c>
       <c r="S280" s="10" t="inlineStr">
         <is>
-          <t>성인 인증, 미성년</t>
+          <t>성인 인증</t>
         </is>
       </c>
     </row>
@@ -19657,12 +19679,12 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C281" s="68" t="inlineStr">
+      <c r="C281" s="69" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
-      <c r="D281" s="74" t="inlineStr">
+      <c r="D281" s="75" t="inlineStr">
         <is>
           <t>계정 전환</t>
         </is>
@@ -19670,7 +19692,7 @@
       <c r="E281" s="13" t="inlineStr"/>
       <c r="F281" s="13" t="inlineStr">
         <is>
-          <t>성인 계정으로 쓰다 로그아웃하고 미성년 계정으로 로그인한 상태</t>
+          <t>미성년 계정으로 쓰다 로그아웃하고 성인 계정으로 로그인한 상태</t>
         </is>
       </c>
       <c r="G281" s="14" t="n">
@@ -19683,7 +19705,7 @@
       </c>
       <c r="I281" s="13" t="inlineStr">
         <is>
-          <t>계정 B의 데이터만 노출된다</t>
+          <t>계정 A의 데이터만 노출된다</t>
         </is>
       </c>
       <c r="J281" s="10" t="inlineStr">
@@ -19705,12 +19727,12 @@
       <c r="O281" s="17" t="n"/>
       <c r="P281" s="13" t="inlineStr">
         <is>
-          <t>반대 방향도 함께 봅니다 — 한 방향만 확인하면 복사가 한쪽으로만 새는 결함을 놓칩니다</t>
+          <t>전환은 로그아웃이 첫 동작이라 MY 탭 소속입니다. 두 상태를 함께 밟는 케이스라 상태 열에 둘을 적습니다</t>
         </is>
       </c>
       <c r="Q281" s="10" t="inlineStr">
         <is>
-          <t>TC-GAT-022</t>
+          <t>TC-GAT-021</t>
         </is>
       </c>
       <c r="R281" s="10" t="inlineStr">
@@ -19720,7 +19742,7 @@
       </c>
       <c r="S281" s="10" t="inlineStr">
         <is>
-          <t>미성년, 성인 인증</t>
+          <t>성인 인증, 미성년</t>
         </is>
       </c>
     </row>
@@ -19729,12 +19751,12 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C282" s="68" t="inlineStr">
+      <c r="C282" s="69" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
-      <c r="D282" s="74" t="inlineStr">
+      <c r="D282" s="75" t="inlineStr">
         <is>
           <t>계정 전환</t>
         </is>
@@ -19745,7 +19767,7 @@
       <c r="H282" s="18" t="n"/>
       <c r="I282" s="13" t="inlineStr">
         <is>
-          <t>계정 A의 데이터가 섞이지 않는다</t>
+          <t>계정 B의 데이터가 섞이지 않는다</t>
         </is>
       </c>
       <c r="J282" s="10" t="inlineStr">
@@ -19768,7 +19790,7 @@
       <c r="P282" s="18" t="n"/>
       <c r="Q282" s="10" t="inlineStr">
         <is>
-          <t>TC-GAT-022</t>
+          <t>TC-GAT-021</t>
         </is>
       </c>
       <c r="R282" s="10" t="inlineStr">
@@ -19778,7 +19800,7 @@
       </c>
       <c r="S282" s="10" t="inlineStr">
         <is>
-          <t>미성년, 성인 인증</t>
+          <t>성인 인증, 미성년</t>
         </is>
       </c>
     </row>
@@ -19787,20 +19809,20 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C283" s="68" t="inlineStr">
+      <c r="C283" s="69" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
       <c r="D283" s="75" t="inlineStr">
         <is>
-          <t>스텁 진입점</t>
+          <t>계정 전환</t>
         </is>
       </c>
       <c r="E283" s="13" t="inlineStr"/>
       <c r="F283" s="13" t="inlineStr">
         <is>
-          <t>성인 계정으로 로그인해 MY 탭을 연 상태</t>
+          <t>성인 계정으로 쓰다 로그아웃하고 미성년 계정으로 로그인한 상태</t>
         </is>
       </c>
       <c r="G283" s="14" t="n">
@@ -19808,22 +19830,22 @@
       </c>
       <c r="H283" s="13" t="inlineStr">
         <is>
-          <t>내 서재 진입점을 선택한다</t>
+          <t>대화·세이브·재화를 확인한다</t>
         </is>
       </c>
       <c r="I283" s="13" t="inlineStr">
         <is>
-          <t>제외 사유 안내 노출된다</t>
+          <t>계정 B의 데이터만 노출된다</t>
         </is>
       </c>
       <c r="J283" s="10" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>자동화 전용</t>
         </is>
       </c>
       <c r="K283" s="10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L283" s="15">
@@ -19835,22 +19857,22 @@
       <c r="O283" s="17" t="n"/>
       <c r="P283" s="13" t="inlineStr">
         <is>
-          <t>트리가 제외 사유의 정본임을 화면에서 읽히게 하는 자리입니다</t>
+          <t>반대 방향도 함께 봅니다 — 한 방향만 확인하면 복사가 한쪽으로만 새는 결함을 놓칩니다</t>
         </is>
       </c>
       <c r="Q283" s="10" t="inlineStr">
         <is>
-          <t>TC-DSC-051</t>
+          <t>TC-GAT-022</t>
         </is>
       </c>
       <c r="R283" s="10" t="inlineStr">
         <is>
-          <t>결정적</t>
+          <t>금칙</t>
         </is>
       </c>
       <c r="S283" s="10" t="inlineStr">
         <is>
-          <t>성인 인증</t>
+          <t>미성년, 성인 인증</t>
         </is>
       </c>
     </row>
@@ -19859,38 +19881,28 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C284" s="76" t="inlineStr">
-        <is>
-          <t>재화</t>
-        </is>
-      </c>
-      <c r="D284" s="77" t="inlineStr">
-        <is>
-          <t>잔액</t>
+      <c r="C284" s="69" t="inlineStr">
+        <is>
+          <t>MY 탭</t>
+        </is>
+      </c>
+      <c r="D284" s="75" t="inlineStr">
+        <is>
+          <t>계정 전환</t>
         </is>
       </c>
       <c r="E284" s="13" t="inlineStr"/>
-      <c r="F284" s="13" t="inlineStr">
-        <is>
-          <t>성인 계정으로 로그인한 상태</t>
-        </is>
-      </c>
-      <c r="G284" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H284" s="13" t="inlineStr">
-        <is>
-          <t>재화 패널을 연다</t>
-        </is>
-      </c>
+      <c r="F284" s="18" t="n"/>
+      <c r="G284" s="18" t="n"/>
+      <c r="H284" s="18" t="n"/>
       <c r="I284" s="13" t="inlineStr">
         <is>
-          <t>캔디와 크리스탈이 분리되어 노출된다</t>
+          <t>계정 A의 데이터가 섞이지 않는다</t>
         </is>
       </c>
       <c r="J284" s="10" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>자동화 전용</t>
         </is>
       </c>
       <c r="K284" s="10" t="inlineStr">
@@ -19905,24 +19917,20 @@
       <c r="M284" s="16" t="n"/>
       <c r="N284" s="17" t="n"/>
       <c r="O284" s="17" t="n"/>
-      <c r="P284" s="13" t="inlineStr">
-        <is>
-          <t>재화 패널은 전역이라 상단 바·대화방 헤더 어디서든 열립니다. 시작 잔액은 캔디 150·크리스탈 0입니다</t>
-        </is>
-      </c>
+      <c r="P284" s="18" t="n"/>
       <c r="Q284" s="10" t="inlineStr">
         <is>
-          <t>TC-CUR-007</t>
+          <t>TC-GAT-022</t>
         </is>
       </c>
       <c r="R284" s="10" t="inlineStr">
         <is>
-          <t>결정적</t>
+          <t>금칙</t>
         </is>
       </c>
       <c r="S284" s="10" t="inlineStr">
         <is>
-          <t>성인 인증</t>
+          <t>미성년, 성인 인증</t>
         </is>
       </c>
     </row>
@@ -19931,23 +19939,33 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C285" s="76" t="inlineStr">
-        <is>
-          <t>재화</t>
-        </is>
-      </c>
-      <c r="D285" s="77" t="inlineStr">
-        <is>
-          <t>잔액</t>
+      <c r="C285" s="69" t="inlineStr">
+        <is>
+          <t>MY 탭</t>
+        </is>
+      </c>
+      <c r="D285" s="76" t="inlineStr">
+        <is>
+          <t>스텁 진입점</t>
         </is>
       </c>
       <c r="E285" s="13" t="inlineStr"/>
-      <c r="F285" s="18" t="n"/>
-      <c r="G285" s="18" t="n"/>
-      <c r="H285" s="18" t="n"/>
+      <c r="F285" s="13" t="inlineStr">
+        <is>
+          <t>성인 계정으로 로그인해 MY 탭을 연 상태</t>
+        </is>
+      </c>
+      <c r="G285" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H285" s="13" t="inlineStr">
+        <is>
+          <t>내 서재 진입점을 선택한다</t>
+        </is>
+      </c>
       <c r="I285" s="13" t="inlineStr">
         <is>
-          <t>요율 안내가 노출된다</t>
+          <t>제외 사유 안내 노출된다</t>
         </is>
       </c>
       <c r="J285" s="10" t="inlineStr">
@@ -19957,7 +19975,7 @@
       </c>
       <c r="K285" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L285" s="15">
@@ -19967,10 +19985,14 @@
       <c r="M285" s="16" t="n"/>
       <c r="N285" s="17" t="n"/>
       <c r="O285" s="17" t="n"/>
-      <c r="P285" s="18" t="n"/>
+      <c r="P285" s="13" t="inlineStr">
+        <is>
+          <t>트리가 제외 사유의 정본임을 화면에서 읽히게 하는 자리입니다</t>
+        </is>
+      </c>
       <c r="Q285" s="10" t="inlineStr">
         <is>
-          <t>TC-CUR-007</t>
+          <t>TC-DSC-051</t>
         </is>
       </c>
       <c r="R285" s="10" t="inlineStr">
@@ -19989,20 +20011,20 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C286" s="76" t="inlineStr">
+      <c r="C286" s="77" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
       <c r="D286" s="78" t="inlineStr">
         <is>
-          <t>획득</t>
+          <t>잔액</t>
         </is>
       </c>
       <c r="E286" s="13" t="inlineStr"/>
       <c r="F286" s="13" t="inlineStr">
         <is>
-          <t>성인 계정으로 로그인해 간편 프로필 패널을 연 상태</t>
+          <t>성인 계정으로 로그인한 상태</t>
         </is>
       </c>
       <c r="G286" s="14" t="n">
@@ -20010,12 +20032,12 @@
       </c>
       <c r="H286" s="13" t="inlineStr">
         <is>
-          <t>데일리 미션 수령을 선택한다</t>
+          <t>재화 패널을 연다</t>
         </is>
       </c>
       <c r="I286" s="13" t="inlineStr">
         <is>
-          <t>캔디가 50 증가한다</t>
+          <t>캔디와 크리스탈이 분리되어 노출된다</t>
         </is>
       </c>
       <c r="J286" s="10" t="inlineStr">
@@ -20025,7 +20047,7 @@
       </c>
       <c r="K286" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L286" s="15">
@@ -20037,12 +20059,12 @@
       <c r="O286" s="17" t="n"/>
       <c r="P286" s="13" t="inlineStr">
         <is>
-          <t>달성 판정 로직은 만들지 않았고 전 항목이 수령 가능 상태로 노출됩니다 — 미구현 사유는 화면에 표기됩니다</t>
+          <t>재화 패널은 전역이라 상단 바·대화방 헤더 어디서든 열립니다. 시작 잔액은 캔디 150·크리스탈 0입니다</t>
         </is>
       </c>
       <c r="Q286" s="10" t="inlineStr">
         <is>
-          <t>TC-CUR-008</t>
+          <t>TC-CUR-007</t>
         </is>
       </c>
       <c r="R286" s="10" t="inlineStr">
@@ -20061,14 +20083,14 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C287" s="76" t="inlineStr">
+      <c r="C287" s="77" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
       <c r="D287" s="78" t="inlineStr">
         <is>
-          <t>획득</t>
+          <t>잔액</t>
         </is>
       </c>
       <c r="E287" s="13" t="inlineStr"/>
@@ -20077,7 +20099,7 @@
       <c r="H287" s="18" t="n"/>
       <c r="I287" s="13" t="inlineStr">
         <is>
-          <t>수령 버튼이 비활성된다</t>
+          <t>요율 안내가 노출된다</t>
         </is>
       </c>
       <c r="J287" s="10" t="inlineStr">
@@ -20087,7 +20109,7 @@
       </c>
       <c r="K287" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L287" s="15">
@@ -20100,7 +20122,7 @@
       <c r="P287" s="18" t="n"/>
       <c r="Q287" s="10" t="inlineStr">
         <is>
-          <t>TC-CUR-008</t>
+          <t>TC-CUR-007</t>
         </is>
       </c>
       <c r="R287" s="10" t="inlineStr">
@@ -20119,12 +20141,12 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C288" s="76" t="inlineStr">
+      <c r="C288" s="77" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
-      <c r="D288" s="78" t="inlineStr">
+      <c r="D288" s="79" t="inlineStr">
         <is>
           <t>획득</t>
         </is>
@@ -20132,7 +20154,7 @@
       <c r="E288" s="13" t="inlineStr"/>
       <c r="F288" s="13" t="inlineStr">
         <is>
-          <t>성인 계정으로 로그인하고 오늘 데일리를 이미 수령한 상태</t>
+          <t>성인 계정으로 로그인해 간편 프로필 패널을 연 상태</t>
         </is>
       </c>
       <c r="G288" s="14" t="n">
@@ -20140,12 +20162,12 @@
       </c>
       <c r="H288" s="13" t="inlineStr">
         <is>
-          <t>다시 수령을 시도한다</t>
+          <t>데일리 미션 수령을 선택한다</t>
         </is>
       </c>
       <c r="I288" s="13" t="inlineStr">
         <is>
-          <t>수령이 차단된다</t>
+          <t>캔디가 50 증가한다</t>
         </is>
       </c>
       <c r="J288" s="10" t="inlineStr">
@@ -20167,17 +20189,17 @@
       <c r="O288" s="17" t="n"/>
       <c r="P288" s="13" t="inlineStr">
         <is>
-          <t>기준일당 1회입니다. 기준일을 바꾸면 다시 수령 가능해지는 것 자체가 검증 대상입니다(§8-1)</t>
+          <t>달성 판정 로직은 만들지 않았고 전 항목이 수령 가능 상태로 노출됩니다 — 미구현 사유는 화면에 표기됩니다</t>
         </is>
       </c>
       <c r="Q288" s="10" t="inlineStr">
         <is>
-          <t>TC-CUR-009</t>
+          <t>TC-CUR-008</t>
         </is>
       </c>
       <c r="R288" s="10" t="inlineStr">
         <is>
-          <t>금칙</t>
+          <t>결정적</t>
         </is>
       </c>
       <c r="S288" s="10" t="inlineStr">
@@ -20191,12 +20213,12 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C289" s="76" t="inlineStr">
+      <c r="C289" s="77" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
-      <c r="D289" s="78" t="inlineStr">
+      <c r="D289" s="79" t="inlineStr">
         <is>
           <t>획득</t>
         </is>
@@ -20207,7 +20229,7 @@
       <c r="H289" s="18" t="n"/>
       <c r="I289" s="13" t="inlineStr">
         <is>
-          <t>잔액이 늘지 않는다</t>
+          <t>수령 버튼이 비활성된다</t>
         </is>
       </c>
       <c r="J289" s="10" t="inlineStr">
@@ -20230,12 +20252,12 @@
       <c r="P289" s="18" t="n"/>
       <c r="Q289" s="10" t="inlineStr">
         <is>
-          <t>TC-CUR-009</t>
+          <t>TC-CUR-008</t>
         </is>
       </c>
       <c r="R289" s="10" t="inlineStr">
         <is>
-          <t>금칙</t>
+          <t>결정적</t>
         </is>
       </c>
       <c r="S289" s="10" t="inlineStr">
@@ -20249,12 +20271,12 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C290" s="76" t="inlineStr">
+      <c r="C290" s="77" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
-      <c r="D290" s="78" t="inlineStr">
+      <c r="D290" s="79" t="inlineStr">
         <is>
           <t>획득</t>
         </is>
@@ -20262,7 +20284,7 @@
       <c r="E290" s="13" t="inlineStr"/>
       <c r="F290" s="13" t="inlineStr">
         <is>
-          <t>성인 계정으로 로그인해 간편 프로필 패널을 연 상태</t>
+          <t>성인 계정으로 로그인하고 오늘 데일리를 이미 수령한 상태</t>
         </is>
       </c>
       <c r="G290" s="14" t="n">
@@ -20270,12 +20292,12 @@
       </c>
       <c r="H290" s="13" t="inlineStr">
         <is>
-          <t>웰컴 미션 한 항목을 수령한다</t>
+          <t>다시 수령을 시도한다</t>
         </is>
       </c>
       <c r="I290" s="13" t="inlineStr">
         <is>
-          <t>캔디가 50 증가한다</t>
+          <t>수령이 차단된다</t>
         </is>
       </c>
       <c r="J290" s="10" t="inlineStr">
@@ -20297,17 +20319,17 @@
       <c r="O290" s="17" t="n"/>
       <c r="P290" s="13" t="inlineStr">
         <is>
-          <t>가입 환영·첫 대화·페르소나 등록 세 항목이며 각각 1회입니다</t>
+          <t>기준일당 1회입니다. 기준일을 바꾸면 다시 수령 가능해지는 것 자체가 검증 대상입니다(§8-1)</t>
         </is>
       </c>
       <c r="Q290" s="10" t="inlineStr">
         <is>
-          <t>TC-CUR-010</t>
+          <t>TC-CUR-009</t>
         </is>
       </c>
       <c r="R290" s="10" t="inlineStr">
         <is>
-          <t>결정적</t>
+          <t>금칙</t>
         </is>
       </c>
       <c r="S290" s="10" t="inlineStr">
@@ -20321,29 +20343,23 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C291" s="76" t="inlineStr">
+      <c r="C291" s="77" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
-      <c r="D291" s="78" t="inlineStr">
+      <c r="D291" s="79" t="inlineStr">
         <is>
           <t>획득</t>
         </is>
       </c>
       <c r="E291" s="13" t="inlineStr"/>
-      <c r="F291" s="13" t="inlineStr"/>
-      <c r="G291" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="H291" s="13" t="inlineStr">
-        <is>
-          <t>같은 항목을 다시 시도한다</t>
-        </is>
-      </c>
+      <c r="F291" s="18" t="n"/>
+      <c r="G291" s="18" t="n"/>
+      <c r="H291" s="18" t="n"/>
       <c r="I291" s="13" t="inlineStr">
         <is>
-          <t>수령이 차단된다</t>
+          <t>잔액이 늘지 않는다</t>
         </is>
       </c>
       <c r="J291" s="10" t="inlineStr">
@@ -20363,15 +20379,15 @@
       <c r="M291" s="16" t="n"/>
       <c r="N291" s="17" t="n"/>
       <c r="O291" s="17" t="n"/>
-      <c r="P291" s="13" t="n"/>
+      <c r="P291" s="18" t="n"/>
       <c r="Q291" s="10" t="inlineStr">
         <is>
-          <t>TC-CUR-010</t>
+          <t>TC-CUR-009</t>
         </is>
       </c>
       <c r="R291" s="10" t="inlineStr">
         <is>
-          <t>결정적</t>
+          <t>금칙</t>
         </is>
       </c>
       <c r="S291" s="10" t="inlineStr">
@@ -20385,12 +20401,12 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C292" s="76" t="inlineStr">
+      <c r="C292" s="77" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
-      <c r="D292" s="78" t="inlineStr">
+      <c r="D292" s="79" t="inlineStr">
         <is>
           <t>획득</t>
         </is>
@@ -20398,7 +20414,7 @@
       <c r="E292" s="13" t="inlineStr"/>
       <c r="F292" s="13" t="inlineStr">
         <is>
-          <t>성인 계정으로 로그인하고 획득·소모가 모두 있는 상태</t>
+          <t>성인 계정으로 로그인해 간편 프로필 패널을 연 상태</t>
         </is>
       </c>
       <c r="G292" s="14" t="n">
@@ -20406,12 +20422,12 @@
       </c>
       <c r="H292" s="13" t="inlineStr">
         <is>
-          <t>재화 패널의 내역을 확인한다</t>
+          <t>웰컴 미션 한 항목을 수령한다</t>
         </is>
       </c>
       <c r="I292" s="13" t="inlineStr">
         <is>
-          <t>획득과 소모가 지갑별로 분리 기록된다</t>
+          <t>캔디가 50 증가한다</t>
         </is>
       </c>
       <c r="J292" s="10" t="inlineStr">
@@ -20421,7 +20437,7 @@
       </c>
       <c r="K292" s="10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L292" s="15">
@@ -20433,12 +20449,12 @@
       <c r="O292" s="17" t="n"/>
       <c r="P292" s="13" t="inlineStr">
         <is>
-          <t>혼합 차감은 캔디와 크리스탈 두 줄로 남습니다. 재화 패널과 간편 프로필 패널이 같은 데이터를 같은 뷰로 봅니다</t>
+          <t>가입 환영·첫 대화·페르소나 등록 세 항목이며 각각 1회입니다</t>
         </is>
       </c>
       <c r="Q292" s="10" t="inlineStr">
         <is>
-          <t>TC-CUR-011</t>
+          <t>TC-CUR-010</t>
         </is>
       </c>
       <c r="R292" s="10" t="inlineStr">
@@ -20457,12 +20473,12 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C293" s="76" t="inlineStr">
+      <c r="C293" s="77" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
-      <c r="D293" s="78" t="inlineStr">
+      <c r="D293" s="79" t="inlineStr">
         <is>
           <t>획득</t>
         </is>
@@ -20474,12 +20490,12 @@
       </c>
       <c r="H293" s="13" t="inlineStr">
         <is>
-          <t>소모 필터를 선택한다</t>
+          <t>같은 항목을 다시 시도한다</t>
         </is>
       </c>
       <c r="I293" s="13" t="inlineStr">
         <is>
-          <t>소모 항목만 남는다</t>
+          <t>수령이 차단된다</t>
         </is>
       </c>
       <c r="J293" s="10" t="inlineStr">
@@ -20489,7 +20505,7 @@
       </c>
       <c r="K293" s="10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L293" s="15">
@@ -20502,7 +20518,7 @@
       <c r="P293" s="13" t="n"/>
       <c r="Q293" s="10" t="inlineStr">
         <is>
-          <t>TC-CUR-011</t>
+          <t>TC-CUR-010</t>
         </is>
       </c>
       <c r="R293" s="10" t="inlineStr">
@@ -20521,33 +20537,33 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C294" s="76" t="inlineStr">
+      <c r="C294" s="77" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
       <c r="D294" s="79" t="inlineStr">
         <is>
-          <t>결제 mock</t>
-        </is>
-      </c>
-      <c r="E294" s="80" t="inlineStr">
-        <is>
-          <t>성인 계정으로 로그인해 재화 패널을 연 상태</t>
-        </is>
-      </c>
-      <c r="F294" s="13" t="inlineStr"/>
+          <t>획득</t>
+        </is>
+      </c>
+      <c r="E294" s="13" t="inlineStr"/>
+      <c r="F294" s="13" t="inlineStr">
+        <is>
+          <t>성인 계정으로 로그인하고 획득·소모가 모두 있는 상태</t>
+        </is>
+      </c>
       <c r="G294" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H294" s="13" t="inlineStr">
         <is>
-          <t>충전 성공을 선택한다</t>
+          <t>재화 패널의 내역을 확인한다</t>
         </is>
       </c>
       <c r="I294" s="13" t="inlineStr">
         <is>
-          <t>크리스탈이 100 증가한다</t>
+          <t>획득과 소모가 지갑별로 분리 기록된다</t>
         </is>
       </c>
       <c r="J294" s="10" t="inlineStr">
@@ -20557,7 +20573,7 @@
       </c>
       <c r="K294" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L294" s="15">
@@ -20569,12 +20585,12 @@
       <c r="O294" s="17" t="n"/>
       <c r="P294" s="13" t="inlineStr">
         <is>
-          <t>실 PG 연동은 검증 불가 항목이며 mock 콜백만 봅니다 — 그 사실을 리포트에 명시합니다</t>
+          <t>혼합 차감은 캔디와 크리스탈 두 줄로 남습니다. 재화 패널과 간편 프로필 패널이 같은 데이터를 같은 뷰로 봅니다</t>
         </is>
       </c>
       <c r="Q294" s="10" t="inlineStr">
         <is>
-          <t>TC-CUR-012</t>
+          <t>TC-CUR-011</t>
         </is>
       </c>
       <c r="R294" s="10" t="inlineStr">
@@ -20593,27 +20609,29 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C295" s="76" t="inlineStr">
+      <c r="C295" s="77" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
       <c r="D295" s="79" t="inlineStr">
         <is>
-          <t>결제 mock</t>
-        </is>
-      </c>
-      <c r="E295" s="80" t="inlineStr">
-        <is>
-          <t>성인 계정으로 로그인해 재화 패널을 연 상태</t>
-        </is>
-      </c>
-      <c r="F295" s="18" t="n"/>
-      <c r="G295" s="18" t="n"/>
-      <c r="H295" s="18" t="n"/>
+          <t>획득</t>
+        </is>
+      </c>
+      <c r="E295" s="13" t="inlineStr"/>
+      <c r="F295" s="13" t="inlineStr"/>
+      <c r="G295" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H295" s="13" t="inlineStr">
+        <is>
+          <t>소모 필터를 선택한다</t>
+        </is>
+      </c>
       <c r="I295" s="13" t="inlineStr">
         <is>
-          <t>획득 내역에 기록된다</t>
+          <t>소모 항목만 남는다</t>
         </is>
       </c>
       <c r="J295" s="10" t="inlineStr">
@@ -20623,7 +20641,7 @@
       </c>
       <c r="K295" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L295" s="15">
@@ -20633,10 +20651,10 @@
       <c r="M295" s="16" t="n"/>
       <c r="N295" s="17" t="n"/>
       <c r="O295" s="17" t="n"/>
-      <c r="P295" s="18" t="n"/>
+      <c r="P295" s="13" t="n"/>
       <c r="Q295" s="10" t="inlineStr">
         <is>
-          <t>TC-CUR-012</t>
+          <t>TC-CUR-011</t>
         </is>
       </c>
       <c r="R295" s="10" t="inlineStr">
@@ -20655,17 +20673,17 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C296" s="76" t="inlineStr">
+      <c r="C296" s="77" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
-      <c r="D296" s="79" t="inlineStr">
+      <c r="D296" s="80" t="inlineStr">
         <is>
           <t>결제 mock</t>
         </is>
       </c>
-      <c r="E296" s="80" t="inlineStr">
+      <c r="E296" s="81" t="inlineStr">
         <is>
           <t>성인 계정으로 로그인해 재화 패널을 연 상태</t>
         </is>
@@ -20676,12 +20694,12 @@
       </c>
       <c r="H296" s="13" t="inlineStr">
         <is>
-          <t>충전 실패를 선택한다</t>
+          <t>충전 성공을 선택한다</t>
         </is>
       </c>
       <c r="I296" s="13" t="inlineStr">
         <is>
-          <t>잔액이 변하지 않는다</t>
+          <t>크리스탈이 100 증가한다</t>
         </is>
       </c>
       <c r="J296" s="10" t="inlineStr">
@@ -20703,17 +20721,17 @@
       <c r="O296" s="17" t="n"/>
       <c r="P296" s="13" t="inlineStr">
         <is>
-          <t>실패가 잔액을 건드리면 결제 정합이 깨집니다 — 내역까지 확인해야 절반만 반영된 상태를 잡습니다</t>
+          <t>실 PG 연동은 검증 불가 항목이며 mock 콜백만 봅니다 — 그 사실을 리포트에 명시합니다</t>
         </is>
       </c>
       <c r="Q296" s="10" t="inlineStr">
         <is>
-          <t>TC-CUR-013</t>
+          <t>TC-CUR-012</t>
         </is>
       </c>
       <c r="R296" s="10" t="inlineStr">
         <is>
-          <t>금칙</t>
+          <t>결정적</t>
         </is>
       </c>
       <c r="S296" s="10" t="inlineStr">
@@ -20727,27 +20745,27 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C297" s="76" t="inlineStr">
+      <c r="C297" s="77" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
-      <c r="D297" s="79" t="inlineStr">
+      <c r="D297" s="80" t="inlineStr">
         <is>
           <t>결제 mock</t>
         </is>
       </c>
-      <c r="E297" s="80" t="inlineStr">
+      <c r="E297" s="81" t="inlineStr">
         <is>
           <t>성인 계정으로 로그인해 재화 패널을 연 상태</t>
         </is>
       </c>
-      <c r="F297" s="27" t="n"/>
-      <c r="G297" s="27" t="n"/>
-      <c r="H297" s="27" t="n"/>
+      <c r="F297" s="18" t="n"/>
+      <c r="G297" s="18" t="n"/>
+      <c r="H297" s="18" t="n"/>
       <c r="I297" s="13" t="inlineStr">
         <is>
-          <t>실패 안내 노출된다</t>
+          <t>획득 내역에 기록된다</t>
         </is>
       </c>
       <c r="J297" s="10" t="inlineStr">
@@ -20767,15 +20785,15 @@
       <c r="M297" s="16" t="n"/>
       <c r="N297" s="17" t="n"/>
       <c r="O297" s="17" t="n"/>
-      <c r="P297" s="27" t="n"/>
+      <c r="P297" s="18" t="n"/>
       <c r="Q297" s="10" t="inlineStr">
         <is>
-          <t>TC-CUR-013</t>
+          <t>TC-CUR-012</t>
         </is>
       </c>
       <c r="R297" s="10" t="inlineStr">
         <is>
-          <t>금칙</t>
+          <t>결정적</t>
         </is>
       </c>
       <c r="S297" s="10" t="inlineStr">
@@ -20789,27 +20807,33 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C298" s="76" t="inlineStr">
+      <c r="C298" s="77" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
-      <c r="D298" s="79" t="inlineStr">
+      <c r="D298" s="80" t="inlineStr">
         <is>
           <t>결제 mock</t>
         </is>
       </c>
-      <c r="E298" s="80" t="inlineStr">
+      <c r="E298" s="81" t="inlineStr">
         <is>
           <t>성인 계정으로 로그인해 재화 패널을 연 상태</t>
         </is>
       </c>
-      <c r="F298" s="18" t="n"/>
-      <c r="G298" s="18" t="n"/>
-      <c r="H298" s="18" t="n"/>
+      <c r="F298" s="13" t="inlineStr"/>
+      <c r="G298" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H298" s="13" t="inlineStr">
+        <is>
+          <t>충전 실패를 선택한다</t>
+        </is>
+      </c>
       <c r="I298" s="13" t="inlineStr">
         <is>
-          <t>내역에 남지 않는다</t>
+          <t>잔액이 변하지 않는다</t>
         </is>
       </c>
       <c r="J298" s="10" t="inlineStr">
@@ -20829,7 +20853,11 @@
       <c r="M298" s="16" t="n"/>
       <c r="N298" s="17" t="n"/>
       <c r="O298" s="17" t="n"/>
-      <c r="P298" s="18" t="n"/>
+      <c r="P298" s="13" t="inlineStr">
+        <is>
+          <t>실패가 잔액을 건드리면 결제 정합이 깨집니다 — 내역까지 확인해야 절반만 반영된 상태를 잡습니다</t>
+        </is>
+      </c>
       <c r="Q298" s="10" t="inlineStr">
         <is>
           <t>TC-CUR-013</t>
@@ -20851,33 +20879,27 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C299" s="76" t="inlineStr">
+      <c r="C299" s="77" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
-      <c r="D299" s="77" t="inlineStr">
-        <is>
-          <t>잔액</t>
-        </is>
-      </c>
-      <c r="E299" s="13" t="inlineStr"/>
-      <c r="F299" s="13" t="inlineStr">
-        <is>
-          <t>성인 계정으로 로그인해 대화방에 있는 상태</t>
-        </is>
-      </c>
-      <c r="G299" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H299" s="13" t="inlineStr">
-        <is>
-          <t>대화방 헤더의 잔액을 선택한다</t>
-        </is>
-      </c>
+      <c r="D299" s="80" t="inlineStr">
+        <is>
+          <t>결제 mock</t>
+        </is>
+      </c>
+      <c r="E299" s="81" t="inlineStr">
+        <is>
+          <t>성인 계정으로 로그인해 재화 패널을 연 상태</t>
+        </is>
+      </c>
+      <c r="F299" s="27" t="n"/>
+      <c r="G299" s="27" t="n"/>
+      <c r="H299" s="27" t="n"/>
       <c r="I299" s="13" t="inlineStr">
         <is>
-          <t>재화 패널이 열린다</t>
+          <t>실패 안내 노출된다</t>
         </is>
       </c>
       <c r="J299" s="10" t="inlineStr">
@@ -20887,7 +20909,7 @@
       </c>
       <c r="K299" s="10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L299" s="15">
@@ -20897,19 +20919,15 @@
       <c r="M299" s="16" t="n"/>
       <c r="N299" s="17" t="n"/>
       <c r="O299" s="17" t="n"/>
-      <c r="P299" s="13" t="inlineStr">
-        <is>
-          <t>패널은 전역이라 상단 바와 대화방 헤더 두 곳에서 열립니다 — 두 경로가 다른 값을 보이면 잔액 정합이 깨진 것입니다</t>
-        </is>
-      </c>
+      <c r="P299" s="27" t="n"/>
       <c r="Q299" s="10" t="inlineStr">
         <is>
-          <t>TC-CUR-014</t>
+          <t>TC-CUR-013</t>
         </is>
       </c>
       <c r="R299" s="10" t="inlineStr">
         <is>
-          <t>결정적</t>
+          <t>금칙</t>
         </is>
       </c>
       <c r="S299" s="10" t="inlineStr">
@@ -20923,29 +20941,27 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C300" s="76" t="inlineStr">
+      <c r="C300" s="77" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
-      <c r="D300" s="77" t="inlineStr">
-        <is>
-          <t>잔액</t>
-        </is>
-      </c>
-      <c r="E300" s="13" t="inlineStr"/>
-      <c r="F300" s="13" t="inlineStr"/>
-      <c r="G300" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="H300" s="13" t="inlineStr">
-        <is>
-          <t>패널을 닫고 상단 바의 잔액을 선택한다</t>
-        </is>
-      </c>
+      <c r="D300" s="80" t="inlineStr">
+        <is>
+          <t>결제 mock</t>
+        </is>
+      </c>
+      <c r="E300" s="81" t="inlineStr">
+        <is>
+          <t>성인 계정으로 로그인해 재화 패널을 연 상태</t>
+        </is>
+      </c>
+      <c r="F300" s="18" t="n"/>
+      <c r="G300" s="18" t="n"/>
+      <c r="H300" s="18" t="n"/>
       <c r="I300" s="13" t="inlineStr">
         <is>
-          <t>같은 패널이 같은 값으로 열린다</t>
+          <t>내역에 남지 않는다</t>
         </is>
       </c>
       <c r="J300" s="10" t="inlineStr">
@@ -20955,7 +20971,7 @@
       </c>
       <c r="K300" s="10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L300" s="15">
@@ -20965,15 +20981,15 @@
       <c r="M300" s="16" t="n"/>
       <c r="N300" s="17" t="n"/>
       <c r="O300" s="17" t="n"/>
-      <c r="P300" s="13" t="n"/>
+      <c r="P300" s="18" t="n"/>
       <c r="Q300" s="10" t="inlineStr">
         <is>
-          <t>TC-CUR-014</t>
+          <t>TC-CUR-013</t>
         </is>
       </c>
       <c r="R300" s="10" t="inlineStr">
         <is>
-          <t>결정적</t>
+          <t>금칙</t>
         </is>
       </c>
       <c r="S300" s="10" t="inlineStr">
@@ -20987,20 +21003,20 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C301" s="81" t="inlineStr">
-        <is>
-          <t>스텁·정적</t>
-        </is>
-      </c>
-      <c r="D301" s="82" t="inlineStr">
-        <is>
-          <t>커뮤니티 탭</t>
+      <c r="C301" s="77" t="inlineStr">
+        <is>
+          <t>재화</t>
+        </is>
+      </c>
+      <c r="D301" s="78" t="inlineStr">
+        <is>
+          <t>잔액</t>
         </is>
       </c>
       <c r="E301" s="13" t="inlineStr"/>
       <c r="F301" s="13" t="inlineStr">
         <is>
-          <t>성인 계정으로 로그인한 상태</t>
+          <t>성인 계정으로 로그인해 대화방에 있는 상태</t>
         </is>
       </c>
       <c r="G301" s="14" t="n">
@@ -21008,12 +21024,12 @@
       </c>
       <c r="H301" s="13" t="inlineStr">
         <is>
-          <t>커뮤니티 탭을 연다</t>
+          <t>대화방 헤더의 잔액을 선택한다</t>
         </is>
       </c>
       <c r="I301" s="13" t="inlineStr">
         <is>
-          <t>창작 게시글이 읽기 전용으로 노출된다</t>
+          <t>재화 패널이 열린다</t>
         </is>
       </c>
       <c r="J301" s="10" t="inlineStr">
@@ -21035,12 +21051,12 @@
       <c r="O301" s="17" t="n"/>
       <c r="P301" s="13" t="inlineStr">
         <is>
-          <t>소셜은 제외 영역이라 데이터 표시만 있고 발생·조작 로직이 없습니다</t>
+          <t>패널은 전역이라 상단 바와 대화방 헤더 두 곳에서 열립니다 — 두 경로가 다른 값을 보이면 잔액 정합이 깨진 것입니다</t>
         </is>
       </c>
       <c r="Q301" s="10" t="inlineStr">
         <is>
-          <t>TC-DSC-052</t>
+          <t>TC-CUR-014</t>
         </is>
       </c>
       <c r="R301" s="10" t="inlineStr">
@@ -21059,23 +21075,29 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C302" s="81" t="inlineStr">
-        <is>
-          <t>스텁·정적</t>
-        </is>
-      </c>
-      <c r="D302" s="82" t="inlineStr">
-        <is>
-          <t>커뮤니티 탭</t>
+      <c r="C302" s="77" t="inlineStr">
+        <is>
+          <t>재화</t>
+        </is>
+      </c>
+      <c r="D302" s="78" t="inlineStr">
+        <is>
+          <t>잔액</t>
         </is>
       </c>
       <c r="E302" s="13" t="inlineStr"/>
-      <c r="F302" s="18" t="n"/>
-      <c r="G302" s="18" t="n"/>
-      <c r="H302" s="18" t="n"/>
+      <c r="F302" s="13" t="inlineStr"/>
+      <c r="G302" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H302" s="13" t="inlineStr">
+        <is>
+          <t>패널을 닫고 상단 바의 잔액을 선택한다</t>
+        </is>
+      </c>
       <c r="I302" s="13" t="inlineStr">
         <is>
-          <t>작성·댓글 수단이 제공되지 않는다</t>
+          <t>같은 패널이 같은 값으로 열린다</t>
         </is>
       </c>
       <c r="J302" s="10" t="inlineStr">
@@ -21095,10 +21117,10 @@
       <c r="M302" s="16" t="n"/>
       <c r="N302" s="17" t="n"/>
       <c r="O302" s="17" t="n"/>
-      <c r="P302" s="18" t="n"/>
+      <c r="P302" s="13" t="n"/>
       <c r="Q302" s="10" t="inlineStr">
         <is>
-          <t>TC-DSC-052</t>
+          <t>TC-CUR-014</t>
         </is>
       </c>
       <c r="R302" s="10" t="inlineStr">
@@ -21117,14 +21139,14 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C303" s="81" t="inlineStr">
+      <c r="C303" s="82" t="inlineStr">
         <is>
           <t>스텁·정적</t>
         </is>
       </c>
       <c r="D303" s="83" t="inlineStr">
         <is>
-          <t>내 작품 탭</t>
+          <t>커뮤니티 탭</t>
         </is>
       </c>
       <c r="E303" s="13" t="inlineStr"/>
@@ -21138,12 +21160,12 @@
       </c>
       <c r="H303" s="13" t="inlineStr">
         <is>
-          <t>내 작품 탭을 연다</t>
+          <t>커뮤니티 탭을 연다</t>
         </is>
       </c>
       <c r="I303" s="13" t="inlineStr">
         <is>
-          <t>검증 범위 제외 사유가 노출된다</t>
+          <t>창작 게시글이 읽기 전용으로 노출된다</t>
         </is>
       </c>
       <c r="J303" s="10" t="inlineStr">
@@ -21165,12 +21187,12 @@
       <c r="O303" s="17" t="n"/>
       <c r="P303" s="13" t="inlineStr">
         <is>
-          <t>트리가 제외 사유의 정본임을 화면에서 읽히게 합니다 — 스텁이 빈 화면이 아니라 판단의 결과임을 보이는 자리입니다</t>
+          <t>소셜은 제외 영역이라 데이터 표시만 있고 발생·조작 로직이 없습니다</t>
         </is>
       </c>
       <c r="Q303" s="10" t="inlineStr">
         <is>
-          <t>TC-DSC-053</t>
+          <t>TC-DSC-052</t>
         </is>
       </c>
       <c r="R303" s="10" t="inlineStr">
@@ -21189,14 +21211,14 @@
         <f>ROW()-9</f>
         <v/>
       </c>
-      <c r="C304" s="81" t="inlineStr">
+      <c r="C304" s="82" t="inlineStr">
         <is>
           <t>스텁·정적</t>
         </is>
       </c>
       <c r="D304" s="83" t="inlineStr">
         <is>
-          <t>내 작품 탭</t>
+          <t>커뮤니티 탭</t>
         </is>
       </c>
       <c r="E304" s="13" t="inlineStr"/>
@@ -21205,7 +21227,7 @@
       <c r="H304" s="18" t="n"/>
       <c r="I304" s="13" t="inlineStr">
         <is>
-          <t>트리 제외 영역의 항목명이 노출된다</t>
+          <t>작성·댓글 수단이 제공되지 않는다</t>
         </is>
       </c>
       <c r="J304" s="10" t="inlineStr">
@@ -21228,22 +21250,152 @@
       <c r="P304" s="18" t="n"/>
       <c r="Q304" s="10" t="inlineStr">
         <is>
+          <t>TC-DSC-052</t>
+        </is>
+      </c>
+      <c r="R304" s="10" t="inlineStr">
+        <is>
+          <t>결정적</t>
+        </is>
+      </c>
+      <c r="S304" s="10" t="inlineStr">
+        <is>
+          <t>성인 인증</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="30" customHeight="1">
+      <c r="B305" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C305" s="82" t="inlineStr">
+        <is>
+          <t>스텁·정적</t>
+        </is>
+      </c>
+      <c r="D305" s="84" t="inlineStr">
+        <is>
+          <t>내 작품 탭</t>
+        </is>
+      </c>
+      <c r="E305" s="13" t="inlineStr"/>
+      <c r="F305" s="13" t="inlineStr">
+        <is>
+          <t>성인 계정으로 로그인한 상태</t>
+        </is>
+      </c>
+      <c r="G305" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H305" s="13" t="inlineStr">
+        <is>
+          <t>내 작품 탭을 연다</t>
+        </is>
+      </c>
+      <c r="I305" s="13" t="inlineStr">
+        <is>
+          <t>검증 범위 제외 사유가 노출된다</t>
+        </is>
+      </c>
+      <c r="J305" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K305" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L305" s="15">
+        <f>IF(COUNTIF(M305:M305,"Fail")&gt;0,"Fail",IF(COUNTIF(M305:M305,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M305:M305,"NI")&gt;0,"NI",IF(COUNTIF(M305:M305,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M305" s="16" t="n"/>
+      <c r="N305" s="17" t="n"/>
+      <c r="O305" s="17" t="n"/>
+      <c r="P305" s="13" t="inlineStr">
+        <is>
+          <t>트리가 제외 사유의 정본임을 화면에서 읽히게 합니다 — 스텁이 빈 화면이 아니라 판단의 결과임을 보이는 자리입니다</t>
+        </is>
+      </c>
+      <c r="Q305" s="10" t="inlineStr">
+        <is>
           <t>TC-DSC-053</t>
         </is>
       </c>
-      <c r="R304" s="10" t="inlineStr">
+      <c r="R305" s="10" t="inlineStr">
         <is>
           <t>결정적</t>
         </is>
       </c>
-      <c r="S304" s="10" t="inlineStr">
+      <c r="S305" s="10" t="inlineStr">
         <is>
           <t>성인 인증</t>
         </is>
       </c>
     </row>
+    <row r="306" ht="30" customHeight="1">
+      <c r="B306" s="10">
+        <f>ROW()-9</f>
+        <v/>
+      </c>
+      <c r="C306" s="82" t="inlineStr">
+        <is>
+          <t>스텁·정적</t>
+        </is>
+      </c>
+      <c r="D306" s="84" t="inlineStr">
+        <is>
+          <t>내 작품 탭</t>
+        </is>
+      </c>
+      <c r="E306" s="13" t="inlineStr"/>
+      <c r="F306" s="18" t="n"/>
+      <c r="G306" s="18" t="n"/>
+      <c r="H306" s="18" t="n"/>
+      <c r="I306" s="13" t="inlineStr">
+        <is>
+          <t>트리 제외 영역의 항목명이 노출된다</t>
+        </is>
+      </c>
+      <c r="J306" s="10" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K306" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L306" s="15">
+        <f>IF(COUNTIF(M306:M306,"Fail")&gt;0,"Fail",IF(COUNTIF(M306:M306,"Blocked")&gt;0,"Blocked",IF(COUNTIF(M306:M306,"NI")&gt;0,"NI",IF(COUNTIF(M306:M306,"Pass")&gt;0,"Pass",""))))</f>
+        <v/>
+      </c>
+      <c r="M306" s="16" t="n"/>
+      <c r="N306" s="17" t="n"/>
+      <c r="O306" s="17" t="n"/>
+      <c r="P306" s="18" t="n"/>
+      <c r="Q306" s="10" t="inlineStr">
+        <is>
+          <t>TC-DSC-053</t>
+        </is>
+      </c>
+      <c r="R306" s="10" t="inlineStr">
+        <is>
+          <t>결정적</t>
+        </is>
+      </c>
+      <c r="S306" s="10" t="inlineStr">
+        <is>
+          <t>성인 인증</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="B4:S304"/>
+  <autoFilter ref="B4:S306"/>
   <mergeCells count="387">
     <mergeCell ref="P35:P36"/>
     <mergeCell ref="F133:F134"/>
@@ -21251,11 +21403,9 @@
     <mergeCell ref="P193:P194"/>
     <mergeCell ref="G82:G83"/>
     <mergeCell ref="B6:K6"/>
-    <mergeCell ref="P257:P258"/>
     <mergeCell ref="H191:H192"/>
     <mergeCell ref="F272:F273"/>
     <mergeCell ref="F262:F263"/>
-    <mergeCell ref="G294:G295"/>
     <mergeCell ref="F28:F29"/>
     <mergeCell ref="H28:H29"/>
     <mergeCell ref="P112:P113"/>
@@ -21264,7 +21414,6 @@
     <mergeCell ref="H184:H185"/>
     <mergeCell ref="H244:H245"/>
     <mergeCell ref="G187:G189"/>
-    <mergeCell ref="P270:P271"/>
     <mergeCell ref="G178:G179"/>
     <mergeCell ref="F204:F205"/>
     <mergeCell ref="H133:H134"/>
@@ -21279,28 +21428,28 @@
     <mergeCell ref="G155:G156"/>
     <mergeCell ref="F288:F289"/>
     <mergeCell ref="H288:H289"/>
+    <mergeCell ref="G254:G256"/>
+    <mergeCell ref="F296:F297"/>
     <mergeCell ref="G262:G263"/>
     <mergeCell ref="G237:G238"/>
     <mergeCell ref="G126:G127"/>
     <mergeCell ref="P262:P263"/>
     <mergeCell ref="P178:P179"/>
+    <mergeCell ref="P276:P277"/>
     <mergeCell ref="P214:P215"/>
     <mergeCell ref="P49:P50"/>
     <mergeCell ref="G28:G29"/>
     <mergeCell ref="H124:H125"/>
     <mergeCell ref="G79:G80"/>
-    <mergeCell ref="F270:F271"/>
     <mergeCell ref="F49:F50"/>
     <mergeCell ref="P133:P134"/>
     <mergeCell ref="G152:G154"/>
     <mergeCell ref="H42:H43"/>
-    <mergeCell ref="F284:F285"/>
-    <mergeCell ref="H284:H285"/>
     <mergeCell ref="P135:P136"/>
     <mergeCell ref="P191:P192"/>
-    <mergeCell ref="P296:P298"/>
     <mergeCell ref="P237:P238"/>
     <mergeCell ref="G170:G171"/>
+    <mergeCell ref="P298:P300"/>
     <mergeCell ref="P174:P175"/>
     <mergeCell ref="H108:H109"/>
     <mergeCell ref="H279:H280"/>
@@ -21308,19 +21457,19 @@
     <mergeCell ref="G174:G175"/>
     <mergeCell ref="F104:F105"/>
     <mergeCell ref="L7"/>
-    <mergeCell ref="F296:F298"/>
     <mergeCell ref="P82:P83"/>
     <mergeCell ref="P57:P58"/>
     <mergeCell ref="F106:F107"/>
     <mergeCell ref="P184:P185"/>
     <mergeCell ref="H32:H33"/>
+    <mergeCell ref="F298:F300"/>
     <mergeCell ref="F170:F171"/>
     <mergeCell ref="H170:H171"/>
     <mergeCell ref="F210:F211"/>
     <mergeCell ref="H272:H273"/>
     <mergeCell ref="H210:H211"/>
     <mergeCell ref="H126:H127"/>
-    <mergeCell ref="P294:P295"/>
+    <mergeCell ref="H259:H260"/>
     <mergeCell ref="P250:P251"/>
     <mergeCell ref="G145:G146"/>
     <mergeCell ref="F286:F287"/>
@@ -21335,7 +21484,6 @@
     <mergeCell ref="H208:H209"/>
     <mergeCell ref="H145:H146"/>
     <mergeCell ref="H152:H154"/>
-    <mergeCell ref="G284:G285"/>
     <mergeCell ref="H139:H140"/>
     <mergeCell ref="G69:G71"/>
     <mergeCell ref="H76:H77"/>
@@ -21345,18 +21493,21 @@
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="F178:F179"/>
+    <mergeCell ref="F305:F306"/>
     <mergeCell ref="B9:K9"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="P223:P224"/>
     <mergeCell ref="G191:G192"/>
+    <mergeCell ref="P254:P256"/>
     <mergeCell ref="P124:P125"/>
     <mergeCell ref="G128:G129"/>
     <mergeCell ref="P126:P127"/>
     <mergeCell ref="P231:P233"/>
     <mergeCell ref="H231:H233"/>
-    <mergeCell ref="H277:H278"/>
     <mergeCell ref="G210:G211"/>
     <mergeCell ref="F246:F248"/>
+    <mergeCell ref="H264:H265"/>
+    <mergeCell ref="G259:G260"/>
     <mergeCell ref="F2:S2"/>
     <mergeCell ref="G274:G275"/>
     <mergeCell ref="L5"/>
@@ -21366,7 +21517,9 @@
     <mergeCell ref="P73:P74"/>
     <mergeCell ref="P244:P245"/>
     <mergeCell ref="F168:F169"/>
+    <mergeCell ref="P290:P291"/>
     <mergeCell ref="F24:F25"/>
+    <mergeCell ref="H290:H291"/>
     <mergeCell ref="G223:G224"/>
     <mergeCell ref="G246:G248"/>
     <mergeCell ref="F242:F243"/>
@@ -21382,15 +21535,15 @@
     <mergeCell ref="H237:H238"/>
     <mergeCell ref="H66:H67"/>
     <mergeCell ref="P28:P29"/>
+    <mergeCell ref="H283:H284"/>
     <mergeCell ref="P3:P4"/>
-    <mergeCell ref="F252:F254"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="P239:P240"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="F239:F240"/>
     <mergeCell ref="H239:H240"/>
-    <mergeCell ref="H301:H302"/>
+    <mergeCell ref="G305:G306"/>
     <mergeCell ref="P18:P19"/>
     <mergeCell ref="H214:H215"/>
     <mergeCell ref="H18:H19"/>
@@ -21405,23 +21558,22 @@
     <mergeCell ref="H168:H169"/>
     <mergeCell ref="G231:G233"/>
     <mergeCell ref="H21:H22"/>
+    <mergeCell ref="G264:G265"/>
     <mergeCell ref="F32:F33"/>
     <mergeCell ref="P145:P146"/>
     <mergeCell ref="P152:P154"/>
     <mergeCell ref="H250:H251"/>
     <mergeCell ref="P95:P96"/>
     <mergeCell ref="B7:K7"/>
+    <mergeCell ref="H296:H297"/>
     <mergeCell ref="G124:G125"/>
     <mergeCell ref="H121:H123"/>
-    <mergeCell ref="P252:P254"/>
-    <mergeCell ref="H252:H254"/>
     <mergeCell ref="G59:G60"/>
     <mergeCell ref="G119:G120"/>
     <mergeCell ref="G168:G169"/>
-    <mergeCell ref="F294:F295"/>
+    <mergeCell ref="G290:G291"/>
     <mergeCell ref="P242:P243"/>
     <mergeCell ref="P42:P43"/>
-    <mergeCell ref="P284:P285"/>
     <mergeCell ref="F53:F54"/>
     <mergeCell ref="H26:H27"/>
     <mergeCell ref="H82:H83"/>
@@ -21434,6 +21586,7 @@
     <mergeCell ref="H55:H56"/>
     <mergeCell ref="H11:H12"/>
     <mergeCell ref="G137:G138"/>
+    <mergeCell ref="G283:G284"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="F42:F43"/>
     <mergeCell ref="I3:I4"/>
@@ -21448,18 +21601,16 @@
     <mergeCell ref="P168:P169"/>
     <mergeCell ref="P24:P25"/>
     <mergeCell ref="H24:H25"/>
-    <mergeCell ref="P260:P261"/>
-    <mergeCell ref="F260:F261"/>
-    <mergeCell ref="H260:H261"/>
     <mergeCell ref="B8:K8"/>
     <mergeCell ref="H235:H236"/>
+    <mergeCell ref="P259:P260"/>
     <mergeCell ref="P26:P27"/>
     <mergeCell ref="G21:G22"/>
     <mergeCell ref="P274:P275"/>
+    <mergeCell ref="G296:G297"/>
     <mergeCell ref="F124:F125"/>
     <mergeCell ref="P286:P287"/>
     <mergeCell ref="B5:K5"/>
-    <mergeCell ref="G252:G254"/>
     <mergeCell ref="F126:F127"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="G235:G236"/>
@@ -21470,12 +21621,12 @@
     <mergeCell ref="P187:P189"/>
     <mergeCell ref="G26:G27"/>
     <mergeCell ref="H14:H15"/>
-    <mergeCell ref="F279:F280"/>
     <mergeCell ref="G11:G12"/>
     <mergeCell ref="F281:F282"/>
     <mergeCell ref="F137:F138"/>
     <mergeCell ref="F208:F209"/>
     <mergeCell ref="H137:H138"/>
+    <mergeCell ref="P305:P306"/>
     <mergeCell ref="M3"/>
     <mergeCell ref="G141:G142"/>
     <mergeCell ref="F145:F146"/>
@@ -21494,13 +21645,13 @@
     <mergeCell ref="G108:G109"/>
     <mergeCell ref="G24:G25"/>
     <mergeCell ref="G95:G96"/>
-    <mergeCell ref="G260:G261"/>
     <mergeCell ref="P106:P107"/>
-    <mergeCell ref="P277:P278"/>
+    <mergeCell ref="P264:P265"/>
     <mergeCell ref="F63:F65"/>
     <mergeCell ref="H63:H65"/>
     <mergeCell ref="L3"/>
     <mergeCell ref="P180:P181"/>
+    <mergeCell ref="F290:F291"/>
     <mergeCell ref="P117:P118"/>
     <mergeCell ref="P55:P56"/>
     <mergeCell ref="G159:G160"/>
@@ -21510,8 +21661,6 @@
     <mergeCell ref="H193:H194"/>
     <mergeCell ref="P197:P199"/>
     <mergeCell ref="G121:G123"/>
-    <mergeCell ref="H270:H271"/>
-    <mergeCell ref="H257:H258"/>
     <mergeCell ref="G63:G65"/>
     <mergeCell ref="G197:G199"/>
     <mergeCell ref="H46:H47"/>
@@ -21544,10 +21693,9 @@
     <mergeCell ref="F59:F60"/>
     <mergeCell ref="F108:F109"/>
     <mergeCell ref="H59:H60"/>
-    <mergeCell ref="P301:P302"/>
-    <mergeCell ref="F301:F302"/>
     <mergeCell ref="F95:F96"/>
     <mergeCell ref="P21:P22"/>
+    <mergeCell ref="F276:F277"/>
     <mergeCell ref="F214:F215"/>
     <mergeCell ref="P61:P62"/>
     <mergeCell ref="F303:F304"/>
@@ -21555,12 +21703,14 @@
     <mergeCell ref="F26:F27"/>
     <mergeCell ref="H159:H160"/>
     <mergeCell ref="H128:H129"/>
+    <mergeCell ref="P296:P297"/>
+    <mergeCell ref="P283:P284"/>
     <mergeCell ref="P69:P71"/>
     <mergeCell ref="G35:G36"/>
     <mergeCell ref="G193:G194"/>
     <mergeCell ref="F250:F251"/>
-    <mergeCell ref="G257:G258"/>
     <mergeCell ref="F212:F213"/>
+    <mergeCell ref="F283:F284"/>
     <mergeCell ref="P76:P77"/>
     <mergeCell ref="H212:H213"/>
     <mergeCell ref="F121:F123"/>
@@ -21568,6 +21718,7 @@
     <mergeCell ref="F40:F41"/>
     <mergeCell ref="P51:P52"/>
     <mergeCell ref="G117:G118"/>
+    <mergeCell ref="H276:H277"/>
     <mergeCell ref="F164:F165"/>
     <mergeCell ref="H164:H165"/>
     <mergeCell ref="H49:H50"/>
@@ -21579,22 +21730,19 @@
     <mergeCell ref="G114:G115"/>
     <mergeCell ref="F180:F181"/>
     <mergeCell ref="G212:G213"/>
-    <mergeCell ref="G277:G278"/>
     <mergeCell ref="F46:F47"/>
     <mergeCell ref="F117:F118"/>
-    <mergeCell ref="G270:G271"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="H104:H105"/>
     <mergeCell ref="P235:P236"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="G301:G302"/>
-    <mergeCell ref="H296:H298"/>
     <mergeCell ref="P128:P129"/>
     <mergeCell ref="H106:H107"/>
     <mergeCell ref="H246:H248"/>
     <mergeCell ref="G61:G62"/>
     <mergeCell ref="G303:G304"/>
+    <mergeCell ref="H298:H300"/>
     <mergeCell ref="P159:P160"/>
     <mergeCell ref="F235:F236"/>
     <mergeCell ref="N5:S9"/>
@@ -21608,12 +21756,13 @@
     <mergeCell ref="F197:F199"/>
     <mergeCell ref="H197:H199"/>
     <mergeCell ref="P212:P213"/>
+    <mergeCell ref="F264:F265"/>
     <mergeCell ref="G250:G251"/>
     <mergeCell ref="P143:P144"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="H101:H102"/>
-    <mergeCell ref="H294:H295"/>
     <mergeCell ref="P14:P15"/>
+    <mergeCell ref="G276:G277"/>
     <mergeCell ref="G214:G215"/>
     <mergeCell ref="P108:P109"/>
     <mergeCell ref="G164:G165"/>
@@ -21622,14 +21771,17 @@
     <mergeCell ref="G184:G185"/>
     <mergeCell ref="H112:H113"/>
     <mergeCell ref="F114:F115"/>
+    <mergeCell ref="F254:F256"/>
     <mergeCell ref="H114:H115"/>
+    <mergeCell ref="H254:H256"/>
     <mergeCell ref="H178:H179"/>
+    <mergeCell ref="H305:H306"/>
     <mergeCell ref="G133:G134"/>
     <mergeCell ref="H242:H243"/>
     <mergeCell ref="G135:G136"/>
     <mergeCell ref="F274:F275"/>
-    <mergeCell ref="G296:G298"/>
     <mergeCell ref="P279:P280"/>
+    <mergeCell ref="G298:G300"/>
     <mergeCell ref="P104:P105"/>
     <mergeCell ref="P164:P165"/>
   </mergeCells>
@@ -21713,536 +21865,536 @@
   </cols>
   <sheetData>
     <row r="2" ht="19" customHeight="1">
-      <c r="B2" s="84" t="inlineStr">
+      <c r="B2" s="85" t="inlineStr">
         <is>
           <t>커버리지 요약</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="85" t="inlineStr">
+      <c r="B3" s="86" t="inlineStr">
         <is>
           <t>Test Case 시트를 참조하는 수식으로 자동 집계됩니다. 행을 추가하면 아래 범위를 넓히세요.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="86" t="inlineStr">
+      <c r="B4" s="87" t="inlineStr">
         <is>
           <t>기준 골격 버전</t>
         </is>
       </c>
-      <c r="C4" s="87" t="inlineStr">
-        <is>
-          <t>qa-lab-miyonchat-tree-v1.13</t>
-        </is>
-      </c>
-      <c r="D4" s="88" t="n"/>
-      <c r="E4" s="88" t="n"/>
+      <c r="C4" s="88" t="inlineStr">
+        <is>
+          <t>qa-lab-miyonchat-tree-v1.14</t>
+        </is>
+      </c>
+      <c r="D4" s="89" t="n"/>
+      <c r="E4" s="89" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="89" t="inlineStr">
+      <c r="B5" s="90" t="inlineStr">
         <is>
           <t>1-Depth (영역)</t>
         </is>
       </c>
-      <c r="C5" s="89" t="inlineStr">
+      <c r="C5" s="90" t="inlineStr">
         <is>
           <t>TC 수</t>
         </is>
       </c>
-      <c r="D5" s="89" t="inlineStr">
+      <c r="D5" s="90" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="E5" s="88" t="n"/>
-      <c r="F5" s="88" t="n"/>
-      <c r="G5" s="89" t="inlineStr">
+      <c r="E5" s="89" t="n"/>
+      <c r="F5" s="89" t="n"/>
+      <c r="G5" s="90" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="H5" s="88" t="n"/>
-      <c r="I5" s="88" t="n"/>
-      <c r="J5" s="88" t="n"/>
-      <c r="K5" s="88" t="n"/>
+      <c r="H5" s="89" t="n"/>
+      <c r="I5" s="89" t="n"/>
+      <c r="J5" s="89" t="n"/>
+      <c r="K5" s="89" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="88" t="n"/>
-      <c r="C6" s="88" t="n"/>
-      <c r="D6" s="90" t="inlineStr">
+      <c r="B6" s="89" t="n"/>
+      <c r="C6" s="89" t="n"/>
+      <c r="D6" s="91" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E6" s="90" t="inlineStr">
+      <c r="E6" s="91" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="F6" s="90" t="inlineStr">
+      <c r="F6" s="91" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G6" s="90" t="inlineStr">
+      <c r="G6" s="91" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="H6" s="90" t="inlineStr">
+      <c r="H6" s="91" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="I6" s="90" t="inlineStr">
+      <c r="I6" s="91" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="J6" s="90" t="inlineStr">
+      <c r="J6" s="91" t="inlineStr">
         <is>
           <t>Pass율</t>
         </is>
       </c>
-      <c r="K6" s="88" t="n"/>
+      <c r="K6" s="89" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="91" t="inlineStr">
+      <c r="B7" s="92" t="inlineStr">
         <is>
           <t>웹 진입</t>
         </is>
       </c>
-      <c r="C7" s="92">
+      <c r="C7" s="93">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B7)</f>
         <v/>
       </c>
-      <c r="D7" s="92">
+      <c r="D7" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B7,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E7" s="92">
+      <c r="E7" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B7,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F7" s="92">
+      <c r="F7" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B7,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G7" s="92">
+      <c r="G7" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B7,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H7" s="92">
+      <c r="H7" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B7,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I7" s="92">
+      <c r="I7" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B7,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J7" s="93">
+      <c r="J7" s="94">
         <f>IF(G7+H7=0,"",G7/(G7+H7))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="91" t="inlineStr">
+      <c r="B8" s="92" t="inlineStr">
         <is>
           <t>전역 셸</t>
         </is>
       </c>
-      <c r="C8" s="92">
+      <c r="C8" s="93">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B8)</f>
         <v/>
       </c>
-      <c r="D8" s="92">
+      <c r="D8" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B8,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E8" s="92">
+      <c r="E8" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B8,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F8" s="92">
+      <c r="F8" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B8,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G8" s="92">
+      <c r="G8" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B8,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H8" s="92">
+      <c r="H8" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B8,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I8" s="92">
+      <c r="I8" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B8,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J8" s="93">
+      <c r="J8" s="94">
         <f>IF(G8+H8=0,"",G8/(G8+H8))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="91" t="inlineStr">
+      <c r="B9" s="92" t="inlineStr">
         <is>
           <t>홈 화면</t>
         </is>
       </c>
-      <c r="C9" s="92">
+      <c r="C9" s="93">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B9)</f>
         <v/>
       </c>
-      <c r="D9" s="92">
+      <c r="D9" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B9,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E9" s="92">
+      <c r="E9" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B9,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F9" s="92">
+      <c r="F9" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B9,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G9" s="92">
+      <c r="G9" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B9,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H9" s="92">
+      <c r="H9" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B9,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I9" s="92">
+      <c r="I9" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B9,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J9" s="93">
+      <c r="J9" s="94">
         <f>IF(G9+H9=0,"",G9/(G9+H9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="91" t="inlineStr">
+      <c r="B10" s="92" t="inlineStr">
         <is>
           <t>캐릭터 페이지</t>
         </is>
       </c>
-      <c r="C10" s="92">
+      <c r="C10" s="93">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B10)</f>
         <v/>
       </c>
-      <c r="D10" s="92">
+      <c r="D10" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B10,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E10" s="92">
+      <c r="E10" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B10,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F10" s="92">
+      <c r="F10" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B10,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G10" s="92">
+      <c r="G10" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B10,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H10" s="92">
+      <c r="H10" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B10,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I10" s="92">
+      <c r="I10" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B10,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J10" s="93">
+      <c r="J10" s="94">
         <f>IF(G10+H10=0,"",G10/(G10+H10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="91" t="inlineStr">
+      <c r="B11" s="92" t="inlineStr">
         <is>
           <t>대화 프로필 화면</t>
         </is>
       </c>
-      <c r="C11" s="92">
+      <c r="C11" s="93">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B11)</f>
         <v/>
       </c>
-      <c r="D11" s="92">
+      <c r="D11" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B11,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E11" s="92">
+      <c r="E11" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B11,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F11" s="92">
+      <c r="F11" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B11,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G11" s="92">
+      <c r="G11" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B11,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H11" s="92">
+      <c r="H11" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B11,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I11" s="92">
+      <c r="I11" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B11,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J11" s="93">
+      <c r="J11" s="94">
         <f>IF(G11+H11=0,"",G11/(G11+H11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="91" t="inlineStr">
+      <c r="B12" s="92" t="inlineStr">
         <is>
           <t>대화방</t>
         </is>
       </c>
-      <c r="C12" s="92">
+      <c r="C12" s="93">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B12)</f>
         <v/>
       </c>
-      <c r="D12" s="92">
+      <c r="D12" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B12,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E12" s="92">
+      <c r="E12" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B12,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F12" s="92">
+      <c r="F12" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B12,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G12" s="92">
+      <c r="G12" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B12,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H12" s="92">
+      <c r="H12" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B12,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I12" s="92">
+      <c r="I12" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B12,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J12" s="93">
+      <c r="J12" s="94">
         <f>IF(G12+H12=0,"",G12/(G12+H12))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="91" t="inlineStr">
+      <c r="B13" s="92" t="inlineStr">
         <is>
           <t>채팅 탭</t>
         </is>
       </c>
-      <c r="C13" s="92">
+      <c r="C13" s="93">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B13)</f>
         <v/>
       </c>
-      <c r="D13" s="92">
+      <c r="D13" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B13,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E13" s="92">
+      <c r="E13" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B13,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F13" s="92">
+      <c r="F13" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B13,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G13" s="92">
+      <c r="G13" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B13,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H13" s="92">
+      <c r="H13" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B13,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I13" s="92">
+      <c r="I13" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B13,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J13" s="93">
+      <c r="J13" s="94">
         <f>IF(G13+H13=0,"",G13/(G13+H13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="91" t="inlineStr">
+      <c r="B14" s="92" t="inlineStr">
         <is>
           <t>MY 탭</t>
         </is>
       </c>
-      <c r="C14" s="92">
+      <c r="C14" s="93">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B14)</f>
         <v/>
       </c>
-      <c r="D14" s="92">
+      <c r="D14" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B14,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E14" s="92">
+      <c r="E14" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B14,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F14" s="92">
+      <c r="F14" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B14,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G14" s="92">
+      <c r="G14" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B14,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H14" s="92">
+      <c r="H14" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B14,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I14" s="92">
+      <c r="I14" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B14,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J14" s="93">
+      <c r="J14" s="94">
         <f>IF(G14+H14=0,"",G14/(G14+H14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="91" t="inlineStr">
+      <c r="B15" s="92" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
-      <c r="C15" s="92">
+      <c r="C15" s="93">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B15)</f>
         <v/>
       </c>
-      <c r="D15" s="92">
+      <c r="D15" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B15,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E15" s="92">
+      <c r="E15" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B15,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F15" s="92">
+      <c r="F15" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B15,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G15" s="92">
+      <c r="G15" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B15,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H15" s="92">
+      <c r="H15" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B15,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I15" s="92">
+      <c r="I15" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B15,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J15" s="93">
+      <c r="J15" s="94">
         <f>IF(G15+H15=0,"",G15/(G15+H15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="91" t="inlineStr">
+      <c r="B16" s="92" t="inlineStr">
         <is>
           <t>스텁·정적</t>
         </is>
       </c>
-      <c r="C16" s="92">
+      <c r="C16" s="93">
         <f>COUNTIF('Test Case'!$C$10:$C$500,$B16)</f>
         <v/>
       </c>
-      <c r="D16" s="92">
+      <c r="D16" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B16,'Test Case'!$K$10:$K$500,"High")</f>
         <v/>
       </c>
-      <c r="E16" s="92">
+      <c r="E16" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B16,'Test Case'!$K$10:$K$500,"Medium")</f>
         <v/>
       </c>
-      <c r="F16" s="92">
+      <c r="F16" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B16,'Test Case'!$K$10:$K$500,"Low")</f>
         <v/>
       </c>
-      <c r="G16" s="92">
+      <c r="G16" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B16,'Test Case'!$M$10:$M$500,"Pass")</f>
         <v/>
       </c>
-      <c r="H16" s="92">
+      <c r="H16" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B16,'Test Case'!$M$10:$M$500,"Fail")</f>
         <v/>
       </c>
-      <c r="I16" s="92">
+      <c r="I16" s="93">
         <f>COUNTIFS('Test Case'!$C$10:$C$500,$B16,'Test Case'!$M$10:$M$500,"Blocked")</f>
         <v/>
       </c>
-      <c r="J16" s="93">
+      <c r="J16" s="94">
         <f>IF(G16+H16=0,"",G16/(G16+H16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="94" t="inlineStr">
+      <c r="B17" s="95" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="C17" s="95">
+      <c r="C17" s="96">
         <f>SUM(C7:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="95">
+      <c r="D17" s="96">
         <f>SUM(D7:D16)</f>
         <v/>
       </c>
-      <c r="E17" s="95">
+      <c r="E17" s="96">
         <f>SUM(E7:E16)</f>
         <v/>
       </c>
-      <c r="F17" s="95">
+      <c r="F17" s="96">
         <f>SUM(F7:F16)</f>
         <v/>
       </c>
-      <c r="G17" s="95">
+      <c r="G17" s="96">
         <f>SUM(G7:G16)</f>
         <v/>
       </c>
-      <c r="H17" s="95">
+      <c r="H17" s="96">
         <f>SUM(H7:H16)</f>
         <v/>
       </c>
-      <c r="I17" s="95">
+      <c r="I17" s="96">
         <f>SUM(I7:I16)</f>
         <v/>
       </c>
-      <c r="J17" s="96">
+      <c r="J17" s="97">
         <f>IF(G17+H17=0,"",G17/(G17+H17))</f>
         <v/>
       </c>
-      <c r="K17" s="95">
+      <c r="K17" s="96">
         <f>SUM(K7:K16)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="85" t="inlineStr">
+      <c r="B19" s="86" t="inlineStr">
         <is>
           <t>TC 수 = 스텝 행 수(1-Depth 기준) · Pass/Fail/Blocked도 같은 행 단위(Result 열) · Pass율 = Pass ÷ (Pass + Fail) — NI·Blocked는 분모에서 제외합니다</t>
         </is>
@@ -22293,129 +22445,129 @@
   </cols>
   <sheetData>
     <row r="2" ht="30" customHeight="1">
-      <c r="B2" s="97" t="inlineStr">
+      <c r="B2" s="98" t="inlineStr">
         <is>
           <t>프로젝트 ID</t>
         </is>
       </c>
-      <c r="C2" s="97" t="inlineStr">
+      <c r="C2" s="98" t="inlineStr">
         <is>
           <t>Issue No.</t>
         </is>
       </c>
-      <c r="D2" s="97" t="inlineStr">
+      <c r="D2" s="98" t="inlineStr">
         <is>
           <t>이슈 상태</t>
         </is>
       </c>
-      <c r="E2" s="97" t="inlineStr">
+      <c r="E2" s="98" t="inlineStr">
         <is>
           <t>요약(Summary)</t>
         </is>
       </c>
-      <c r="F2" s="97" t="inlineStr">
+      <c r="F2" s="98" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="G2" s="97" t="inlineStr">
+      <c r="G2" s="98" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="H2" s="97" t="inlineStr">
+      <c r="H2" s="98" t="inlineStr">
         <is>
           <t>빈도</t>
         </is>
       </c>
-      <c r="I2" s="97" t="inlineStr">
+      <c r="I2" s="98" t="inlineStr">
         <is>
           <t>영향 받는 버전</t>
         </is>
       </c>
-      <c r="J2" s="97" t="inlineStr">
+      <c r="J2" s="98" t="inlineStr">
         <is>
           <t>수정 버전</t>
         </is>
       </c>
-      <c r="K2" s="97" t="inlineStr">
+      <c r="K2" s="98" t="inlineStr">
         <is>
           <t>해결책</t>
         </is>
       </c>
-      <c r="L2" s="97" t="inlineStr">
+      <c r="L2" s="98" t="inlineStr">
         <is>
           <t>환경</t>
         </is>
       </c>
-      <c r="M2" s="97" t="inlineStr">
+      <c r="M2" s="98" t="inlineStr">
         <is>
           <t>레이블</t>
         </is>
       </c>
-      <c r="N2" s="97" t="inlineStr">
+      <c r="N2" s="98" t="inlineStr">
         <is>
           <t>보고자</t>
         </is>
       </c>
-      <c r="O2" s="97" t="inlineStr">
+      <c r="O2" s="98" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="P2" s="97" t="inlineStr">
+      <c r="P2" s="98" t="inlineStr">
         <is>
           <t>관측자</t>
         </is>
       </c>
-      <c r="Q2" s="97" t="inlineStr">
+      <c r="Q2" s="98" t="inlineStr">
         <is>
           <t>첨부파일</t>
         </is>
       </c>
-      <c r="R2" s="97" t="inlineStr">
+      <c r="R2" s="98" t="inlineStr">
         <is>
           <t>스프린트</t>
         </is>
       </c>
-      <c r="S2" s="97" t="inlineStr">
+      <c r="S2" s="98" t="inlineStr">
         <is>
           <t>이슈 등록일</t>
         </is>
       </c>
-      <c r="T2" s="97" t="inlineStr">
+      <c r="T2" s="98" t="inlineStr">
         <is>
           <t>이슈 최종 수정일자</t>
         </is>
       </c>
-      <c r="U2" s="97" t="inlineStr">
+      <c r="U2" s="98" t="inlineStr">
         <is>
           <t>이슈 상태 최종 변경일자</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="98" t="inlineStr">
+      <c r="B3" s="99" t="inlineStr">
         <is>
           <t>miyonchat</t>
         </is>
       </c>
-      <c r="C3" s="98" t="inlineStr">
+      <c r="C3" s="99" t="inlineStr">
         <is>
           <t>miyonchat-1</t>
         </is>
       </c>
-      <c r="D3" s="98" t="inlineStr">
+      <c r="D3" s="99" t="inlineStr">
         <is>
           <t>Resolved</t>
         </is>
       </c>
-      <c r="E3" s="99" t="inlineStr">
+      <c r="E3" s="100" t="inlineStr">
         <is>
           <t>디버그 콘솔 &gt; 전체 초기화(reset) 수행 &gt; 계정 A 로그인 시, 성인 인증이 해제된 상태로 시작됨</t>
         </is>
       </c>
-      <c r="F3" s="99" t="inlineStr">
+      <c r="F3" s="100" t="inlineStr">
         <is>
           <t>Pre-condition: SUT 진입
 Reproduce Step: 디버그 콘솔 열기 &gt; [전체 초기화] 선택 &gt; 계정 A로 로그인 &gt; 간편 프로필 확인
@@ -22424,96 +22576,96 @@
 QA Comment: 계정 상태 생성 함수에 계정 식별자를 전달하지 않아 기본값 판정이 항상 거짓이 됨. 자동화가 매 테스트 전 reset()을 호출하는 구조라, 남아 있으면 게이팅 계열 TC 전체가 미인증 상태에서 실행되어 결과를 신뢰할 수 없음</t>
         </is>
       </c>
-      <c r="G3" s="98" t="inlineStr">
+      <c r="G3" s="99" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H3" s="98" t="inlineStr">
+      <c r="H3" s="99" t="inlineStr">
         <is>
           <t>Always</t>
         </is>
       </c>
-      <c r="I3" s="98" t="inlineStr">
+      <c r="I3" s="99" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev_RC1</t>
         </is>
       </c>
-      <c r="J3" s="98" t="inlineStr">
+      <c r="J3" s="99" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev_RC2</t>
         </is>
       </c>
-      <c r="K3" s="98" t="inlineStr">
+      <c r="K3" s="99" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="L3" s="98" t="inlineStr">
+      <c r="L3" s="99" t="inlineStr">
         <is>
           <t>PC웹</t>
         </is>
       </c>
-      <c r="M3" s="98" t="inlineStr">
+      <c r="M3" s="99" t="inlineStr">
         <is>
           <t>계정/게이팅</t>
         </is>
       </c>
-      <c r="N3" s="98" t="inlineStr">
+      <c r="N3" s="99" t="inlineStr">
         <is>
           <t>정준호</t>
         </is>
       </c>
-      <c r="O3" s="98" t="inlineStr">
+      <c r="O3" s="99" t="inlineStr">
         <is>
           <t>Claude Opus 5</t>
         </is>
       </c>
-      <c r="P3" s="98" t="inlineStr"/>
-      <c r="Q3" s="98" t="inlineStr"/>
-      <c r="R3" s="98" t="inlineStr">
+      <c r="P3" s="99" t="inlineStr"/>
+      <c r="Q3" s="99" t="inlineStr"/>
+      <c r="R3" s="99" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev</t>
         </is>
       </c>
-      <c r="S3" s="98" t="inlineStr">
+      <c r="S3" s="99" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="T3" s="98" t="inlineStr">
+      <c r="T3" s="99" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="U3" s="98" t="inlineStr">
+      <c r="U3" s="99" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="98" t="inlineStr">
+      <c r="B4" s="99" t="inlineStr">
         <is>
           <t>miyonchat</t>
         </is>
       </c>
-      <c r="C4" s="98" t="inlineStr">
+      <c r="C4" s="99" t="inlineStr">
         <is>
           <t>miyonchat-2</t>
         </is>
       </c>
-      <c r="D4" s="98" t="inlineStr">
+      <c r="D4" s="99" t="inlineStr">
         <is>
           <t>Resolved</t>
         </is>
       </c>
-      <c r="E4" s="99" t="inlineStr">
+      <c r="E4" s="100" t="inlineStr">
         <is>
           <t>세션 만료 상태에서 브라우저 새로고침 시, 만료가 풀리고 로그인 상태로 되살아남</t>
         </is>
       </c>
-      <c r="F4" s="99" t="inlineStr">
+      <c r="F4" s="100" t="inlineStr">
         <is>
           <t>Pre-condition: 계정 A로 로그인한 상태
 Reproduce Step: 디버그 콘솔 &gt; 상태 스위처 [세션 만료] &gt; [저장] &gt; 브라우저 새로고침(F5)
@@ -22522,96 +22674,96 @@
 QA Comment: 세션 지속(RC22)을 넣으면서 expireSession()이 메모리 상태만 만료로 바꾸고 브라우저 저장소의 세션은 그대로 두어, 다음 부팅의 복원이 그 저장분을 읽어 만료를 덮어씀. 실서비스라면 만료된 세션을 새로고침만으로 되살릴 수 있는 우회 경로가 됨. TC-GAT-011(만료 상태 로그인 필요 화면 직접 진입)을 자동화하다 검출</t>
         </is>
       </c>
-      <c r="G4" s="98" t="inlineStr">
+      <c r="G4" s="99" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H4" s="98" t="inlineStr">
+      <c r="H4" s="99" t="inlineStr">
         <is>
           <t>Always</t>
         </is>
       </c>
-      <c r="I4" s="98" t="inlineStr">
+      <c r="I4" s="99" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev_RC22</t>
         </is>
       </c>
-      <c r="J4" s="98" t="inlineStr">
+      <c r="J4" s="99" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev_RC23</t>
         </is>
       </c>
-      <c r="K4" s="98" t="inlineStr">
+      <c r="K4" s="99" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="L4" s="98" t="inlineStr">
+      <c r="L4" s="99" t="inlineStr">
         <is>
           <t>PC웹</t>
         </is>
       </c>
-      <c r="M4" s="98" t="inlineStr">
+      <c r="M4" s="99" t="inlineStr">
         <is>
           <t>계정/게이팅</t>
         </is>
       </c>
-      <c r="N4" s="98" t="inlineStr">
+      <c r="N4" s="99" t="inlineStr">
         <is>
           <t>정준호</t>
         </is>
       </c>
-      <c r="O4" s="98" t="inlineStr">
+      <c r="O4" s="99" t="inlineStr">
         <is>
           <t>Claude Opus 5</t>
         </is>
       </c>
-      <c r="P4" s="98" t="inlineStr"/>
-      <c r="Q4" s="98" t="inlineStr"/>
-      <c r="R4" s="98" t="inlineStr">
+      <c r="P4" s="99" t="inlineStr"/>
+      <c r="Q4" s="99" t="inlineStr"/>
+      <c r="R4" s="99" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev</t>
         </is>
       </c>
-      <c r="S4" s="98" t="inlineStr">
+      <c r="S4" s="99" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="T4" s="98" t="inlineStr">
+      <c r="T4" s="99" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="U4" s="98" t="inlineStr">
+      <c r="U4" s="99" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="98" t="inlineStr">
+      <c r="B5" s="99" t="inlineStr">
         <is>
           <t>miyonchat</t>
         </is>
       </c>
-      <c r="C5" s="98" t="inlineStr">
+      <c r="C5" s="99" t="inlineStr">
         <is>
           <t>miyonchat-3</t>
         </is>
       </c>
-      <c r="D5" s="98" t="inlineStr">
+      <c r="D5" s="99" t="inlineStr">
         <is>
           <t>Resolved</t>
         </is>
       </c>
-      <c r="E5" s="99" t="inlineStr">
+      <c r="E5" s="100" t="inlineStr">
         <is>
           <t>세션 만료 상태에서 전송·저장·미션 수령이 그대로 수행됨 (차단이 안내 모달의 딤에만 의존)</t>
         </is>
       </c>
-      <c r="F5" s="99" t="inlineStr">
+      <c r="F5" s="100" t="inlineStr">
         <is>
           <t>Pre-condition: 계정 A로 로그인해 대화방에 진입한 상태
 Reproduce Step: 디버그 콘솔 &gt; 상태 스위처 [세션 만료] &gt; [저장] &gt; 대화방에서 전송 시도(자동화는 sendMessage 직접 호출) &gt; 잔액·메시지 확인
@@ -22620,69 +22772,69 @@
 QA Comment: `canAct()`가 「만료 상태에서는 전송·저장·수령이 모두 막힙니다」라는 주석과 함께 정의되어 있으나 **어디에서도 호출되지 않는 죽은 코드**였음. 실제 차단은 만료 안내 모달이 화면을 덮는 것에만 의존하고 있어, 모달이 뜨지 않는 경로가 생기면 게이트가 통째로 사라짐. sendMessage·saveSlot·claimDaily·claimWelcome 네 곳에 게이트를 넣어 동작 자체에서 막도록 수정. TC-ENT-004(만료 상태 전송 차단)를 자동화하다 검출</t>
         </is>
       </c>
-      <c r="G5" s="98" t="inlineStr">
+      <c r="G5" s="99" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H5" s="98" t="inlineStr">
+      <c r="H5" s="99" t="inlineStr">
         <is>
           <t>Always</t>
         </is>
       </c>
-      <c r="I5" s="98" t="inlineStr">
+      <c r="I5" s="99" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev_RC23</t>
         </is>
       </c>
-      <c r="J5" s="98" t="inlineStr">
+      <c r="J5" s="99" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev_RC24</t>
         </is>
       </c>
-      <c r="K5" s="98" t="inlineStr">
+      <c r="K5" s="99" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="L5" s="98" t="inlineStr">
+      <c r="L5" s="99" t="inlineStr">
         <is>
           <t>PC웹</t>
         </is>
       </c>
-      <c r="M5" s="98" t="inlineStr">
+      <c r="M5" s="99" t="inlineStr">
         <is>
           <t>앱 진입/세션</t>
         </is>
       </c>
-      <c r="N5" s="98" t="inlineStr">
+      <c r="N5" s="99" t="inlineStr">
         <is>
           <t>정준호</t>
         </is>
       </c>
-      <c r="O5" s="98" t="inlineStr">
+      <c r="O5" s="99" t="inlineStr">
         <is>
           <t>Claude Opus 5</t>
         </is>
       </c>
-      <c r="P5" s="98" t="inlineStr"/>
-      <c r="Q5" s="98" t="inlineStr"/>
-      <c r="R5" s="98" t="inlineStr">
+      <c r="P5" s="99" t="inlineStr"/>
+      <c r="Q5" s="99" t="inlineStr"/>
+      <c r="R5" s="99" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev</t>
         </is>
       </c>
-      <c r="S5" s="98" t="inlineStr">
+      <c r="S5" s="99" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="T5" s="98" t="inlineStr">
+      <c r="T5" s="99" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="U5" s="98" t="inlineStr">
+      <c r="U5" s="99" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
@@ -22786,327 +22938,327 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="100" t="inlineStr">
+      <c r="B2" s="101" t="inlineStr">
         <is>
           <t>프로젝트</t>
         </is>
       </c>
-      <c r="C2" s="100" t="inlineStr">
+      <c r="C2" s="101" t="inlineStr">
         <is>
           <t>실행 주체</t>
         </is>
       </c>
-      <c r="D2" s="100" t="inlineStr">
+      <c r="D2" s="101" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="E2" s="100" t="inlineStr">
+      <c r="E2" s="101" t="inlineStr">
         <is>
           <t>이슈 상태</t>
         </is>
       </c>
-      <c r="F2" s="100" t="inlineStr">
+      <c r="F2" s="101" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="G2" s="100" t="inlineStr">
+      <c r="G2" s="101" t="inlineStr">
         <is>
           <t>빈도</t>
         </is>
       </c>
-      <c r="H2" s="100" t="inlineStr">
+      <c r="H2" s="101" t="inlineStr">
         <is>
           <t>버전(영향/수정 공용)</t>
         </is>
       </c>
-      <c r="I2" s="100" t="inlineStr">
+      <c r="I2" s="101" t="inlineStr">
         <is>
           <t>해결책</t>
         </is>
       </c>
-      <c r="J2" s="100" t="inlineStr">
+      <c r="J2" s="101" t="inlineStr">
         <is>
           <t>환경</t>
         </is>
       </c>
-      <c r="K2" s="100" t="inlineStr">
+      <c r="K2" s="101" t="inlineStr">
         <is>
           <t>레이블</t>
         </is>
       </c>
-      <c r="L2" s="100" t="inlineStr">
+      <c r="L2" s="101" t="inlineStr">
         <is>
           <t>보고자</t>
         </is>
       </c>
-      <c r="M2" s="100" t="inlineStr">
+      <c r="M2" s="101" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="N2" s="100" t="inlineStr">
+      <c r="N2" s="101" t="inlineStr">
         <is>
           <t>스프린트</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="101" t="inlineStr">
+      <c r="B3" s="102" t="inlineStr">
         <is>
           <t>miyonchat</t>
         </is>
       </c>
-      <c r="C3" s="101" t="inlineStr">
+      <c r="C3" s="102" t="inlineStr">
         <is>
           <t>자동화 전용</t>
         </is>
       </c>
-      <c r="D3" s="101" t="inlineStr">
+      <c r="D3" s="102" t="inlineStr">
         <is>
           <t>미로그인</t>
         </is>
       </c>
-      <c r="E3" s="101" t="inlineStr">
+      <c r="E3" s="102" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="F3" s="101" t="inlineStr">
+      <c r="F3" s="102" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="G3" s="101" t="inlineStr">
+      <c r="G3" s="102" t="inlineStr">
         <is>
           <t>Always</t>
         </is>
       </c>
-      <c r="H3" s="101" t="inlineStr">
+      <c r="H3" s="102" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev_RC1</t>
         </is>
       </c>
-      <c r="I3" s="101" t="inlineStr">
+      <c r="I3" s="102" t="inlineStr">
         <is>
           <t>Fixed</t>
         </is>
       </c>
-      <c r="J3" s="101" t="inlineStr">
+      <c r="J3" s="102" t="inlineStr">
         <is>
           <t>PC웹</t>
         </is>
       </c>
-      <c r="K3" s="101" t="inlineStr">
+      <c r="K3" s="102" t="inlineStr">
         <is>
           <t>앱 진입/세션</t>
         </is>
       </c>
-      <c r="L3" s="101" t="inlineStr">
+      <c r="L3" s="102" t="inlineStr">
         <is>
           <t>정준호</t>
         </is>
       </c>
-      <c r="M3" s="101" t="inlineStr">
+      <c r="M3" s="102" t="inlineStr">
         <is>
           <t>Claude Opus 5</t>
         </is>
       </c>
-      <c r="N3" s="101" t="inlineStr">
+      <c r="N3" s="102" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="C4" s="101" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="D4" s="101" t="inlineStr">
+      <c r="C4" s="102" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="D4" s="102" t="inlineStr">
         <is>
           <t>본인인증 미진행</t>
         </is>
       </c>
-      <c r="E4" s="101" t="inlineStr">
+      <c r="E4" s="102" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="F4" s="101" t="inlineStr">
+      <c r="F4" s="102" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G4" s="101" t="inlineStr">
+      <c r="G4" s="102" t="inlineStr">
         <is>
           <t>Often</t>
         </is>
       </c>
-      <c r="H4" s="101" t="inlineStr">
+      <c r="H4" s="102" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev_RC2</t>
         </is>
       </c>
-      <c r="I4" s="101" t="inlineStr">
+      <c r="I4" s="102" t="inlineStr">
         <is>
           <t>Won't Do</t>
         </is>
       </c>
-      <c r="K4" s="101" t="inlineStr">
+      <c r="K4" s="102" t="inlineStr">
         <is>
           <t>계정/게이팅</t>
         </is>
       </c>
-      <c r="N4" s="101" t="inlineStr">
+      <c r="N4" s="102" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_RT1</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="101" t="inlineStr">
+      <c r="C5" s="102" t="inlineStr">
         <is>
           <t>사람 전용</t>
         </is>
       </c>
-      <c r="D5" s="101" t="inlineStr">
+      <c r="D5" s="102" t="inlineStr">
         <is>
           <t>성인 인증</t>
         </is>
       </c>
-      <c r="E5" s="101" t="inlineStr">
+      <c r="E5" s="102" t="inlineStr">
         <is>
           <t>Resolved</t>
         </is>
       </c>
-      <c r="F5" s="101" t="inlineStr">
+      <c r="F5" s="102" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G5" s="101" t="inlineStr">
+      <c r="G5" s="102" t="inlineStr">
         <is>
           <t>Sometimes</t>
         </is>
       </c>
-      <c r="H5" s="101" t="inlineStr">
+      <c r="H5" s="102" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_Dev_RC3</t>
         </is>
       </c>
-      <c r="I5" s="101" t="inlineStr">
+      <c r="I5" s="102" t="inlineStr">
         <is>
           <t>Won't Fix</t>
         </is>
       </c>
-      <c r="K5" s="101" t="inlineStr">
+      <c r="K5" s="102" t="inlineStr">
         <is>
           <t>탐색/발견</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="D6" s="101" t="inlineStr">
+      <c r="D6" s="102" t="inlineStr">
         <is>
           <t>미성년</t>
         </is>
       </c>
-      <c r="E6" s="101" t="inlineStr">
+      <c r="E6" s="102" t="inlineStr">
         <is>
           <t>Reopen</t>
         </is>
       </c>
-      <c r="G6" s="101" t="inlineStr">
+      <c r="G6" s="102" t="inlineStr">
         <is>
           <t>Once</t>
         </is>
       </c>
-      <c r="H6" s="101" t="inlineStr">
+      <c r="H6" s="102" t="inlineStr">
         <is>
           <t>PC웹_Ver1.0_RT1_RC1</t>
         </is>
       </c>
-      <c r="I6" s="101" t="inlineStr">
+      <c r="I6" s="102" t="inlineStr">
         <is>
           <t>Duplicate</t>
         </is>
       </c>
-      <c r="K6" s="101" t="inlineStr">
+      <c r="K6" s="102" t="inlineStr">
         <is>
           <t>유저 페르소나</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="D7" s="101" t="inlineStr">
+      <c r="D7" s="102" t="inlineStr">
         <is>
           <t>세션 만료</t>
         </is>
       </c>
-      <c r="E7" s="101" t="inlineStr">
+      <c r="E7" s="102" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="I7" s="101" t="inlineStr">
+      <c r="I7" s="102" t="inlineStr">
         <is>
           <t>Incomplete</t>
         </is>
       </c>
-      <c r="K7" s="101" t="inlineStr">
+      <c r="K7" s="102" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="I8" s="101" t="inlineStr">
+      <c r="I8" s="102" t="inlineStr">
         <is>
           <t>Cannot Reproduce</t>
         </is>
       </c>
-      <c r="K8" s="101" t="inlineStr">
+      <c r="K8" s="102" t="inlineStr">
         <is>
           <t>서사 시스템</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="I9" s="101" t="inlineStr">
+      <c r="I9" s="102" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="K9" s="101" t="inlineStr">
+      <c r="K9" s="102" t="inlineStr">
         <is>
           <t>대화 세션</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="I10" s="101" t="inlineStr">
+      <c r="I10" s="102" t="inlineStr">
         <is>
           <t>Declined</t>
         </is>
       </c>
-      <c r="K10" s="101" t="inlineStr">
+      <c r="K10" s="102" t="inlineStr">
         <is>
           <t>세이브/로드</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="K11" s="101" t="inlineStr">
+      <c r="K11" s="102" t="inlineStr">
         <is>
           <t>메모리/컨텍스트</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="K12" s="101" t="inlineStr">
+      <c r="K12" s="102" t="inlineStr">
         <is>
           <t>입력/출력 세이프티</t>
         </is>
@@ -23161,1099 +23313,1099 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="102" t="inlineStr">
+      <c r="B2" s="103" t="inlineStr">
         <is>
           <t>명세서 — 시트 규칙 정본</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="103" t="inlineStr">
+      <c r="B3" s="104" t="inlineStr">
         <is>
           <t>이 시트가 구조 규칙의 정본입니다. rules/tc-sheet-format.md와 짝으로 교차 검증하며, 불일치 발견 시 임의 판단 없이 사용자에게 기준을 확인합니다. 서식(색·테두리·폰트)의 정본은 design-template/xlsx-design-guide.md입니다.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="84" t="inlineStr">
+      <c r="B5" s="85" t="inlineStr">
         <is>
           <t>1. 시트 구성</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="100" t="inlineStr">
+      <c r="B6" s="101" t="inlineStr">
         <is>
           <t>시트</t>
         </is>
       </c>
-      <c r="C6" s="100" t="inlineStr">
+      <c r="C6" s="101" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="99" t="inlineStr">
+      <c r="B7" s="100" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="C7" s="99" t="inlineStr">
+      <c r="C7" s="100" t="inlineStr">
         <is>
           <t>TC 작성과 실행 기록. 노란 셀은 실행 단계에서 채워집니다</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="99" t="inlineStr">
+      <c r="B8" s="100" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
-      <c r="C8" s="99" t="inlineStr">
+      <c r="C8" s="100" t="inlineStr">
         <is>
           <t>행 단위 자동 집계(1-Depth 기준). 기준 골격 버전(C4)은 생성 시 자동 기입됩니다</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="99" t="inlineStr">
+      <c r="B9" s="100" t="inlineStr">
         <is>
           <t>이슈 관리 시트</t>
         </is>
       </c>
-      <c r="C9" s="99" t="inlineStr">
+      <c r="C9" s="100" t="inlineStr">
         <is>
           <t>결함 기록(내장 운영, JIRA 미사용) — JIRA 이슈 등록·관리 방식을 시트로 표현. Issue No.로 Test Case와 연결합니다. 정본은 별도 파일 test-case/{프로젝트}-issues.json이며 이 시트는 그 파생입니다</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="99" t="inlineStr">
+      <c r="B10" s="100" t="inlineStr">
         <is>
           <t>목록</t>
         </is>
       </c>
-      <c r="C10" s="99" t="inlineStr">
+      <c r="C10" s="100" t="inlineStr">
         <is>
           <t>드롭다운 참조 목록의 정본. 숨기지 않고 맨 뒤에 둡니다</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="99" t="inlineStr">
+      <c r="B11" s="100" t="inlineStr">
         <is>
           <t>명세서</t>
         </is>
       </c>
-      <c r="C11" s="99" t="inlineStr">
+      <c r="C11" s="100" t="inlineStr">
         <is>
           <t>이 시트 — 구조 규칙의 정본</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="84" t="inlineStr">
+      <c r="B13" s="85" t="inlineStr">
         <is>
           <t>2. 컬럼 정의 (Test Case)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="100" t="inlineStr">
+      <c r="B14" s="101" t="inlineStr">
         <is>
           <t>컬럼</t>
         </is>
       </c>
-      <c r="C14" s="100" t="inlineStr">
+      <c r="C14" s="101" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="D14" s="100" t="inlineStr">
+      <c r="D14" s="101" t="inlineStr">
         <is>
           <t>채우는 규칙</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="99" t="inlineStr">
+      <c r="B15" s="100" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C15" s="99" t="inlineStr">
+      <c r="C15" s="100" t="inlineStr">
         <is>
           <t>행 번호</t>
         </is>
       </c>
-      <c r="D15" s="99" t="inlineStr">
+      <c r="D15" s="100" t="inlineStr">
         <is>
           <t>자동 수식(ROW() 기준). 직접 입력하지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="99" t="inlineStr">
+      <c r="B16" s="100" t="inlineStr">
         <is>
           <t>1~7-Depth</t>
         </is>
       </c>
-      <c r="C16" s="99" t="inlineStr">
+      <c r="C16" s="100" t="inlineStr">
         <is>
           <t>기능 계층</t>
         </is>
       </c>
-      <c r="D16" s="99" t="inlineStr">
+      <c r="D16" s="100" t="inlineStr">
         <is>
           <t>행마다 반복(기대결과 추가 행 포함 — 집계·필터의 전제). 의미 있는 깊이까지만 쓰고 나머지는 빈칸. 병합하지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="99" t="inlineStr">
+      <c r="B17" s="100" t="inlineStr">
         <is>
           <t>Pre-Condition</t>
         </is>
       </c>
-      <c r="C17" s="99" t="inlineStr">
+      <c r="C17" s="100" t="inlineStr">
         <is>
           <t>사전조건</t>
         </is>
       </c>
-      <c r="D17" s="99" t="inlineStr">
+      <c r="D17" s="100" t="inlineStr">
         <is>
           <t>TN 1행에 케이스 진입 조건. 중간 스텝에 앞 스텝이 만들지 못하는 새 상태(시간 경과·외부 변화 등)가 필요하면 그 행에도 적습니다 — 앞 스텝의 결과로 성립한 상태는 제외. 같은 조건이 걸리는 스텝 행 범위는 세로 병합하되 케이스 전체 병합은 금지</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="99" t="inlineStr">
+      <c r="B18" s="100" t="inlineStr">
         <is>
           <t>TN</t>
         </is>
       </c>
-      <c r="C18" s="99" t="inlineStr">
+      <c r="C18" s="100" t="inlineStr">
         <is>
           <t>스텝 번호</t>
         </is>
       </c>
-      <c r="D18" s="99" t="inlineStr">
+      <c r="D18" s="100" t="inlineStr">
         <is>
           <t>케이스마다 1부터. 새 케이스가 시작되면 1로 복귀. 한 스텝의 기대결과가 여러 행이면(TN 값 무관) Test-Step과 함께 그 범위를 세로 병합합니다 — 반복 기재하면 독립 동작 여러 개로 오독됩니다</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="99" t="inlineStr">
+      <c r="B19" s="100" t="inlineStr">
         <is>
           <t>Test-Step</t>
         </is>
       </c>
-      <c r="C19" s="99" t="inlineStr">
+      <c r="C19" s="100" t="inlineStr">
         <is>
           <t>수행 동작</t>
         </is>
       </c>
-      <c r="D19" s="99" t="inlineStr">
+      <c r="D19" s="100" t="inlineStr">
         <is>
           <t>「~한다」 체. TN과 같은 범위로 세로 병합</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="99" t="inlineStr">
+      <c r="B20" s="100" t="inlineStr">
         <is>
           <t>Expected-Result</t>
         </is>
       </c>
-      <c r="C20" s="99" t="inlineStr">
+      <c r="C20" s="100" t="inlineStr">
         <is>
           <t>기대 결과</t>
         </is>
       </c>
-      <c r="D20" s="99" t="inlineStr">
+      <c r="D20" s="100" t="inlineStr">
         <is>
           <t>「~된다」 체. 판정 가능한 문장 — 임계·합격선·시도 횟수는 문장 안에 숫자로. 한 행 = 한 판정이므로 병합하지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="99" t="inlineStr">
+      <c r="B21" s="100" t="inlineStr">
         <is>
           <t>실행 주체</t>
         </is>
       </c>
-      <c r="C21" s="99" t="inlineStr">
+      <c r="C21" s="100" t="inlineStr">
         <is>
           <t>누가 수행하는가</t>
         </is>
       </c>
-      <c r="D21" s="99" t="inlineStr">
+      <c r="D21" s="100" t="inlineStr">
         <is>
           <t>행마다 반복(드롭다운 3종). 자동화 전용 = 사람이 화면만 봐서 판정 불가 / 사람 전용 = 자동화가 판정 기준을 못 세움 / 공통 = 기본값. 반복 횟수는 판정 근거가 아니며 「사람이 1회 봐도 의미가 있는가」로 갈립니다</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="99" t="inlineStr">
+      <c r="B22" s="100" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="C22" s="99" t="inlineStr">
+      <c r="C22" s="100" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="D22" s="99" t="inlineStr">
+      <c r="D22" s="100" t="inlineStr">
         <is>
           <t>행마다 반복. High/Medium/Low — 케이스의 속성이지만 Summary가 행 단위로 집계하므로 행마다 값을 둡니다</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="99" t="inlineStr">
+      <c r="B23" s="100" t="inlineStr">
         <is>
           <t>Total Result</t>
         </is>
       </c>
-      <c r="C23" s="99" t="inlineStr">
+      <c r="C23" s="100" t="inlineStr">
         <is>
           <t>행 판정</t>
         </is>
       </c>
-      <c r="D23" s="99" t="inlineStr">
+      <c r="D23" s="100" t="inlineStr">
         <is>
           <t>수식 열. 병합하지 않고 데이터 한 행씩 세웁니다 — 같은 플랫폼에 단말이 여럿일 때 그 행의 단말 결과를 요약합니다. 직접 입력하지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="99" t="inlineStr">
+      <c r="B24" s="100" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="C24" s="99" t="inlineStr">
+      <c r="C24" s="100" t="inlineStr">
         <is>
           <t>스텝 실행 결과</t>
         </is>
       </c>
-      <c r="D24" s="99" t="inlineStr">
+      <c r="D24" s="100" t="inlineStr">
         <is>
           <t>드롭다운 4종(아래 상태값 정의). 실행 단계에서 채움 — 노란 셀</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="99" t="inlineStr">
+      <c r="B25" s="100" t="inlineStr">
         <is>
           <t>Issue No.</t>
         </is>
       </c>
-      <c r="C25" s="99" t="inlineStr">
+      <c r="C25" s="100" t="inlineStr">
         <is>
           <t>관련 이슈</t>
         </is>
       </c>
-      <c r="D25" s="99" t="inlineStr">
+      <c r="D25" s="100" t="inlineStr">
         <is>
           <t>해당 TC를 수행하는 과정에서 이슈가 발생하면, 먼저 이슈 관리 시트에 이슈를 등록하고 거기서 부여된 Issue No.를 이 칸에 적습니다. 실행 단계에서 채움 — 노란 셀</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="99" t="inlineStr">
+      <c r="B26" s="100" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="C26" s="99" t="inlineStr">
+      <c r="C26" s="100" t="inlineStr">
         <is>
           <t>수행 중 기록</t>
         </is>
       </c>
-      <c r="D26" s="99" t="inlineStr">
+      <c r="D26" s="100" t="inlineStr">
         <is>
           <t>TC를 수행하다 생긴 문제·관찰을 실행 단계에서 적습니다 — 노란 셀. 설계 시점에는 비어 있습니다</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="99" t="inlineStr">
+      <c r="B27" s="100" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="C27" s="99" t="inlineStr">
+      <c r="C27" s="100" t="inlineStr">
         <is>
           <t>수행 전 참고사항</t>
         </is>
       </c>
-      <c r="D27" s="99" t="inlineStr">
+      <c r="D27" s="100" t="inlineStr">
         <is>
           <t>사람이 읽을 안내만 담습니다 — ①함께 볼 것 ②수행 방법 ③조건 만드는 법. 케이스 메타는 2026-08-03 개정으로 TC ID·검증유형 열이 따로 갖습니다. 스텝 범위 세로 병합</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="99" t="inlineStr">
+      <c r="B28" s="100" t="inlineStr">
         <is>
           <t>TC ID</t>
         </is>
       </c>
-      <c r="C28" s="99" t="inlineStr">
+      <c r="C28" s="100" t="inlineStr">
         <is>
           <t>조인 키</t>
         </is>
       </c>
-      <c r="D28" s="99" t="inlineStr">
+      <c r="D28" s="100" t="inlineStr">
         <is>
           <t>행마다 반복. 자동화 케이스명·추적 매트릭스·이슈 연결이 참조합니다. 사람의 실행 동선에서 빼려고 Note 우측 참조 블록에 둡니다</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="99" t="inlineStr">
+      <c r="B29" s="100" t="inlineStr">
         <is>
           <t>검증유형</t>
         </is>
       </c>
-      <c r="C29" s="99" t="inlineStr">
+      <c r="C29" s="100" t="inlineStr">
         <is>
           <t>판정 방식</t>
         </is>
       </c>
-      <c r="D29" s="99" t="inlineStr">
+      <c r="D29" s="100" t="inlineStr">
         <is>
           <t>행마다 반복(드롭다운 4종). 반복 횟수는 시트에 적지 않습니다 — 수동 실행자가 자기에게 내려진 지시로 오독하기 때문입니다. 반복은 자동화가 수행하며, 사람은 어떤 유형이든 1회입니다. 확률적·루브릭을 사람이 1회 수행했다면 결과는 Pass가 아니라 관찰 기록이고, 판정은 자동화 반복이나 채점이 담당합니다</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="99" t="inlineStr">
+      <c r="B30" s="100" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="C30" s="99" t="inlineStr">
+      <c r="C30" s="100" t="inlineStr">
         <is>
           <t>케이스가 밟는 게이팅·세션 상태 (2026-08-04 신설)</t>
         </is>
       </c>
-      <c r="D30" s="99" t="inlineStr">
+      <c r="D30" s="100" t="inlineStr">
         <is>
           <t>행마다 반복. 값 5종은 목록 시트가 정본이고 복수 상태는 쉼표로 적습니다(전환 케이스 — 드롭다운을 걸지 않는 이유). 자동 필터를 「포함」 조건으로 걸어 상태별 TC를 추출하고, 트리의 [상태:] 선언과 맞물려 잎×상태 커버리지를 대조합니다</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="84" t="inlineStr">
+      <c r="B32" s="85" t="inlineStr">
         <is>
           <t>3. 상태값 정의</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="100" t="inlineStr">
+      <c r="B33" s="101" t="inlineStr">
         <is>
           <t>상태</t>
         </is>
       </c>
-      <c r="C33" s="100" t="inlineStr">
+      <c r="C33" s="101" t="inlineStr">
         <is>
           <t>정의</t>
         </is>
       </c>
-      <c r="D33" s="100" t="inlineStr">
+      <c r="D33" s="101" t="inlineStr">
         <is>
           <t>Pass율 분모</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="99" t="inlineStr">
+      <c r="B34" s="100" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="C34" s="99" t="inlineStr">
+      <c r="C34" s="100" t="inlineStr">
         <is>
           <t>성공</t>
         </is>
       </c>
-      <c r="D34" s="99" t="inlineStr">
+      <c r="D34" s="100" t="inlineStr">
         <is>
           <t>포함</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="99" t="inlineStr">
+      <c r="B35" s="100" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="C35" s="99" t="inlineStr">
+      <c r="C35" s="100" t="inlineStr">
         <is>
           <t>실패</t>
         </is>
       </c>
-      <c r="D35" s="99" t="inlineStr">
+      <c r="D35" s="100" t="inlineStr">
         <is>
           <t>포함</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="99" t="inlineStr">
+      <c r="B36" s="100" t="inlineStr">
         <is>
           <t>NI</t>
         </is>
       </c>
-      <c r="C36" s="99" t="inlineStr">
+      <c r="C36" s="100" t="inlineStr">
         <is>
           <t>미구현이거나 스펙에 없어 실행 대상이 아님 (Not Implemented)</t>
         </is>
       </c>
-      <c r="D36" s="99" t="inlineStr">
+      <c r="D36" s="100" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="99" t="inlineStr">
+      <c r="B37" s="100" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="C37" s="99" t="inlineStr">
+      <c r="C37" s="100" t="inlineStr">
         <is>
           <t>기능은 구현됐으나 확인할 수 없는 상태 — 선행 케이스 Fail·환경 결함·데이터 준비 불가 등. 사유는 실행 과정에서 Comment에 적습니다</t>
         </is>
       </c>
-      <c r="D37" s="99" t="inlineStr">
+      <c r="D37" s="100" t="inlineStr">
         <is>
           <t>제외</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="103" t="inlineStr">
+      <c r="B38" s="104" t="inlineStr">
         <is>
           <t>Pass율 = Pass ÷ (Pass + Fail). NI·Blocked를 분모에 넣지 않는 이유는 결함 1건이 후속 Blocked 수만큼 중복 계상되는 것을 막기 위해서입니다.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="84" t="inlineStr">
+      <c r="B40" s="85" t="inlineStr">
         <is>
           <t>4. Total Result 규칙</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="100" t="inlineStr">
+      <c r="B41" s="101" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C41" s="100" t="inlineStr">
+      <c r="C41" s="101" t="inlineStr">
         <is>
           <t>규칙</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="99" t="inlineStr">
+      <c r="B42" s="100" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="C42" s="99" t="inlineStr">
+      <c r="C42" s="100" t="inlineStr">
         <is>
           <t>Fail &gt; Blocked &gt; NI &gt; Pass — 스텝 중 하나라도 Fail이면 케이스 Fail</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="99" t="inlineStr">
+      <c r="B43" s="100" t="inlineStr">
         <is>
           <t>수식 원형</t>
         </is>
       </c>
-      <c r="C43" s="99" t="inlineStr">
+      <c r="C43" s="100" t="inlineStr">
         <is>
           <t>IF(COUNTIF(범위,"Fail")&gt;0,"Fail",IF(COUNTIF(범위,"Blocked")&gt;0,"Blocked",IF(COUNTIF(범위,"NI")&gt;0,"NI",IF(COUNTIF(범위,"Pass")&gt;0,"Pass","")))) — 셀에는 앞에 = 를 붙여 사용합니다. 아무것도 실행되지 않은 케이스는 빈칸입니다</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="99" t="inlineStr">
+      <c r="B44" s="100" t="inlineStr">
         <is>
           <t>병합</t>
         </is>
       </c>
-      <c r="C44" s="99" t="inlineStr">
+      <c r="C44" s="100" t="inlineStr">
         <is>
           <t>하지 않습니다 — 데이터 한 행씩 세웁니다. 같은 플랫폼에 단말이 여럿일 때 그 행의 단말 결과를 하나로 요약하는 자리입니다</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="84" t="inlineStr">
+      <c r="B46" s="85" t="inlineStr">
         <is>
           <t>5. TC ID 체계</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="100" t="inlineStr">
+      <c r="B47" s="101" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C47" s="100" t="inlineStr">
+      <c r="C47" s="101" t="inlineStr">
         <is>
           <t>규칙</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="99" t="inlineStr">
+      <c r="B48" s="100" t="inlineStr">
         <is>
           <t>형식</t>
         </is>
       </c>
-      <c r="C48" s="99" t="inlineStr">
+      <c r="C48" s="100" t="inlineStr">
         <is>
           <t>TC-{영역코드}-{번호 3자리} — 예: TC-ENT-001</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="99" t="inlineStr">
+      <c r="B49" s="100" t="inlineStr">
         <is>
           <t>번호</t>
         </is>
       </c>
-      <c r="C49" s="99" t="inlineStr">
+      <c r="C49" s="100" t="inlineStr">
         <is>
           <t>영역 안에서만 증가합니다. 다른 영역에 케이스가 추가돼도 기존 ID가 흔들리지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="99" t="inlineStr">
+      <c r="B50" s="100" t="inlineStr">
         <is>
           <t>영역코드</t>
         </is>
       </c>
-      <c r="C50" s="99" t="inlineStr">
+      <c r="C50" s="100" t="inlineStr">
         <is>
           <t>기능 트리 1-Depth당 하나. 프로젝트별 매핑표는 아래 §5-1이며, 정의가 없는 프로젝트에서는 그 절이 나오지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="99" t="inlineStr">
+      <c r="B51" s="100" t="inlineStr">
         <is>
           <t>기재 위치</t>
         </is>
       </c>
-      <c r="C51" s="99" t="inlineStr">
+      <c r="C51" s="100" t="inlineStr">
         <is>
           <t>Note의 첫 토큰(케이스 메타의 맨 앞). 자동화 케이스명·추적 매트릭스·이슈 연결이 이 ID를 참조합니다. Comment는 설계 시점에 비어 있는 실행 기록 칸이므로 설계 데이터를 두지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="84" t="inlineStr">
+      <c r="B53" s="85" t="inlineStr">
         <is>
           <t>5-1. 영역코드 매핑</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="103" t="inlineStr">
+      <c r="B54" s="104" t="inlineStr">
         <is>
           <t>키는 기능 트리 1-Depth 영역명이며, 이슈 관리 시트 「레이블」 목록과 같은 값을 씁니다. 코드는 영문 표기의 앞 세 글자이고, 한 영역에 하나씩만 둡니다. 정본은 TC 설계 입력(tc-input json)의 area_codes입니다.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="100" t="inlineStr">
+      <c r="B55" s="101" t="inlineStr">
         <is>
           <t>영역 (기능 트리 1-Depth)</t>
         </is>
       </c>
-      <c r="C55" s="100" t="inlineStr">
+      <c r="C55" s="101" t="inlineStr">
         <is>
           <t>코드</t>
         </is>
       </c>
-      <c r="D55" s="100" t="inlineStr">
+      <c r="D55" s="101" t="inlineStr">
         <is>
           <t>영문 표기</t>
         </is>
       </c>
-      <c r="E55" s="100" t="inlineStr">
+      <c r="E55" s="101" t="inlineStr">
         <is>
           <t>TC ID 예</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="99" t="inlineStr">
+      <c r="B56" s="100" t="inlineStr">
         <is>
           <t>앱 진입/세션</t>
         </is>
       </c>
-      <c r="C56" s="99" t="inlineStr">
+      <c r="C56" s="100" t="inlineStr">
         <is>
           <t>ENT</t>
         </is>
       </c>
-      <c r="D56" s="99" t="inlineStr">
+      <c r="D56" s="100" t="inlineStr">
         <is>
           <t>Entry &amp; Session</t>
         </is>
       </c>
-      <c r="E56" s="99" t="inlineStr">
+      <c r="E56" s="100" t="inlineStr">
         <is>
           <t>TC-ENT-001</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="99" t="inlineStr">
+      <c r="B57" s="100" t="inlineStr">
         <is>
           <t>계정/게이팅</t>
         </is>
       </c>
-      <c r="C57" s="99" t="inlineStr">
+      <c r="C57" s="100" t="inlineStr">
         <is>
           <t>GAT</t>
         </is>
       </c>
-      <c r="D57" s="99" t="inlineStr">
+      <c r="D57" s="100" t="inlineStr">
         <is>
           <t>Gating (account &amp; age)</t>
         </is>
       </c>
-      <c r="E57" s="99" t="inlineStr">
+      <c r="E57" s="100" t="inlineStr">
         <is>
           <t>TC-GAT-001</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="99" t="inlineStr">
+      <c r="B58" s="100" t="inlineStr">
         <is>
           <t>탐색/발견</t>
         </is>
       </c>
-      <c r="C58" s="99" t="inlineStr">
+      <c r="C58" s="100" t="inlineStr">
         <is>
           <t>DSC</t>
         </is>
       </c>
-      <c r="D58" s="99" t="inlineStr">
+      <c r="D58" s="100" t="inlineStr">
         <is>
           <t>Discovery</t>
         </is>
       </c>
-      <c r="E58" s="99" t="inlineStr">
+      <c r="E58" s="100" t="inlineStr">
         <is>
           <t>TC-DSC-001</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="99" t="inlineStr">
+      <c r="B59" s="100" t="inlineStr">
         <is>
           <t>유저 페르소나</t>
         </is>
       </c>
-      <c r="C59" s="99" t="inlineStr">
+      <c r="C59" s="100" t="inlineStr">
         <is>
           <t>PRF</t>
         </is>
       </c>
-      <c r="D59" s="99" t="inlineStr">
+      <c r="D59" s="100" t="inlineStr">
         <is>
           <t>Profile (dialogue persona)</t>
         </is>
       </c>
-      <c r="E59" s="99" t="inlineStr">
+      <c r="E59" s="100" t="inlineStr">
         <is>
           <t>TC-PRF-001</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="99" t="inlineStr">
+      <c r="B60" s="100" t="inlineStr">
         <is>
           <t>재화</t>
         </is>
       </c>
-      <c r="C60" s="99" t="inlineStr">
+      <c r="C60" s="100" t="inlineStr">
         <is>
           <t>CUR</t>
         </is>
       </c>
-      <c r="D60" s="99" t="inlineStr">
+      <c r="D60" s="100" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="E60" s="99" t="inlineStr">
+      <c r="E60" s="100" t="inlineStr">
         <is>
           <t>TC-CUR-001</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="99" t="inlineStr">
+      <c r="B61" s="100" t="inlineStr">
         <is>
           <t>서사 시스템</t>
         </is>
       </c>
-      <c r="C61" s="99" t="inlineStr">
+      <c r="C61" s="100" t="inlineStr">
         <is>
           <t>NAR</t>
         </is>
       </c>
-      <c r="D61" s="99" t="inlineStr">
+      <c r="D61" s="100" t="inlineStr">
         <is>
           <t>Narrative</t>
         </is>
       </c>
-      <c r="E61" s="99" t="inlineStr">
+      <c r="E61" s="100" t="inlineStr">
         <is>
           <t>TC-NAR-001</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="99" t="inlineStr">
+      <c r="B62" s="100" t="inlineStr">
         <is>
           <t>대화 세션</t>
         </is>
       </c>
-      <c r="C62" s="99" t="inlineStr">
+      <c r="C62" s="100" t="inlineStr">
         <is>
           <t>CHT</t>
         </is>
       </c>
-      <c r="D62" s="99" t="inlineStr">
+      <c r="D62" s="100" t="inlineStr">
         <is>
           <t>Chat session</t>
         </is>
       </c>
-      <c r="E62" s="99" t="inlineStr">
+      <c r="E62" s="100" t="inlineStr">
         <is>
           <t>TC-CHT-001</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="99" t="inlineStr">
+      <c r="B63" s="100" t="inlineStr">
         <is>
           <t>세이브/로드</t>
         </is>
       </c>
-      <c r="C63" s="99" t="inlineStr">
+      <c r="C63" s="100" t="inlineStr">
         <is>
           <t>SAV</t>
         </is>
       </c>
-      <c r="D63" s="99" t="inlineStr">
+      <c r="D63" s="100" t="inlineStr">
         <is>
           <t>Save &amp; Load</t>
         </is>
       </c>
-      <c r="E63" s="99" t="inlineStr">
+      <c r="E63" s="100" t="inlineStr">
         <is>
           <t>TC-SAV-001</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="99" t="inlineStr">
+      <c r="B64" s="100" t="inlineStr">
         <is>
           <t>메모리/컨텍스트</t>
         </is>
       </c>
-      <c r="C64" s="99" t="inlineStr">
+      <c r="C64" s="100" t="inlineStr">
         <is>
           <t>MEM</t>
         </is>
       </c>
-      <c r="D64" s="99" t="inlineStr">
+      <c r="D64" s="100" t="inlineStr">
         <is>
           <t>Memory &amp; Context</t>
         </is>
       </c>
-      <c r="E64" s="99" t="inlineStr">
+      <c r="E64" s="100" t="inlineStr">
         <is>
           <t>TC-MEM-001</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="99" t="inlineStr">
+      <c r="B65" s="100" t="inlineStr">
         <is>
           <t>입력/출력 세이프티</t>
         </is>
       </c>
-      <c r="C65" s="99" t="inlineStr">
+      <c r="C65" s="100" t="inlineStr">
         <is>
           <t>SAF</t>
         </is>
       </c>
-      <c r="D65" s="99" t="inlineStr">
+      <c r="D65" s="100" t="inlineStr">
         <is>
           <t>Safety (input &amp; output)</t>
         </is>
       </c>
-      <c r="E65" s="99" t="inlineStr">
+      <c r="E65" s="100" t="inlineStr">
         <is>
           <t>TC-SAF-001</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="84" t="inlineStr">
+      <c r="B67" s="85" t="inlineStr">
         <is>
           <t>6. 플랫폼 열 규칙</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="100" t="inlineStr">
+      <c r="B68" s="101" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C68" s="100" t="inlineStr">
+      <c r="C68" s="101" t="inlineStr">
         <is>
           <t>규칙</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="99" t="inlineStr">
+      <c r="B69" s="100" t="inlineStr">
         <is>
           <t>기본값</t>
         </is>
       </c>
-      <c r="C69" s="99" t="inlineStr">
+      <c r="C69" s="100" t="inlineStr">
         <is>
           <t>마스터는 Web / And / iOS 3열</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="99" t="inlineStr">
+      <c r="B70" s="100" t="inlineStr">
         <is>
           <t>프로젝트 조정</t>
         </is>
       </c>
-      <c r="C70" s="99" t="inlineStr">
+      <c r="C70" s="100" t="inlineStr">
         <is>
           <t>TC 설계 시작 시 대상 플랫폼을 사용자에게 재확인하고, Test Case의 Total Result·Result 하위 열과 Summary의 플랫폼 열을 함께 조정합니다</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="84" t="inlineStr">
+      <c r="B72" s="85" t="inlineStr">
         <is>
           <t>7. 입력 규칙</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="100" t="inlineStr">
+      <c r="B73" s="101" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C73" s="100" t="inlineStr">
+      <c r="C73" s="101" t="inlineStr">
         <is>
           <t>규칙</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="99" t="inlineStr">
+      <c r="B74" s="100" t="inlineStr">
         <is>
           <t>실행 채움 셀(노랑)</t>
         </is>
       </c>
-      <c r="C74" s="99" t="inlineStr">
+      <c r="C74" s="100" t="inlineStr">
         <is>
           <t>설계 시점에는 비어 있고 실행 단계에서 채워지는 칸 — 환경 블록·Result·Issue No.·Comment. 채우는 주체가 사람이든 자동화든 설계자는 건드리지 않습니다. 설계 데이터는 노란 칸에 두지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="99" t="inlineStr">
+      <c r="B75" s="100" t="inlineStr">
         <is>
           <t>설계 셀</t>
         </is>
       </c>
-      <c r="C75" s="99" t="inlineStr">
+      <c r="C75" s="100" t="inlineStr">
         <is>
           <t>Depth·절차·기대결과는 실행 중 수정하지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="99" t="inlineStr">
+      <c r="B76" s="100" t="inlineStr">
         <is>
           <t>틀 고정</t>
         </is>
       </c>
-      <c r="C76" s="99" t="inlineStr">
+      <c r="C76" s="100" t="inlineStr">
         <is>
           <t>데이터 첫 행 위. 스크롤해도 2행 제목·헤더·환경 블록이 남으며, 그 구간은 회색(#BFBFBF)과 Total/Result 띠(#F9D7BE)로 데이터와 갈라 둡니다. A열과 1행은 값도 색도 두지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="99" t="inlineStr">
+      <c r="B77" s="100" t="inlineStr">
         <is>
           <t>자동 필터</t>
         </is>
       </c>
-      <c r="C77" s="99" t="inlineStr">
+      <c r="C77" s="100" t="inlineStr">
         <is>
           <t>헤더 행에 걸어 둡니다. 실행 주체·검증유형·Priority처럼 케이스 단위 값으로 거르면 한 케이스의 행이 통째로 남거나 빠져 스텝 범위 병합이 깨지지 않습니다. Result 같은 행 단위 값으로 거르면 케이스 중간이 잘려 병합이 어색해집니다</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="99" t="inlineStr">
+      <c r="B78" s="100" t="inlineStr">
         <is>
           <t>뎁스 채움 색</t>
         </is>
       </c>
-      <c r="C78" s="99" t="inlineStr">
+      <c r="C78" s="100" t="inlineStr">
         <is>
           <t>뎁스 열의 값 있는 셀만 텍스트별 고유색으로 채웁니다 — 같은 텍스트는 같은 색, 인접한 다른 텍스트와는 색상환에서 멀어지게 배정. 케이스명 칸과 빈칸은 흰 배경. 규칙 정본은 xlsx-design-guide.md §5</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="99" t="inlineStr">
+      <c r="B79" s="100" t="inlineStr">
         <is>
           <t>기준 골격 버전</t>
         </is>
       </c>
-      <c r="C79" s="99" t="inlineStr">
+      <c r="C79" s="100" t="inlineStr">
         <is>
           <t>Summary C4에 생성 스크립트가 자동 기입합니다 — 형식 {프로젝트}-tree-v{X.Y}. TC 설계 입력(tc-input json)의 값을 그대로 쓰므로 사람이 옮겨 적지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="84" t="inlineStr">
+      <c r="B81" s="85" t="inlineStr">
         <is>
           <t>8. 컬럼 정의 (이슈 관리 시트)</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="103" t="inlineStr">
+      <c r="B82" s="104" t="inlineStr">
         <is>
           <t>이슈 기록의 정본은 test-case/{프로젝트}-issues.json입니다. TC 설계 원본과 파일을 나눈 이유는 크기가 아니라 생명주기입니다 — TC 세트는 확정되면 고정되지만 이슈는 실행하면서 계속 늘고 상태가 바뀌므로, 한 파일에 두면 이슈 갱신 때마다 설계 원본이 변경되어 확정 시점이 흐려집니다.</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="100" t="inlineStr">
+      <c r="B83" s="101" t="inlineStr">
         <is>
           <t>컬럼</t>
         </is>
       </c>
-      <c r="C83" s="100" t="inlineStr">
+      <c r="C83" s="101" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
       </c>
-      <c r="D83" s="100" t="inlineStr">
+      <c r="D83" s="101" t="inlineStr">
         <is>
           <t>채우는 규칙</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="99" t="inlineStr">
+      <c r="B84" s="100" t="inlineStr">
         <is>
           <t>프로젝트 ID</t>
         </is>
       </c>
-      <c r="C84" s="99" t="inlineStr">
+      <c r="C84" s="100" t="inlineStr">
         <is>
           <t>프로젝트 식별자</t>
         </is>
       </c>
-      <c r="D84" s="99" t="inlineStr">
+      <c r="D84" s="100" t="inlineStr">
         <is>
           <t>SUT명 기준. 목록 시트 참조</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="99" t="inlineStr">
+      <c r="B85" s="100" t="inlineStr">
         <is>
           <t>Issue No.</t>
         </is>
       </c>
-      <c r="C85" s="99" t="inlineStr">
+      <c r="C85" s="100" t="inlineStr">
         <is>
           <t>발생한 이슈의 식별자</t>
         </is>
       </c>
-      <c r="D85" s="99" t="inlineStr">
+      <c r="D85" s="100" t="inlineStr">
         <is>
           <t>발생한 이슈를 등록하며 부여합니다 — {프로젝트}-{생성 번호순} (1 &gt; 2 &gt; 3 &gt; …). TC 수행 중 발생한 이슈라면 이 번호를 Test Case 시트의 Issue No.에 적어 잇습니다</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="99" t="inlineStr">
+      <c r="B86" s="100" t="inlineStr">
         <is>
           <t>이슈 상태</t>
         </is>
       </c>
-      <c r="C86" s="99" t="inlineStr">
+      <c r="C86" s="100" t="inlineStr">
         <is>
           <t>이슈의 현재 상태</t>
         </is>
       </c>
-      <c r="D86" s="99" t="inlineStr">
+      <c r="D86" s="100" t="inlineStr">
         <is>
           <t>Open: 열린 상태(재현됨) / In Progress: 담당자가 수정 진행 중 / Resolved: 해결됨 / Reopen: 해결된 이슈가 재현되어 다시 엶 / Closed: 재현되지 않아 닫음</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="99" t="inlineStr">
+      <c r="B87" s="100" t="inlineStr">
         <is>
           <t>요약(Summary)</t>
         </is>
       </c>
-      <c r="C87" s="99" t="inlineStr">
+      <c r="C87" s="100" t="inlineStr">
         <is>
           <t>이슈 제목</t>
         </is>
       </c>
-      <c r="D87" s="99" t="inlineStr">
+      <c r="D87" s="100" t="inlineStr">
         <is>
           <t>재현 경로 요약 — 문단 구분은 "&gt;", 마지막은 무엇이 잘못됐는지 수동태로.
 ex) rules/ 폴더 이동 &gt; A.md 실행 시, 크래시 발생됨</t>
@@ -24261,68 +24413,68 @@
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="99" t="inlineStr">
+      <c r="B88" s="100" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
-      <c r="C88" s="99" t="inlineStr">
+      <c r="C88" s="100" t="inlineStr">
         <is>
           <t>재현 방법 상세</t>
         </is>
       </c>
-      <c r="D88" s="99" t="inlineStr">
+      <c r="D88" s="100" t="inlineStr">
         <is>
           <t>Pre-condition(사전 조건) / Reproduce Step(재현 스텝) / Actual Result(실제 결과, ~됨) / Expected Result(기대 결과, ~되어야 함) / QA Comment(참고) 순서로 작성</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="99" t="inlineStr">
+      <c r="B89" s="100" t="inlineStr">
         <is>
           <t>우선순위</t>
         </is>
       </c>
-      <c r="C89" s="99" t="inlineStr">
+      <c r="C89" s="100" t="inlineStr">
         <is>
           <t>이슈 심각도</t>
         </is>
       </c>
-      <c r="D89" s="99" t="inlineStr">
+      <c r="D89" s="100" t="inlineStr">
         <is>
           <t>High: 크래시·진입 불가 등 치명 / Medium: 진입은 되나 기능 미동작 / Low: 문구·표기 오류</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="99" t="inlineStr">
+      <c r="B90" s="100" t="inlineStr">
         <is>
           <t>빈도</t>
         </is>
       </c>
-      <c r="C90" s="99" t="inlineStr">
+      <c r="C90" s="100" t="inlineStr">
         <is>
           <t>발생 빈도</t>
         </is>
       </c>
-      <c r="D90" s="99" t="inlineStr">
+      <c r="D90" s="100" t="inlineStr">
         <is>
           <t>Always: 항상 / Often: 종종(70% 이상) / Sometimes: 가끔(70% 미만) / Once: 1회만</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="99" t="inlineStr">
+      <c r="B91" s="100" t="inlineStr">
         <is>
           <t>영향 받는 버전</t>
         </is>
       </c>
-      <c r="C91" s="99" t="inlineStr">
+      <c r="C91" s="100" t="inlineStr">
         <is>
           <t>이슈가 재현되는 빌드</t>
         </is>
       </c>
-      <c r="D91" s="99" t="inlineStr">
+      <c r="D91" s="100" t="inlineStr">
         <is>
           <t>{테스트환경}_{개발목표버전}_{스프린트}_{확인버전} 네 토막.
 테스트환경=어디서 확인했는가(PC웹) / 개발목표버전=무엇을 향해 개발 중인가(Ver1.0) / 스프린트=그 목표 버전의 주 목표(Dev, RT1=Release Train 1차) / 확인버전=그 시점의 RC 빌드(RC=Release Candidate).
@@ -24332,271 +24484,271 @@
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="99" t="inlineStr">
+      <c r="B92" s="100" t="inlineStr">
         <is>
           <t>수정 버전</t>
         </is>
       </c>
-      <c r="C92" s="99" t="inlineStr">
+      <c r="C92" s="100" t="inlineStr">
         <is>
           <t>이슈가 수정된 버전</t>
         </is>
       </c>
-      <c r="D92" s="99" t="inlineStr">
+      <c r="D92" s="100" t="inlineStr">
         <is>
           <t>영향 받는 버전과 같은 목록을 사용합니다</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="99" t="inlineStr">
+      <c r="B93" s="100" t="inlineStr">
         <is>
           <t>해결책</t>
         </is>
       </c>
-      <c r="C93" s="99" t="inlineStr">
+      <c r="C93" s="100" t="inlineStr">
         <is>
           <t>수정 방향</t>
         </is>
       </c>
-      <c r="D93" s="99" t="inlineStr">
+      <c r="D93" s="100" t="inlineStr">
         <is>
           <t>Fixed: 코드 수정으로 대응 / Won't Do: 환경·기술 지원 불가로 미대응 / Won't Fix: 수정 필요하나 지금은 안 함 / Duplicate: 동일 건 존재 / Incomplete: 이슈 자체가 잘못됨 / Cannot Reproduce: 재현 불가 / Done: 기획·정책 결정으로 이슈 아님 확정 / Declined(QA Only): QA선에서 이슈로 보지 않음</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="99" t="inlineStr">
+      <c r="B94" s="100" t="inlineStr">
         <is>
           <t>환경</t>
         </is>
       </c>
-      <c r="C94" s="99" t="inlineStr">
+      <c r="C94" s="100" t="inlineStr">
         <is>
           <t>발생 디바이스</t>
         </is>
       </c>
-      <c r="D94" s="99" t="inlineStr">
+      <c r="D94" s="100" t="inlineStr">
         <is>
           <t>PC웹 / Android / iOS</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="99" t="inlineStr">
+      <c r="B95" s="100" t="inlineStr">
         <is>
           <t>레이블</t>
         </is>
       </c>
-      <c r="C95" s="99" t="inlineStr">
+      <c r="C95" s="100" t="inlineStr">
         <is>
           <t>발생 영역</t>
         </is>
       </c>
-      <c r="D95" s="99" t="inlineStr">
+      <c r="D95" s="100" t="inlineStr">
         <is>
           <t>기능 트리 1-Depth 영역명 — 목록 시트 참조. 트리 개정 시 목록만 갱신하고 기존 행 값은 소급 변경하지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="99" t="inlineStr">
+      <c r="B96" s="100" t="inlineStr">
         <is>
           <t>보고자</t>
         </is>
       </c>
-      <c r="C96" s="99" t="inlineStr">
+      <c r="C96" s="100" t="inlineStr">
         <is>
           <t>이슈 등록자</t>
         </is>
       </c>
-      <c r="D96" s="99" t="inlineStr">
+      <c r="D96" s="100" t="inlineStr">
         <is>
           <t>목록 참조</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="99" t="inlineStr">
+      <c r="B97" s="100" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="C97" s="99" t="inlineStr">
+      <c r="C97" s="100" t="inlineStr">
         <is>
           <t>이슈 수정 담당자</t>
         </is>
       </c>
-      <c r="D97" s="99" t="inlineStr">
+      <c r="D97" s="100" t="inlineStr">
         <is>
           <t>목록 참조</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="99" t="inlineStr">
+      <c r="B98" s="100" t="inlineStr">
         <is>
           <t>관측자</t>
         </is>
       </c>
-      <c r="C98" s="99" t="inlineStr">
+      <c r="C98" s="100" t="inlineStr">
         <is>
           <t>함께 팔로우할 인원</t>
         </is>
       </c>
-      <c r="D98" s="99" t="inlineStr">
+      <c r="D98" s="100" t="inlineStr">
         <is>
           <t>드롭다운 없음 — 쉼표 구분 자유 입력(멀티 선택은 xlsx 표준 기능에 없음)</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="99" t="inlineStr">
+      <c r="B99" s="100" t="inlineStr">
         <is>
           <t>첨부파일</t>
         </is>
       </c>
-      <c r="C99" s="99" t="inlineStr">
+      <c r="C99" s="100" t="inlineStr">
         <is>
           <t>재현 증적</t>
         </is>
       </c>
-      <c r="D99" s="99" t="inlineStr">
+      <c r="D99" s="100" t="inlineStr">
         <is>
           <t>재현 영상·이미지의 경로 또는 링크</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="99" t="inlineStr">
+      <c r="B100" s="100" t="inlineStr">
         <is>
           <t>스프린트</t>
         </is>
       </c>
-      <c r="C100" s="99" t="inlineStr">
+      <c r="C100" s="100" t="inlineStr">
         <is>
           <t>QA 진행 단위</t>
         </is>
       </c>
-      <c r="D100" s="99" t="inlineStr">
+      <c r="D100" s="100" t="inlineStr">
         <is>
           <t>영향 받는 버전에서 확인버전(RC)을 뺀 앞 세 토막 — {테스트환경}_{개발목표버전}_{스프린트}. 스프린트 하나가 RC1·RC2·RC3에 걸치므로 스프린트는 사이클을, 버전은 그 안의 빌드를 가리킵니다. 발견 단계도 이 칸으로 갈립니다 — ex) PC웹_Ver1.0_Dev(개발 단계 자체 발견) / PC웹_Ver1.0_RT1(QA 사이클 검출). 목록 참조</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="99" t="inlineStr">
+      <c r="B101" s="100" t="inlineStr">
         <is>
           <t>이슈 등록일</t>
         </is>
       </c>
-      <c r="C101" s="99" t="inlineStr">
+      <c r="C101" s="100" t="inlineStr">
         <is>
           <t>최초 등록일</t>
         </is>
       </c>
-      <c r="D101" s="99" t="inlineStr">
+      <c r="D101" s="100" t="inlineStr">
         <is>
           <t>YYYY-MM-DD. 이후 변경하지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="99" t="inlineStr">
+      <c r="B102" s="100" t="inlineStr">
         <is>
           <t>이슈 최종 수정일자</t>
         </is>
       </c>
-      <c r="C102" s="99" t="inlineStr">
+      <c r="C102" s="100" t="inlineStr">
         <is>
           <t>내용 최종 수정일</t>
         </is>
       </c>
-      <c r="D102" s="99" t="inlineStr">
+      <c r="D102" s="100" t="inlineStr">
         <is>
           <t>YYYY-MM-DD. 요약·설명 등 내용이 바뀔 때 갱신</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="B103" s="99" t="inlineStr">
+      <c r="B103" s="100" t="inlineStr">
         <is>
           <t>이슈 상태 최종 변경일자</t>
         </is>
       </c>
-      <c r="C103" s="99" t="inlineStr">
+      <c r="C103" s="100" t="inlineStr">
         <is>
           <t>상태 최종 변경일</t>
         </is>
       </c>
-      <c r="D103" s="99" t="inlineStr">
+      <c r="D103" s="100" t="inlineStr">
         <is>
           <t>YYYY-MM-DD. 이슈 상태가 바뀔 때 갱신</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="B105" s="84" t="inlineStr">
+      <c r="B105" s="85" t="inlineStr">
         <is>
           <t>9. 목록 시트 규칙</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="B106" s="100" t="inlineStr">
+      <c r="B106" s="101" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C106" s="100" t="inlineStr">
+      <c r="C106" s="101" t="inlineStr">
         <is>
           <t>규칙</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="B107" s="99" t="inlineStr">
+      <c r="B107" s="100" t="inlineStr">
         <is>
           <t>지위</t>
         </is>
       </c>
-      <c r="C107" s="99" t="inlineStr">
+      <c r="C107" s="100" t="inlineStr">
         <is>
           <t>드롭다운 참조의 정본 — 전 시트의 데이터 검증이 이 시트를 참조합니다</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="B108" s="99" t="inlineStr">
+      <c r="B108" s="100" t="inlineStr">
         <is>
           <t>노출</t>
         </is>
       </c>
-      <c r="C108" s="99" t="inlineStr">
+      <c r="C108" s="100" t="inlineStr">
         <is>
           <t>숨기지 않고 맨 뒤 배치 — 값 체계 자체가 전시물입니다</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="B109" s="99" t="inlineStr">
+      <c r="B109" s="100" t="inlineStr">
         <is>
           <t>갱신</t>
         </is>
       </c>
-      <c r="C109" s="99" t="inlineStr">
+      <c r="C109" s="100" t="inlineStr">
         <is>
           <t>항목 추가는 행 추가로. 명칭 변경은 목록만 교체하고 기존 데이터 행은 소급 변경하지 않습니다(검증은 신규 입력에만 작동)</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="B110" s="99" t="inlineStr">
+      <c r="B110" s="100" t="inlineStr">
         <is>
           <t>레이블 동기</t>
         </is>
       </c>
-      <c r="C110" s="99" t="inlineStr">
+      <c r="C110" s="100" t="inlineStr">
         <is>
           <t>기능 트리 개정 시 레이블 목록을 함께 갱신합니다(정본 수정 체크리스트 연동)</t>
         </is>

--- a/projects/qa-lab-miyonchat/test-case/qa-lab-miyonchat-tc-v1.0.xlsx
+++ b/projects/qa-lab-miyonchat/test-case/qa-lab-miyonchat-tc-v1.0.xlsx
@@ -22564,7 +22564,7 @@
       </c>
       <c r="E3" s="100" t="inlineStr">
         <is>
-          <t>디버그 콘솔 &gt; 전체 초기화(reset) 수행 &gt; 계정 A 로그인 시, 성인 인증이 해제된 상태로 시작됨</t>
+          <t>전체 초기화 직후 성인 계정으로 로그인하면, 성인 인증이 해제된 상태로 시작됨</t>
         </is>
       </c>
       <c r="F3" s="100" t="inlineStr">
@@ -23697,7 +23697,7 @@
       </c>
       <c r="D30" s="100" t="inlineStr">
         <is>
-          <t>행마다 반복. 값 5종은 목록 시트가 정본이고 복수 상태는 쉼표로 적습니다(전환 케이스 — 드롭다운을 걸지 않는 이유). 자동 필터를 「포함」 조건으로 걸어 상태별 TC를 추출하고, 트리의 [상태:] 선언과 맞물려 잎×상태 커버리지를 대조합니다</t>
+          <t>행마다 반복. 값 5종은 목록 시트가 정본이고 복수 상태는 쉼표로 적습니다(전환 케이스 — 드롭다운을 걸지 않는 이유). 자동 필터를 「포함」 조건으로 걸어 상태별 TC를 추출하고, 트리의 [상태:] 선언과 맞물려 기능 단위×상태 커버리지를 대조합니다</t>
         </is>
       </c>
     </row>

--- a/projects/qa-lab-miyonchat/test-case/qa-lab-miyonchat-tc-v1.0.xlsx
+++ b/projects/qa-lab-miyonchat/test-case/qa-lab-miyonchat-tc-v1.0.xlsx
@@ -2764,7 +2764,7 @@
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>숨기지 않고 맨 뒤 배치 — 값 체계 자체가 전시물입니다</t>
+          <t>숨기지 않습니다 — 값 체계 자체가 전시물입니다. 탭 순서는 읽는 순서를 따라 규칙 다음 자리입니다</t>
         </is>
       </c>
     </row>
